--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>623.0</v>
+        <v>625.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>775</v>
       </c>
       <c r="F14" t="n">
-        <v>483.0</v>
+        <v>487.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -3323,13 +3323,13 @@
         <v>775</v>
       </c>
       <c r="F36" t="n">
-        <v>539.0</v>
+        <v>542.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="37">
@@ -3453,7 +3453,7 @@
         <v>775</v>
       </c>
       <c r="F41" t="n">
-        <v>345.0</v>
+        <v>347.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -3791,7 +3791,7 @@
         <v>775</v>
       </c>
       <c r="F54" t="n">
-        <v>133.0</v>
+        <v>136.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>205.0</v>
+        <v>206.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4259,7 +4259,7 @@
         <v>775</v>
       </c>
       <c r="F72" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4441,7 +4441,7 @@
         <v>775</v>
       </c>
       <c r="F79" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G79" t="n">
         <v>81.0</v>
@@ -4987,7 +4987,7 @@
         <v>776</v>
       </c>
       <c r="F100" t="n">
-        <v>446.0</v>
+        <v>447.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>529.0</v>
+        <v>532.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -5559,7 +5559,7 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>469.0</v>
+        <v>471.0</v>
       </c>
       <c r="G122" t="n">
         <v>12.0</v>
@@ -6027,7 +6027,7 @@
         <v>775</v>
       </c>
       <c r="F140" t="n">
-        <v>682.0</v>
+        <v>683.0</v>
       </c>
       <c r="G140" t="n">
         <v>2.0</v>
@@ -6365,7 +6365,7 @@
         <v>776</v>
       </c>
       <c r="F153" t="n">
-        <v>146.0</v>
+        <v>151.0</v>
       </c>
       <c r="G153" t="n">
         <v>0.0</v>
@@ -6781,7 +6781,7 @@
         <v>776</v>
       </c>
       <c r="F169" t="n">
-        <v>198.0</v>
+        <v>199.0</v>
       </c>
       <c r="G169" t="n">
         <v>1.0</v>
@@ -6833,7 +6833,7 @@
         <v>775</v>
       </c>
       <c r="F171" t="n">
-        <v>327.0</v>
+        <v>328.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -7015,7 +7015,7 @@
         <v>775</v>
       </c>
       <c r="F178" t="n">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="G178" t="n">
         <v>4.0</v>
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>533.0</v>
+        <v>535.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7847,7 +7847,7 @@
         <v>776</v>
       </c>
       <c r="F210" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G210" t="n">
         <v>0.0</v>
@@ -8835,13 +8835,13 @@
         <v>775</v>
       </c>
       <c r="F248" t="n">
-        <v>156.0</v>
+        <v>165.0</v>
       </c>
       <c r="G248" t="n">
         <v>1.0</v>
       </c>
       <c r="H248" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="249">
@@ -10291,7 +10291,7 @@
         <v>775</v>
       </c>
       <c r="F304" t="n">
-        <v>402.0</v>
+        <v>403.0</v>
       </c>
       <c r="G304" t="n">
         <v>0.0</v>
@@ -10577,7 +10577,7 @@
         <v>775</v>
       </c>
       <c r="F315" t="n">
-        <v>528.0</v>
+        <v>530.0</v>
       </c>
       <c r="G315" t="n">
         <v>0.0</v>
@@ -10915,7 +10915,7 @@
         <v>776</v>
       </c>
       <c r="F328" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="G328" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         <v>775</v>
       </c>
       <c r="F340" t="n">
-        <v>419.0</v>
+        <v>420.0</v>
       </c>
       <c r="G340" t="n">
         <v>1.0</v>
@@ -12553,7 +12553,7 @@
         <v>775</v>
       </c>
       <c r="F391" t="n">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="G391" t="n">
         <v>1.0</v>
@@ -13151,7 +13151,7 @@
         <v>775</v>
       </c>
       <c r="F414" t="n">
-        <v>320.0</v>
+        <v>326.0</v>
       </c>
       <c r="G414" t="n">
         <v>28.0</v>
@@ -14633,7 +14633,7 @@
         <v>775</v>
       </c>
       <c r="F471" t="n">
-        <v>185.0</v>
+        <v>189.0</v>
       </c>
       <c r="G471" t="n">
         <v>3.0</v>
@@ -14997,13 +14997,13 @@
         <v>775</v>
       </c>
       <c r="F485" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="G485" t="n">
         <v>8.0</v>
       </c>
       <c r="H485" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="486">
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>636.0</v>
+        <v>637.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -16323,7 +16323,7 @@
         <v>775</v>
       </c>
       <c r="F536" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G536" t="n">
         <v>5.0</v>
@@ -17701,7 +17701,7 @@
         <v>775</v>
       </c>
       <c r="F589" t="n">
-        <v>325.0</v>
+        <v>326.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>
@@ -19735,7 +19735,7 @@
         <v>0.0</v>
       </c>
       <c r="H667" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="668">
@@ -19755,7 +19755,7 @@
         <v>775</v>
       </c>
       <c r="F668" t="n">
-        <v>101.0</v>
+        <v>105.0</v>
       </c>
       <c r="G668" t="n">
         <v>0.0</v>
@@ -19833,7 +19833,7 @@
         <v>776</v>
       </c>
       <c r="F671" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G671" t="n">
         <v>0.0</v>
@@ -19859,7 +19859,7 @@
         <v>776</v>
       </c>
       <c r="F672" t="n">
-        <v>115.0</v>
+        <v>119.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -19885,7 +19885,7 @@
         <v>775</v>
       </c>
       <c r="F673" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19937,7 +19937,7 @@
         <v>776</v>
       </c>
       <c r="F675" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -20041,7 +20041,7 @@
         <v>776</v>
       </c>
       <c r="F679" t="n">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
       <c r="G679" t="n">
         <v>0.0</v>
@@ -20067,7 +20067,7 @@
         <v>776</v>
       </c>
       <c r="F680" t="n">
-        <v>112.0</v>
+        <v>114.0</v>
       </c>
       <c r="G680" t="n">
         <v>0.0</v>
@@ -20327,7 +20327,7 @@
         <v>775</v>
       </c>
       <c r="F690" t="n">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
       <c r="G690" t="n">
         <v>0.0</v>
@@ -20379,7 +20379,7 @@
         <v>776</v>
       </c>
       <c r="F692" t="n">
-        <v>133.0</v>
+        <v>137.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>431.0</v>
+        <v>434.0</v>
       </c>
       <c r="G693" t="n">
         <v>1.0</v>
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>167.0</v>
+        <v>169.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20509,7 +20509,7 @@
         <v>776</v>
       </c>
       <c r="F697" t="n">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20535,7 +20535,7 @@
         <v>776</v>
       </c>
       <c r="F698" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20665,7 +20665,7 @@
         <v>775</v>
       </c>
       <c r="F703" t="n">
-        <v>97.0</v>
+        <v>100.0</v>
       </c>
       <c r="G703" t="n">
         <v>0.0</v>
@@ -20691,7 +20691,7 @@
         <v>775</v>
       </c>
       <c r="F704" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G704" t="n">
         <v>0.0</v>
@@ -20743,7 +20743,7 @@
         <v>776</v>
       </c>
       <c r="F706" t="n">
-        <v>88.0</v>
+        <v>90.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20769,7 +20769,7 @@
         <v>775</v>
       </c>
       <c r="F707" t="n">
-        <v>123.0</v>
+        <v>128.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20795,7 +20795,7 @@
         <v>776</v>
       </c>
       <c r="F708" t="n">
-        <v>86.0</v>
+        <v>90.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -21003,7 +21003,7 @@
         <v>775</v>
       </c>
       <c r="F716" t="n">
-        <v>107.0</v>
+        <v>110.0</v>
       </c>
       <c r="G716" t="n">
         <v>0.0</v>
@@ -21055,7 +21055,7 @@
         <v>777</v>
       </c>
       <c r="F718" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G718" t="n">
         <v>1.0</v>
@@ -21081,7 +21081,7 @@
         <v>776</v>
       </c>
       <c r="F719" t="n">
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
@@ -21133,7 +21133,7 @@
         <v>776</v>
       </c>
       <c r="F721" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G721" t="n">
         <v>0.0</v>
@@ -21159,7 +21159,7 @@
         <v>776</v>
       </c>
       <c r="F722" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G722" t="n">
         <v>0.0</v>
@@ -21185,7 +21185,7 @@
         <v>776</v>
       </c>
       <c r="F723" t="n">
-        <v>71.0</v>
+        <v>75.0</v>
       </c>
       <c r="G723" t="n">
         <v>0.0</v>
@@ -21913,7 +21913,7 @@
         <v>776</v>
       </c>
       <c r="F751" t="n">
-        <v>160.0</v>
+        <v>162.0</v>
       </c>
       <c r="G751" t="n">
         <v>0.0</v>
@@ -22069,7 +22069,7 @@
         <v>777</v>
       </c>
       <c r="F757" t="n">
-        <v>75.0</v>
+        <v>79.0</v>
       </c>
       <c r="G757" t="n">
         <v>11.0</v>
@@ -22121,7 +22121,7 @@
         <v>776</v>
       </c>
       <c r="F759" t="n">
-        <v>422.0</v>
+        <v>424.0</v>
       </c>
       <c r="G759" t="n">
         <v>0.0</v>
@@ -22147,7 +22147,7 @@
         <v>775</v>
       </c>
       <c r="F760" t="n">
-        <v>204.0</v>
+        <v>206.0</v>
       </c>
       <c r="G760" t="n">
         <v>0.0</v>
@@ -22225,7 +22225,7 @@
         <v>775</v>
       </c>
       <c r="F763" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G763" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2673,7 +2673,7 @@
         <v>775</v>
       </c>
       <c r="F11" t="n">
-        <v>303.0</v>
+        <v>304.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -3349,7 +3349,7 @@
         <v>775</v>
       </c>
       <c r="F37" t="n">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -4311,7 +4311,7 @@
         <v>775</v>
       </c>
       <c r="F74" t="n">
-        <v>160.0</v>
+        <v>163.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>437.0</v>
+        <v>438.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -5357,7 +5357,7 @@
         <v>7.0</v>
       </c>
       <c r="H114" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="115">
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="G127" t="n">
         <v>11.0</v>
@@ -5715,7 +5715,7 @@
         <v>775</v>
       </c>
       <c r="F128" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G128" t="n">
         <v>11.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7587,7 +7587,7 @@
         <v>776</v>
       </c>
       <c r="F200" t="n">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="G200" t="n">
         <v>0.0</v>
@@ -8133,7 +8133,7 @@
         <v>775</v>
       </c>
       <c r="F221" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8419,7 +8419,7 @@
         <v>775</v>
       </c>
       <c r="F232" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
@@ -8523,7 +8523,7 @@
         <v>776</v>
       </c>
       <c r="F236" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G236" t="n">
         <v>0.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -10603,7 +10603,7 @@
         <v>775</v>
       </c>
       <c r="F316" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G316" t="n">
         <v>6.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>263.0</v>
+        <v>264.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -10785,7 +10785,7 @@
         <v>775</v>
       </c>
       <c r="F323" t="n">
-        <v>562.0</v>
+        <v>563.0</v>
       </c>
       <c r="G323" t="n">
         <v>8.0</v>
@@ -10967,7 +10967,7 @@
         <v>775</v>
       </c>
       <c r="F330" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G330" t="n">
         <v>0.0</v>
@@ -11305,13 +11305,13 @@
         <v>775</v>
       </c>
       <c r="F343" t="n">
-        <v>214.0</v>
+        <v>223.0</v>
       </c>
       <c r="G343" t="n">
         <v>23.0</v>
       </c>
       <c r="H343" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="344">
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>541.0</v>
+        <v>542.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12137,7 +12137,7 @@
         <v>776</v>
       </c>
       <c r="F375" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="G375" t="n">
         <v>0.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>593.0</v>
+        <v>595.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -15283,7 +15283,7 @@
         <v>776</v>
       </c>
       <c r="F496" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -15315,7 +15315,7 @@
         <v>0.0</v>
       </c>
       <c r="H497" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="498">
@@ -15569,7 +15569,7 @@
         <v>776</v>
       </c>
       <c r="F507" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -15621,7 +15621,7 @@
         <v>775</v>
       </c>
       <c r="F509" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="G509" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2959,7 +2959,7 @@
         <v>776</v>
       </c>
       <c r="F22" t="n">
-        <v>385.0</v>
+        <v>389.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3323,7 +3323,7 @@
         <v>775</v>
       </c>
       <c r="F36" t="n">
-        <v>542.0</v>
+        <v>543.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3791,7 +3791,7 @@
         <v>775</v>
       </c>
       <c r="F54" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>206.0</v>
+        <v>208.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4337,7 +4337,7 @@
         <v>776</v>
       </c>
       <c r="F75" t="n">
-        <v>367.0</v>
+        <v>369.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -4415,7 +4415,7 @@
         <v>775</v>
       </c>
       <c r="F78" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>438.0</v>
+        <v>439.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4805,7 +4805,7 @@
         <v>775</v>
       </c>
       <c r="F93" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G93" t="n">
         <v>17.0</v>
@@ -4987,7 +4987,7 @@
         <v>776</v>
       </c>
       <c r="F100" t="n">
-        <v>447.0</v>
+        <v>448.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>532.0</v>
+        <v>533.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>535.0</v>
+        <v>539.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7301,7 +7301,7 @@
         <v>776</v>
       </c>
       <c r="F189" t="n">
-        <v>699.0</v>
+        <v>702.0</v>
       </c>
       <c r="G189" t="n">
         <v>1.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1020.0</v>
+        <v>1021.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -9979,7 +9979,7 @@
         <v>775</v>
       </c>
       <c r="F292" t="n">
-        <v>48.0</v>
+        <v>51.0</v>
       </c>
       <c r="G292" t="n">
         <v>6.0</v>
@@ -10395,7 +10395,7 @@
         <v>775</v>
       </c>
       <c r="F308" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G308" t="n">
         <v>0.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>264.0</v>
+        <v>266.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>146.0</v>
+        <v>148.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -12475,7 +12475,7 @@
         <v>776</v>
       </c>
       <c r="F388" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
@@ -12553,7 +12553,7 @@
         <v>775</v>
       </c>
       <c r="F391" t="n">
-        <v>262.0</v>
+        <v>264.0</v>
       </c>
       <c r="G391" t="n">
         <v>1.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>595.0</v>
+        <v>596.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -14087,7 +14087,7 @@
         <v>775</v>
       </c>
       <c r="F450" t="n">
-        <v>192.0</v>
+        <v>194.0</v>
       </c>
       <c r="G450" t="n">
         <v>11.0</v>
@@ -14451,7 +14451,7 @@
         <v>775</v>
       </c>
       <c r="F464" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G464" t="n">
         <v>14.0</v>
@@ -14997,7 +14997,7 @@
         <v>775</v>
       </c>
       <c r="F485" t="n">
-        <v>249.0</v>
+        <v>251.0</v>
       </c>
       <c r="G485" t="n">
         <v>8.0</v>
@@ -15023,7 +15023,7 @@
         <v>776</v>
       </c>
       <c r="F486" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
       <c r="G486" t="n">
         <v>0.0</v>
@@ -15283,7 +15283,7 @@
         <v>776</v>
       </c>
       <c r="F496" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>637.0</v>
+        <v>641.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15725,7 +15725,7 @@
         <v>776</v>
       </c>
       <c r="F513" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G513" t="n">
         <v>0.0</v>
@@ -16245,7 +16245,7 @@
         <v>775</v>
       </c>
       <c r="F533" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="G533" t="n">
         <v>1.0</v>
@@ -16401,7 +16401,7 @@
         <v>776</v>
       </c>
       <c r="F539" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -16609,7 +16609,7 @@
         <v>776</v>
       </c>
       <c r="F547" t="n">
-        <v>279.0</v>
+        <v>280.0</v>
       </c>
       <c r="G547" t="n">
         <v>1.0</v>
@@ -17025,7 +17025,7 @@
         <v>776</v>
       </c>
       <c r="F563" t="n">
-        <v>351.0</v>
+        <v>354.0</v>
       </c>
       <c r="G563" t="n">
         <v>0.0</v>
@@ -17519,7 +17519,7 @@
         <v>776</v>
       </c>
       <c r="F582" t="n">
-        <v>293.0</v>
+        <v>295.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -18013,7 +18013,7 @@
         <v>775</v>
       </c>
       <c r="F601" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G601" t="n">
         <v>0.0</v>
@@ -18195,7 +18195,7 @@
         <v>776</v>
       </c>
       <c r="F608" t="n">
-        <v>403.0</v>
+        <v>405.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -19443,7 +19443,7 @@
         <v>776</v>
       </c>
       <c r="F656" t="n">
-        <v>130.0</v>
+        <v>134.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -20327,7 +20327,7 @@
         <v>775</v>
       </c>
       <c r="F690" t="n">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
       <c r="G690" t="n">
         <v>0.0</v>
@@ -20379,7 +20379,7 @@
         <v>776</v>
       </c>
       <c r="F692" t="n">
-        <v>137.0</v>
+        <v>140.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20535,7 +20535,7 @@
         <v>776</v>
       </c>
       <c r="F698" t="n">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20691,7 +20691,7 @@
         <v>775</v>
       </c>
       <c r="F704" t="n">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
       <c r="G704" t="n">
         <v>0.0</v>
@@ -20769,7 +20769,7 @@
         <v>775</v>
       </c>
       <c r="F707" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20795,7 +20795,7 @@
         <v>776</v>
       </c>
       <c r="F708" t="n">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -21003,7 +21003,7 @@
         <v>775</v>
       </c>
       <c r="F716" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G716" t="n">
         <v>0.0</v>
@@ -21601,7 +21601,7 @@
         <v>778</v>
       </c>
       <c r="F739" t="n">
-        <v>107.0</v>
+        <v>109.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>
@@ -21627,7 +21627,7 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>199.0</v>
+        <v>201.0</v>
       </c>
       <c r="G740" t="n">
         <v>4.0</v>
@@ -21991,7 +21991,7 @@
         <v>775</v>
       </c>
       <c r="F754" t="n">
-        <v>408.0</v>
+        <v>410.0</v>
       </c>
       <c r="G754" t="n">
         <v>0.0</v>
@@ -22147,7 +22147,7 @@
         <v>775</v>
       </c>
       <c r="F760" t="n">
-        <v>206.0</v>
+        <v>208.0</v>
       </c>
       <c r="G760" t="n">
         <v>0.0</v>
@@ -22277,7 +22277,7 @@
         <v>776</v>
       </c>
       <c r="F765" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="G765" t="n">
         <v>0.0</v>
@@ -22355,7 +22355,7 @@
         <v>776</v>
       </c>
       <c r="F768" t="n">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="G768" t="n">
         <v>0.0</v>
@@ -22433,7 +22433,7 @@
         <v>778</v>
       </c>
       <c r="F771" t="n">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>
@@ -22641,7 +22641,7 @@
         <v>778</v>
       </c>
       <c r="F779" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G779" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>509.0</v>
+        <v>511.0</v>
       </c>
       <c r="G780" t="n">
         <v>2.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>509.0</v>
+        <v>511.0</v>
       </c>
       <c r="G782" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3037,7 +3037,7 @@
         <v>775</v>
       </c>
       <c r="F25" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -3349,7 +3349,7 @@
         <v>775</v>
       </c>
       <c r="F37" t="n">
-        <v>218.0</v>
+        <v>222.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -5611,7 +5611,7 @@
         <v>775</v>
       </c>
       <c r="F124" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G124" t="n">
         <v>0.0</v>
@@ -10031,7 +10031,7 @@
         <v>775</v>
       </c>
       <c r="F294" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="G294" t="n">
         <v>11.0</v>
@@ -10785,7 +10785,7 @@
         <v>775</v>
       </c>
       <c r="F323" t="n">
-        <v>563.0</v>
+        <v>565.0</v>
       </c>
       <c r="G323" t="n">
         <v>8.0</v>
@@ -12917,7 +12917,7 @@
         <v>777</v>
       </c>
       <c r="F405" t="n">
-        <v>443.0</v>
+        <v>446.0</v>
       </c>
       <c r="G405" t="n">
         <v>0.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>596.0</v>
+        <v>599.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -14971,7 +14971,7 @@
         <v>775</v>
       </c>
       <c r="F484" t="n">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="G484" t="n">
         <v>0.0</v>
@@ -19680,7 +19680,7 @@
         <v>0.0</v>
       </c>
       <c r="G665" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="H665" t="n">
         <v>0.0</v>
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20275,7 +20275,7 @@
         <v>777</v>
       </c>
       <c r="F688" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G688" t="n">
         <v>12.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>434.0</v>
+        <v>435.0</v>
       </c>
       <c r="G693" t="n">
         <v>1.0</v>
@@ -20509,7 +20509,7 @@
         <v>776</v>
       </c>
       <c r="F697" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20587,7 +20587,7 @@
         <v>777</v>
       </c>
       <c r="F700" t="n">
-        <v>187.0</v>
+        <v>191.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -21058,7 +21058,7 @@
         <v>51.0</v>
       </c>
       <c r="G718" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H718" t="n">
         <v>0.0</v>
@@ -21263,7 +21263,7 @@
         <v>776</v>
       </c>
       <c r="F726" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G726" t="n">
         <v>0.0</v>
@@ -21601,7 +21601,7 @@
         <v>778</v>
       </c>
       <c r="F739" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>
@@ -21627,7 +21627,7 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G740" t="n">
         <v>4.0</v>
@@ -21731,7 +21731,7 @@
         <v>778</v>
       </c>
       <c r="F744" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G744" t="n">
         <v>0.0</v>
@@ -22615,7 +22615,7 @@
         <v>778</v>
       </c>
       <c r="F778" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G778" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2829,7 +2829,7 @@
         <v>777</v>
       </c>
       <c r="F17" t="n">
-        <v>253.0</v>
+        <v>255.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>439.0</v>
+        <v>442.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4753,7 +4753,7 @@
         <v>777</v>
       </c>
       <c r="F91" t="n">
-        <v>471.0</v>
+        <v>472.0</v>
       </c>
       <c r="G91" t="n">
         <v>1.0</v>
@@ -5195,7 +5195,7 @@
         <v>776</v>
       </c>
       <c r="F108" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -5351,7 +5351,7 @@
         <v>775</v>
       </c>
       <c r="F114" t="n">
-        <v>243.0</v>
+        <v>244.0</v>
       </c>
       <c r="G114" t="n">
         <v>7.0</v>
@@ -5715,7 +5715,7 @@
         <v>775</v>
       </c>
       <c r="F128" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G128" t="n">
         <v>11.0</v>
@@ -5741,7 +5741,7 @@
         <v>775</v>
       </c>
       <c r="F129" t="n">
-        <v>296.0</v>
+        <v>297.0</v>
       </c>
       <c r="G129" t="n">
         <v>0.0</v>
@@ -6495,7 +6495,7 @@
         <v>775</v>
       </c>
       <c r="F158" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G158" t="n">
         <v>2.0</v>
@@ -6677,7 +6677,7 @@
         <v>775</v>
       </c>
       <c r="F165" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G165" t="n">
         <v>4.0</v>
@@ -6703,7 +6703,7 @@
         <v>775</v>
       </c>
       <c r="F166" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G166" t="n">
         <v>0.0</v>
@@ -7457,7 +7457,7 @@
         <v>775</v>
       </c>
       <c r="F195" t="n">
-        <v>164.0</v>
+        <v>167.0</v>
       </c>
       <c r="G195" t="n">
         <v>1.0</v>
@@ -8133,7 +8133,7 @@
         <v>775</v>
       </c>
       <c r="F221" t="n">
-        <v>149.0</v>
+        <v>156.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8393,7 +8393,7 @@
         <v>775</v>
       </c>
       <c r="F231" t="n">
-        <v>264.0</v>
+        <v>268.0</v>
       </c>
       <c r="G231" t="n">
         <v>6.0</v>
@@ -10005,7 +10005,7 @@
         <v>777</v>
       </c>
       <c r="F293" t="n">
-        <v>282.0</v>
+        <v>283.0</v>
       </c>
       <c r="G293" t="n">
         <v>13.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>542.0</v>
+        <v>543.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>119.0</v>
+        <v>122.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -16999,7 +16999,7 @@
         <v>775</v>
       </c>
       <c r="F562" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
       <c r="G562" t="n">
         <v>29.0</v>
@@ -17233,7 +17233,7 @@
         <v>776</v>
       </c>
       <c r="F571" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G571" t="n">
         <v>0.0</v>
@@ -18871,7 +18871,7 @@
         <v>775</v>
       </c>
       <c r="F634" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="G634" t="n">
         <v>8.0</v>
@@ -19183,7 +19183,7 @@
         <v>775</v>
       </c>
       <c r="F646" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>435.0</v>
+        <v>436.0</v>
       </c>
       <c r="G693" t="n">
         <v>1.0</v>
@@ -20561,7 +20561,7 @@
         <v>776</v>
       </c>
       <c r="F699" t="n">
-        <v>62.0</v>
+        <v>69.0</v>
       </c>
       <c r="G699" t="n">
         <v>0.0</v>
@@ -20587,7 +20587,7 @@
         <v>777</v>
       </c>
       <c r="F700" t="n">
-        <v>191.0</v>
+        <v>202.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -21601,7 +21601,7 @@
         <v>778</v>
       </c>
       <c r="F739" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>
@@ -21757,7 +21757,7 @@
         <v>778</v>
       </c>
       <c r="F745" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G745" t="n">
         <v>0.0</v>
@@ -21991,7 +21991,7 @@
         <v>775</v>
       </c>
       <c r="F754" t="n">
-        <v>410.0</v>
+        <v>411.0</v>
       </c>
       <c r="G754" t="n">
         <v>0.0</v>
@@ -22277,7 +22277,7 @@
         <v>776</v>
       </c>
       <c r="F765" t="n">
-        <v>59.0</v>
+        <v>61.0</v>
       </c>
       <c r="G765" t="n">
         <v>0.0</v>
@@ -22615,7 +22615,7 @@
         <v>778</v>
       </c>
       <c r="F778" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G778" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2907,7 +2907,7 @@
         <v>775</v>
       </c>
       <c r="F20" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -5351,7 +5351,7 @@
         <v>775</v>
       </c>
       <c r="F114" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="G114" t="n">
         <v>7.0</v>
@@ -5455,7 +5455,7 @@
         <v>775</v>
       </c>
       <c r="F118" t="n">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="G118" t="n">
         <v>12.0</v>
@@ -6235,7 +6235,7 @@
         <v>775</v>
       </c>
       <c r="F148" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6521,7 +6521,7 @@
         <v>775</v>
       </c>
       <c r="F159" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G159" t="n">
         <v>1.0</v>
@@ -7197,7 +7197,7 @@
         <v>775</v>
       </c>
       <c r="F185" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="G185" t="n">
         <v>0.0</v>
@@ -7483,7 +7483,7 @@
         <v>775</v>
       </c>
       <c r="F196" t="n">
-        <v>334.0</v>
+        <v>335.0</v>
       </c>
       <c r="G196" t="n">
         <v>0.0</v>
@@ -7587,7 +7587,7 @@
         <v>776</v>
       </c>
       <c r="F200" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="G200" t="n">
         <v>0.0</v>
@@ -7795,7 +7795,7 @@
         <v>775</v>
       </c>
       <c r="F208" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G208" t="n">
         <v>2.0</v>
@@ -8523,7 +8523,7 @@
         <v>776</v>
       </c>
       <c r="F236" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G236" t="n">
         <v>0.0</v>
@@ -9927,7 +9927,7 @@
         <v>775</v>
       </c>
       <c r="F290" t="n">
-        <v>557.0</v>
+        <v>560.0</v>
       </c>
       <c r="G290" t="n">
         <v>42.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1044.0</v>
+        <v>1049.0</v>
       </c>
       <c r="G310" t="n">
         <v>20.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>266.0</v>
+        <v>267.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -10785,7 +10785,7 @@
         <v>775</v>
       </c>
       <c r="F323" t="n">
-        <v>565.0</v>
+        <v>567.0</v>
       </c>
       <c r="G323" t="n">
         <v>8.0</v>
@@ -13333,7 +13333,7 @@
         <v>775</v>
       </c>
       <c r="F421" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G421" t="n">
         <v>5.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>599.0</v>
+        <v>600.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -14009,7 +14009,7 @@
         <v>775</v>
       </c>
       <c r="F447" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
       <c r="G447" t="n">
         <v>1.0</v>
@@ -14113,7 +14113,7 @@
         <v>775</v>
       </c>
       <c r="F451" t="n">
-        <v>775.0</v>
+        <v>778.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -14503,7 +14503,7 @@
         <v>775</v>
       </c>
       <c r="F466" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
       <c r="G466" t="n">
         <v>0.0</v>
@@ -14685,7 +14685,7 @@
         <v>775</v>
       </c>
       <c r="F473" t="n">
-        <v>107.0</v>
+        <v>109.0</v>
       </c>
       <c r="G473" t="n">
         <v>0.0</v>
@@ -15205,7 +15205,7 @@
         <v>775</v>
       </c>
       <c r="F493" t="n">
-        <v>381.0</v>
+        <v>382.0</v>
       </c>
       <c r="G493" t="n">
         <v>39.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2439.0</v>
+        <v>2449.0</v>
       </c>
       <c r="G518" t="n">
         <v>307.0</v>
@@ -16167,7 +16167,7 @@
         <v>775</v>
       </c>
       <c r="F530" t="n">
-        <v>426.0</v>
+        <v>431.0</v>
       </c>
       <c r="G530" t="n">
         <v>3.0</v>
@@ -16297,7 +16297,7 @@
         <v>775</v>
       </c>
       <c r="F535" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
       <c r="G535" t="n">
         <v>0.0</v>
@@ -16869,7 +16869,7 @@
         <v>775</v>
       </c>
       <c r="F557" t="n">
-        <v>106.0</v>
+        <v>108.0</v>
       </c>
       <c r="G557" t="n">
         <v>0.0</v>
@@ -18273,7 +18273,7 @@
         <v>775</v>
       </c>
       <c r="F611" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="G611" t="n">
         <v>7.0</v>
@@ -18377,7 +18377,7 @@
         <v>775</v>
       </c>
       <c r="F615" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G615" t="n">
         <v>0.0</v>
@@ -21627,7 +21627,7 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G740" t="n">
         <v>4.0</v>
@@ -21653,7 +21653,7 @@
         <v>778</v>
       </c>
       <c r="F741" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -22433,7 +22433,7 @@
         <v>778</v>
       </c>
       <c r="F771" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -9693,7 +9693,7 @@
         <v>775</v>
       </c>
       <c r="F281" t="n">
-        <v>510.0</v>
+        <v>511.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -20275,7 +20275,7 @@
         <v>777</v>
       </c>
       <c r="F688" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G688" t="n">
         <v>12.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>511.0</v>
+        <v>512.0</v>
       </c>
       <c r="G780" t="n">
         <v>2.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>511.0</v>
+        <v>512.0</v>
       </c>
       <c r="G782" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -4311,7 +4311,7 @@
         <v>775</v>
       </c>
       <c r="F74" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>442.0</v>
+        <v>443.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4727,7 +4727,7 @@
         <v>775</v>
       </c>
       <c r="F90" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -6209,7 +6209,7 @@
         <v>775</v>
       </c>
       <c r="F147" t="n">
-        <v>171.0</v>
+        <v>176.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1021.0</v>
+        <v>1023.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -8393,7 +8393,7 @@
         <v>775</v>
       </c>
       <c r="F231" t="n">
-        <v>268.0</v>
+        <v>271.0</v>
       </c>
       <c r="G231" t="n">
         <v>6.0</v>
@@ -9615,7 +9615,7 @@
         <v>775</v>
       </c>
       <c r="F278" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G278" t="n">
         <v>7.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11305,13 +11305,13 @@
         <v>775</v>
       </c>
       <c r="F343" t="n">
-        <v>223.0</v>
+        <v>227.0</v>
       </c>
       <c r="G343" t="n">
         <v>23.0</v>
       </c>
       <c r="H343" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="344">
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>543.0</v>
+        <v>544.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>600.0</v>
+        <v>601.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -17623,7 +17623,7 @@
         <v>775</v>
       </c>
       <c r="F586" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G586" t="n">
         <v>0.0</v>
@@ -18975,7 +18975,7 @@
         <v>775</v>
       </c>
       <c r="F638" t="n">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
       <c r="G638" t="n">
         <v>3.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>625.0</v>
+        <v>631.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>775</v>
       </c>
       <c r="F14" t="n">
-        <v>487.0</v>
+        <v>489.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2803,7 +2803,7 @@
         <v>775</v>
       </c>
       <c r="F16" t="n">
-        <v>416.0</v>
+        <v>418.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2959,7 +2959,7 @@
         <v>776</v>
       </c>
       <c r="F22" t="n">
-        <v>389.0</v>
+        <v>392.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3011,7 +3011,7 @@
         <v>776</v>
       </c>
       <c r="F24" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3323,7 +3323,7 @@
         <v>775</v>
       </c>
       <c r="F36" t="n">
-        <v>543.0</v>
+        <v>548.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>208.0</v>
+        <v>210.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4259,7 +4259,7 @@
         <v>775</v>
       </c>
       <c r="F72" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4337,7 +4337,7 @@
         <v>776</v>
       </c>
       <c r="F75" t="n">
-        <v>369.0</v>
+        <v>371.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -4441,7 +4441,7 @@
         <v>775</v>
       </c>
       <c r="F79" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G79" t="n">
         <v>81.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>443.0</v>
+        <v>445.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4987,7 +4987,7 @@
         <v>776</v>
       </c>
       <c r="F100" t="n">
-        <v>448.0</v>
+        <v>452.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>533.0</v>
+        <v>536.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -5559,7 +5559,7 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>471.0</v>
+        <v>473.0</v>
       </c>
       <c r="G122" t="n">
         <v>12.0</v>
@@ -6027,7 +6027,7 @@
         <v>775</v>
       </c>
       <c r="F140" t="n">
-        <v>683.0</v>
+        <v>685.0</v>
       </c>
       <c r="G140" t="n">
         <v>2.0</v>
@@ -6313,7 +6313,7 @@
         <v>775</v>
       </c>
       <c r="F151" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="G151" t="n">
         <v>2.0</v>
@@ -6391,7 +6391,7 @@
         <v>776</v>
       </c>
       <c r="F154" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G154" t="n">
         <v>0.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -6781,7 +6781,7 @@
         <v>776</v>
       </c>
       <c r="F169" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
       <c r="G169" t="n">
         <v>1.0</v>
@@ -6833,7 +6833,7 @@
         <v>775</v>
       </c>
       <c r="F171" t="n">
-        <v>328.0</v>
+        <v>330.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7015,7 +7015,7 @@
         <v>775</v>
       </c>
       <c r="F178" t="n">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="G178" t="n">
         <v>4.0</v>
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>539.0</v>
+        <v>540.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7301,7 +7301,7 @@
         <v>776</v>
       </c>
       <c r="F189" t="n">
-        <v>702.0</v>
+        <v>704.0</v>
       </c>
       <c r="G189" t="n">
         <v>1.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7847,7 +7847,7 @@
         <v>776</v>
       </c>
       <c r="F210" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G210" t="n">
         <v>0.0</v>
@@ -9771,7 +9771,7 @@
         <v>776</v>
       </c>
       <c r="F284" t="n">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
       <c r="G284" t="n">
         <v>2.0</v>
@@ -10291,7 +10291,7 @@
         <v>775</v>
       </c>
       <c r="F304" t="n">
-        <v>403.0</v>
+        <v>404.0</v>
       </c>
       <c r="G304" t="n">
         <v>0.0</v>
@@ -10395,7 +10395,7 @@
         <v>775</v>
       </c>
       <c r="F308" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G308" t="n">
         <v>0.0</v>
@@ -10915,7 +10915,7 @@
         <v>776</v>
       </c>
       <c r="F328" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G328" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         <v>775</v>
       </c>
       <c r="F340" t="n">
-        <v>420.0</v>
+        <v>422.0</v>
       </c>
       <c r="G340" t="n">
         <v>1.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>149.0</v>
+        <v>153.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>544.0</v>
+        <v>545.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -11877,7 +11877,7 @@
         <v>775</v>
       </c>
       <c r="F365" t="n">
-        <v>106.0</v>
+        <v>109.0</v>
       </c>
       <c r="G365" t="n">
         <v>10.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>122.0</v>
+        <v>124.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12839,7 +12839,7 @@
         <v>775</v>
       </c>
       <c r="F402" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="G402" t="n">
         <v>1.0</v>
@@ -13151,7 +13151,7 @@
         <v>775</v>
       </c>
       <c r="F414" t="n">
-        <v>326.0</v>
+        <v>328.0</v>
       </c>
       <c r="G414" t="n">
         <v>28.0</v>
@@ -13749,7 +13749,7 @@
         <v>775</v>
       </c>
       <c r="F437" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G437" t="n">
         <v>4.0</v>
@@ -14035,7 +14035,7 @@
         <v>775</v>
       </c>
       <c r="F448" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G448" t="n">
         <v>4.0</v>
@@ -14633,7 +14633,7 @@
         <v>775</v>
       </c>
       <c r="F471" t="n">
-        <v>189.0</v>
+        <v>191.0</v>
       </c>
       <c r="G471" t="n">
         <v>3.0</v>
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>641.0</v>
+        <v>645.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15569,7 +15569,7 @@
         <v>776</v>
       </c>
       <c r="F507" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -15725,7 +15725,7 @@
         <v>776</v>
       </c>
       <c r="F513" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G513" t="n">
         <v>0.0</v>
@@ -16401,7 +16401,7 @@
         <v>776</v>
       </c>
       <c r="F539" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -16531,7 +16531,7 @@
         <v>776</v>
       </c>
       <c r="F544" t="n">
-        <v>323.0</v>
+        <v>324.0</v>
       </c>
       <c r="G544" t="n">
         <v>1.0</v>
@@ -17519,7 +17519,7 @@
         <v>776</v>
       </c>
       <c r="F582" t="n">
-        <v>295.0</v>
+        <v>297.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -17701,7 +17701,7 @@
         <v>775</v>
       </c>
       <c r="F589" t="n">
-        <v>326.0</v>
+        <v>328.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>
@@ -18195,7 +18195,7 @@
         <v>776</v>
       </c>
       <c r="F608" t="n">
-        <v>405.0</v>
+        <v>409.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18663,7 +18663,7 @@
         <v>775</v>
       </c>
       <c r="F626" t="n">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="G626" t="n">
         <v>32.0</v>
@@ -18767,7 +18767,7 @@
         <v>776</v>
       </c>
       <c r="F630" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G630" t="n">
         <v>1851.0</v>
@@ -18793,7 +18793,7 @@
         <v>775</v>
       </c>
       <c r="F631" t="n">
-        <v>59.0</v>
+        <v>61.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -19443,7 +19443,7 @@
         <v>776</v>
       </c>
       <c r="F656" t="n">
-        <v>134.0</v>
+        <v>136.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19885,7 +19885,7 @@
         <v>775</v>
       </c>
       <c r="F673" t="n">
-        <v>138.0</v>
+        <v>145.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19911,7 +19911,7 @@
         <v>775</v>
       </c>
       <c r="F674" t="n">
-        <v>67.0</v>
+        <v>71.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -20041,7 +20041,7 @@
         <v>776</v>
       </c>
       <c r="F679" t="n">
-        <v>80.0</v>
+        <v>84.0</v>
       </c>
       <c r="G679" t="n">
         <v>0.0</v>
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>169.0</v>
+        <v>171.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20769,7 +20769,7 @@
         <v>775</v>
       </c>
       <c r="F707" t="n">
-        <v>129.0</v>
+        <v>131.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20795,7 +20795,7 @@
         <v>776</v>
       </c>
       <c r="F708" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -21003,7 +21003,7 @@
         <v>775</v>
       </c>
       <c r="F716" t="n">
-        <v>111.0</v>
+        <v>113.0</v>
       </c>
       <c r="G716" t="n">
         <v>0.0</v>
@@ -21081,7 +21081,7 @@
         <v>776</v>
       </c>
       <c r="F719" t="n">
-        <v>61.0</v>
+        <v>63.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
@@ -21601,7 +21601,7 @@
         <v>778</v>
       </c>
       <c r="F739" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>
@@ -21627,7 +21627,7 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>203.0</v>
+        <v>210.0</v>
       </c>
       <c r="G740" t="n">
         <v>4.0</v>
@@ -21913,7 +21913,7 @@
         <v>776</v>
       </c>
       <c r="F751" t="n">
-        <v>162.0</v>
+        <v>167.0</v>
       </c>
       <c r="G751" t="n">
         <v>0.0</v>
@@ -22020,7 +22020,7 @@
         <v>0.0</v>
       </c>
       <c r="G755" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="H755" t="n">
         <v>0.0</v>
@@ -22043,7 +22043,7 @@
         <v>775</v>
       </c>
       <c r="F756" t="n">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="G756" t="n">
         <v>0.0</v>
@@ -22121,7 +22121,7 @@
         <v>776</v>
       </c>
       <c r="F759" t="n">
-        <v>424.0</v>
+        <v>426.0</v>
       </c>
       <c r="G759" t="n">
         <v>0.0</v>
@@ -22511,7 +22511,7 @@
         <v>778</v>
       </c>
       <c r="F774" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G774" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2725,7 +2725,7 @@
         <v>777</v>
       </c>
       <c r="F13" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -3349,7 +3349,7 @@
         <v>775</v>
       </c>
       <c r="F37" t="n">
-        <v>222.0</v>
+        <v>225.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3401,7 +3401,7 @@
         <v>775</v>
       </c>
       <c r="F39" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>445.0</v>
+        <v>446.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4727,7 +4727,7 @@
         <v>775</v>
       </c>
       <c r="F90" t="n">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -4779,7 +4779,7 @@
         <v>775</v>
       </c>
       <c r="F92" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -6235,7 +6235,7 @@
         <v>775</v>
       </c>
       <c r="F148" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6495,7 +6495,7 @@
         <v>775</v>
       </c>
       <c r="F158" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G158" t="n">
         <v>2.0</v>
@@ -6703,7 +6703,7 @@
         <v>775</v>
       </c>
       <c r="F166" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G166" t="n">
         <v>0.0</v>
@@ -7067,7 +7067,7 @@
         <v>775</v>
       </c>
       <c r="F180" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G180" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1023.0</v>
+        <v>1024.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -7769,7 +7769,7 @@
         <v>776</v>
       </c>
       <c r="F207" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="G207" t="n">
         <v>0.0</v>
@@ -8263,7 +8263,7 @@
         <v>776</v>
       </c>
       <c r="F226" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -8393,7 +8393,7 @@
         <v>775</v>
       </c>
       <c r="F231" t="n">
-        <v>271.0</v>
+        <v>274.0</v>
       </c>
       <c r="G231" t="n">
         <v>6.0</v>
@@ -8809,7 +8809,7 @@
         <v>775</v>
       </c>
       <c r="F247" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
       <c r="G247" t="n">
         <v>14.0</v>
@@ -8994,7 +8994,7 @@
         <v>80.0</v>
       </c>
       <c r="G254" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="H254" t="n">
         <v>1.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11123,7 +11123,7 @@
         <v>775</v>
       </c>
       <c r="F336" t="n">
-        <v>266.0</v>
+        <v>268.0</v>
       </c>
       <c r="G336" t="n">
         <v>10.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>545.0</v>
+        <v>546.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12319,7 +12319,7 @@
         <v>775</v>
       </c>
       <c r="F382" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G382" t="n">
         <v>0.0</v>
@@ -12917,7 +12917,7 @@
         <v>777</v>
       </c>
       <c r="F405" t="n">
-        <v>446.0</v>
+        <v>448.0</v>
       </c>
       <c r="G405" t="n">
         <v>0.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>601.0</v>
+        <v>607.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -14763,7 +14763,7 @@
         <v>775</v>
       </c>
       <c r="F476" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G476" t="n">
         <v>4.0</v>
@@ -14971,7 +14971,7 @@
         <v>775</v>
       </c>
       <c r="F484" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G484" t="n">
         <v>0.0</v>
@@ -16479,7 +16479,7 @@
         <v>775</v>
       </c>
       <c r="F542" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G542" t="n">
         <v>11.0</v>
@@ -16999,7 +16999,7 @@
         <v>775</v>
       </c>
       <c r="F562" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
       <c r="G562" t="n">
         <v>29.0</v>
@@ -17311,7 +17311,7 @@
         <v>775</v>
       </c>
       <c r="F574" t="n">
-        <v>284.0</v>
+        <v>285.0</v>
       </c>
       <c r="G574" t="n">
         <v>0.0</v>
@@ -18013,7 +18013,7 @@
         <v>775</v>
       </c>
       <c r="F601" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G601" t="n">
         <v>0.0</v>
@@ -18377,7 +18377,7 @@
         <v>775</v>
       </c>
       <c r="F615" t="n">
-        <v>82.0</v>
+        <v>85.0</v>
       </c>
       <c r="G615" t="n">
         <v>0.0</v>
@@ -19183,7 +19183,7 @@
         <v>775</v>
       </c>
       <c r="F646" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>201.0</v>
+        <v>203.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>436.0</v>
+        <v>441.0</v>
       </c>
       <c r="G693" t="n">
         <v>1.0</v>
@@ -20509,7 +20509,7 @@
         <v>776</v>
       </c>
       <c r="F697" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20613,7 +20613,7 @@
         <v>776</v>
       </c>
       <c r="F701" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="G701" t="n">
         <v>0.0</v>
@@ -20899,7 +20899,7 @@
         <v>776</v>
       </c>
       <c r="F712" t="n">
-        <v>32.0</v>
+        <v>38.0</v>
       </c>
       <c r="G712" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -21601,7 +21601,7 @@
         <v>778</v>
       </c>
       <c r="F739" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>
@@ -22641,7 +22641,7 @@
         <v>778</v>
       </c>
       <c r="F779" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G779" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>512.0</v>
+        <v>515.0</v>
       </c>
       <c r="G780" t="n">
         <v>2.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>512.0</v>
+        <v>515.0</v>
       </c>
       <c r="G782" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>631.0</v>
+        <v>635.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2517,7 +2517,7 @@
         <v>776</v>
       </c>
       <c r="F5" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -2751,7 +2751,7 @@
         <v>775</v>
       </c>
       <c r="F14" t="n">
-        <v>489.0</v>
+        <v>493.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2803,7 +2803,7 @@
         <v>775</v>
       </c>
       <c r="F16" t="n">
-        <v>418.0</v>
+        <v>420.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2959,7 +2959,7 @@
         <v>776</v>
       </c>
       <c r="F22" t="n">
-        <v>392.0</v>
+        <v>397.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3011,7 +3011,7 @@
         <v>776</v>
       </c>
       <c r="F24" t="n">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3323,7 +3323,7 @@
         <v>775</v>
       </c>
       <c r="F36" t="n">
-        <v>548.0</v>
+        <v>552.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3791,7 +3791,7 @@
         <v>775</v>
       </c>
       <c r="F54" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>210.0</v>
+        <v>212.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4311,7 +4311,7 @@
         <v>775</v>
       </c>
       <c r="F74" t="n">
-        <v>164.0</v>
+        <v>166.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>446.0</v>
+        <v>451.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>536.0</v>
+        <v>539.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
       <c r="G127" t="n">
         <v>11.0</v>
@@ -5715,7 +5715,7 @@
         <v>775</v>
       </c>
       <c r="F128" t="n">
-        <v>82.0</v>
+        <v>87.0</v>
       </c>
       <c r="G128" t="n">
         <v>11.0</v>
@@ -6027,7 +6027,7 @@
         <v>775</v>
       </c>
       <c r="F140" t="n">
-        <v>685.0</v>
+        <v>688.0</v>
       </c>
       <c r="G140" t="n">
         <v>2.0</v>
@@ -6703,7 +6703,7 @@
         <v>775</v>
       </c>
       <c r="F166" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G166" t="n">
         <v>0.0</v>
@@ -6833,7 +6833,7 @@
         <v>775</v>
       </c>
       <c r="F171" t="n">
-        <v>330.0</v>
+        <v>332.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>540.0</v>
+        <v>541.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7587,7 +7587,7 @@
         <v>776</v>
       </c>
       <c r="F200" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="G200" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1024.0</v>
+        <v>1025.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -7795,7 +7795,7 @@
         <v>775</v>
       </c>
       <c r="F208" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G208" t="n">
         <v>2.0</v>
@@ -8133,7 +8133,7 @@
         <v>775</v>
       </c>
       <c r="F221" t="n">
-        <v>156.0</v>
+        <v>158.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8396,7 +8396,7 @@
         <v>274.0</v>
       </c>
       <c r="G231" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="H231" t="n">
         <v>4.0</v>
@@ -8419,7 +8419,7 @@
         <v>775</v>
       </c>
       <c r="F232" t="n">
-        <v>145.0</v>
+        <v>148.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
@@ -9355,7 +9355,7 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="G268" t="n">
         <v>7.0</v>
@@ -9589,7 +9589,7 @@
         <v>775</v>
       </c>
       <c r="F277" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G277" t="n">
         <v>40.0</v>
@@ -9927,7 +9927,7 @@
         <v>775</v>
       </c>
       <c r="F290" t="n">
-        <v>560.0</v>
+        <v>561.0</v>
       </c>
       <c r="G290" t="n">
         <v>42.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -10291,7 +10291,7 @@
         <v>775</v>
       </c>
       <c r="F304" t="n">
-        <v>404.0</v>
+        <v>408.0</v>
       </c>
       <c r="G304" t="n">
         <v>0.0</v>
@@ -10421,7 +10421,7 @@
         <v>775</v>
       </c>
       <c r="F309" t="n">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="G309" t="n">
         <v>16.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1049.0</v>
+        <v>1050.0</v>
       </c>
       <c r="G310" t="n">
         <v>20.0</v>
@@ -10577,7 +10577,7 @@
         <v>775</v>
       </c>
       <c r="F315" t="n">
-        <v>530.0</v>
+        <v>535.0</v>
       </c>
       <c r="G315" t="n">
         <v>0.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         <v>775</v>
       </c>
       <c r="F340" t="n">
-        <v>422.0</v>
+        <v>424.0</v>
       </c>
       <c r="G340" t="n">
         <v>1.0</v>
@@ -11903,7 +11903,7 @@
         <v>776</v>
       </c>
       <c r="F366" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G366" t="n">
         <v>0.0</v>
@@ -13489,7 +13489,7 @@
         <v>775</v>
       </c>
       <c r="F427" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G427" t="n">
         <v>0.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>607.0</v>
+        <v>608.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -14685,7 +14685,7 @@
         <v>775</v>
       </c>
       <c r="F473" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G473" t="n">
         <v>0.0</v>
@@ -14997,7 +14997,7 @@
         <v>775</v>
       </c>
       <c r="F485" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="G485" t="n">
         <v>8.0</v>
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>645.0</v>
+        <v>648.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2449.0</v>
+        <v>2460.0</v>
       </c>
       <c r="G518" t="n">
         <v>307.0</v>
@@ -17025,7 +17025,7 @@
         <v>776</v>
       </c>
       <c r="F563" t="n">
-        <v>354.0</v>
+        <v>357.0</v>
       </c>
       <c r="G563" t="n">
         <v>0.0</v>
@@ -17701,7 +17701,7 @@
         <v>775</v>
       </c>
       <c r="F589" t="n">
-        <v>328.0</v>
+        <v>330.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>
@@ -18793,7 +18793,7 @@
         <v>775</v>
       </c>
       <c r="F631" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -19131,7 +19131,7 @@
         <v>776</v>
       </c>
       <c r="F644" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G644" t="n">
         <v>0.0</v>
@@ -19443,7 +19443,7 @@
         <v>776</v>
       </c>
       <c r="F656" t="n">
-        <v>136.0</v>
+        <v>141.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19833,7 +19833,7 @@
         <v>776</v>
       </c>
       <c r="F671" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G671" t="n">
         <v>0.0</v>
@@ -19859,7 +19859,7 @@
         <v>776</v>
       </c>
       <c r="F672" t="n">
-        <v>119.0</v>
+        <v>121.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -19911,7 +19911,7 @@
         <v>775</v>
       </c>
       <c r="F674" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -20119,7 +20119,7 @@
         <v>776</v>
       </c>
       <c r="F682" t="n">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20145,7 +20145,7 @@
         <v>776</v>
       </c>
       <c r="F683" t="n">
-        <v>78.0</v>
+        <v>84.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20171,7 +20171,7 @@
         <v>776</v>
       </c>
       <c r="F684" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -20379,7 +20379,7 @@
         <v>776</v>
       </c>
       <c r="F692" t="n">
-        <v>140.0</v>
+        <v>145.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>171.0</v>
+        <v>174.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20587,7 +20587,7 @@
         <v>777</v>
       </c>
       <c r="F700" t="n">
-        <v>202.0</v>
+        <v>210.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -20743,7 +20743,7 @@
         <v>776</v>
       </c>
       <c r="F706" t="n">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -21835,7 +21835,7 @@
         <v>775</v>
       </c>
       <c r="F748" t="n">
-        <v>328.0</v>
+        <v>333.0</v>
       </c>
       <c r="G748" t="n">
         <v>0.0</v>
@@ -21913,7 +21913,7 @@
         <v>776</v>
       </c>
       <c r="F751" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G751" t="n">
         <v>0.0</v>
@@ -21939,7 +21939,7 @@
         <v>775</v>
       </c>
       <c r="F752" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G752" t="n">
         <v>0.0</v>
@@ -22277,7 +22277,7 @@
         <v>776</v>
       </c>
       <c r="F765" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G765" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>515.0</v>
+        <v>516.0</v>
       </c>
       <c r="G780" t="n">
         <v>2.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>515.0</v>
+        <v>516.0</v>
       </c>
       <c r="G782" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2933,7 +2933,7 @@
         <v>775</v>
       </c>
       <c r="F21" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2985,7 +2985,7 @@
         <v>776</v>
       </c>
       <c r="F23" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -4363,7 +4363,7 @@
         <v>776</v>
       </c>
       <c r="F76" t="n">
-        <v>353.0</v>
+        <v>359.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>451.0</v>
+        <v>453.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4779,7 +4779,7 @@
         <v>775</v>
       </c>
       <c r="F92" t="n">
-        <v>122.0</v>
+        <v>124.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -5195,7 +5195,7 @@
         <v>776</v>
       </c>
       <c r="F108" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>237.0</v>
+        <v>238.0</v>
       </c>
       <c r="G127" t="n">
         <v>11.0</v>
@@ -5747,7 +5747,7 @@
         <v>0.0</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="130">
@@ -6209,7 +6209,7 @@
         <v>775</v>
       </c>
       <c r="F147" t="n">
-        <v>176.0</v>
+        <v>183.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -7353,7 +7353,7 @@
         <v>775</v>
       </c>
       <c r="F191" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G191" t="n">
         <v>0.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -8263,7 +8263,7 @@
         <v>776</v>
       </c>
       <c r="F226" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -8399,7 +8399,7 @@
         <v>9.0</v>
       </c>
       <c r="H231" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="232">
@@ -8523,7 +8523,7 @@
         <v>776</v>
       </c>
       <c r="F236" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G236" t="n">
         <v>0.0</v>
@@ -9927,7 +9927,7 @@
         <v>775</v>
       </c>
       <c r="F290" t="n">
-        <v>561.0</v>
+        <v>562.0</v>
       </c>
       <c r="G290" t="n">
         <v>42.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>546.0</v>
+        <v>547.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>124.0</v>
+        <v>126.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -14555,7 +14555,7 @@
         <v>777</v>
       </c>
       <c r="F468" t="n">
-        <v>539.0</v>
+        <v>540.0</v>
       </c>
       <c r="G468" t="n">
         <v>0.0</v>
@@ -14919,7 +14919,7 @@
         <v>776</v>
       </c>
       <c r="F482" t="n">
-        <v>148.0</v>
+        <v>151.0</v>
       </c>
       <c r="G482" t="n">
         <v>0.0</v>
@@ -15569,7 +15569,7 @@
         <v>776</v>
       </c>
       <c r="F507" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -19131,7 +19131,7 @@
         <v>776</v>
       </c>
       <c r="F644" t="n">
-        <v>169.0</v>
+        <v>174.0</v>
       </c>
       <c r="G644" t="n">
         <v>0.0</v>
@@ -21601,7 +21601,7 @@
         <v>778</v>
       </c>
       <c r="F739" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>
@@ -21627,7 +21627,7 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>210.0</v>
+        <v>212.0</v>
       </c>
       <c r="G740" t="n">
         <v>4.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>516.0</v>
+        <v>518.0</v>
       </c>
       <c r="G780" t="n">
         <v>2.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>516.0</v>
+        <v>518.0</v>
       </c>
       <c r="G782" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -20275,7 +20275,7 @@
         <v>777</v>
       </c>
       <c r="F688" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G688" t="n">
         <v>12.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>441.0</v>
+        <v>442.0</v>
       </c>
       <c r="G693" t="n">
         <v>1.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>243.0</v>
+        <v>246.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -21627,13 +21627,13 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>212.0</v>
+        <v>215.0</v>
       </c>
       <c r="G740" t="n">
         <v>4.0</v>
       </c>
       <c r="H740" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="741">
@@ -22433,7 +22433,7 @@
         <v>778</v>
       </c>
       <c r="F771" t="n">
-        <v>106.0</v>
+        <v>108.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2673,7 +2673,7 @@
         <v>775</v>
       </c>
       <c r="F11" t="n">
-        <v>304.0</v>
+        <v>305.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>775</v>
       </c>
       <c r="F14" t="n">
-        <v>493.0</v>
+        <v>494.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -3323,7 +3323,7 @@
         <v>775</v>
       </c>
       <c r="F36" t="n">
-        <v>552.0</v>
+        <v>554.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3453,7 +3453,7 @@
         <v>775</v>
       </c>
       <c r="F41" t="n">
-        <v>347.0</v>
+        <v>349.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -4051,7 +4051,7 @@
         <v>775</v>
       </c>
       <c r="F64" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>453.0</v>
+        <v>454.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4987,7 +4987,7 @@
         <v>776</v>
       </c>
       <c r="F100" t="n">
-        <v>452.0</v>
+        <v>454.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5559,7 +5559,7 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>473.0</v>
+        <v>475.0</v>
       </c>
       <c r="G122" t="n">
         <v>12.0</v>
@@ -6157,7 +6157,7 @@
         <v>776</v>
       </c>
       <c r="F145" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -6209,7 +6209,7 @@
         <v>775</v>
       </c>
       <c r="F147" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -7015,7 +7015,7 @@
         <v>775</v>
       </c>
       <c r="F178" t="n">
-        <v>282.0</v>
+        <v>283.0</v>
       </c>
       <c r="G178" t="n">
         <v>4.0</v>
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>541.0</v>
+        <v>543.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -9927,7 +9927,7 @@
         <v>775</v>
       </c>
       <c r="F290" t="n">
-        <v>562.0</v>
+        <v>563.0</v>
       </c>
       <c r="G290" t="n">
         <v>42.0</v>
@@ -10031,7 +10031,7 @@
         <v>775</v>
       </c>
       <c r="F294" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="G294" t="n">
         <v>11.0</v>
@@ -10291,7 +10291,7 @@
         <v>775</v>
       </c>
       <c r="F304" t="n">
-        <v>408.0</v>
+        <v>409.0</v>
       </c>
       <c r="G304" t="n">
         <v>0.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1050.0</v>
+        <v>1051.0</v>
       </c>
       <c r="G310" t="n">
         <v>20.0</v>
@@ -10551,7 +10551,7 @@
         <v>775</v>
       </c>
       <c r="F314" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G314" t="n">
         <v>0.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>154.0</v>
+        <v>157.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>547.0</v>
+        <v>548.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -11877,7 +11877,7 @@
         <v>775</v>
       </c>
       <c r="F365" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G365" t="n">
         <v>10.0</v>
@@ -12501,7 +12501,7 @@
         <v>775</v>
       </c>
       <c r="F389" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G389" t="n">
         <v>2.0</v>
@@ -12553,7 +12553,7 @@
         <v>775</v>
       </c>
       <c r="F391" t="n">
-        <v>264.0</v>
+        <v>265.0</v>
       </c>
       <c r="G391" t="n">
         <v>1.0</v>
@@ -12839,7 +12839,7 @@
         <v>775</v>
       </c>
       <c r="F402" t="n">
-        <v>147.0</v>
+        <v>153.0</v>
       </c>
       <c r="G402" t="n">
         <v>1.0</v>
@@ -13151,7 +13151,7 @@
         <v>775</v>
       </c>
       <c r="F414" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="G414" t="n">
         <v>28.0</v>
@@ -13671,7 +13671,7 @@
         <v>775</v>
       </c>
       <c r="F434" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G434" t="n">
         <v>1.0</v>
@@ -13905,7 +13905,7 @@
         <v>775</v>
       </c>
       <c r="F443" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G443" t="n">
         <v>0.0</v>
@@ -14633,7 +14633,7 @@
         <v>775</v>
       </c>
       <c r="F471" t="n">
-        <v>191.0</v>
+        <v>196.0</v>
       </c>
       <c r="G471" t="n">
         <v>3.0</v>
@@ -14997,7 +14997,7 @@
         <v>775</v>
       </c>
       <c r="F485" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G485" t="n">
         <v>8.0</v>
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>648.0</v>
+        <v>649.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -16401,7 +16401,7 @@
         <v>776</v>
       </c>
       <c r="F539" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -16479,7 +16479,7 @@
         <v>775</v>
       </c>
       <c r="F542" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G542" t="n">
         <v>11.0</v>
@@ -17233,7 +17233,7 @@
         <v>776</v>
       </c>
       <c r="F571" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G571" t="n">
         <v>0.0</v>
@@ -17987,7 +17987,7 @@
         <v>775</v>
       </c>
       <c r="F600" t="n">
-        <v>99.0</v>
+        <v>103.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
@@ -19859,7 +19859,7 @@
         <v>776</v>
       </c>
       <c r="F672" t="n">
-        <v>121.0</v>
+        <v>124.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -19885,7 +19885,7 @@
         <v>775</v>
       </c>
       <c r="F673" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19911,7 +19911,7 @@
         <v>775</v>
       </c>
       <c r="F674" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19937,7 +19937,7 @@
         <v>776</v>
       </c>
       <c r="F675" t="n">
-        <v>97.0</v>
+        <v>102.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -20119,7 +20119,7 @@
         <v>776</v>
       </c>
       <c r="F682" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20145,7 +20145,7 @@
         <v>776</v>
       </c>
       <c r="F683" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20171,7 +20171,7 @@
         <v>776</v>
       </c>
       <c r="F684" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -20301,7 +20301,7 @@
         <v>776</v>
       </c>
       <c r="F689" t="n">
-        <v>92.0</v>
+        <v>95.0</v>
       </c>
       <c r="G689" t="n">
         <v>0.0</v>
@@ -20665,7 +20665,7 @@
         <v>775</v>
       </c>
       <c r="F703" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G703" t="n">
         <v>0.0</v>
@@ -20795,7 +20795,7 @@
         <v>776</v>
       </c>
       <c r="F708" t="n">
-        <v>94.0</v>
+        <v>97.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -22043,7 +22043,7 @@
         <v>775</v>
       </c>
       <c r="F756" t="n">
-        <v>220.0</v>
+        <v>222.0</v>
       </c>
       <c r="G756" t="n">
         <v>0.0</v>
@@ -22069,7 +22069,7 @@
         <v>777</v>
       </c>
       <c r="F757" t="n">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
       <c r="G757" t="n">
         <v>11.0</v>
@@ -22121,7 +22121,7 @@
         <v>776</v>
       </c>
       <c r="F759" t="n">
-        <v>426.0</v>
+        <v>428.0</v>
       </c>
       <c r="G759" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2517,7 +2517,7 @@
         <v>776</v>
       </c>
       <c r="F5" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -3505,7 +3505,7 @@
         <v>775</v>
       </c>
       <c r="F43" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="G43" t="n">
         <v>11.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>454.0</v>
+        <v>455.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7301,7 +7301,7 @@
         <v>776</v>
       </c>
       <c r="F189" t="n">
-        <v>704.0</v>
+        <v>705.0</v>
       </c>
       <c r="G189" t="n">
         <v>1.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1025.0</v>
+        <v>1026.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -8393,7 +8393,7 @@
         <v>775</v>
       </c>
       <c r="F231" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="G231" t="n">
         <v>9.0</v>
@@ -9043,7 +9043,7 @@
         <v>775</v>
       </c>
       <c r="F256" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G256" t="n">
         <v>4.0</v>
@@ -9095,7 +9095,7 @@
         <v>775</v>
       </c>
       <c r="F258" t="n">
-        <v>953.0</v>
+        <v>954.0</v>
       </c>
       <c r="G258" t="n">
         <v>23.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -10005,7 +10005,7 @@
         <v>777</v>
       </c>
       <c r="F293" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
       <c r="G293" t="n">
         <v>13.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -12475,7 +12475,7 @@
         <v>776</v>
       </c>
       <c r="F388" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
@@ -12845,7 +12845,7 @@
         <v>1.0</v>
       </c>
       <c r="H402" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="403">
@@ -16167,7 +16167,7 @@
         <v>775</v>
       </c>
       <c r="F530" t="n">
-        <v>431.0</v>
+        <v>437.0</v>
       </c>
       <c r="G530" t="n">
         <v>3.0</v>
@@ -16557,7 +16557,7 @@
         <v>775</v>
       </c>
       <c r="F545" t="n">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="G545" t="n">
         <v>0.0</v>
@@ -16609,7 +16609,7 @@
         <v>776</v>
       </c>
       <c r="F547" t="n">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="G547" t="n">
         <v>1.0</v>
@@ -16765,7 +16765,7 @@
         <v>775</v>
       </c>
       <c r="F553" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G553" t="n">
         <v>1.0</v>
@@ -16895,7 +16895,7 @@
         <v>775</v>
       </c>
       <c r="F558" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G558" t="n">
         <v>0.0</v>
@@ -17181,7 +17181,7 @@
         <v>776</v>
       </c>
       <c r="F569" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G569" t="n">
         <v>0.0</v>
@@ -17519,7 +17519,7 @@
         <v>776</v>
       </c>
       <c r="F582" t="n">
-        <v>297.0</v>
+        <v>298.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -18871,7 +18871,7 @@
         <v>775</v>
       </c>
       <c r="F634" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G634" t="n">
         <v>8.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>635.0</v>
+        <v>640.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2517,7 +2517,7 @@
         <v>776</v>
       </c>
       <c r="F5" t="n">
-        <v>128.0</v>
+        <v>130.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -2592,7 +2592,7 @@
         <v>773</v>
       </c>
       <c r="E8" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F8" t="n">
         <v>193.0</v>
@@ -2803,7 +2803,7 @@
         <v>775</v>
       </c>
       <c r="F16" t="n">
-        <v>420.0</v>
+        <v>422.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2826,7 +2826,7 @@
         <v>773</v>
       </c>
       <c r="E17" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F17" t="n">
         <v>255.0</v>
@@ -2959,7 +2959,7 @@
         <v>776</v>
       </c>
       <c r="F22" t="n">
-        <v>397.0</v>
+        <v>399.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -2985,7 +2985,7 @@
         <v>776</v>
       </c>
       <c r="F23" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>
@@ -3011,7 +3011,7 @@
         <v>776</v>
       </c>
       <c r="F24" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3973,7 +3973,7 @@
         <v>775</v>
       </c>
       <c r="F61" t="n">
-        <v>108.0</v>
+        <v>110.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -4022,7 +4022,7 @@
         <v>773</v>
       </c>
       <c r="E63" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F63" t="n">
         <v>5.0</v>
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>212.0</v>
+        <v>214.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4259,7 +4259,7 @@
         <v>775</v>
       </c>
       <c r="F72" t="n">
-        <v>143.0</v>
+        <v>146.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4389,7 +4389,7 @@
         <v>775</v>
       </c>
       <c r="F77" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -4727,7 +4727,7 @@
         <v>775</v>
       </c>
       <c r="F90" t="n">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -4750,10 +4750,10 @@
         <v>773</v>
       </c>
       <c r="E91" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F91" t="n">
-        <v>472.0</v>
+        <v>477.0</v>
       </c>
       <c r="G91" t="n">
         <v>1.0</v>
@@ -4883,7 +4883,7 @@
         <v>775</v>
       </c>
       <c r="F96" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -5065,7 +5065,7 @@
         <v>775</v>
       </c>
       <c r="F103" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="G103" t="n">
         <v>1.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>539.0</v>
+        <v>541.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -5166,7 +5166,7 @@
         <v>773</v>
       </c>
       <c r="E107" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F107" t="n">
         <v>38.0</v>
@@ -5273,7 +5273,7 @@
         <v>777</v>
       </c>
       <c r="F111" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
@@ -5504,10 +5504,10 @@
         <v>773</v>
       </c>
       <c r="E120" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F120" t="n">
-        <v>409.0</v>
+        <v>412.0</v>
       </c>
       <c r="G120" t="n">
         <v>11.0</v>
@@ -5559,7 +5559,7 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>475.0</v>
+        <v>476.0</v>
       </c>
       <c r="G122" t="n">
         <v>12.0</v>
@@ -5637,7 +5637,7 @@
         <v>775</v>
       </c>
       <c r="F125" t="n">
-        <v>118.0</v>
+        <v>120.0</v>
       </c>
       <c r="G125" t="n">
         <v>11.0</v>
@@ -5946,10 +5946,10 @@
         <v>773</v>
       </c>
       <c r="E137" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F137" t="n">
-        <v>133.0</v>
+        <v>136.0</v>
       </c>
       <c r="G137" t="n">
         <v>0.0</v>
@@ -6027,7 +6027,7 @@
         <v>775</v>
       </c>
       <c r="F140" t="n">
-        <v>688.0</v>
+        <v>691.0</v>
       </c>
       <c r="G140" t="n">
         <v>2.0</v>
@@ -6235,7 +6235,7 @@
         <v>775</v>
       </c>
       <c r="F148" t="n">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6570,7 +6570,7 @@
         <v>773</v>
       </c>
       <c r="E161" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F161" t="n">
         <v>199.0</v>
@@ -6677,7 +6677,7 @@
         <v>775</v>
       </c>
       <c r="F165" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G165" t="n">
         <v>4.0</v>
@@ -6781,7 +6781,7 @@
         <v>776</v>
       </c>
       <c r="F169" t="n">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="G169" t="n">
         <v>1.0</v>
@@ -6807,7 +6807,7 @@
         <v>775</v>
       </c>
       <c r="F170" t="n">
-        <v>67.0</v>
+        <v>73.0</v>
       </c>
       <c r="G170" t="n">
         <v>8.0</v>
@@ -6833,7 +6833,7 @@
         <v>775</v>
       </c>
       <c r="F171" t="n">
-        <v>332.0</v>
+        <v>334.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -7093,7 +7093,7 @@
         <v>775</v>
       </c>
       <c r="F181" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G181" t="n">
         <v>40.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7561,7 +7561,7 @@
         <v>775</v>
       </c>
       <c r="F199" t="n">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -8471,7 +8471,7 @@
         <v>775</v>
       </c>
       <c r="F234" t="n">
-        <v>376.0</v>
+        <v>378.0</v>
       </c>
       <c r="G234" t="n">
         <v>0.0</v>
@@ -8572,7 +8572,7 @@
         <v>773</v>
       </c>
       <c r="E238" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F238" t="n">
         <v>51.0</v>
@@ -8754,7 +8754,7 @@
         <v>773</v>
       </c>
       <c r="E245" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F245" t="n">
         <v>88.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>239.0</v>
+        <v>242.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -9355,7 +9355,7 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>243.0</v>
+        <v>247.0</v>
       </c>
       <c r="G268" t="n">
         <v>7.0</v>
@@ -9615,7 +9615,7 @@
         <v>775</v>
       </c>
       <c r="F278" t="n">
-        <v>169.0</v>
+        <v>173.0</v>
       </c>
       <c r="G278" t="n">
         <v>7.0</v>
@@ -9638,7 +9638,7 @@
         <v>773</v>
       </c>
       <c r="E279" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F279" t="n">
         <v>115.0</v>
@@ -9693,7 +9693,7 @@
         <v>775</v>
       </c>
       <c r="F281" t="n">
-        <v>511.0</v>
+        <v>512.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -10002,10 +10002,10 @@
         <v>773</v>
       </c>
       <c r="E293" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F293" t="n">
-        <v>284.0</v>
+        <v>287.0</v>
       </c>
       <c r="G293" t="n">
         <v>13.0</v>
@@ -10132,10 +10132,10 @@
         <v>773</v>
       </c>
       <c r="E298" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F298" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="G298" t="n">
         <v>3.0</v>
@@ -10395,7 +10395,7 @@
         <v>775</v>
       </c>
       <c r="F308" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G308" t="n">
         <v>0.0</v>
@@ -10785,7 +10785,7 @@
         <v>775</v>
       </c>
       <c r="F323" t="n">
-        <v>567.0</v>
+        <v>568.0</v>
       </c>
       <c r="G323" t="n">
         <v>8.0</v>
@@ -11227,7 +11227,7 @@
         <v>775</v>
       </c>
       <c r="F340" t="n">
-        <v>424.0</v>
+        <v>425.0</v>
       </c>
       <c r="G340" t="n">
         <v>1.0</v>
@@ -11305,7 +11305,7 @@
         <v>775</v>
       </c>
       <c r="F343" t="n">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="G343" t="n">
         <v>23.0</v>
@@ -11458,7 +11458,7 @@
         <v>773</v>
       </c>
       <c r="E349" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F349" t="n">
         <v>123.0</v>
@@ -11536,7 +11536,7 @@
         <v>773</v>
       </c>
       <c r="E352" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F352" t="n">
         <v>37.0</v>
@@ -11903,7 +11903,7 @@
         <v>776</v>
       </c>
       <c r="F366" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G366" t="n">
         <v>0.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>126.0</v>
+        <v>132.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12137,7 +12137,7 @@
         <v>776</v>
       </c>
       <c r="F375" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G375" t="n">
         <v>0.0</v>
@@ -12160,7 +12160,7 @@
         <v>773</v>
       </c>
       <c r="E376" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F376" t="n">
         <v>14.0</v>
@@ -12631,7 +12631,7 @@
         <v>776</v>
       </c>
       <c r="F394" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G394" t="n">
         <v>0.0</v>
@@ -12943,7 +12943,7 @@
         <v>776</v>
       </c>
       <c r="F406" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G406" t="n">
         <v>0.0</v>
@@ -13177,7 +13177,7 @@
         <v>775</v>
       </c>
       <c r="F415" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G415" t="n">
         <v>0.0</v>
@@ -13411,7 +13411,7 @@
         <v>777</v>
       </c>
       <c r="F424" t="n">
-        <v>268.0</v>
+        <v>270.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
@@ -13642,7 +13642,7 @@
         <v>773</v>
       </c>
       <c r="E433" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F433" t="n">
         <v>46.0</v>
@@ -13905,7 +13905,7 @@
         <v>775</v>
       </c>
       <c r="F443" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G443" t="n">
         <v>0.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>608.0</v>
+        <v>609.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -14113,7 +14113,7 @@
         <v>775</v>
       </c>
       <c r="F451" t="n">
-        <v>778.0</v>
+        <v>779.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -14162,7 +14162,7 @@
         <v>773</v>
       </c>
       <c r="E453" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F453" t="n">
         <v>136.0</v>
@@ -14243,7 +14243,7 @@
         <v>775</v>
       </c>
       <c r="F456" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G456" t="n">
         <v>0.0</v>
@@ -14292,7 +14292,7 @@
         <v>773</v>
       </c>
       <c r="E458" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F458" t="n">
         <v>196.0</v>
@@ -14552,10 +14552,10 @@
         <v>773</v>
       </c>
       <c r="E468" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F468" t="n">
-        <v>540.0</v>
+        <v>541.0</v>
       </c>
       <c r="G468" t="n">
         <v>0.0</v>
@@ -14656,7 +14656,7 @@
         <v>773</v>
       </c>
       <c r="E472" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F472" t="n">
         <v>129.0</v>
@@ -14864,7 +14864,7 @@
         <v>773</v>
       </c>
       <c r="E480" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F480" t="n">
         <v>64.0</v>
@@ -14945,7 +14945,7 @@
         <v>775</v>
       </c>
       <c r="F483" t="n">
-        <v>532.0</v>
+        <v>534.0</v>
       </c>
       <c r="G483" t="n">
         <v>5.0</v>
@@ -15254,7 +15254,7 @@
         <v>773</v>
       </c>
       <c r="E495" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F495" t="n">
         <v>143.0</v>
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>649.0</v>
+        <v>652.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15959,7 +15959,7 @@
         <v>775</v>
       </c>
       <c r="F522" t="n">
-        <v>203.0</v>
+        <v>206.0</v>
       </c>
       <c r="G522" t="n">
         <v>9.0</v>
@@ -16034,7 +16034,7 @@
         <v>773</v>
       </c>
       <c r="E525" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F525" t="n">
         <v>62.0</v>
@@ -16060,7 +16060,7 @@
         <v>773</v>
       </c>
       <c r="E526" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F526" t="n">
         <v>216.0</v>
@@ -16297,7 +16297,7 @@
         <v>775</v>
       </c>
       <c r="F535" t="n">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="G535" t="n">
         <v>0.0</v>
@@ -16401,7 +16401,7 @@
         <v>776</v>
       </c>
       <c r="F539" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -16450,7 +16450,7 @@
         <v>773</v>
       </c>
       <c r="E541" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F541" t="n">
         <v>16.0</v>
@@ -16840,7 +16840,7 @@
         <v>773</v>
       </c>
       <c r="E556" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F556" t="n">
         <v>210.0</v>
@@ -17256,7 +17256,7 @@
         <v>773</v>
       </c>
       <c r="E572" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F572" t="n">
         <v>92.0</v>
@@ -17311,7 +17311,7 @@
         <v>775</v>
       </c>
       <c r="F574" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="G574" t="n">
         <v>0.0</v>
@@ -17958,10 +17958,10 @@
         <v>773</v>
       </c>
       <c r="E599" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F599" t="n">
-        <v>276.0</v>
+        <v>280.0</v>
       </c>
       <c r="G599" t="n">
         <v>0.0</v>
@@ -18013,7 +18013,7 @@
         <v>775</v>
       </c>
       <c r="F601" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="G601" t="n">
         <v>0.0</v>
@@ -18195,7 +18195,7 @@
         <v>776</v>
       </c>
       <c r="F608" t="n">
-        <v>409.0</v>
+        <v>410.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18377,7 +18377,7 @@
         <v>775</v>
       </c>
       <c r="F615" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G615" t="n">
         <v>0.0</v>
@@ -18403,7 +18403,7 @@
         <v>776</v>
       </c>
       <c r="F616" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
@@ -18920,7 +18920,7 @@
         <v>773</v>
       </c>
       <c r="E636" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F636" t="n">
         <v>15.0</v>
@@ -18946,7 +18946,7 @@
         <v>773</v>
       </c>
       <c r="E637" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F637" t="n">
         <v>78.0</v>
@@ -19443,7 +19443,7 @@
         <v>776</v>
       </c>
       <c r="F656" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>203.0</v>
+        <v>206.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20119,7 +20119,7 @@
         <v>776</v>
       </c>
       <c r="F682" t="n">
-        <v>70.0</v>
+        <v>73.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20353,7 +20353,7 @@
         <v>776</v>
       </c>
       <c r="F691" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G691" t="n">
         <v>0.0</v>
@@ -20379,7 +20379,7 @@
         <v>776</v>
       </c>
       <c r="F692" t="n">
-        <v>145.0</v>
+        <v>148.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>442.0</v>
+        <v>445.0</v>
       </c>
       <c r="G693" t="n">
         <v>1.0</v>
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>174.0</v>
+        <v>178.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20691,7 +20691,7 @@
         <v>775</v>
       </c>
       <c r="F704" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G704" t="n">
         <v>0.0</v>
@@ -20769,7 +20769,7 @@
         <v>775</v>
       </c>
       <c r="F707" t="n">
-        <v>131.0</v>
+        <v>133.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20795,7 +20795,7 @@
         <v>776</v>
       </c>
       <c r="F708" t="n">
-        <v>97.0</v>
+        <v>99.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>246.0</v>
+        <v>249.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -21003,7 +21003,7 @@
         <v>775</v>
       </c>
       <c r="F716" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
       <c r="G716" t="n">
         <v>0.0</v>
@@ -21081,7 +21081,7 @@
         <v>776</v>
       </c>
       <c r="F719" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
@@ -21159,7 +21159,7 @@
         <v>776</v>
       </c>
       <c r="F722" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G722" t="n">
         <v>0.0</v>
@@ -21185,7 +21185,7 @@
         <v>776</v>
       </c>
       <c r="F723" t="n">
-        <v>75.0</v>
+        <v>80.0</v>
       </c>
       <c r="G723" t="n">
         <v>0.0</v>
@@ -21419,7 +21419,7 @@
         <v>776</v>
       </c>
       <c r="F732" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G732" t="n">
         <v>0.0</v>
@@ -21630,10 +21630,10 @@
         <v>215.0</v>
       </c>
       <c r="G740" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H740" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H740" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="741">
@@ -21991,7 +21991,7 @@
         <v>775</v>
       </c>
       <c r="F754" t="n">
-        <v>411.0</v>
+        <v>413.0</v>
       </c>
       <c r="G754" t="n">
         <v>0.0</v>
@@ -22121,7 +22121,7 @@
         <v>776</v>
       </c>
       <c r="F759" t="n">
-        <v>428.0</v>
+        <v>429.0</v>
       </c>
       <c r="G759" t="n">
         <v>0.0</v>
@@ -22225,7 +22225,7 @@
         <v>775</v>
       </c>
       <c r="F763" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G763" t="n">
         <v>0.0</v>
@@ -22277,7 +22277,7 @@
         <v>776</v>
       </c>
       <c r="F765" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G765" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -4158,7 +4158,7 @@
         <v>154.0</v>
       </c>
       <c r="G68" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="H68" t="n">
         <v>3.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>455.0</v>
+        <v>457.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -5611,7 +5611,7 @@
         <v>775</v>
       </c>
       <c r="F124" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G124" t="n">
         <v>0.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7483,7 +7483,7 @@
         <v>775</v>
       </c>
       <c r="F196" t="n">
-        <v>335.0</v>
+        <v>337.0</v>
       </c>
       <c r="G196" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1026.0</v>
+        <v>1027.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -9355,7 +9355,7 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>247.0</v>
+        <v>250.0</v>
       </c>
       <c r="G268" t="n">
         <v>7.0</v>
@@ -10005,7 +10005,7 @@
         <v>775</v>
       </c>
       <c r="F293" t="n">
-        <v>287.0</v>
+        <v>288.0</v>
       </c>
       <c r="G293" t="n">
         <v>13.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>548.0</v>
+        <v>549.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12839,7 +12839,7 @@
         <v>775</v>
       </c>
       <c r="F402" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
       <c r="G402" t="n">
         <v>1.0</v>
@@ -13177,7 +13177,7 @@
         <v>775</v>
       </c>
       <c r="F415" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G415" t="n">
         <v>0.0</v>
@@ -14685,7 +14685,7 @@
         <v>775</v>
       </c>
       <c r="F473" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G473" t="n">
         <v>0.0</v>
@@ -15829,7 +15829,7 @@
         <v>777</v>
       </c>
       <c r="F517" t="n">
-        <v>335.0</v>
+        <v>336.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
@@ -17233,7 +17233,7 @@
         <v>776</v>
       </c>
       <c r="F571" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G571" t="n">
         <v>0.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>445.0</v>
+        <v>451.0</v>
       </c>
       <c r="G693" t="n">
         <v>1.0</v>
@@ -20483,7 +20483,7 @@
         <v>776</v>
       </c>
       <c r="F696" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G696" t="n">
         <v>0.0</v>
@@ -20587,7 +20587,7 @@
         <v>777</v>
       </c>
       <c r="F700" t="n">
-        <v>210.0</v>
+        <v>212.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -20847,7 +20847,7 @@
         <v>777</v>
       </c>
       <c r="F710" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G710" t="n">
         <v>0.0</v>
@@ -20899,7 +20899,7 @@
         <v>776</v>
       </c>
       <c r="F712" t="n">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="G712" t="n">
         <v>0.0</v>
@@ -21029,7 +21029,7 @@
         <v>777</v>
       </c>
       <c r="F717" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G717" t="n">
         <v>19.0</v>
@@ -21607,7 +21607,7 @@
         <v>0.0</v>
       </c>
       <c r="H739" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="740">
@@ -21627,13 +21627,13 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>215.0</v>
+        <v>218.0</v>
       </c>
       <c r="G740" t="n">
         <v>8.0</v>
       </c>
       <c r="H740" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="741">
@@ -21679,7 +21679,7 @@
         <v>778</v>
       </c>
       <c r="F742" t="n">
-        <v>198.0</v>
+        <v>202.0</v>
       </c>
       <c r="G742" t="n">
         <v>0.0</v>
@@ -22413,7 +22413,7 @@
         <v>0.0</v>
       </c>
       <c r="H770" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="771">
@@ -22459,7 +22459,7 @@
         <v>778</v>
       </c>
       <c r="F772" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G772" t="n">
         <v>0.0</v>
@@ -22667,13 +22667,13 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>518.0</v>
+        <v>520.0</v>
       </c>
       <c r="G780" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H780" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="781">
@@ -22719,13 +22719,13 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>518.0</v>
+        <v>520.0</v>
       </c>
       <c r="G782" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H782" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>457.0</v>
+        <v>459.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="G127" t="n">
         <v>11.0</v>
@@ -6625,7 +6625,7 @@
         <v>775</v>
       </c>
       <c r="F163" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G163" t="n">
         <v>23.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7327,7 +7327,7 @@
         <v>775</v>
       </c>
       <c r="F190" t="n">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="G190" t="n">
         <v>0.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -8133,7 +8133,7 @@
         <v>775</v>
       </c>
       <c r="F221" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8393,7 +8393,7 @@
         <v>775</v>
       </c>
       <c r="F231" t="n">
-        <v>275.0</v>
+        <v>277.0</v>
       </c>
       <c r="G231" t="n">
         <v>9.0</v>
@@ -8471,7 +8471,7 @@
         <v>775</v>
       </c>
       <c r="F234" t="n">
-        <v>378.0</v>
+        <v>380.0</v>
       </c>
       <c r="G234" t="n">
         <v>0.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>270.0</v>
+        <v>271.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -10811,7 +10811,7 @@
         <v>776</v>
       </c>
       <c r="F324" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>609.0</v>
+        <v>610.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2460.0</v>
+        <v>2462.0</v>
       </c>
       <c r="G518" t="n">
         <v>307.0</v>
@@ -16456,7 +16456,7 @@
         <v>16.0</v>
       </c>
       <c r="G541" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H541" t="n">
         <v>0.0</v>
@@ -16820,7 +16820,7 @@
         <v>418.0</v>
       </c>
       <c r="G555" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H555" t="n">
         <v>3.0</v>
@@ -17103,7 +17103,7 @@
         <v>775</v>
       </c>
       <c r="F566" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G566" t="n">
         <v>0.0</v>
@@ -19183,7 +19183,7 @@
         <v>775</v>
       </c>
       <c r="F646" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -20587,7 +20587,7 @@
         <v>777</v>
       </c>
       <c r="F700" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3557,7 +3557,7 @@
         <v>775</v>
       </c>
       <c r="F45" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G45" t="n">
         <v>2.0</v>
@@ -8263,7 +8263,7 @@
         <v>776</v>
       </c>
       <c r="F226" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -8471,7 +8471,7 @@
         <v>775</v>
       </c>
       <c r="F234" t="n">
-        <v>380.0</v>
+        <v>383.0</v>
       </c>
       <c r="G234" t="n">
         <v>0.0</v>
@@ -19183,7 +19183,7 @@
         <v>775</v>
       </c>
       <c r="F646" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -21627,7 +21627,7 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="G740" t="n">
         <v>8.0</v>
@@ -21653,7 +21653,7 @@
         <v>778</v>
       </c>
       <c r="F741" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>520.0</v>
+        <v>521.0</v>
       </c>
       <c r="G780" t="n">
         <v>3.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>520.0</v>
+        <v>521.0</v>
       </c>
       <c r="G782" t="n">
         <v>3.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2595,7 +2595,7 @@
         <v>775</v>
       </c>
       <c r="F8" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -2673,13 +2673,13 @@
         <v>775</v>
       </c>
       <c r="F11" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="12">
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>459.0</v>
+        <v>460.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4753,7 +4753,7 @@
         <v>775</v>
       </c>
       <c r="F91" t="n">
-        <v>477.0</v>
+        <v>479.0</v>
       </c>
       <c r="G91" t="n">
         <v>1.0</v>
@@ -5923,7 +5923,7 @@
         <v>775</v>
       </c>
       <c r="F136" t="n">
-        <v>110.0</v>
+        <v>112.0</v>
       </c>
       <c r="G136" t="n">
         <v>3.0</v>
@@ -6079,7 +6079,7 @@
         <v>775</v>
       </c>
       <c r="F142" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -6807,7 +6807,7 @@
         <v>775</v>
       </c>
       <c r="F170" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G170" t="n">
         <v>8.0</v>
@@ -6963,7 +6963,7 @@
         <v>775</v>
       </c>
       <c r="F176" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -7119,7 +7119,7 @@
         <v>776</v>
       </c>
       <c r="F182" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G182" t="n">
         <v>0.0</v>
@@ -7483,7 +7483,7 @@
         <v>775</v>
       </c>
       <c r="F196" t="n">
-        <v>337.0</v>
+        <v>338.0</v>
       </c>
       <c r="G196" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1027.0</v>
+        <v>1029.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -8783,7 +8783,7 @@
         <v>776</v>
       </c>
       <c r="F246" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G246" t="n">
         <v>0.0</v>
@@ -10005,7 +10005,7 @@
         <v>775</v>
       </c>
       <c r="F293" t="n">
-        <v>288.0</v>
+        <v>292.0</v>
       </c>
       <c r="G293" t="n">
         <v>13.0</v>
@@ -10213,7 +10213,7 @@
         <v>775</v>
       </c>
       <c r="F301" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G301" t="n">
         <v>11.0</v>
@@ -10551,7 +10551,7 @@
         <v>775</v>
       </c>
       <c r="F314" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G314" t="n">
         <v>0.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>271.0</v>
+        <v>272.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -10811,7 +10811,7 @@
         <v>776</v>
       </c>
       <c r="F324" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -10863,7 +10863,7 @@
         <v>775</v>
       </c>
       <c r="F326" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G326" t="n">
         <v>0.0</v>
@@ -10889,7 +10889,7 @@
         <v>775</v>
       </c>
       <c r="F327" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G327" t="n">
         <v>1.0</v>
@@ -11305,13 +11305,13 @@
         <v>775</v>
       </c>
       <c r="F343" t="n">
-        <v>228.0</v>
+        <v>231.0</v>
       </c>
       <c r="G343" t="n">
         <v>23.0</v>
       </c>
       <c r="H343" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="344">
@@ -11539,7 +11539,7 @@
         <v>775</v>
       </c>
       <c r="F352" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="G352" t="n">
         <v>8.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>158.0</v>
+        <v>161.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>132.0</v>
+        <v>137.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12631,7 +12631,7 @@
         <v>776</v>
       </c>
       <c r="F394" t="n">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="G394" t="n">
         <v>0.0</v>
@@ -12943,7 +12943,7 @@
         <v>776</v>
       </c>
       <c r="F406" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G406" t="n">
         <v>0.0</v>
@@ -13255,7 +13255,7 @@
         <v>775</v>
       </c>
       <c r="F418" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="G418" t="n">
         <v>1.0</v>
@@ -14061,7 +14061,7 @@
         <v>776</v>
       </c>
       <c r="F449" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G449" t="n">
         <v>0.0</v>
@@ -15075,7 +15075,7 @@
         <v>776</v>
       </c>
       <c r="F488" t="n">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
       <c r="G488" t="n">
         <v>0.0</v>
@@ -15205,10 +15205,10 @@
         <v>775</v>
       </c>
       <c r="F493" t="n">
-        <v>382.0</v>
+        <v>383.0</v>
       </c>
       <c r="G493" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="H493" t="n">
         <v>2.0</v>
@@ -15283,7 +15283,7 @@
         <v>776</v>
       </c>
       <c r="F496" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -15309,13 +15309,13 @@
         <v>776</v>
       </c>
       <c r="F497" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G497" t="n">
         <v>0.0</v>
       </c>
       <c r="H497" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="498">
@@ -15569,7 +15569,7 @@
         <v>776</v>
       </c>
       <c r="F507" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2462.0</v>
+        <v>2466.0</v>
       </c>
       <c r="G518" t="n">
         <v>307.0</v>
@@ -16063,7 +16063,7 @@
         <v>775</v>
       </c>
       <c r="F526" t="n">
-        <v>216.0</v>
+        <v>219.0</v>
       </c>
       <c r="G526" t="n">
         <v>3.0</v>
@@ -16167,7 +16167,7 @@
         <v>775</v>
       </c>
       <c r="F530" t="n">
-        <v>437.0</v>
+        <v>440.0</v>
       </c>
       <c r="G530" t="n">
         <v>3.0</v>
@@ -16459,7 +16459,7 @@
         <v>13.0</v>
       </c>
       <c r="H541" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="542">
@@ -16635,7 +16635,7 @@
         <v>775</v>
       </c>
       <c r="F548" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="G548" t="n">
         <v>0.0</v>
@@ -16869,7 +16869,7 @@
         <v>775</v>
       </c>
       <c r="F557" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G557" t="n">
         <v>0.0</v>
@@ -17025,7 +17025,7 @@
         <v>776</v>
       </c>
       <c r="F563" t="n">
-        <v>357.0</v>
+        <v>359.0</v>
       </c>
       <c r="G563" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>640.0</v>
+        <v>642.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>775</v>
       </c>
       <c r="F14" t="n">
-        <v>494.0</v>
+        <v>496.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2803,7 +2803,7 @@
         <v>775</v>
       </c>
       <c r="F16" t="n">
-        <v>422.0</v>
+        <v>423.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2959,7 +2959,7 @@
         <v>776</v>
       </c>
       <c r="F22" t="n">
-        <v>399.0</v>
+        <v>402.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3193,7 +3193,7 @@
         <v>775</v>
       </c>
       <c r="F31" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -3323,7 +3323,7 @@
         <v>775</v>
       </c>
       <c r="F36" t="n">
-        <v>554.0</v>
+        <v>557.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3791,7 +3791,7 @@
         <v>775</v>
       </c>
       <c r="F54" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -3843,7 +3843,7 @@
         <v>775</v>
       </c>
       <c r="F56" t="n">
-        <v>60.0</v>
+        <v>62.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>214.0</v>
+        <v>216.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4311,7 +4311,7 @@
         <v>775</v>
       </c>
       <c r="F74" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4337,7 +4337,7 @@
         <v>776</v>
       </c>
       <c r="F75" t="n">
-        <v>371.0</v>
+        <v>375.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -4389,7 +4389,7 @@
         <v>775</v>
       </c>
       <c r="F77" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>460.0</v>
+        <v>462.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4805,7 +4805,7 @@
         <v>775</v>
       </c>
       <c r="F93" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
       <c r="G93" t="n">
         <v>17.0</v>
@@ -4987,7 +4987,7 @@
         <v>776</v>
       </c>
       <c r="F100" t="n">
-        <v>454.0</v>
+        <v>456.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>541.0</v>
+        <v>543.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -5559,7 +5559,7 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>476.0</v>
+        <v>478.0</v>
       </c>
       <c r="G122" t="n">
         <v>12.0</v>
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>239.0</v>
+        <v>246.0</v>
       </c>
       <c r="G127" t="n">
         <v>11.0</v>
@@ -5897,7 +5897,7 @@
         <v>775</v>
       </c>
       <c r="F135" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G135" t="n">
         <v>0.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -6833,7 +6833,7 @@
         <v>775</v>
       </c>
       <c r="F171" t="n">
-        <v>334.0</v>
+        <v>335.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7015,7 +7015,7 @@
         <v>775</v>
       </c>
       <c r="F178" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
       <c r="G178" t="n">
         <v>4.0</v>
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>543.0</v>
+        <v>546.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7301,7 +7301,7 @@
         <v>776</v>
       </c>
       <c r="F189" t="n">
-        <v>705.0</v>
+        <v>708.0</v>
       </c>
       <c r="G189" t="n">
         <v>1.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7431,7 +7431,7 @@
         <v>776</v>
       </c>
       <c r="F194" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G194" t="n">
         <v>0.0</v>
@@ -7613,7 +7613,7 @@
         <v>775</v>
       </c>
       <c r="F201" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G201" t="n">
         <v>0.0</v>
@@ -8133,7 +8133,7 @@
         <v>775</v>
       </c>
       <c r="F221" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8315,7 +8315,7 @@
         <v>775</v>
       </c>
       <c r="F228" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G228" t="n">
         <v>0.0</v>
@@ -8393,7 +8393,7 @@
         <v>775</v>
       </c>
       <c r="F231" t="n">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
       <c r="G231" t="n">
         <v>9.0</v>
@@ -8523,7 +8523,7 @@
         <v>776</v>
       </c>
       <c r="F236" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G236" t="n">
         <v>0.0</v>
@@ -9927,7 +9927,7 @@
         <v>775</v>
       </c>
       <c r="F290" t="n">
-        <v>563.0</v>
+        <v>568.0</v>
       </c>
       <c r="G290" t="n">
         <v>42.0</v>
@@ -10291,7 +10291,7 @@
         <v>775</v>
       </c>
       <c r="F304" t="n">
-        <v>409.0</v>
+        <v>411.0</v>
       </c>
       <c r="G304" t="n">
         <v>0.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1051.0</v>
+        <v>1057.0</v>
       </c>
       <c r="G310" t="n">
         <v>20.0</v>
@@ -10577,7 +10577,7 @@
         <v>775</v>
       </c>
       <c r="F315" t="n">
-        <v>535.0</v>
+        <v>539.0</v>
       </c>
       <c r="G315" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         <v>775</v>
       </c>
       <c r="F340" t="n">
-        <v>425.0</v>
+        <v>428.0</v>
       </c>
       <c r="G340" t="n">
         <v>1.0</v>
@@ -11435,7 +11435,7 @@
         <v>776</v>
       </c>
       <c r="F348" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G348" t="n">
         <v>0.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>161.0</v>
+        <v>163.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12137,7 +12137,7 @@
         <v>776</v>
       </c>
       <c r="F375" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
       <c r="G375" t="n">
         <v>0.0</v>
@@ -12475,7 +12475,7 @@
         <v>776</v>
       </c>
       <c r="F388" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
@@ -12553,7 +12553,7 @@
         <v>775</v>
       </c>
       <c r="F391" t="n">
-        <v>265.0</v>
+        <v>266.0</v>
       </c>
       <c r="G391" t="n">
         <v>1.0</v>
@@ -12631,7 +12631,7 @@
         <v>776</v>
       </c>
       <c r="F394" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="G394" t="n">
         <v>0.0</v>
@@ -13203,7 +13203,7 @@
         <v>776</v>
       </c>
       <c r="F416" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G416" t="n">
         <v>0.0</v>
@@ -13437,7 +13437,7 @@
         <v>775</v>
       </c>
       <c r="F425" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G425" t="n">
         <v>3.0</v>
@@ -13567,7 +13567,7 @@
         <v>775</v>
       </c>
       <c r="F430" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G430" t="n">
         <v>3.0</v>
@@ -13775,7 +13775,7 @@
         <v>775</v>
       </c>
       <c r="F438" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="G438" t="n">
         <v>0.0</v>
@@ -14087,7 +14087,7 @@
         <v>775</v>
       </c>
       <c r="F450" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
       <c r="G450" t="n">
         <v>11.0</v>
@@ -14581,7 +14581,7 @@
         <v>775</v>
       </c>
       <c r="F469" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
       <c r="G469" t="n">
         <v>0.0</v>
@@ -14997,7 +14997,7 @@
         <v>775</v>
       </c>
       <c r="F485" t="n">
-        <v>253.0</v>
+        <v>254.0</v>
       </c>
       <c r="G485" t="n">
         <v>8.0</v>
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>652.0</v>
+        <v>657.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -16531,7 +16531,7 @@
         <v>776</v>
       </c>
       <c r="F544" t="n">
-        <v>324.0</v>
+        <v>326.0</v>
       </c>
       <c r="G544" t="n">
         <v>1.0</v>
@@ -16609,7 +16609,7 @@
         <v>776</v>
       </c>
       <c r="F547" t="n">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="G547" t="n">
         <v>1.0</v>
@@ -16895,7 +16895,7 @@
         <v>775</v>
       </c>
       <c r="F558" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G558" t="n">
         <v>0.0</v>
@@ -17519,7 +17519,7 @@
         <v>776</v>
       </c>
       <c r="F582" t="n">
-        <v>298.0</v>
+        <v>301.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -17623,7 +17623,7 @@
         <v>775</v>
       </c>
       <c r="F586" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G586" t="n">
         <v>0.0</v>
@@ -17701,7 +17701,7 @@
         <v>775</v>
       </c>
       <c r="F589" t="n">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>
@@ -17805,7 +17805,7 @@
         <v>775</v>
       </c>
       <c r="F593" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="G593" t="n">
         <v>0.0</v>
@@ -18195,7 +18195,7 @@
         <v>776</v>
       </c>
       <c r="F608" t="n">
-        <v>410.0</v>
+        <v>411.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18793,7 +18793,7 @@
         <v>775</v>
       </c>
       <c r="F631" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -19651,7 +19651,7 @@
         <v>775</v>
       </c>
       <c r="F664" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G664" t="n">
         <v>35.0</v>
@@ -20041,7 +20041,7 @@
         <v>776</v>
       </c>
       <c r="F679" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G679" t="n">
         <v>0.0</v>
@@ -20379,7 +20379,7 @@
         <v>776</v>
       </c>
       <c r="F692" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>178.0</v>
+        <v>182.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20535,7 +20535,7 @@
         <v>776</v>
       </c>
       <c r="F698" t="n">
-        <v>161.0</v>
+        <v>163.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -21835,7 +21835,7 @@
         <v>775</v>
       </c>
       <c r="F748" t="n">
-        <v>333.0</v>
+        <v>335.0</v>
       </c>
       <c r="G748" t="n">
         <v>0.0</v>
@@ -21913,7 +21913,7 @@
         <v>776</v>
       </c>
       <c r="F751" t="n">
-        <v>168.0</v>
+        <v>171.0</v>
       </c>
       <c r="G751" t="n">
         <v>0.0</v>
@@ -22121,7 +22121,7 @@
         <v>776</v>
       </c>
       <c r="F759" t="n">
-        <v>429.0</v>
+        <v>430.0</v>
       </c>
       <c r="G759" t="n">
         <v>0.0</v>
@@ -22485,7 +22485,7 @@
         <v>778</v>
       </c>
       <c r="F773" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G773" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3401,7 +3401,7 @@
         <v>775</v>
       </c>
       <c r="F39" t="n">
-        <v>260.0</v>
+        <v>263.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -4103,7 +4103,7 @@
         <v>775</v>
       </c>
       <c r="F66" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -4727,7 +4727,7 @@
         <v>775</v>
       </c>
       <c r="F90" t="n">
-        <v>54.0</v>
+        <v>57.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -4779,7 +4779,7 @@
         <v>775</v>
       </c>
       <c r="F92" t="n">
-        <v>124.0</v>
+        <v>129.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -5143,7 +5143,7 @@
         <v>775</v>
       </c>
       <c r="F106" t="n">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -5403,7 +5403,7 @@
         <v>775</v>
       </c>
       <c r="F116" t="n">
-        <v>189.0</v>
+        <v>192.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -6235,7 +6235,7 @@
         <v>775</v>
       </c>
       <c r="F148" t="n">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -8133,7 +8133,7 @@
         <v>775</v>
       </c>
       <c r="F221" t="n">
-        <v>160.0</v>
+        <v>162.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8448,7 +8448,7 @@
         <v>0.0</v>
       </c>
       <c r="G233" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="H233" t="n">
         <v>0.0</v>
@@ -8471,7 +8471,7 @@
         <v>775</v>
       </c>
       <c r="F234" t="n">
-        <v>383.0</v>
+        <v>384.0</v>
       </c>
       <c r="G234" t="n">
         <v>0.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>242.0</v>
+        <v>244.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -9693,7 +9693,7 @@
         <v>775</v>
       </c>
       <c r="F281" t="n">
-        <v>512.0</v>
+        <v>514.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -12917,7 +12917,7 @@
         <v>777</v>
       </c>
       <c r="F405" t="n">
-        <v>448.0</v>
+        <v>460.0</v>
       </c>
       <c r="G405" t="n">
         <v>0.0</v>
@@ -13411,7 +13411,7 @@
         <v>777</v>
       </c>
       <c r="F424" t="n">
-        <v>270.0</v>
+        <v>272.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
@@ -13671,7 +13671,7 @@
         <v>775</v>
       </c>
       <c r="F434" t="n">
-        <v>98.0</v>
+        <v>102.0</v>
       </c>
       <c r="G434" t="n">
         <v>1.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>610.0</v>
+        <v>612.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -18377,7 +18377,7 @@
         <v>775</v>
       </c>
       <c r="F615" t="n">
-        <v>86.0</v>
+        <v>90.0</v>
       </c>
       <c r="G615" t="n">
         <v>0.0</v>
@@ -19183,7 +19183,7 @@
         <v>775</v>
       </c>
       <c r="F646" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>206.0</v>
+        <v>211.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20509,7 +20509,7 @@
         <v>776</v>
       </c>
       <c r="F697" t="n">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20587,10 +20587,10 @@
         <v>777</v>
       </c>
       <c r="F700" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
       <c r="G700" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H700" t="n">
         <v>0.0</v>
@@ -20899,7 +20899,7 @@
         <v>776</v>
       </c>
       <c r="F712" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G712" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>249.0</v>
+        <v>251.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -21627,7 +21627,7 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="G740" t="n">
         <v>8.0</v>
@@ -21991,7 +21991,7 @@
         <v>775</v>
       </c>
       <c r="F754" t="n">
-        <v>413.0</v>
+        <v>415.0</v>
       </c>
       <c r="G754" t="n">
         <v>0.0</v>
@@ -22303,7 +22303,7 @@
         <v>776</v>
       </c>
       <c r="F766" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G766" t="n">
         <v>0.0</v>
@@ -22407,7 +22407,7 @@
         <v>778</v>
       </c>
       <c r="F770" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G770" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2517,7 +2517,7 @@
         <v>776</v>
       </c>
       <c r="F5" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -2725,7 +2725,7 @@
         <v>777</v>
       </c>
       <c r="F13" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -2933,7 +2933,7 @@
         <v>775</v>
       </c>
       <c r="F21" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>136.0</v>
+        <v>142.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -4285,7 +4285,7 @@
         <v>775</v>
       </c>
       <c r="F73" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>462.0</v>
+        <v>463.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4753,7 +4753,7 @@
         <v>775</v>
       </c>
       <c r="F91" t="n">
-        <v>479.0</v>
+        <v>480.0</v>
       </c>
       <c r="G91" t="n">
         <v>1.0</v>
@@ -4883,7 +4883,7 @@
         <v>775</v>
       </c>
       <c r="F96" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -5065,7 +5065,7 @@
         <v>775</v>
       </c>
       <c r="F103" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G103" t="n">
         <v>1.0</v>
@@ -5611,7 +5611,7 @@
         <v>775</v>
       </c>
       <c r="F124" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="G124" t="n">
         <v>0.0</v>
@@ -5637,7 +5637,7 @@
         <v>775</v>
       </c>
       <c r="F125" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G125" t="n">
         <v>11.0</v>
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>246.0</v>
+        <v>249.0</v>
       </c>
       <c r="G127" t="n">
         <v>11.0</v>
@@ -5949,7 +5949,7 @@
         <v>775</v>
       </c>
       <c r="F137" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G137" t="n">
         <v>0.0</v>
@@ -6079,7 +6079,7 @@
         <v>775</v>
       </c>
       <c r="F142" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -6573,7 +6573,7 @@
         <v>775</v>
       </c>
       <c r="F161" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6677,7 +6677,7 @@
         <v>775</v>
       </c>
       <c r="F165" t="n">
-        <v>55.0</v>
+        <v>58.0</v>
       </c>
       <c r="G165" t="n">
         <v>4.0</v>
@@ -6703,7 +6703,7 @@
         <v>775</v>
       </c>
       <c r="F166" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="G166" t="n">
         <v>0.0</v>
@@ -7197,7 +7197,7 @@
         <v>775</v>
       </c>
       <c r="F185" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
       <c r="G185" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1029.0</v>
+        <v>1030.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -8783,7 +8783,7 @@
         <v>776</v>
       </c>
       <c r="F246" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G246" t="n">
         <v>0.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>244.0</v>
+        <v>247.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -9355,7 +9355,7 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="G268" t="n">
         <v>7.0</v>
@@ -9485,7 +9485,7 @@
         <v>775</v>
       </c>
       <c r="F273" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G273" t="n">
         <v>53.0</v>
@@ -9693,7 +9693,7 @@
         <v>775</v>
       </c>
       <c r="F281" t="n">
-        <v>514.0</v>
+        <v>516.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -9927,7 +9927,7 @@
         <v>775</v>
       </c>
       <c r="F290" t="n">
-        <v>568.0</v>
+        <v>571.0</v>
       </c>
       <c r="G290" t="n">
         <v>42.0</v>
@@ -10005,7 +10005,7 @@
         <v>775</v>
       </c>
       <c r="F293" t="n">
-        <v>292.0</v>
+        <v>297.0</v>
       </c>
       <c r="G293" t="n">
         <v>13.0</v>
@@ -10031,7 +10031,7 @@
         <v>775</v>
       </c>
       <c r="F294" t="n">
-        <v>243.0</v>
+        <v>244.0</v>
       </c>
       <c r="G294" t="n">
         <v>11.0</v>
@@ -10135,7 +10135,7 @@
         <v>775</v>
       </c>
       <c r="F298" t="n">
-        <v>213.0</v>
+        <v>215.0</v>
       </c>
       <c r="G298" t="n">
         <v>3.0</v>
@@ -10395,7 +10395,7 @@
         <v>775</v>
       </c>
       <c r="F308" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G308" t="n">
         <v>0.0</v>
@@ -10551,7 +10551,7 @@
         <v>775</v>
       </c>
       <c r="F314" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="G314" t="n">
         <v>0.0</v>
@@ -10941,7 +10941,7 @@
         <v>775</v>
       </c>
       <c r="F329" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G329" t="n">
         <v>25.0</v>
@@ -11311,7 +11311,7 @@
         <v>23.0</v>
       </c>
       <c r="H343" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="344">
@@ -11539,7 +11539,7 @@
         <v>775</v>
       </c>
       <c r="F352" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="G352" t="n">
         <v>8.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>549.0</v>
+        <v>550.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12137,7 +12137,7 @@
         <v>776</v>
       </c>
       <c r="F375" t="n">
-        <v>183.0</v>
+        <v>186.0</v>
       </c>
       <c r="G375" t="n">
         <v>0.0</v>
@@ -12189,7 +12189,7 @@
         <v>775</v>
       </c>
       <c r="F377" t="n">
-        <v>128.0</v>
+        <v>133.0</v>
       </c>
       <c r="G377" t="n">
         <v>7.0</v>
@@ -12319,7 +12319,7 @@
         <v>775</v>
       </c>
       <c r="F382" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G382" t="n">
         <v>0.0</v>
@@ -12631,7 +12631,7 @@
         <v>776</v>
       </c>
       <c r="F394" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G394" t="n">
         <v>0.0</v>
@@ -12735,7 +12735,7 @@
         <v>776</v>
       </c>
       <c r="F398" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G398" t="n">
         <v>0.0</v>
@@ -12839,7 +12839,7 @@
         <v>775</v>
       </c>
       <c r="F402" t="n">
-        <v>154.0</v>
+        <v>159.0</v>
       </c>
       <c r="G402" t="n">
         <v>1.0</v>
@@ -13411,7 +13411,7 @@
         <v>777</v>
       </c>
       <c r="F424" t="n">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
@@ -13469,7 +13469,7 @@
         <v>0.0</v>
       </c>
       <c r="H426" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="427">
@@ -13775,7 +13775,7 @@
         <v>775</v>
       </c>
       <c r="F438" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G438" t="n">
         <v>0.0</v>
@@ -14061,7 +14061,7 @@
         <v>776</v>
       </c>
       <c r="F449" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G449" t="n">
         <v>0.0</v>
@@ -14587,7 +14587,7 @@
         <v>0.0</v>
       </c>
       <c r="H469" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="470">
@@ -14789,7 +14789,7 @@
         <v>776</v>
       </c>
       <c r="F477" t="n">
-        <v>165.0</v>
+        <v>167.0</v>
       </c>
       <c r="G477" t="n">
         <v>0.0</v>
@@ -16037,7 +16037,7 @@
         <v>775</v>
       </c>
       <c r="F525" t="n">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="G525" t="n">
         <v>0.0</v>
@@ -16063,7 +16063,7 @@
         <v>775</v>
       </c>
       <c r="F526" t="n">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="G526" t="n">
         <v>3.0</v>
@@ -16635,7 +16635,7 @@
         <v>775</v>
       </c>
       <c r="F548" t="n">
-        <v>73.0</v>
+        <v>81.0</v>
       </c>
       <c r="G548" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         <v>775</v>
       </c>
       <c r="F599" t="n">
-        <v>280.0</v>
+        <v>283.0</v>
       </c>
       <c r="G599" t="n">
         <v>0.0</v>
@@ -18221,7 +18221,7 @@
         <v>776</v>
       </c>
       <c r="F609" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G609" t="n">
         <v>0.0</v>
@@ -18585,7 +18585,7 @@
         <v>776</v>
       </c>
       <c r="F623" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G623" t="n">
         <v>0.0</v>
@@ -20743,7 +20743,7 @@
         <v>776</v>
       </c>
       <c r="F706" t="n">
-        <v>92.0</v>
+        <v>98.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20873,7 +20873,7 @@
         <v>776</v>
       </c>
       <c r="F711" t="n">
-        <v>40.0</v>
+        <v>46.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -21341,7 +21341,7 @@
         <v>776</v>
       </c>
       <c r="F729" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G729" t="n">
         <v>0.0</v>
@@ -21367,7 +21367,7 @@
         <v>776</v>
       </c>
       <c r="F730" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G730" t="n">
         <v>0.0</v>
@@ -21627,13 +21627,13 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>220.0</v>
+        <v>235.0</v>
       </c>
       <c r="G740" t="n">
         <v>8.0</v>
       </c>
       <c r="H740" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="741">
@@ -21939,7 +21939,7 @@
         <v>775</v>
       </c>
       <c r="F752" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="G752" t="n">
         <v>0.0</v>
@@ -22433,7 +22433,7 @@
         <v>778</v>
       </c>
       <c r="F771" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G127" t="n">
         <v>11.0</v>
@@ -5741,7 +5741,7 @@
         <v>775</v>
       </c>
       <c r="F129" t="n">
-        <v>297.0</v>
+        <v>299.0</v>
       </c>
       <c r="G129" t="n">
         <v>0.0</v>
@@ -6495,7 +6495,7 @@
         <v>775</v>
       </c>
       <c r="F158" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G158" t="n">
         <v>2.0</v>
@@ -6963,7 +6963,7 @@
         <v>775</v>
       </c>
       <c r="F176" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -8133,7 +8133,7 @@
         <v>775</v>
       </c>
       <c r="F221" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8393,7 +8393,7 @@
         <v>775</v>
       </c>
       <c r="F231" t="n">
-        <v>278.0</v>
+        <v>280.0</v>
       </c>
       <c r="G231" t="n">
         <v>9.0</v>
@@ -9875,7 +9875,7 @@
         <v>775</v>
       </c>
       <c r="F288" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="G288" t="n">
         <v>0.0</v>
@@ -9927,7 +9927,7 @@
         <v>775</v>
       </c>
       <c r="F290" t="n">
-        <v>571.0</v>
+        <v>587.0</v>
       </c>
       <c r="G290" t="n">
         <v>42.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>138.0</v>
+        <v>141.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -22277,7 +22277,7 @@
         <v>776</v>
       </c>
       <c r="F765" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G765" t="n">
         <v>0.0</v>
@@ -22673,7 +22673,7 @@
         <v>3.0</v>
       </c>
       <c r="H780" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="781">
@@ -22725,7 +22725,7 @@
         <v>3.0</v>
       </c>
       <c r="H782" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -8471,7 +8471,7 @@
         <v>775</v>
       </c>
       <c r="F234" t="n">
-        <v>384.0</v>
+        <v>386.0</v>
       </c>
       <c r="G234" t="n">
         <v>0.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>247.0</v>
+        <v>248.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>211.0</v>
+        <v>214.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20275,7 +20275,7 @@
         <v>777</v>
       </c>
       <c r="F688" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G688" t="n">
         <v>12.0</v>
@@ -20743,7 +20743,7 @@
         <v>776</v>
       </c>
       <c r="F706" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -21029,7 +21029,7 @@
         <v>777</v>
       </c>
       <c r="F717" t="n">
-        <v>188.0</v>
+        <v>193.0</v>
       </c>
       <c r="G717" t="n">
         <v>19.0</v>
@@ -21679,7 +21679,7 @@
         <v>778</v>
       </c>
       <c r="F742" t="n">
-        <v>202.0</v>
+        <v>205.0</v>
       </c>
       <c r="G742" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>642.0</v>
+        <v>647.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2751,7 +2751,7 @@
         <v>775</v>
       </c>
       <c r="F14" t="n">
-        <v>496.0</v>
+        <v>498.0</v>
       </c>
       <c r="G14" t="n">
         <v>3.0</v>
@@ -2803,7 +2803,7 @@
         <v>775</v>
       </c>
       <c r="F16" t="n">
-        <v>423.0</v>
+        <v>426.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2959,7 +2959,7 @@
         <v>776</v>
       </c>
       <c r="F22" t="n">
-        <v>402.0</v>
+        <v>403.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3323,7 +3323,7 @@
         <v>775</v>
       </c>
       <c r="F36" t="n">
-        <v>557.0</v>
+        <v>560.0</v>
       </c>
       <c r="G36" t="n">
         <v>5.0</v>
@@ -3479,7 +3479,7 @@
         <v>775</v>
       </c>
       <c r="F42" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G42" t="n">
         <v>15.0</v>
@@ -3661,7 +3661,7 @@
         <v>775</v>
       </c>
       <c r="F49" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -3791,7 +3791,7 @@
         <v>775</v>
       </c>
       <c r="F54" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="G54" t="n">
         <v>52.0</v>
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>216.0</v>
+        <v>218.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4259,7 +4259,7 @@
         <v>775</v>
       </c>
       <c r="F72" t="n">
-        <v>146.0</v>
+        <v>148.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4311,7 +4311,7 @@
         <v>775</v>
       </c>
       <c r="F74" t="n">
-        <v>167.0</v>
+        <v>169.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -4363,7 +4363,7 @@
         <v>776</v>
       </c>
       <c r="F76" t="n">
-        <v>359.0</v>
+        <v>360.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>463.0</v>
+        <v>466.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4987,7 +4987,7 @@
         <v>776</v>
       </c>
       <c r="F100" t="n">
-        <v>456.0</v>
+        <v>458.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>543.0</v>
+        <v>547.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -5507,7 +5507,7 @@
         <v>775</v>
       </c>
       <c r="F120" t="n">
-        <v>412.0</v>
+        <v>415.0</v>
       </c>
       <c r="G120" t="n">
         <v>11.0</v>
@@ -5559,7 +5559,7 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>478.0</v>
+        <v>481.0</v>
       </c>
       <c r="G122" t="n">
         <v>12.0</v>
@@ -5747,7 +5747,7 @@
         <v>0.0</v>
       </c>
       <c r="H129" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="130">
@@ -6027,7 +6027,7 @@
         <v>775</v>
       </c>
       <c r="F140" t="n">
-        <v>691.0</v>
+        <v>695.0</v>
       </c>
       <c r="G140" t="n">
         <v>2.0</v>
@@ -6365,7 +6365,7 @@
         <v>776</v>
       </c>
       <c r="F153" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
       <c r="G153" t="n">
         <v>0.0</v>
@@ -6443,7 +6443,7 @@
         <v>776</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" t="n">
         <v>0.0</v>
@@ -6625,7 +6625,7 @@
         <v>775</v>
       </c>
       <c r="F163" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G163" t="n">
         <v>23.0</v>
@@ -6781,7 +6781,7 @@
         <v>776</v>
       </c>
       <c r="F169" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G169" t="n">
         <v>1.0</v>
@@ -6807,7 +6807,7 @@
         <v>775</v>
       </c>
       <c r="F170" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G170" t="n">
         <v>8.0</v>
@@ -6833,7 +6833,7 @@
         <v>775</v>
       </c>
       <c r="F171" t="n">
-        <v>335.0</v>
+        <v>337.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -7015,7 +7015,7 @@
         <v>775</v>
       </c>
       <c r="F178" t="n">
-        <v>284.0</v>
+        <v>285.0</v>
       </c>
       <c r="G178" t="n">
         <v>4.0</v>
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>546.0</v>
+        <v>548.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1030.0</v>
+        <v>1031.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -7847,7 +7847,7 @@
         <v>776</v>
       </c>
       <c r="F210" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G210" t="n">
         <v>0.0</v>
@@ -7925,7 +7925,7 @@
         <v>775</v>
       </c>
       <c r="F213" t="n">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
       <c r="G213" t="n">
         <v>2.0</v>
@@ -8523,7 +8523,7 @@
         <v>776</v>
       </c>
       <c r="F236" t="n">
-        <v>112.0</v>
+        <v>114.0</v>
       </c>
       <c r="G236" t="n">
         <v>0.0</v>
@@ -8731,7 +8731,7 @@
         <v>775</v>
       </c>
       <c r="F244" t="n">
-        <v>234.0</v>
+        <v>235.0</v>
       </c>
       <c r="G244" t="n">
         <v>10.0</v>
@@ -8991,7 +8991,7 @@
         <v>775</v>
       </c>
       <c r="F254" t="n">
-        <v>80.0</v>
+        <v>84.0</v>
       </c>
       <c r="G254" t="n">
         <v>30.0</v>
@@ -9329,7 +9329,7 @@
         <v>775</v>
       </c>
       <c r="F267" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="G267" t="n">
         <v>0.0</v>
@@ -9355,7 +9355,7 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="G268" t="n">
         <v>7.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>56.0</v>
+        <v>63.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -10291,7 +10291,7 @@
         <v>775</v>
       </c>
       <c r="F304" t="n">
-        <v>411.0</v>
+        <v>413.0</v>
       </c>
       <c r="G304" t="n">
         <v>0.0</v>
@@ -10577,7 +10577,7 @@
         <v>775</v>
       </c>
       <c r="F315" t="n">
-        <v>539.0</v>
+        <v>544.0</v>
       </c>
       <c r="G315" t="n">
         <v>0.0</v>
@@ -10811,7 +10811,7 @@
         <v>776</v>
       </c>
       <c r="F324" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         <v>775</v>
       </c>
       <c r="F340" t="n">
-        <v>428.0</v>
+        <v>431.0</v>
       </c>
       <c r="G340" t="n">
         <v>1.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>550.0</v>
+        <v>551.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -11883,7 +11883,7 @@
         <v>10.0</v>
       </c>
       <c r="H365" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="366">
@@ -11903,7 +11903,7 @@
         <v>776</v>
       </c>
       <c r="F366" t="n">
-        <v>106.0</v>
+        <v>108.0</v>
       </c>
       <c r="G366" t="n">
         <v>0.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12137,7 +12137,7 @@
         <v>776</v>
       </c>
       <c r="F375" t="n">
-        <v>186.0</v>
+        <v>188.0</v>
       </c>
       <c r="G375" t="n">
         <v>0.0</v>
@@ -12553,7 +12553,7 @@
         <v>775</v>
       </c>
       <c r="F391" t="n">
-        <v>266.0</v>
+        <v>267.0</v>
       </c>
       <c r="G391" t="n">
         <v>1.0</v>
@@ -13255,7 +13255,7 @@
         <v>775</v>
       </c>
       <c r="F418" t="n">
-        <v>186.0</v>
+        <v>188.0</v>
       </c>
       <c r="G418" t="n">
         <v>1.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>612.0</v>
+        <v>613.0</v>
       </c>
       <c r="G446" t="n">
         <v>0.0</v>
@@ -14997,13 +14997,13 @@
         <v>775</v>
       </c>
       <c r="F485" t="n">
-        <v>254.0</v>
+        <v>257.0</v>
       </c>
       <c r="G485" t="n">
         <v>8.0</v>
       </c>
       <c r="H485" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="486">
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>657.0</v>
+        <v>661.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15569,7 +15569,7 @@
         <v>776</v>
       </c>
       <c r="F507" t="n">
-        <v>21.0</v>
+        <v>25.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -15647,7 +15647,7 @@
         <v>776</v>
       </c>
       <c r="F510" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G510" t="n">
         <v>0.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2466.0</v>
+        <v>2489.0</v>
       </c>
       <c r="G518" t="n">
         <v>307.0</v>
@@ -17103,7 +17103,7 @@
         <v>775</v>
       </c>
       <c r="F566" t="n">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G566" t="n">
         <v>0.0</v>
@@ -18195,7 +18195,7 @@
         <v>776</v>
       </c>
       <c r="F608" t="n">
-        <v>411.0</v>
+        <v>416.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18793,7 +18793,7 @@
         <v>775</v>
       </c>
       <c r="F631" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -19443,7 +19443,7 @@
         <v>776</v>
       </c>
       <c r="F656" t="n">
-        <v>143.0</v>
+        <v>145.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19807,7 +19807,7 @@
         <v>775</v>
       </c>
       <c r="F670" t="n">
-        <v>128.0</v>
+        <v>132.0</v>
       </c>
       <c r="G670" t="n">
         <v>0.0</v>
@@ -19885,7 +19885,7 @@
         <v>775</v>
       </c>
       <c r="F673" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19911,7 +19911,7 @@
         <v>775</v>
       </c>
       <c r="F674" t="n">
-        <v>73.0</v>
+        <v>75.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -20041,7 +20041,7 @@
         <v>776</v>
       </c>
       <c r="F679" t="n">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="G679" t="n">
         <v>0.0</v>
@@ -20067,7 +20067,7 @@
         <v>776</v>
       </c>
       <c r="F680" t="n">
-        <v>114.0</v>
+        <v>118.0</v>
       </c>
       <c r="G680" t="n">
         <v>0.0</v>
@@ -20119,7 +20119,7 @@
         <v>776</v>
       </c>
       <c r="F682" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20171,7 +20171,7 @@
         <v>776</v>
       </c>
       <c r="F684" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -20301,7 +20301,7 @@
         <v>776</v>
       </c>
       <c r="F689" t="n">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="G689" t="n">
         <v>0.0</v>
@@ -20327,7 +20327,7 @@
         <v>775</v>
       </c>
       <c r="F690" t="n">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
       <c r="G690" t="n">
         <v>0.0</v>
@@ -20379,7 +20379,7 @@
         <v>776</v>
       </c>
       <c r="F692" t="n">
-        <v>149.0</v>
+        <v>153.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>182.0</v>
+        <v>184.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20535,7 +20535,7 @@
         <v>776</v>
       </c>
       <c r="F698" t="n">
-        <v>163.0</v>
+        <v>167.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20665,7 +20665,7 @@
         <v>775</v>
       </c>
       <c r="F703" t="n">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="G703" t="n">
         <v>0.0</v>
@@ -20691,7 +20691,7 @@
         <v>775</v>
       </c>
       <c r="F704" t="n">
-        <v>74.0</v>
+        <v>78.0</v>
       </c>
       <c r="G704" t="n">
         <v>0.0</v>
@@ -20717,7 +20717,7 @@
         <v>775</v>
       </c>
       <c r="F705" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G705" t="n">
         <v>0.0</v>
@@ -20769,7 +20769,7 @@
         <v>775</v>
       </c>
       <c r="F707" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -21003,7 +21003,7 @@
         <v>775</v>
       </c>
       <c r="F716" t="n">
-        <v>115.0</v>
+        <v>117.0</v>
       </c>
       <c r="G716" t="n">
         <v>0.0</v>
@@ -21081,7 +21081,7 @@
         <v>776</v>
       </c>
       <c r="F719" t="n">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
@@ -21107,7 +21107,7 @@
         <v>777</v>
       </c>
       <c r="F720" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G720" t="n">
         <v>0.0</v>
@@ -21185,7 +21185,7 @@
         <v>776</v>
       </c>
       <c r="F723" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G723" t="n">
         <v>0.0</v>
@@ -21601,13 +21601,13 @@
         <v>778</v>
       </c>
       <c r="F739" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G739" t="n">
         <v>0.0</v>
       </c>
       <c r="H739" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="740">
@@ -21627,13 +21627,13 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>235.0</v>
+        <v>240.0</v>
       </c>
       <c r="G740" t="n">
         <v>8.0</v>
       </c>
       <c r="H740" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="741">
@@ -21835,7 +21835,7 @@
         <v>775</v>
       </c>
       <c r="F748" t="n">
-        <v>335.0</v>
+        <v>337.0</v>
       </c>
       <c r="G748" t="n">
         <v>0.0</v>
@@ -21913,7 +21913,7 @@
         <v>776</v>
       </c>
       <c r="F751" t="n">
-        <v>171.0</v>
+        <v>173.0</v>
       </c>
       <c r="G751" t="n">
         <v>0.0</v>
@@ -22069,7 +22069,7 @@
         <v>777</v>
       </c>
       <c r="F757" t="n">
-        <v>81.0</v>
+        <v>84.0</v>
       </c>
       <c r="G757" t="n">
         <v>11.0</v>
@@ -22121,7 +22121,7 @@
         <v>776</v>
       </c>
       <c r="F759" t="n">
-        <v>430.0</v>
+        <v>432.0</v>
       </c>
       <c r="G759" t="n">
         <v>0.0</v>
@@ -22407,13 +22407,13 @@
         <v>778</v>
       </c>
       <c r="F770" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G770" t="n">
         <v>0.0</v>
       </c>
       <c r="H770" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="771">
@@ -22667,13 +22667,13 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>521.0</v>
+        <v>522.0</v>
       </c>
       <c r="G780" t="n">
         <v>3.0</v>
       </c>
       <c r="H780" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="781">
@@ -22719,13 +22719,13 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>521.0</v>
+        <v>522.0</v>
       </c>
       <c r="G782" t="n">
         <v>3.0</v>
       </c>
       <c r="H782" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3531,7 +3531,7 @@
         <v>775</v>
       </c>
       <c r="F44" t="n">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="G44" t="n">
         <v>21.0</v>
@@ -3635,7 +3635,7 @@
         <v>775</v>
       </c>
       <c r="F48" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G48" t="n">
         <v>2.0</v>
@@ -4051,7 +4051,7 @@
         <v>775</v>
       </c>
       <c r="F64" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -4285,7 +4285,7 @@
         <v>775</v>
       </c>
       <c r="F73" t="n">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -4337,7 +4337,7 @@
         <v>776</v>
       </c>
       <c r="F75" t="n">
-        <v>375.0</v>
+        <v>377.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>466.0</v>
+        <v>468.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4701,7 +4701,7 @@
         <v>775</v>
       </c>
       <c r="F89" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G89" t="n">
         <v>16.0</v>
@@ -4805,7 +4805,7 @@
         <v>775</v>
       </c>
       <c r="F93" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G93" t="n">
         <v>17.0</v>
@@ -5663,7 +5663,7 @@
         <v>775</v>
       </c>
       <c r="F126" t="n">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="G126" t="n">
         <v>0.0</v>
@@ -5975,7 +5975,7 @@
         <v>775</v>
       </c>
       <c r="F138" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="G138" t="n">
         <v>25.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7119,7 +7119,7 @@
         <v>776</v>
       </c>
       <c r="F182" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G182" t="n">
         <v>0.0</v>
@@ -7301,7 +7301,7 @@
         <v>776</v>
       </c>
       <c r="F189" t="n">
-        <v>708.0</v>
+        <v>711.0</v>
       </c>
       <c r="G189" t="n">
         <v>1.0</v>
@@ -8315,7 +8315,7 @@
         <v>775</v>
       </c>
       <c r="F228" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G228" t="n">
         <v>0.0</v>
@@ -8994,7 +8994,7 @@
         <v>84.0</v>
       </c>
       <c r="G254" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="H254" t="n">
         <v>1.0</v>
@@ -9875,7 +9875,7 @@
         <v>775</v>
       </c>
       <c r="F288" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G288" t="n">
         <v>0.0</v>
@@ -10005,7 +10005,7 @@
         <v>775</v>
       </c>
       <c r="F293" t="n">
-        <v>297.0</v>
+        <v>299.0</v>
       </c>
       <c r="G293" t="n">
         <v>13.0</v>
@@ -10473,7 +10473,7 @@
         <v>775</v>
       </c>
       <c r="F311" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G311" t="n">
         <v>7.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -11305,13 +11305,13 @@
         <v>775</v>
       </c>
       <c r="F343" t="n">
-        <v>231.0</v>
+        <v>233.0</v>
       </c>
       <c r="G343" t="n">
         <v>23.0</v>
       </c>
       <c r="H343" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="344">
@@ -12475,7 +12475,7 @@
         <v>776</v>
       </c>
       <c r="F388" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
@@ -14321,7 +14321,7 @@
         <v>776</v>
       </c>
       <c r="F459" t="n">
-        <v>382.0</v>
+        <v>383.0</v>
       </c>
       <c r="G459" t="n">
         <v>0.0</v>
@@ -14581,13 +14581,13 @@
         <v>775</v>
       </c>
       <c r="F469" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
       <c r="G469" t="n">
         <v>0.0</v>
       </c>
       <c r="H469" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="470">
@@ -15751,7 +15751,7 @@
         <v>775</v>
       </c>
       <c r="F514" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G514" t="n">
         <v>1.0</v>
@@ -16453,13 +16453,13 @@
         <v>775</v>
       </c>
       <c r="F541" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G541" t="n">
         <v>13.0</v>
       </c>
       <c r="H541" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="542">
@@ -16531,7 +16531,7 @@
         <v>776</v>
       </c>
       <c r="F544" t="n">
-        <v>326.0</v>
+        <v>327.0</v>
       </c>
       <c r="G544" t="n">
         <v>1.0</v>
@@ -16609,7 +16609,7 @@
         <v>776</v>
       </c>
       <c r="F547" t="n">
-        <v>282.0</v>
+        <v>285.0</v>
       </c>
       <c r="G547" t="n">
         <v>1.0</v>
@@ -16947,7 +16947,7 @@
         <v>775</v>
       </c>
       <c r="F560" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G560" t="n">
         <v>0.0</v>
@@ -17519,7 +17519,7 @@
         <v>776</v>
       </c>
       <c r="F582" t="n">
-        <v>301.0</v>
+        <v>303.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -18013,7 +18013,7 @@
         <v>775</v>
       </c>
       <c r="F601" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="G601" t="n">
         <v>0.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>451.0</v>
+        <v>452.0</v>
       </c>
       <c r="G693" t="n">
         <v>1.0</v>
@@ -21627,13 +21627,13 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>240.0</v>
+        <v>242.0</v>
       </c>
       <c r="G740" t="n">
         <v>8.0</v>
       </c>
       <c r="H740" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="741">
@@ -22407,7 +22407,7 @@
         <v>778</v>
       </c>
       <c r="F770" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G770" t="n">
         <v>0.0</v>
@@ -22667,13 +22667,13 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>522.0</v>
+        <v>523.0</v>
       </c>
       <c r="G780" t="n">
         <v>3.0</v>
       </c>
       <c r="H780" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="781">
@@ -22719,13 +22719,13 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>522.0</v>
+        <v>523.0</v>
       </c>
       <c r="G782" t="n">
         <v>3.0</v>
       </c>
       <c r="H782" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2855,7 +2855,7 @@
         <v>775</v>
       </c>
       <c r="F18" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -2933,7 +2933,7 @@
         <v>775</v>
       </c>
       <c r="F21" t="n">
-        <v>86.0</v>
+        <v>95.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3895,7 +3895,7 @@
         <v>775</v>
       </c>
       <c r="F58" t="n">
-        <v>268.0</v>
+        <v>273.0</v>
       </c>
       <c r="G58" t="n">
         <v>8.0</v>
@@ -3973,7 +3973,7 @@
         <v>775</v>
       </c>
       <c r="F61" t="n">
-        <v>110.0</v>
+        <v>115.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -4389,7 +4389,7 @@
         <v>775</v>
       </c>
       <c r="F77" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>468.0</v>
+        <v>469.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4727,7 +4727,7 @@
         <v>775</v>
       </c>
       <c r="F90" t="n">
-        <v>57.0</v>
+        <v>62.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -4753,7 +4753,7 @@
         <v>775</v>
       </c>
       <c r="F91" t="n">
-        <v>480.0</v>
+        <v>481.0</v>
       </c>
       <c r="G91" t="n">
         <v>1.0</v>
@@ -5143,7 +5143,7 @@
         <v>775</v>
       </c>
       <c r="F106" t="n">
-        <v>102.0</v>
+        <v>105.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -5273,7 +5273,7 @@
         <v>777</v>
       </c>
       <c r="F111" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
@@ -5403,7 +5403,7 @@
         <v>775</v>
       </c>
       <c r="F116" t="n">
-        <v>192.0</v>
+        <v>193.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -5507,7 +5507,7 @@
         <v>775</v>
       </c>
       <c r="F120" t="n">
-        <v>415.0</v>
+        <v>417.0</v>
       </c>
       <c r="G120" t="n">
         <v>11.0</v>
@@ -5611,7 +5611,7 @@
         <v>775</v>
       </c>
       <c r="F124" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="G124" t="n">
         <v>0.0</v>
@@ -6079,7 +6079,7 @@
         <v>775</v>
       </c>
       <c r="F142" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -6261,7 +6261,7 @@
         <v>775</v>
       </c>
       <c r="F149" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
       <c r="G149" t="n">
         <v>0.0</v>
@@ -7197,7 +7197,7 @@
         <v>775</v>
       </c>
       <c r="F185" t="n">
-        <v>154.0</v>
+        <v>159.0</v>
       </c>
       <c r="G185" t="n">
         <v>0.0</v>
@@ -7275,7 +7275,7 @@
         <v>776</v>
       </c>
       <c r="F188" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G188" t="n">
         <v>0.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>30.0</v>
+        <v>36.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1031.0</v>
+        <v>1032.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -8055,7 +8055,7 @@
         <v>775</v>
       </c>
       <c r="F218" t="n">
-        <v>205.0</v>
+        <v>206.0</v>
       </c>
       <c r="G218" t="n">
         <v>0.0</v>
@@ -8263,7 +8263,7 @@
         <v>776</v>
       </c>
       <c r="F226" t="n">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -8341,7 +8341,7 @@
         <v>775</v>
       </c>
       <c r="F229" t="n">
-        <v>282.0</v>
+        <v>283.0</v>
       </c>
       <c r="G229" t="n">
         <v>20.0</v>
@@ -8471,7 +8471,7 @@
         <v>775</v>
       </c>
       <c r="F234" t="n">
-        <v>386.0</v>
+        <v>388.0</v>
       </c>
       <c r="G234" t="n">
         <v>0.0</v>
@@ -8887,7 +8887,7 @@
         <v>775</v>
       </c>
       <c r="F250" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="G250" t="n">
         <v>2.0</v>
@@ -8913,7 +8913,7 @@
         <v>775</v>
       </c>
       <c r="F251" t="n">
-        <v>149.0</v>
+        <v>155.0</v>
       </c>
       <c r="G251" t="n">
         <v>16.0</v>
@@ -9095,7 +9095,7 @@
         <v>775</v>
       </c>
       <c r="F258" t="n">
-        <v>954.0</v>
+        <v>955.0</v>
       </c>
       <c r="G258" t="n">
         <v>23.0</v>
@@ -9199,7 +9199,7 @@
         <v>775</v>
       </c>
       <c r="F262" t="n">
-        <v>34.0</v>
+        <v>39.0</v>
       </c>
       <c r="G262" t="n">
         <v>14.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>248.0</v>
+        <v>251.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -9407,7 +9407,7 @@
         <v>775</v>
       </c>
       <c r="F270" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G270" t="n">
         <v>37.0</v>
@@ -9615,7 +9615,7 @@
         <v>775</v>
       </c>
       <c r="F278" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G278" t="n">
         <v>7.0</v>
@@ -9693,7 +9693,7 @@
         <v>775</v>
       </c>
       <c r="F281" t="n">
-        <v>516.0</v>
+        <v>519.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -9849,7 +9849,7 @@
         <v>775</v>
       </c>
       <c r="F287" t="n">
-        <v>234.0</v>
+        <v>235.0</v>
       </c>
       <c r="G287" t="n">
         <v>8.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -10008,7 +10008,7 @@
         <v>299.0</v>
       </c>
       <c r="G293" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="H293" t="n">
         <v>2.0</v>
@@ -10031,7 +10031,7 @@
         <v>775</v>
       </c>
       <c r="F294" t="n">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="G294" t="n">
         <v>11.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1057.0</v>
+        <v>1058.0</v>
       </c>
       <c r="G310" t="n">
         <v>20.0</v>
@@ -10603,7 +10603,7 @@
         <v>775</v>
       </c>
       <c r="F316" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G316" t="n">
         <v>6.0</v>
@@ -10889,7 +10889,7 @@
         <v>775</v>
       </c>
       <c r="F327" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G327" t="n">
         <v>1.0</v>
@@ -11019,7 +11019,7 @@
         <v>775</v>
       </c>
       <c r="F332" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G332" t="n">
         <v>1.0</v>
@@ -11461,7 +11461,7 @@
         <v>775</v>
       </c>
       <c r="F349" t="n">
-        <v>123.0</v>
+        <v>126.0</v>
       </c>
       <c r="G349" t="n">
         <v>3.0</v>
@@ -11695,7 +11695,7 @@
         <v>775</v>
       </c>
       <c r="F358" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G358" t="n">
         <v>0.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>165.0</v>
+        <v>168.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>551.0</v>
+        <v>552.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>143.0</v>
+        <v>145.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12189,7 +12189,7 @@
         <v>775</v>
       </c>
       <c r="F377" t="n">
-        <v>133.0</v>
+        <v>135.0</v>
       </c>
       <c r="G377" t="n">
         <v>7.0</v>
@@ -12631,7 +12631,7 @@
         <v>776</v>
       </c>
       <c r="F394" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G394" t="n">
         <v>0.0</v>
@@ -12839,7 +12839,7 @@
         <v>775</v>
       </c>
       <c r="F402" t="n">
-        <v>159.0</v>
+        <v>168.0</v>
       </c>
       <c r="G402" t="n">
         <v>1.0</v>
@@ -12917,7 +12917,7 @@
         <v>777</v>
       </c>
       <c r="F405" t="n">
-        <v>460.0</v>
+        <v>478.0</v>
       </c>
       <c r="G405" t="n">
         <v>0.0</v>
@@ -13411,7 +13411,7 @@
         <v>777</v>
       </c>
       <c r="F424" t="n">
-        <v>273.0</v>
+        <v>278.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
@@ -13593,7 +13593,7 @@
         <v>776</v>
       </c>
       <c r="F431" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G431" t="n">
         <v>0.0</v>
@@ -14009,7 +14009,7 @@
         <v>775</v>
       </c>
       <c r="F447" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
       <c r="G447" t="n">
         <v>1.0</v>
@@ -14347,7 +14347,7 @@
         <v>775</v>
       </c>
       <c r="F460" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G460" t="n">
         <v>22.0</v>
@@ -15153,7 +15153,7 @@
         <v>775</v>
       </c>
       <c r="F491" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G491" t="n">
         <v>18.0</v>
@@ -15699,7 +15699,7 @@
         <v>775</v>
       </c>
       <c r="F512" t="n">
-        <v>96.0</v>
+        <v>98.0</v>
       </c>
       <c r="G512" t="n">
         <v>2.0</v>
@@ -15829,7 +15829,7 @@
         <v>777</v>
       </c>
       <c r="F517" t="n">
-        <v>336.0</v>
+        <v>339.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2489.0</v>
+        <v>2495.0</v>
       </c>
       <c r="G518" t="n">
         <v>307.0</v>
@@ -16115,7 +16115,7 @@
         <v>775</v>
       </c>
       <c r="F528" t="n">
-        <v>66.0</v>
+        <v>72.0</v>
       </c>
       <c r="G528" t="n">
         <v>0.0</v>
@@ -16479,7 +16479,7 @@
         <v>775</v>
       </c>
       <c r="F542" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G542" t="n">
         <v>11.0</v>
@@ -16869,7 +16869,7 @@
         <v>775</v>
       </c>
       <c r="F557" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G557" t="n">
         <v>0.0</v>
@@ -17077,7 +17077,7 @@
         <v>775</v>
       </c>
       <c r="F565" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
@@ -17311,7 +17311,7 @@
         <v>775</v>
       </c>
       <c r="F574" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
       <c r="G574" t="n">
         <v>0.0</v>
@@ -17389,7 +17389,7 @@
         <v>775</v>
       </c>
       <c r="F577" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G577" t="n">
         <v>10.0</v>
@@ -17805,7 +17805,7 @@
         <v>775</v>
       </c>
       <c r="F593" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G593" t="n">
         <v>0.0</v>
@@ -18013,7 +18013,7 @@
         <v>775</v>
       </c>
       <c r="F601" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="G601" t="n">
         <v>0.0</v>
@@ -18403,7 +18403,7 @@
         <v>776</v>
       </c>
       <c r="F616" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
@@ -18897,7 +18897,7 @@
         <v>775</v>
       </c>
       <c r="F635" t="n">
-        <v>247.0</v>
+        <v>249.0</v>
       </c>
       <c r="G635" t="n">
         <v>0.0</v>
@@ -19183,7 +19183,7 @@
         <v>775</v>
       </c>
       <c r="F646" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -19495,7 +19495,7 @@
         <v>775</v>
       </c>
       <c r="F658" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G658" t="n">
         <v>44.0</v>
@@ -19625,7 +19625,7 @@
         <v>775</v>
       </c>
       <c r="F663" t="n">
-        <v>55.0</v>
+        <v>57.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>214.0</v>
+        <v>217.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20252,7 +20252,7 @@
         <v>4.0</v>
       </c>
       <c r="G687" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H687" t="n">
         <v>0.0</v>
@@ -20353,7 +20353,7 @@
         <v>776</v>
       </c>
       <c r="F691" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="G691" t="n">
         <v>0.0</v>
@@ -20483,7 +20483,7 @@
         <v>776</v>
       </c>
       <c r="F696" t="n">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="G696" t="n">
         <v>0.0</v>
@@ -20587,10 +20587,10 @@
         <v>777</v>
       </c>
       <c r="F700" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="G700" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H700" t="n">
         <v>0.0</v>
@@ -20613,7 +20613,7 @@
         <v>776</v>
       </c>
       <c r="F701" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G701" t="n">
         <v>0.0</v>
@@ -20873,7 +20873,7 @@
         <v>776</v>
       </c>
       <c r="F711" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G711" t="n">
         <v>0.0</v>
@@ -21032,7 +21032,7 @@
         <v>193.0</v>
       </c>
       <c r="G717" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="H717" t="n">
         <v>1.0</v>
@@ -21627,7 +21627,7 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="G740" t="n">
         <v>8.0</v>
@@ -21653,7 +21653,7 @@
         <v>778</v>
       </c>
       <c r="F741" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -21991,7 +21991,7 @@
         <v>775</v>
       </c>
       <c r="F754" t="n">
-        <v>415.0</v>
+        <v>416.0</v>
       </c>
       <c r="G754" t="n">
         <v>0.0</v>
@@ -22277,7 +22277,7 @@
         <v>776</v>
       </c>
       <c r="F765" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G765" t="n">
         <v>0.0</v>
@@ -22407,7 +22407,7 @@
         <v>778</v>
       </c>
       <c r="F770" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G770" t="n">
         <v>0.0</v>
@@ -22459,7 +22459,7 @@
         <v>778</v>
       </c>
       <c r="F772" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G772" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>523.0</v>
+        <v>524.0</v>
       </c>
       <c r="G780" t="n">
         <v>3.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>523.0</v>
+        <v>524.0</v>
       </c>
       <c r="G782" t="n">
         <v>3.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>647.0</v>
+        <v>648.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2595,7 +2595,7 @@
         <v>775</v>
       </c>
       <c r="F8" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -2803,7 +2803,7 @@
         <v>775</v>
       </c>
       <c r="F16" t="n">
-        <v>426.0</v>
+        <v>427.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -2959,7 +2959,7 @@
         <v>776</v>
       </c>
       <c r="F22" t="n">
-        <v>403.0</v>
+        <v>409.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3453,7 +3453,7 @@
         <v>775</v>
       </c>
       <c r="F41" t="n">
-        <v>349.0</v>
+        <v>350.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -4051,7 +4051,7 @@
         <v>775</v>
       </c>
       <c r="F64" t="n">
-        <v>215.0</v>
+        <v>219.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4207,7 +4207,7 @@
         <v>775</v>
       </c>
       <c r="F70" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G70" t="n">
         <v>27.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>469.0</v>
+        <v>471.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4623,7 +4623,7 @@
         <v>775</v>
       </c>
       <c r="F86" t="n">
-        <v>61.0</v>
+        <v>64.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -4987,7 +4987,7 @@
         <v>776</v>
       </c>
       <c r="F100" t="n">
-        <v>458.0</v>
+        <v>460.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>547.0</v>
+        <v>551.0</v>
       </c>
       <c r="G104" t="n">
         <v>3.0</v>
@@ -5559,7 +5559,7 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>481.0</v>
+        <v>482.0</v>
       </c>
       <c r="G122" t="n">
         <v>12.0</v>
@@ -5637,7 +5637,7 @@
         <v>775</v>
       </c>
       <c r="F125" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G125" t="n">
         <v>11.0</v>
@@ -6105,7 +6105,7 @@
         <v>775</v>
       </c>
       <c r="F143" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="G143" t="n">
         <v>22.0</v>
@@ -6911,7 +6911,7 @@
         <v>775</v>
       </c>
       <c r="F174" t="n">
-        <v>102.0</v>
+        <v>104.0</v>
       </c>
       <c r="G174" t="n">
         <v>4.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1032.0</v>
+        <v>1033.0</v>
       </c>
       <c r="G203" t="n">
         <v>0.0</v>
@@ -7899,7 +7899,7 @@
         <v>775</v>
       </c>
       <c r="F212" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G212" t="n">
         <v>10.0</v>
@@ -10005,7 +10005,7 @@
         <v>775</v>
       </c>
       <c r="F293" t="n">
-        <v>299.0</v>
+        <v>302.0</v>
       </c>
       <c r="G293" t="n">
         <v>14.0</v>
@@ -10135,7 +10135,7 @@
         <v>775</v>
       </c>
       <c r="F298" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="G298" t="n">
         <v>3.0</v>
@@ -10291,7 +10291,7 @@
         <v>775</v>
       </c>
       <c r="F304" t="n">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
       <c r="G304" t="n">
         <v>0.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -10889,7 +10889,7 @@
         <v>775</v>
       </c>
       <c r="F327" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G327" t="n">
         <v>1.0</v>
@@ -10941,7 +10941,7 @@
         <v>775</v>
       </c>
       <c r="F329" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G329" t="n">
         <v>25.0</v>
@@ -11643,7 +11643,7 @@
         <v>775</v>
       </c>
       <c r="F356" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G356" t="n">
         <v>19.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>168.0</v>
+        <v>170.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -12553,7 +12553,7 @@
         <v>775</v>
       </c>
       <c r="F391" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="G391" t="n">
         <v>1.0</v>
@@ -12735,7 +12735,7 @@
         <v>776</v>
       </c>
       <c r="F398" t="n">
-        <v>64.0</v>
+        <v>69.0</v>
       </c>
       <c r="G398" t="n">
         <v>0.0</v>
@@ -12787,7 +12787,7 @@
         <v>775</v>
       </c>
       <c r="F400" t="n">
-        <v>202.0</v>
+        <v>204.0</v>
       </c>
       <c r="G400" t="n">
         <v>2.0</v>
@@ -12865,7 +12865,7 @@
         <v>775</v>
       </c>
       <c r="F403" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
       <c r="G403" t="n">
         <v>3.0</v>
@@ -13151,7 +13151,7 @@
         <v>775</v>
       </c>
       <c r="F414" t="n">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="G414" t="n">
         <v>28.0</v>
@@ -13177,7 +13177,7 @@
         <v>775</v>
       </c>
       <c r="F415" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G415" t="n">
         <v>0.0</v>
@@ -13255,7 +13255,7 @@
         <v>775</v>
       </c>
       <c r="F418" t="n">
-        <v>188.0</v>
+        <v>190.0</v>
       </c>
       <c r="G418" t="n">
         <v>1.0</v>
@@ -13359,7 +13359,7 @@
         <v>776</v>
       </c>
       <c r="F422" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G422" t="n">
         <v>0.0</v>
@@ -14061,7 +14061,7 @@
         <v>776</v>
       </c>
       <c r="F449" t="n">
-        <v>123.0</v>
+        <v>125.0</v>
       </c>
       <c r="G449" t="n">
         <v>0.0</v>
@@ -14243,7 +14243,7 @@
         <v>775</v>
       </c>
       <c r="F456" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G456" t="n">
         <v>0.0</v>
@@ -14295,7 +14295,7 @@
         <v>775</v>
       </c>
       <c r="F458" t="n">
-        <v>196.0</v>
+        <v>200.0</v>
       </c>
       <c r="G458" t="n">
         <v>2.0</v>
@@ -14919,7 +14919,7 @@
         <v>776</v>
       </c>
       <c r="F482" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
       <c r="G482" t="n">
         <v>0.0</v>
@@ -14945,7 +14945,7 @@
         <v>775</v>
       </c>
       <c r="F483" t="n">
-        <v>534.0</v>
+        <v>535.0</v>
       </c>
       <c r="G483" t="n">
         <v>5.0</v>
@@ -15283,7 +15283,7 @@
         <v>776</v>
       </c>
       <c r="F496" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>661.0</v>
+        <v>665.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2495.0</v>
+        <v>2502.0</v>
       </c>
       <c r="G518" t="n">
         <v>307.0</v>
@@ -16037,7 +16037,7 @@
         <v>775</v>
       </c>
       <c r="F525" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G525" t="n">
         <v>0.0</v>
@@ -16323,7 +16323,7 @@
         <v>775</v>
       </c>
       <c r="F536" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G536" t="n">
         <v>5.0</v>
@@ -16349,7 +16349,7 @@
         <v>776</v>
       </c>
       <c r="F537" t="n">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="G537" t="n">
         <v>0.0</v>
@@ -16401,7 +16401,7 @@
         <v>776</v>
       </c>
       <c r="F539" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -16635,7 +16635,7 @@
         <v>775</v>
       </c>
       <c r="F548" t="n">
-        <v>81.0</v>
+        <v>86.0</v>
       </c>
       <c r="G548" t="n">
         <v>0.0</v>
@@ -16791,7 +16791,7 @@
         <v>776</v>
       </c>
       <c r="F554" t="n">
-        <v>169.0</v>
+        <v>175.0</v>
       </c>
       <c r="G554" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         <v>775</v>
       </c>
       <c r="F599" t="n">
-        <v>283.0</v>
+        <v>288.0</v>
       </c>
       <c r="G599" t="n">
         <v>0.0</v>
@@ -18143,7 +18143,7 @@
         <v>775</v>
       </c>
       <c r="F606" t="n">
-        <v>255.0</v>
+        <v>257.0</v>
       </c>
       <c r="G606" t="n">
         <v>3.0</v>
@@ -18195,7 +18195,7 @@
         <v>776</v>
       </c>
       <c r="F608" t="n">
-        <v>416.0</v>
+        <v>419.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18221,7 +18221,7 @@
         <v>776</v>
       </c>
       <c r="F609" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G609" t="n">
         <v>0.0</v>
@@ -18429,7 +18429,7 @@
         <v>775</v>
       </c>
       <c r="F617" t="n">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G617" t="n">
         <v>2.0</v>
@@ -18897,7 +18897,7 @@
         <v>775</v>
       </c>
       <c r="F635" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G635" t="n">
         <v>0.0</v>
@@ -18923,7 +18923,7 @@
         <v>775</v>
       </c>
       <c r="F636" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G636" t="n">
         <v>0.0</v>
@@ -19443,7 +19443,7 @@
         <v>776</v>
       </c>
       <c r="F656" t="n">
-        <v>145.0</v>
+        <v>148.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19729,7 +19729,7 @@
         <v>775</v>
       </c>
       <c r="F667" t="n">
-        <v>58.0</v>
+        <v>64.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -19807,7 +19807,7 @@
         <v>775</v>
       </c>
       <c r="F670" t="n">
-        <v>132.0</v>
+        <v>135.0</v>
       </c>
       <c r="G670" t="n">
         <v>0.0</v>
@@ -19833,7 +19833,7 @@
         <v>776</v>
       </c>
       <c r="F671" t="n">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
       <c r="G671" t="n">
         <v>0.0</v>
@@ -19885,7 +19885,7 @@
         <v>775</v>
       </c>
       <c r="F673" t="n">
-        <v>148.0</v>
+        <v>153.0</v>
       </c>
       <c r="G673" t="n">
         <v>0.0</v>
@@ -19911,7 +19911,7 @@
         <v>775</v>
       </c>
       <c r="F674" t="n">
-        <v>75.0</v>
+        <v>78.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19937,7 +19937,7 @@
         <v>776</v>
       </c>
       <c r="F675" t="n">
-        <v>102.0</v>
+        <v>105.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19963,7 +19963,7 @@
         <v>776</v>
       </c>
       <c r="F676" t="n">
-        <v>123.0</v>
+        <v>128.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -20301,7 +20301,7 @@
         <v>776</v>
       </c>
       <c r="F689" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G689" t="n">
         <v>0.0</v>
@@ -20327,7 +20327,7 @@
         <v>775</v>
       </c>
       <c r="F690" t="n">
-        <v>72.0</v>
+        <v>75.0</v>
       </c>
       <c r="G690" t="n">
         <v>0.0</v>
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>184.0</v>
+        <v>186.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20743,7 +20743,7 @@
         <v>776</v>
       </c>
       <c r="F706" t="n">
-        <v>99.0</v>
+        <v>101.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20769,7 +20769,7 @@
         <v>775</v>
       </c>
       <c r="F707" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20795,7 +20795,7 @@
         <v>776</v>
       </c>
       <c r="F708" t="n">
-        <v>99.0</v>
+        <v>102.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>251.0</v>
+        <v>253.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -21003,7 +21003,7 @@
         <v>775</v>
       </c>
       <c r="F716" t="n">
-        <v>117.0</v>
+        <v>119.0</v>
       </c>
       <c r="G716" t="n">
         <v>0.0</v>
@@ -21029,7 +21029,7 @@
         <v>777</v>
       </c>
       <c r="F717" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="G717" t="n">
         <v>20.0</v>
@@ -21055,7 +21055,7 @@
         <v>777</v>
       </c>
       <c r="F718" t="n">
-        <v>51.0</v>
+        <v>55.0</v>
       </c>
       <c r="G718" t="n">
         <v>2.0</v>
@@ -21133,7 +21133,7 @@
         <v>776</v>
       </c>
       <c r="F721" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G721" t="n">
         <v>0.0</v>
@@ -21549,7 +21549,7 @@
         <v>776</v>
       </c>
       <c r="F737" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G737" t="n">
         <v>0.0</v>
@@ -21913,7 +21913,7 @@
         <v>776</v>
       </c>
       <c r="F751" t="n">
-        <v>173.0</v>
+        <v>175.0</v>
       </c>
       <c r="G751" t="n">
         <v>0.0</v>
@@ -22043,7 +22043,7 @@
         <v>775</v>
       </c>
       <c r="F756" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="G756" t="n">
         <v>0.0</v>
@@ -22069,7 +22069,7 @@
         <v>777</v>
       </c>
       <c r="F757" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G757" t="n">
         <v>11.0</v>
@@ -22121,7 +22121,7 @@
         <v>776</v>
       </c>
       <c r="F759" t="n">
-        <v>432.0</v>
+        <v>433.0</v>
       </c>
       <c r="G759" t="n">
         <v>0.0</v>
@@ -22147,7 +22147,7 @@
         <v>775</v>
       </c>
       <c r="F760" t="n">
-        <v>208.0</v>
+        <v>210.0</v>
       </c>
       <c r="G760" t="n">
         <v>0.0</v>
@@ -22199,7 +22199,7 @@
         <v>777</v>
       </c>
       <c r="F762" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G762" t="n">
         <v>0.0</v>
@@ -22511,7 +22511,7 @@
         <v>778</v>
       </c>
       <c r="F774" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G774" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2907,7 +2907,7 @@
         <v>775</v>
       </c>
       <c r="F20" t="n">
-        <v>163.0</v>
+        <v>168.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -2933,7 +2933,7 @@
         <v>775</v>
       </c>
       <c r="F21" t="n">
-        <v>95.0</v>
+        <v>99.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3479,7 +3479,7 @@
         <v>775</v>
       </c>
       <c r="F42" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G42" t="n">
         <v>15.0</v>
@@ -3765,7 +3765,7 @@
         <v>775</v>
       </c>
       <c r="F53" t="n">
-        <v>202.0</v>
+        <v>217.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>471.0</v>
+        <v>472.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -5143,7 +5143,7 @@
         <v>775</v>
       </c>
       <c r="F106" t="n">
-        <v>105.0</v>
+        <v>108.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -5403,7 +5403,7 @@
         <v>775</v>
       </c>
       <c r="F116" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>250.0</v>
+        <v>255.0</v>
       </c>
       <c r="G127" t="n">
         <v>11.0</v>
@@ -5741,7 +5741,7 @@
         <v>775</v>
       </c>
       <c r="F129" t="n">
-        <v>299.0</v>
+        <v>300.0</v>
       </c>
       <c r="G129" t="n">
         <v>0.0</v>
@@ -6157,7 +6157,7 @@
         <v>776</v>
       </c>
       <c r="F145" t="n">
-        <v>197.0</v>
+        <v>202.0</v>
       </c>
       <c r="G145" t="n">
         <v>0.0</v>
@@ -6339,7 +6339,7 @@
         <v>776</v>
       </c>
       <c r="F152" t="n">
-        <v>54.0</v>
+        <v>59.0</v>
       </c>
       <c r="G152" t="n">
         <v>0.0</v>
@@ -6547,7 +6547,7 @@
         <v>776</v>
       </c>
       <c r="F160" t="n">
-        <v>54.0</v>
+        <v>57.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -6703,7 +6703,7 @@
         <v>775</v>
       </c>
       <c r="F166" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G166" t="n">
         <v>0.0</v>
@@ -7379,7 +7379,7 @@
         <v>776</v>
       </c>
       <c r="F192" t="n">
-        <v>77.0</v>
+        <v>85.0</v>
       </c>
       <c r="G192" t="n">
         <v>0.0</v>
@@ -7873,7 +7873,7 @@
         <v>776</v>
       </c>
       <c r="F211" t="n">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
       <c r="G211" t="n">
         <v>0.0</v>
@@ -7951,7 +7951,7 @@
         <v>775</v>
       </c>
       <c r="F214" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G214" t="n">
         <v>1.0</v>
@@ -8133,7 +8133,7 @@
         <v>775</v>
       </c>
       <c r="F221" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="G221" t="n">
         <v>0.0</v>
@@ -8367,7 +8367,7 @@
         <v>775</v>
       </c>
       <c r="F230" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="G230" t="n">
         <v>0.0</v>
@@ -8393,7 +8393,7 @@
         <v>775</v>
       </c>
       <c r="F231" t="n">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
       <c r="G231" t="n">
         <v>9.0</v>
@@ -8419,7 +8419,7 @@
         <v>775</v>
       </c>
       <c r="F232" t="n">
-        <v>148.0</v>
+        <v>151.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
@@ -9095,7 +9095,7 @@
         <v>775</v>
       </c>
       <c r="F258" t="n">
-        <v>955.0</v>
+        <v>957.0</v>
       </c>
       <c r="G258" t="n">
         <v>23.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1058.0</v>
+        <v>1078.0</v>
       </c>
       <c r="G310" t="n">
         <v>20.0</v>
@@ -10681,7 +10681,7 @@
         <v>775</v>
       </c>
       <c r="F319" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G319" t="n">
         <v>6.0</v>
@@ -10785,7 +10785,7 @@
         <v>775</v>
       </c>
       <c r="F323" t="n">
-        <v>568.0</v>
+        <v>579.0</v>
       </c>
       <c r="G323" t="n">
         <v>8.0</v>
@@ -12345,7 +12345,7 @@
         <v>775</v>
       </c>
       <c r="F383" t="n">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="G383" t="n">
         <v>0.0</v>
@@ -13463,7 +13463,7 @@
         <v>776</v>
       </c>
       <c r="F426" t="n">
-        <v>222.0</v>
+        <v>242.0</v>
       </c>
       <c r="G426" t="n">
         <v>0.0</v>
@@ -14113,7 +14113,7 @@
         <v>775</v>
       </c>
       <c r="F451" t="n">
-        <v>779.0</v>
+        <v>783.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -14503,7 +14503,7 @@
         <v>775</v>
       </c>
       <c r="F466" t="n">
-        <v>209.0</v>
+        <v>212.0</v>
       </c>
       <c r="G466" t="n">
         <v>0.0</v>
@@ -15309,7 +15309,7 @@
         <v>776</v>
       </c>
       <c r="F497" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
       <c r="G497" t="n">
         <v>0.0</v>
@@ -15517,7 +15517,7 @@
         <v>776</v>
       </c>
       <c r="F505" t="n">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="G505" t="n">
         <v>2.0</v>
@@ -15621,7 +15621,7 @@
         <v>775</v>
       </c>
       <c r="F509" t="n">
-        <v>191.0</v>
+        <v>192.0</v>
       </c>
       <c r="G509" t="n">
         <v>1.0</v>
@@ -16167,7 +16167,7 @@
         <v>775</v>
       </c>
       <c r="F530" t="n">
-        <v>440.0</v>
+        <v>445.0</v>
       </c>
       <c r="G530" t="n">
         <v>3.0</v>
@@ -16297,7 +16297,7 @@
         <v>775</v>
       </c>
       <c r="F535" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G535" t="n">
         <v>0.0</v>
@@ -17025,7 +17025,7 @@
         <v>776</v>
       </c>
       <c r="F563" t="n">
-        <v>359.0</v>
+        <v>360.0</v>
       </c>
       <c r="G563" t="n">
         <v>0.0</v>
@@ -17311,7 +17311,7 @@
         <v>775</v>
       </c>
       <c r="F574" t="n">
-        <v>287.0</v>
+        <v>288.0</v>
       </c>
       <c r="G574" t="n">
         <v>0.0</v>
@@ -18013,7 +18013,7 @@
         <v>775</v>
       </c>
       <c r="F601" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G601" t="n">
         <v>0.0</v>
@@ -18299,7 +18299,7 @@
         <v>775</v>
       </c>
       <c r="F612" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G612" t="n">
         <v>0.0</v>
@@ -18975,7 +18975,7 @@
         <v>775</v>
       </c>
       <c r="F638" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G638" t="n">
         <v>3.0</v>
@@ -19027,7 +19027,7 @@
         <v>775</v>
       </c>
       <c r="F640" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G640" t="n">
         <v>0.0</v>
@@ -19053,7 +19053,7 @@
         <v>775</v>
       </c>
       <c r="F641" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G641" t="n">
         <v>79.0</v>
@@ -19625,7 +19625,7 @@
         <v>775</v>
       </c>
       <c r="F663" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -20431,7 +20431,7 @@
         <v>776</v>
       </c>
       <c r="F694" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>253.0</v>
+        <v>256.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -22407,7 +22407,7 @@
         <v>778</v>
       </c>
       <c r="F770" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G770" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3401,7 +3401,7 @@
         <v>775</v>
       </c>
       <c r="F39" t="n">
-        <v>263.0</v>
+        <v>264.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -5403,7 +5403,7 @@
         <v>775</v>
       </c>
       <c r="F116" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -8471,7 +8471,7 @@
         <v>775</v>
       </c>
       <c r="F234" t="n">
-        <v>388.0</v>
+        <v>390.0</v>
       </c>
       <c r="G234" t="n">
         <v>0.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>251.0</v>
+        <v>260.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -9693,7 +9693,7 @@
         <v>775</v>
       </c>
       <c r="F281" t="n">
-        <v>519.0</v>
+        <v>523.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -13411,7 +13411,7 @@
         <v>777</v>
       </c>
       <c r="F424" t="n">
-        <v>278.0</v>
+        <v>281.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
@@ -15829,7 +15829,7 @@
         <v>777</v>
       </c>
       <c r="F517" t="n">
-        <v>339.0</v>
+        <v>340.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
@@ -19625,7 +19625,7 @@
         <v>775</v>
       </c>
       <c r="F663" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -20951,7 +20951,7 @@
         <v>776</v>
       </c>
       <c r="F714" t="n">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="G714" t="n">
         <v>0.0</v>
@@ -21445,7 +21445,7 @@
         <v>776</v>
       </c>
       <c r="F733" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G733" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>524.0</v>
+        <v>525.0</v>
       </c>
       <c r="G780" t="n">
         <v>3.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>524.0</v>
+        <v>525.0</v>
       </c>
       <c r="G782" t="n">
         <v>3.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3765,7 +3765,7 @@
         <v>775</v>
       </c>
       <c r="F53" t="n">
-        <v>217.0</v>
+        <v>221.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -3921,7 +3921,7 @@
         <v>775</v>
       </c>
       <c r="F59" t="n">
-        <v>287.0</v>
+        <v>290.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>472.0</v>
+        <v>475.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4701,7 +4701,7 @@
         <v>775</v>
       </c>
       <c r="F89" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G89" t="n">
         <v>16.0</v>
@@ -4753,7 +4753,7 @@
         <v>775</v>
       </c>
       <c r="F91" t="n">
-        <v>481.0</v>
+        <v>482.0</v>
       </c>
       <c r="G91" t="n">
         <v>1.0</v>
@@ -5065,7 +5065,7 @@
         <v>775</v>
       </c>
       <c r="F103" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G103" t="n">
         <v>1.0</v>
@@ -5507,7 +5507,7 @@
         <v>775</v>
       </c>
       <c r="F120" t="n">
-        <v>417.0</v>
+        <v>419.0</v>
       </c>
       <c r="G120" t="n">
         <v>11.0</v>
@@ -6521,7 +6521,7 @@
         <v>775</v>
       </c>
       <c r="F159" t="n">
-        <v>136.0</v>
+        <v>141.0</v>
       </c>
       <c r="G159" t="n">
         <v>1.0</v>
@@ -6625,7 +6625,7 @@
         <v>775</v>
       </c>
       <c r="F163" t="n">
-        <v>62.0</v>
+        <v>67.0</v>
       </c>
       <c r="G163" t="n">
         <v>23.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -6807,7 +6807,7 @@
         <v>775</v>
       </c>
       <c r="F170" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G170" t="n">
         <v>8.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7587,7 +7587,7 @@
         <v>776</v>
       </c>
       <c r="F200" t="n">
-        <v>275.0</v>
+        <v>276.0</v>
       </c>
       <c r="G200" t="n">
         <v>0.0</v>
@@ -7613,7 +7613,7 @@
         <v>775</v>
       </c>
       <c r="F201" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G201" t="n">
         <v>0.0</v>
@@ -8341,7 +8341,7 @@
         <v>775</v>
       </c>
       <c r="F229" t="n">
-        <v>283.0</v>
+        <v>288.0</v>
       </c>
       <c r="G229" t="n">
         <v>20.0</v>
@@ -8419,7 +8419,7 @@
         <v>775</v>
       </c>
       <c r="F232" t="n">
-        <v>151.0</v>
+        <v>153.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
@@ -8913,7 +8913,7 @@
         <v>775</v>
       </c>
       <c r="F251" t="n">
-        <v>155.0</v>
+        <v>157.0</v>
       </c>
       <c r="G251" t="n">
         <v>16.0</v>
@@ -9095,7 +9095,7 @@
         <v>775</v>
       </c>
       <c r="F258" t="n">
-        <v>957.0</v>
+        <v>959.0</v>
       </c>
       <c r="G258" t="n">
         <v>23.0</v>
@@ -9355,7 +9355,7 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G268" t="n">
         <v>7.0</v>
@@ -9927,7 +9927,7 @@
         <v>775</v>
       </c>
       <c r="F290" t="n">
-        <v>587.0</v>
+        <v>591.0</v>
       </c>
       <c r="G290" t="n">
         <v>42.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="G291" t="n">
         <v>0.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1078.0</v>
+        <v>1083.0</v>
       </c>
       <c r="G310" t="n">
         <v>20.0</v>
@@ -10603,7 +10603,7 @@
         <v>775</v>
       </c>
       <c r="F316" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="G316" t="n">
         <v>6.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -10889,7 +10889,7 @@
         <v>775</v>
       </c>
       <c r="F327" t="n">
-        <v>108.0</v>
+        <v>111.0</v>
       </c>
       <c r="G327" t="n">
         <v>1.0</v>
@@ -11097,7 +11097,7 @@
         <v>775</v>
       </c>
       <c r="F335" t="n">
-        <v>143.0</v>
+        <v>148.0</v>
       </c>
       <c r="G335" t="n">
         <v>10.0</v>
@@ -11331,7 +11331,7 @@
         <v>775</v>
       </c>
       <c r="F344" t="n">
-        <v>81.0</v>
+        <v>83.0</v>
       </c>
       <c r="G344" t="n">
         <v>0.0</v>
@@ -11591,7 +11591,7 @@
         <v>776</v>
       </c>
       <c r="F354" t="n">
-        <v>139.0</v>
+        <v>141.0</v>
       </c>
       <c r="G354" t="n">
         <v>0.0</v>
@@ -11799,7 +11799,7 @@
         <v>775</v>
       </c>
       <c r="F362" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G362" t="n">
         <v>4.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>552.0</v>
+        <v>553.0</v>
       </c>
       <c r="G363" t="n">
         <v>0.0</v>
@@ -12501,7 +12501,7 @@
         <v>775</v>
       </c>
       <c r="F389" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G389" t="n">
         <v>2.0</v>
@@ -13177,7 +13177,7 @@
         <v>775</v>
       </c>
       <c r="F415" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G415" t="n">
         <v>0.0</v>
@@ -14113,7 +14113,7 @@
         <v>775</v>
       </c>
       <c r="F451" t="n">
-        <v>783.0</v>
+        <v>784.0</v>
       </c>
       <c r="G451" t="n">
         <v>0.0</v>
@@ -14165,7 +14165,7 @@
         <v>775</v>
       </c>
       <c r="F453" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G453" t="n">
         <v>0.0</v>
@@ -14269,7 +14269,7 @@
         <v>775</v>
       </c>
       <c r="F457" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G457" t="n">
         <v>24.0</v>
@@ -15205,7 +15205,7 @@
         <v>775</v>
       </c>
       <c r="F493" t="n">
-        <v>383.0</v>
+        <v>384.0</v>
       </c>
       <c r="G493" t="n">
         <v>40.0</v>
@@ -15621,7 +15621,7 @@
         <v>775</v>
       </c>
       <c r="F509" t="n">
-        <v>192.0</v>
+        <v>197.0</v>
       </c>
       <c r="G509" t="n">
         <v>1.0</v>
@@ -15699,7 +15699,7 @@
         <v>775</v>
       </c>
       <c r="F512" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G512" t="n">
         <v>2.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2502.0</v>
+        <v>2508.0</v>
       </c>
       <c r="G518" t="n">
         <v>307.0</v>
@@ -16297,7 +16297,7 @@
         <v>775</v>
       </c>
       <c r="F535" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G535" t="n">
         <v>0.0</v>
@@ -17831,7 +17831,7 @@
         <v>775</v>
       </c>
       <c r="F594" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G594" t="n">
         <v>0.0</v>
@@ -17987,7 +17987,7 @@
         <v>775</v>
       </c>
       <c r="F600" t="n">
-        <v>103.0</v>
+        <v>106.0</v>
       </c>
       <c r="G600" t="n">
         <v>0.0</v>
@@ -18377,7 +18377,7 @@
         <v>775</v>
       </c>
       <c r="F615" t="n">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="G615" t="n">
         <v>0.0</v>
@@ -21627,13 +21627,13 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>243.0</v>
+        <v>244.0</v>
       </c>
       <c r="G740" t="n">
         <v>8.0</v>
       </c>
       <c r="H740" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="741">

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -32,10 +32,10 @@
     <t>Negativo</t>
   </si>
   <si>
+    <t>Non idoneo</t>
+  </si>
+  <si>
     <t>Positivo</t>
-  </si>
-  <si>
-    <t>Non idoneo</t>
   </si>
   <si>
     <t>EMILIA ROMAGNA</t>
@@ -2439,13 +2439,13 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>648.0</v>
+        <v>652.0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -2468,10 +2468,10 @@
         <v>59.0</v>
       </c>
       <c r="G3" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H3" t="n">
         <v>42.0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="4">
@@ -2494,10 +2494,10 @@
         <v>91.0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -2520,10 +2520,10 @@
         <v>132.0</v>
       </c>
       <c r="G5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H5" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -2546,10 +2546,10 @@
         <v>39.0</v>
       </c>
       <c r="G6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H6" t="n">
         <v>21.0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -2572,10 +2572,10 @@
         <v>98.0</v>
       </c>
       <c r="G7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H7" t="n">
         <v>22.0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -2624,10 +2624,10 @@
         <v>14.0</v>
       </c>
       <c r="G9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H9" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -2650,10 +2650,10 @@
         <v>21.0</v>
       </c>
       <c r="G10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H10" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -2676,10 +2676,10 @@
         <v>306.0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -2702,10 +2702,10 @@
         <v>0.0</v>
       </c>
       <c r="G12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H12" t="n">
         <v>22.0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -2751,13 +2751,13 @@
         <v>775</v>
       </c>
       <c r="F14" t="n">
-        <v>498.0</v>
+        <v>504.0</v>
       </c>
       <c r="G14" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="H14" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>9.0</v>
       </c>
     </row>
     <row r="15">
@@ -2780,10 +2780,10 @@
         <v>236.0</v>
       </c>
       <c r="G15" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="H15" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>9.0</v>
       </c>
     </row>
     <row r="16">
@@ -2803,13 +2803,13 @@
         <v>775</v>
       </c>
       <c r="F16" t="n">
-        <v>427.0</v>
+        <v>429.0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -2884,10 +2884,10 @@
         <v>4.0</v>
       </c>
       <c r="G19" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H19" t="n">
         <v>1191.0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -2910,10 +2910,10 @@
         <v>168.0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -2936,10 +2936,10 @@
         <v>99.0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -2959,7 +2959,7 @@
         <v>776</v>
       </c>
       <c r="F22" t="n">
-        <v>409.0</v>
+        <v>411.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3118,10 +3118,10 @@
         <v>10.0</v>
       </c>
       <c r="G28" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H28" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="29">
@@ -3144,10 +3144,10 @@
         <v>11.0</v>
       </c>
       <c r="G29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H29" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -3170,10 +3170,10 @@
         <v>39.0</v>
       </c>
       <c r="G30" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H30" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -3193,7 +3193,7 @@
         <v>775</v>
       </c>
       <c r="F31" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -3248,10 +3248,10 @@
         <v>118.0</v>
       </c>
       <c r="G33" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H33" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="34">
@@ -3274,10 +3274,10 @@
         <v>21.0</v>
       </c>
       <c r="G34" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H34" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -3300,10 +3300,10 @@
         <v>213.0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -3323,13 +3323,13 @@
         <v>775</v>
       </c>
       <c r="F36" t="n">
-        <v>560.0</v>
+        <v>563.0</v>
       </c>
       <c r="G36" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H36" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="37">
@@ -3378,10 +3378,10 @@
         <v>0.0</v>
       </c>
       <c r="G38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H38" t="n">
         <v>34.0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3453,13 +3453,13 @@
         <v>775</v>
       </c>
       <c r="F41" t="n">
-        <v>350.0</v>
+        <v>351.0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -3482,10 +3482,10 @@
         <v>69.0</v>
       </c>
       <c r="G42" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H42" t="n">
         <v>15.0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -3508,10 +3508,10 @@
         <v>147.0</v>
       </c>
       <c r="G43" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H43" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="44">
@@ -3534,10 +3534,10 @@
         <v>47.0</v>
       </c>
       <c r="G44" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H44" t="n">
         <v>21.0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="45">
@@ -3560,10 +3560,10 @@
         <v>64.0</v>
       </c>
       <c r="G45" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H45" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -3586,10 +3586,10 @@
         <v>297.0</v>
       </c>
       <c r="G46" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H46" t="n">
         <v>13.0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>8.0</v>
       </c>
     </row>
     <row r="47">
@@ -3612,10 +3612,10 @@
         <v>185.0</v>
       </c>
       <c r="G47" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H47" t="n">
         <v>12.0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="48">
@@ -3638,10 +3638,10 @@
         <v>32.0</v>
       </c>
       <c r="G48" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H48" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="49">
@@ -3690,10 +3690,10 @@
         <v>103.0</v>
       </c>
       <c r="G50" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H50" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="51">
@@ -3742,10 +3742,10 @@
         <v>21.0</v>
       </c>
       <c r="G52" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H52" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -3768,10 +3768,10 @@
         <v>221.0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
@@ -3791,13 +3791,13 @@
         <v>775</v>
       </c>
       <c r="F54" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="G54" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H54" t="n">
         <v>52.0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="55">
@@ -3820,10 +3820,10 @@
         <v>83.0</v>
       </c>
       <c r="G55" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H55" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="56">
@@ -3898,10 +3898,10 @@
         <v>273.0</v>
       </c>
       <c r="G58" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H58" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="59">
@@ -3950,10 +3950,10 @@
         <v>27.0</v>
       </c>
       <c r="G60" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H60" t="n">
         <v>49.0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -4002,10 +4002,10 @@
         <v>24.0</v>
       </c>
       <c r="G62" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H62" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>219.0</v>
+        <v>222.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4158,10 +4158,10 @@
         <v>154.0</v>
       </c>
       <c r="G68" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H68" t="n">
         <v>21.0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="69">
@@ -4210,10 +4210,10 @@
         <v>36.0</v>
       </c>
       <c r="G70" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="H70" t="n">
         <v>27.0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>31.0</v>
       </c>
     </row>
     <row r="71">
@@ -4259,7 +4259,7 @@
         <v>775</v>
       </c>
       <c r="F72" t="n">
-        <v>148.0</v>
+        <v>150.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4314,10 +4314,10 @@
         <v>169.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H74" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -4337,13 +4337,13 @@
         <v>776</v>
       </c>
       <c r="F75" t="n">
-        <v>377.0</v>
+        <v>378.0</v>
       </c>
       <c r="G75" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H75" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="76">
@@ -4366,10 +4366,10 @@
         <v>360.0</v>
       </c>
       <c r="G76" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H76" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -4441,13 +4441,13 @@
         <v>775</v>
       </c>
       <c r="F79" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="G79" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="H79" t="n">
         <v>81.0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>15.0</v>
       </c>
     </row>
     <row r="80">
@@ -4496,10 +4496,10 @@
         <v>39.0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H81" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -4522,10 +4522,10 @@
         <v>475.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H82" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
@@ -4571,13 +4571,13 @@
         <v>775</v>
       </c>
       <c r="F84" t="n">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="G84" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H84" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -4600,10 +4600,10 @@
         <v>41.0</v>
       </c>
       <c r="G85" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H85" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="86">
@@ -4652,10 +4652,10 @@
         <v>63.0</v>
       </c>
       <c r="G87" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H87" t="n">
         <v>15.0</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -4678,10 +4678,10 @@
         <v>73.0</v>
       </c>
       <c r="G88" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H88" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="89">
@@ -4704,10 +4704,10 @@
         <v>114.0</v>
       </c>
       <c r="G89" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H89" t="n">
         <v>16.0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="90">
@@ -4753,13 +4753,13 @@
         <v>775</v>
       </c>
       <c r="F91" t="n">
-        <v>482.0</v>
+        <v>486.0</v>
       </c>
       <c r="G91" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H91" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="92">
@@ -4779,13 +4779,13 @@
         <v>775</v>
       </c>
       <c r="F92" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G92" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H92" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="93">
@@ -4808,10 +4808,10 @@
         <v>144.0</v>
       </c>
       <c r="G93" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H93" t="n">
         <v>17.0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="94">
@@ -4860,10 +4860,10 @@
         <v>16.0</v>
       </c>
       <c r="G95" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H95" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="96">
@@ -4912,10 +4912,10 @@
         <v>48.0</v>
       </c>
       <c r="G97" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H97" t="n">
         <v>17.0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="98">
@@ -4964,10 +4964,10 @@
         <v>51.0</v>
       </c>
       <c r="G99" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H99" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="100">
@@ -4987,7 +4987,7 @@
         <v>776</v>
       </c>
       <c r="F100" t="n">
-        <v>460.0</v>
+        <v>464.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5016,10 +5016,10 @@
         <v>25.0</v>
       </c>
       <c r="G101" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H101" t="n">
         <v>23.0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -5068,10 +5068,10 @@
         <v>43.0</v>
       </c>
       <c r="G103" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H103" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -5091,13 +5091,13 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>551.0</v>
+        <v>554.0</v>
       </c>
       <c r="G104" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H104" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="105">
@@ -5120,10 +5120,10 @@
         <v>9.0</v>
       </c>
       <c r="G105" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H105" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="106">
@@ -5146,10 +5146,10 @@
         <v>108.0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -5172,10 +5172,10 @@
         <v>38.0</v>
       </c>
       <c r="G107" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H107" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="108">
@@ -5221,7 +5221,7 @@
         <v>776</v>
       </c>
       <c r="F109" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -5250,10 +5250,10 @@
         <v>0.0</v>
       </c>
       <c r="G110" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H110" t="n">
         <v>14.0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -5302,10 +5302,10 @@
         <v>76.0</v>
       </c>
       <c r="G112" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H112" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="113">
@@ -5328,10 +5328,10 @@
         <v>23.0</v>
       </c>
       <c r="G113" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H113" t="n">
         <v>24.0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="114">
@@ -5354,10 +5354,10 @@
         <v>245.0</v>
       </c>
       <c r="G114" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H114" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H114" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="115">
@@ -5380,10 +5380,10 @@
         <v>0.0</v>
       </c>
       <c r="G115" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H115" t="n">
         <v>23.0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -5455,13 +5455,13 @@
         <v>775</v>
       </c>
       <c r="F118" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G118" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H118" t="n">
         <v>12.0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -5481,13 +5481,13 @@
         <v>775</v>
       </c>
       <c r="F119" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G119" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H119" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -5510,10 +5510,10 @@
         <v>419.0</v>
       </c>
       <c r="G120" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H120" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="121">
@@ -5536,10 +5536,10 @@
         <v>16.0</v>
       </c>
       <c r="G121" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H121" t="n">
         <v>23.0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -5559,13 +5559,13 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>482.0</v>
+        <v>484.0</v>
       </c>
       <c r="G122" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H122" t="n">
         <v>12.0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="123">
@@ -5614,10 +5614,10 @@
         <v>260.0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H124" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="125">
@@ -5637,13 +5637,13 @@
         <v>775</v>
       </c>
       <c r="F125" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G125" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H125" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="126">
@@ -5692,10 +5692,10 @@
         <v>255.0</v>
       </c>
       <c r="G127" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H127" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="128">
@@ -5718,10 +5718,10 @@
         <v>87.0</v>
       </c>
       <c r="G128" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H128" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="129">
@@ -5744,10 +5744,10 @@
         <v>300.0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H129" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="130">
@@ -5770,10 +5770,10 @@
         <v>101.0</v>
       </c>
       <c r="G130" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H130" t="n">
         <v>13.0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="131">
@@ -5796,10 +5796,10 @@
         <v>74.0</v>
       </c>
       <c r="G131" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H131" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -5874,10 +5874,10 @@
         <v>66.0</v>
       </c>
       <c r="G134" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H134" t="n">
         <v>13.0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="135">
@@ -5926,10 +5926,10 @@
         <v>112.0</v>
       </c>
       <c r="G136" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H136" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="137">
@@ -5952,10 +5952,10 @@
         <v>137.0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H137" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="138">
@@ -5975,13 +5975,13 @@
         <v>775</v>
       </c>
       <c r="F138" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G138" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H138" t="n">
         <v>25.0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="139">
@@ -6004,10 +6004,10 @@
         <v>35.0</v>
       </c>
       <c r="G139" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H139" t="n">
         <v>16.0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="140">
@@ -6027,7 +6027,7 @@
         <v>775</v>
       </c>
       <c r="F140" t="n">
-        <v>695.0</v>
+        <v>698.0</v>
       </c>
       <c r="G140" t="n">
         <v>2.0</v>
@@ -6056,10 +6056,10 @@
         <v>45.0</v>
       </c>
       <c r="G141" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H141" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="142">
@@ -6108,10 +6108,10 @@
         <v>274.0</v>
       </c>
       <c r="G143" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H143" t="n">
         <v>22.0</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="144">
@@ -6134,10 +6134,10 @@
         <v>74.0</v>
       </c>
       <c r="G144" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H144" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="145">
@@ -6160,10 +6160,10 @@
         <v>202.0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H145" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="146">
@@ -6264,10 +6264,10 @@
         <v>141.0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H149" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="150">
@@ -6313,13 +6313,13 @@
         <v>775</v>
       </c>
       <c r="F151" t="n">
-        <v>224.0</v>
+        <v>226.0</v>
       </c>
       <c r="G151" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H151" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="152">
@@ -6472,10 +6472,10 @@
         <v>62.0</v>
       </c>
       <c r="G157" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H157" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="158">
@@ -6498,10 +6498,10 @@
         <v>39.0</v>
       </c>
       <c r="G158" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H158" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="159">
@@ -6628,10 +6628,10 @@
         <v>67.0</v>
       </c>
       <c r="G163" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H163" t="n">
         <v>23.0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="164">
@@ -6677,13 +6677,13 @@
         <v>775</v>
       </c>
       <c r="F165" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G165" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H165" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="166">
@@ -6758,10 +6758,10 @@
         <v>8.0</v>
       </c>
       <c r="G168" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H168" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H168" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="169">
@@ -6781,13 +6781,13 @@
         <v>776</v>
       </c>
       <c r="F169" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G169" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H169" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H169" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="170">
@@ -6810,10 +6810,10 @@
         <v>76.0</v>
       </c>
       <c r="G170" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H170" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H170" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="171">
@@ -6833,7 +6833,7 @@
         <v>775</v>
       </c>
       <c r="F171" t="n">
-        <v>337.0</v>
+        <v>338.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6888,10 +6888,10 @@
         <v>247.0</v>
       </c>
       <c r="G173" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H173" t="n">
         <v>56.0</v>
-      </c>
-      <c r="H173" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="174">
@@ -6914,10 +6914,10 @@
         <v>104.0</v>
       </c>
       <c r="G174" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H174" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H174" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="175">
@@ -6940,10 +6940,10 @@
         <v>19.0</v>
       </c>
       <c r="G175" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H175" t="n">
         <v>40.0</v>
-      </c>
-      <c r="H175" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="176">
@@ -6966,10 +6966,10 @@
         <v>112.0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H176" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="177">
@@ -7015,13 +7015,13 @@
         <v>775</v>
       </c>
       <c r="F178" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="G178" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H178" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H178" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="179">
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>548.0</v>
+        <v>550.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7096,10 +7096,10 @@
         <v>105.0</v>
       </c>
       <c r="G181" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H181" t="n">
         <v>40.0</v>
-      </c>
-      <c r="H181" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="182">
@@ -7148,10 +7148,10 @@
         <v>122.0</v>
       </c>
       <c r="G183" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H183" t="n">
         <v>17.0</v>
-      </c>
-      <c r="H183" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="184">
@@ -7174,10 +7174,10 @@
         <v>14.0</v>
       </c>
       <c r="G184" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H184" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H184" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="185">
@@ -7226,10 +7226,10 @@
         <v>70.0</v>
       </c>
       <c r="G186" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H186" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H186" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="187">
@@ -7249,7 +7249,7 @@
         <v>776</v>
       </c>
       <c r="F187" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7301,13 +7301,13 @@
         <v>776</v>
       </c>
       <c r="F189" t="n">
-        <v>711.0</v>
+        <v>714.0</v>
       </c>
       <c r="G189" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H189" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H189" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="190">
@@ -7460,10 +7460,10 @@
         <v>167.0</v>
       </c>
       <c r="G195" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H195" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H195" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="196">
@@ -7486,10 +7486,10 @@
         <v>338.0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H196" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="197">
@@ -7538,10 +7538,10 @@
         <v>0.0</v>
       </c>
       <c r="G198" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H198" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H198" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="199">
@@ -7590,10 +7590,10 @@
         <v>276.0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H200" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="201">
@@ -7668,10 +7668,10 @@
         <v>1033.0</v>
       </c>
       <c r="G203" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H203" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="204">
@@ -7694,10 +7694,10 @@
         <v>21.0</v>
       </c>
       <c r="G204" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H204" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H204" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="205">
@@ -7746,10 +7746,10 @@
         <v>97.0</v>
       </c>
       <c r="G206" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H206" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H206" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="207">
@@ -7798,10 +7798,10 @@
         <v>24.0</v>
       </c>
       <c r="G208" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H208" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H208" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="209">
@@ -7824,10 +7824,10 @@
         <v>18.0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H209" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="210">
@@ -7847,7 +7847,7 @@
         <v>776</v>
       </c>
       <c r="F210" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G210" t="n">
         <v>0.0</v>
@@ -7902,10 +7902,10 @@
         <v>24.0</v>
       </c>
       <c r="G212" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H212" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H212" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="213">
@@ -7925,13 +7925,13 @@
         <v>775</v>
       </c>
       <c r="F213" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G213" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H213" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H213" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="214">
@@ -7954,10 +7954,10 @@
         <v>33.0</v>
       </c>
       <c r="G214" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H214" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H214" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="215">
@@ -7977,7 +7977,7 @@
         <v>776</v>
       </c>
       <c r="F215" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G215" t="n">
         <v>0.0</v>
@@ -8006,10 +8006,10 @@
         <v>26.0</v>
       </c>
       <c r="G216" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H216" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H216" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="217">
@@ -8032,10 +8032,10 @@
         <v>27.0</v>
       </c>
       <c r="G217" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H217" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H217" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="218">
@@ -8110,10 +8110,10 @@
         <v>91.0</v>
       </c>
       <c r="G220" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H220" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H220" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="221">
@@ -8162,10 +8162,10 @@
         <v>0.0</v>
       </c>
       <c r="G222" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H222" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H222" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="223">
@@ -8188,10 +8188,10 @@
         <v>166.0</v>
       </c>
       <c r="G223" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H223" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H223" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="224">
@@ -8240,10 +8240,10 @@
         <v>221.0</v>
       </c>
       <c r="G225" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H225" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H225" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="226">
@@ -8292,10 +8292,10 @@
         <v>261.0</v>
       </c>
       <c r="G227" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H227" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H227" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="228">
@@ -8344,10 +8344,10 @@
         <v>288.0</v>
       </c>
       <c r="G229" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H229" t="n">
         <v>20.0</v>
-      </c>
-      <c r="H229" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="230">
@@ -8370,10 +8370,10 @@
         <v>140.0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H230" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="231">
@@ -8396,10 +8396,10 @@
         <v>281.0</v>
       </c>
       <c r="G231" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="H231" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H231" t="n">
-        <v>5.0</v>
       </c>
     </row>
     <row r="232">
@@ -8448,10 +8448,10 @@
         <v>0.0</v>
       </c>
       <c r="G233" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H233" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H233" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="234">
@@ -8523,7 +8523,7 @@
         <v>776</v>
       </c>
       <c r="F236" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G236" t="n">
         <v>0.0</v>
@@ -8578,10 +8578,10 @@
         <v>51.0</v>
       </c>
       <c r="G238" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H238" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H238" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="239">
@@ -8708,10 +8708,10 @@
         <v>89.0</v>
       </c>
       <c r="G243" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H243" t="n">
         <v>9735.0</v>
-      </c>
-      <c r="H243" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="244">
@@ -8734,10 +8734,10 @@
         <v>235.0</v>
       </c>
       <c r="G244" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H244" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H244" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="245">
@@ -8760,10 +8760,10 @@
         <v>88.0</v>
       </c>
       <c r="G245" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H245" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="246">
@@ -8812,10 +8812,10 @@
         <v>143.0</v>
       </c>
       <c r="G247" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H247" t="n">
         <v>14.0</v>
-      </c>
-      <c r="H247" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="248">
@@ -8838,10 +8838,10 @@
         <v>165.0</v>
       </c>
       <c r="G248" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H248" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H248" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="249">
@@ -8864,10 +8864,10 @@
         <v>36.0</v>
       </c>
       <c r="G249" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H249" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="250">
@@ -8890,10 +8890,10 @@
         <v>29.0</v>
       </c>
       <c r="G250" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H250" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H250" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="251">
@@ -8916,10 +8916,10 @@
         <v>157.0</v>
       </c>
       <c r="G251" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H251" t="n">
         <v>16.0</v>
-      </c>
-      <c r="H251" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="252">
@@ -8968,10 +8968,10 @@
         <v>47.0</v>
       </c>
       <c r="G253" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H253" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H253" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="254">
@@ -8994,10 +8994,10 @@
         <v>84.0</v>
       </c>
       <c r="G254" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H254" t="n">
         <v>32.0</v>
-      </c>
-      <c r="H254" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="255">
@@ -9020,10 +9020,10 @@
         <v>58.0</v>
       </c>
       <c r="G255" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H255" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H255" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="256">
@@ -9046,10 +9046,10 @@
         <v>56.0</v>
       </c>
       <c r="G256" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H256" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H256" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="257">
@@ -9072,10 +9072,10 @@
         <v>44.0</v>
       </c>
       <c r="G257" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H257" t="n">
         <v>54.0</v>
-      </c>
-      <c r="H257" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="258">
@@ -9098,10 +9098,10 @@
         <v>959.0</v>
       </c>
       <c r="G258" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H258" t="n">
         <v>23.0</v>
-      </c>
-      <c r="H258" t="n">
-        <v>16.0</v>
       </c>
     </row>
     <row r="259">
@@ -9124,10 +9124,10 @@
         <v>18.0</v>
       </c>
       <c r="G259" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H259" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H259" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="260">
@@ -9176,10 +9176,10 @@
         <v>80.0</v>
       </c>
       <c r="G261" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H261" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="262">
@@ -9202,10 +9202,10 @@
         <v>39.0</v>
       </c>
       <c r="G262" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H262" t="n">
         <v>14.0</v>
-      </c>
-      <c r="H262" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="263">
@@ -9228,10 +9228,10 @@
         <v>0.0</v>
       </c>
       <c r="G263" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H263" t="n">
         <v>75.0</v>
-      </c>
-      <c r="H263" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="264">
@@ -9306,10 +9306,10 @@
         <v>25.0</v>
       </c>
       <c r="G266" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H266" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H266" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="267">
@@ -9355,13 +9355,13 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>253.0</v>
+        <v>254.0</v>
       </c>
       <c r="G268" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H268" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H268" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="269">
@@ -9384,10 +9384,10 @@
         <v>39.0</v>
       </c>
       <c r="G269" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H269" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H269" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="270">
@@ -9410,10 +9410,10 @@
         <v>58.0</v>
       </c>
       <c r="G270" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H270" t="n">
         <v>37.0</v>
-      </c>
-      <c r="H270" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="271">
@@ -9436,10 +9436,10 @@
         <v>56.0</v>
       </c>
       <c r="G271" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H271" t="n">
         <v>31.0</v>
-      </c>
-      <c r="H271" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="272">
@@ -9462,10 +9462,10 @@
         <v>613.0</v>
       </c>
       <c r="G272" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H272" t="n">
         <v>25.0</v>
-      </c>
-      <c r="H272" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="273">
@@ -9488,10 +9488,10 @@
         <v>37.0</v>
       </c>
       <c r="G273" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H273" t="n">
         <v>53.0</v>
-      </c>
-      <c r="H273" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="274">
@@ -9540,10 +9540,10 @@
         <v>70.0</v>
       </c>
       <c r="G275" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H275" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H275" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="276">
@@ -9566,10 +9566,10 @@
         <v>27.0</v>
       </c>
       <c r="G276" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H276" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H276" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="277">
@@ -9592,10 +9592,10 @@
         <v>39.0</v>
       </c>
       <c r="G277" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H277" t="n">
         <v>40.0</v>
-      </c>
-      <c r="H277" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="278">
@@ -9618,10 +9618,10 @@
         <v>174.0</v>
       </c>
       <c r="G278" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H278" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H278" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="279">
@@ -9670,10 +9670,10 @@
         <v>0.0</v>
       </c>
       <c r="G280" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H280" t="n">
         <v>15.0</v>
-      </c>
-      <c r="H280" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="281">
@@ -9774,10 +9774,10 @@
         <v>73.0</v>
       </c>
       <c r="G284" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H284" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H284" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="285">
@@ -9826,10 +9826,10 @@
         <v>277.0</v>
       </c>
       <c r="G286" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H286" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H286" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="287">
@@ -9852,10 +9852,10 @@
         <v>235.0</v>
       </c>
       <c r="G287" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H287" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H287" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="288">
@@ -9901,13 +9901,13 @@
         <v>775</v>
       </c>
       <c r="F289" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G289" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H289" t="n">
         <v>13.0</v>
-      </c>
-      <c r="H289" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="290">
@@ -9930,10 +9930,10 @@
         <v>591.0</v>
       </c>
       <c r="G290" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H290" t="n">
         <v>42.0</v>
-      </c>
-      <c r="H290" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="291">
@@ -9956,10 +9956,10 @@
         <v>67.0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H291" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="292">
@@ -9982,10 +9982,10 @@
         <v>51.0</v>
       </c>
       <c r="G292" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H292" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H292" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="293">
@@ -10005,13 +10005,13 @@
         <v>775</v>
       </c>
       <c r="F293" t="n">
-        <v>302.0</v>
+        <v>306.0</v>
       </c>
       <c r="G293" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H293" t="n">
         <v>14.0</v>
-      </c>
-      <c r="H293" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="294">
@@ -10034,10 +10034,10 @@
         <v>246.0</v>
       </c>
       <c r="G294" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H294" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H294" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="295">
@@ -10060,10 +10060,10 @@
         <v>82.0</v>
       </c>
       <c r="G295" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H295" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H295" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="296">
@@ -10112,10 +10112,10 @@
         <v>94.0</v>
       </c>
       <c r="G297" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H297" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H297" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="298">
@@ -10138,10 +10138,10 @@
         <v>216.0</v>
       </c>
       <c r="G298" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H298" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H298" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="299">
@@ -10164,10 +10164,10 @@
         <v>74.0</v>
       </c>
       <c r="G299" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H299" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H299" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="300">
@@ -10190,10 +10190,10 @@
         <v>22.0</v>
       </c>
       <c r="G300" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H300" t="n">
         <v>48.0</v>
-      </c>
-      <c r="H300" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="301">
@@ -10216,10 +10216,10 @@
         <v>91.0</v>
       </c>
       <c r="G301" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H301" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H301" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="302">
@@ -10268,10 +10268,10 @@
         <v>35.0</v>
       </c>
       <c r="G303" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H303" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H303" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="304">
@@ -10291,10 +10291,10 @@
         <v>775</v>
       </c>
       <c r="F304" t="n">
-        <v>414.0</v>
+        <v>418.0</v>
       </c>
       <c r="G304" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H304" t="n">
         <v>0.0</v>
@@ -10346,10 +10346,10 @@
         <v>58.0</v>
       </c>
       <c r="G306" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H306" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H306" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="307">
@@ -10369,7 +10369,7 @@
         <v>775</v>
       </c>
       <c r="F307" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G307" t="n">
         <v>0.0</v>
@@ -10398,10 +10398,10 @@
         <v>137.0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H308" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="309">
@@ -10424,10 +10424,10 @@
         <v>318.0</v>
       </c>
       <c r="G309" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H309" t="n">
         <v>16.0</v>
-      </c>
-      <c r="H309" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="310">
@@ -10450,10 +10450,10 @@
         <v>1083.0</v>
       </c>
       <c r="G310" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H310" t="n">
         <v>20.0</v>
-      </c>
-      <c r="H310" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="311">
@@ -10476,10 +10476,10 @@
         <v>146.0</v>
       </c>
       <c r="G311" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H311" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H311" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="312">
@@ -10502,10 +10502,10 @@
         <v>6.0</v>
       </c>
       <c r="G312" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H312" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H312" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="313">
@@ -10528,10 +10528,10 @@
         <v>12.0</v>
       </c>
       <c r="G313" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H313" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H313" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="314">
@@ -10554,10 +10554,10 @@
         <v>11.0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H314" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="315">
@@ -10577,13 +10577,13 @@
         <v>775</v>
       </c>
       <c r="F315" t="n">
-        <v>544.0</v>
+        <v>547.0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H315" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="316">
@@ -10606,10 +10606,10 @@
         <v>190.0</v>
       </c>
       <c r="G316" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H316" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H316" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="317">
@@ -10632,10 +10632,10 @@
         <v>23.0</v>
       </c>
       <c r="G317" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H317" t="n">
         <v>40.0</v>
-      </c>
-      <c r="H317" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="318">
@@ -10658,10 +10658,10 @@
         <v>20.0</v>
       </c>
       <c r="G318" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H318" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H318" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="319">
@@ -10684,10 +10684,10 @@
         <v>103.0</v>
       </c>
       <c r="G319" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H319" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H319" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="320">
@@ -10788,10 +10788,10 @@
         <v>579.0</v>
       </c>
       <c r="G323" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H323" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H323" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="324">
@@ -10840,10 +10840,10 @@
         <v>14.0</v>
       </c>
       <c r="G325" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H325" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H325" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="326">
@@ -10941,13 +10941,13 @@
         <v>775</v>
       </c>
       <c r="F329" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G329" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H329" t="n">
         <v>25.0</v>
-      </c>
-      <c r="H329" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="330">
@@ -10970,10 +10970,10 @@
         <v>55.0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H330" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="331">
@@ -10996,10 +10996,10 @@
         <v>33.0</v>
       </c>
       <c r="G331" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H331" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="332">
@@ -11022,10 +11022,10 @@
         <v>52.0</v>
       </c>
       <c r="G332" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H332" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H332" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="333">
@@ -11048,10 +11048,10 @@
         <v>2.0</v>
       </c>
       <c r="G333" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H333" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="334">
@@ -11100,10 +11100,10 @@
         <v>148.0</v>
       </c>
       <c r="G335" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H335" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H335" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="336">
@@ -11126,10 +11126,10 @@
         <v>268.0</v>
       </c>
       <c r="G336" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H336" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H336" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="337">
@@ -11152,10 +11152,10 @@
         <v>78.0</v>
       </c>
       <c r="G337" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H337" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H337" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="338">
@@ -11178,10 +11178,10 @@
         <v>16.0</v>
       </c>
       <c r="G338" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H338" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H338" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="339">
@@ -11227,13 +11227,13 @@
         <v>775</v>
       </c>
       <c r="F340" t="n">
-        <v>431.0</v>
+        <v>433.0</v>
       </c>
       <c r="G340" t="n">
         <v>1.0</v>
       </c>
       <c r="H340" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="341">
@@ -11256,10 +11256,10 @@
         <v>51.0</v>
       </c>
       <c r="G341" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H341" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H341" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="342">
@@ -11282,10 +11282,10 @@
         <v>0.0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H342" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="343">
@@ -11308,10 +11308,10 @@
         <v>233.0</v>
       </c>
       <c r="G343" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H343" t="n">
         <v>23.0</v>
-      </c>
-      <c r="H343" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="344">
@@ -11386,10 +11386,10 @@
         <v>5.0</v>
       </c>
       <c r="G346" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H346" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H346" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="347">
@@ -11412,10 +11412,10 @@
         <v>12.0</v>
       </c>
       <c r="G347" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H347" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H347" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="348">
@@ -11464,10 +11464,10 @@
         <v>126.0</v>
       </c>
       <c r="G349" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H349" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H349" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="350">
@@ -11542,10 +11542,10 @@
         <v>41.0</v>
       </c>
       <c r="G352" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H352" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H352" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="353">
@@ -11594,10 +11594,10 @@
         <v>141.0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H354" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="355">
@@ -11646,10 +11646,10 @@
         <v>26.0</v>
       </c>
       <c r="G356" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H356" t="n">
         <v>19.0</v>
-      </c>
-      <c r="H356" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="357">
@@ -11672,10 +11672,10 @@
         <v>0.0</v>
       </c>
       <c r="G357" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H357" t="n">
         <v>12.0</v>
-      </c>
-      <c r="H357" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="358">
@@ -11750,10 +11750,10 @@
         <v>13.0</v>
       </c>
       <c r="G360" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H360" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H360" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="361">
@@ -11802,10 +11802,10 @@
         <v>171.0</v>
       </c>
       <c r="G362" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H362" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H362" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="363">
@@ -11825,13 +11825,13 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>553.0</v>
+        <v>554.0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H363" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="364">
@@ -11854,10 +11854,10 @@
         <v>54.0</v>
       </c>
       <c r="G364" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H364" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H364" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="365">
@@ -11877,13 +11877,13 @@
         <v>775</v>
       </c>
       <c r="F365" t="n">
-        <v>110.0</v>
+        <v>112.0</v>
       </c>
       <c r="G365" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H365" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H365" t="n">
-        <v>13.0</v>
       </c>
     </row>
     <row r="366">
@@ -11932,10 +11932,10 @@
         <v>19.0</v>
       </c>
       <c r="G367" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H367" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H367" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="368">
@@ -11958,10 +11958,10 @@
         <v>20.0</v>
       </c>
       <c r="G368" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H368" t="n">
         <v>18.0</v>
-      </c>
-      <c r="H368" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="369">
@@ -11984,10 +11984,10 @@
         <v>22.0</v>
       </c>
       <c r="G369" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H369" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H369" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="370">
@@ -12010,10 +12010,10 @@
         <v>28.0</v>
       </c>
       <c r="G370" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H370" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H370" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="371">
@@ -12036,10 +12036,10 @@
         <v>15.0</v>
       </c>
       <c r="G371" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H371" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H371" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="372">
@@ -12062,10 +12062,10 @@
         <v>48.0</v>
       </c>
       <c r="G372" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H372" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H372" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="373">
@@ -12088,10 +12088,10 @@
         <v>104.0</v>
       </c>
       <c r="G373" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H373" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H373" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="374">
@@ -12166,10 +12166,10 @@
         <v>14.0</v>
       </c>
       <c r="G376" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H376" t="n">
         <v>27.0</v>
-      </c>
-      <c r="H376" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="377">
@@ -12189,13 +12189,13 @@
         <v>775</v>
       </c>
       <c r="F377" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G377" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H377" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H377" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="378">
@@ -12296,10 +12296,10 @@
         <v>0.0</v>
       </c>
       <c r="G381" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H381" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H381" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="382">
@@ -12374,10 +12374,10 @@
         <v>71.0</v>
       </c>
       <c r="G384" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H384" t="n">
         <v>34.0</v>
-      </c>
-      <c r="H384" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="385">
@@ -12452,10 +12452,10 @@
         <v>100.0</v>
       </c>
       <c r="G387" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H387" t="n">
         <v>15.0</v>
-      </c>
-      <c r="H387" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="388">
@@ -12475,7 +12475,7 @@
         <v>776</v>
       </c>
       <c r="F388" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
@@ -12504,10 +12504,10 @@
         <v>36.0</v>
       </c>
       <c r="G389" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H389" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H389" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="390">
@@ -12527,13 +12527,13 @@
         <v>775</v>
       </c>
       <c r="F390" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H390" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="391">
@@ -12553,13 +12553,13 @@
         <v>775</v>
       </c>
       <c r="F391" t="n">
-        <v>268.0</v>
+        <v>270.0</v>
       </c>
       <c r="G391" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H391" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H391" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="392">
@@ -12660,10 +12660,10 @@
         <v>14.0</v>
       </c>
       <c r="G395" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H395" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="396">
@@ -12712,10 +12712,10 @@
         <v>69.0</v>
       </c>
       <c r="G397" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H397" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="398">
@@ -12764,10 +12764,10 @@
         <v>138.0</v>
       </c>
       <c r="G399" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="H399" t="n">
         <v>36.0</v>
-      </c>
-      <c r="H399" t="n">
-        <v>5.0</v>
       </c>
     </row>
     <row r="400">
@@ -12790,10 +12790,10 @@
         <v>204.0</v>
       </c>
       <c r="G400" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H400" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H400" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="401">
@@ -12842,10 +12842,10 @@
         <v>168.0</v>
       </c>
       <c r="G402" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H402" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H402" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="403">
@@ -12868,10 +12868,10 @@
         <v>143.0</v>
       </c>
       <c r="G403" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H403" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H403" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="404">
@@ -12894,10 +12894,10 @@
         <v>0.0</v>
       </c>
       <c r="G404" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H404" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H404" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="405">
@@ -12920,10 +12920,10 @@
         <v>478.0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H405" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="406">
@@ -12946,10 +12946,10 @@
         <v>69.0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H406" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="407">
@@ -12972,10 +12972,10 @@
         <v>39.0</v>
       </c>
       <c r="G407" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H407" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H407" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="408">
@@ -13024,10 +13024,10 @@
         <v>8.0</v>
       </c>
       <c r="G409" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H409" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H409" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="410">
@@ -13076,10 +13076,10 @@
         <v>36.0</v>
       </c>
       <c r="G411" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H411" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H411" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="412">
@@ -13128,10 +13128,10 @@
         <v>2.0</v>
       </c>
       <c r="G413" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H413" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H413" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="414">
@@ -13151,13 +13151,13 @@
         <v>775</v>
       </c>
       <c r="F414" t="n">
-        <v>330.0</v>
+        <v>333.0</v>
       </c>
       <c r="G414" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H414" t="n">
         <v>28.0</v>
-      </c>
-      <c r="H414" t="n">
-        <v>13.0</v>
       </c>
     </row>
     <row r="415">
@@ -13232,10 +13232,10 @@
         <v>88.0</v>
       </c>
       <c r="G417" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H417" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H417" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="418">
@@ -13258,10 +13258,10 @@
         <v>190.0</v>
       </c>
       <c r="G418" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H418" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H418" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="419">
@@ -13336,10 +13336,10 @@
         <v>74.0</v>
       </c>
       <c r="G421" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H421" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H421" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="422">
@@ -13388,10 +13388,10 @@
         <v>0.0</v>
       </c>
       <c r="G423" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H423" t="n">
         <v>38.0</v>
-      </c>
-      <c r="H423" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="424">
@@ -13437,13 +13437,13 @@
         <v>775</v>
       </c>
       <c r="F425" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G425" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H425" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H425" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="426">
@@ -13466,10 +13466,10 @@
         <v>242.0</v>
       </c>
       <c r="G426" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H426" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="427">
@@ -13570,10 +13570,10 @@
         <v>50.0</v>
       </c>
       <c r="G430" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H430" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H430" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="431">
@@ -13674,10 +13674,10 @@
         <v>102.0</v>
       </c>
       <c r="G434" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H434" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H434" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="435">
@@ -13700,10 +13700,10 @@
         <v>23.0</v>
       </c>
       <c r="G435" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H435" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H435" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="436">
@@ -13726,10 +13726,10 @@
         <v>99.0</v>
       </c>
       <c r="G436" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H436" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H436" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="437">
@@ -13752,10 +13752,10 @@
         <v>27.0</v>
       </c>
       <c r="G437" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H437" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H437" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="438">
@@ -13804,10 +13804,10 @@
         <v>86.0</v>
       </c>
       <c r="G439" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H439" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H439" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="440">
@@ -13830,10 +13830,10 @@
         <v>105.0</v>
       </c>
       <c r="G440" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H440" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H440" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="441">
@@ -13882,10 +13882,10 @@
         <v>221.0</v>
       </c>
       <c r="G442" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H442" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H442" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="443">
@@ -13908,10 +13908,10 @@
         <v>86.0</v>
       </c>
       <c r="G443" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H443" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="444">
@@ -13986,10 +13986,10 @@
         <v>613.0</v>
       </c>
       <c r="G446" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H446" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="447">
@@ -14012,10 +14012,10 @@
         <v>152.0</v>
       </c>
       <c r="G447" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H447" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H447" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="448">
@@ -14038,10 +14038,10 @@
         <v>144.0</v>
       </c>
       <c r="G448" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H448" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H448" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="449">
@@ -14064,10 +14064,10 @@
         <v>125.0</v>
       </c>
       <c r="G449" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H449" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="450">
@@ -14090,10 +14090,10 @@
         <v>195.0</v>
       </c>
       <c r="G450" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H450" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H450" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="451">
@@ -14116,10 +14116,10 @@
         <v>784.0</v>
       </c>
       <c r="G451" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H451" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="452">
@@ -14142,10 +14142,10 @@
         <v>59.0</v>
       </c>
       <c r="G452" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H452" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H452" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="453">
@@ -14165,7 +14165,7 @@
         <v>775</v>
       </c>
       <c r="F453" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G453" t="n">
         <v>0.0</v>
@@ -14194,10 +14194,10 @@
         <v>32.0</v>
       </c>
       <c r="G454" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H454" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H454" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="455">
@@ -14217,13 +14217,13 @@
         <v>775</v>
       </c>
       <c r="F455" t="n">
-        <v>27.0</v>
+        <v>36.0</v>
       </c>
       <c r="G455" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H455" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H455" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="456">
@@ -14272,10 +14272,10 @@
         <v>123.0</v>
       </c>
       <c r="G457" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H457" t="n">
         <v>24.0</v>
-      </c>
-      <c r="H457" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="458">
@@ -14298,10 +14298,10 @@
         <v>200.0</v>
       </c>
       <c r="G458" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H458" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H458" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="459">
@@ -14350,10 +14350,10 @@
         <v>59.0</v>
       </c>
       <c r="G460" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H460" t="n">
         <v>22.0</v>
-      </c>
-      <c r="H460" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="461">
@@ -14376,10 +14376,10 @@
         <v>16.0</v>
       </c>
       <c r="G461" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H461" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H461" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="462">
@@ -14454,10 +14454,10 @@
         <v>136.0</v>
       </c>
       <c r="G464" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H464" t="n">
         <v>14.0</v>
-      </c>
-      <c r="H464" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="465">
@@ -14532,10 +14532,10 @@
         <v>18.0</v>
       </c>
       <c r="G467" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H467" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H467" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="468">
@@ -14558,10 +14558,10 @@
         <v>541.0</v>
       </c>
       <c r="G468" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H468" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="469">
@@ -14584,10 +14584,10 @@
         <v>197.0</v>
       </c>
       <c r="G469" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H469" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="470">
@@ -14610,10 +14610,10 @@
         <v>32.0</v>
       </c>
       <c r="G470" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H470" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H470" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="471">
@@ -14636,10 +14636,10 @@
         <v>196.0</v>
       </c>
       <c r="G471" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H471" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H471" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="472">
@@ -14659,13 +14659,13 @@
         <v>775</v>
       </c>
       <c r="F472" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G472" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H472" t="n">
         <v>44.0</v>
-      </c>
-      <c r="H472" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="473">
@@ -14766,10 +14766,10 @@
         <v>221.0</v>
       </c>
       <c r="G476" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H476" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H476" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="477">
@@ -14818,10 +14818,10 @@
         <v>96.0</v>
       </c>
       <c r="G478" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H478" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H478" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="479">
@@ -14870,10 +14870,10 @@
         <v>64.0</v>
       </c>
       <c r="G480" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H480" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H480" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="481">
@@ -14948,10 +14948,10 @@
         <v>535.0</v>
       </c>
       <c r="G483" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H483" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H483" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="484">
@@ -15000,10 +15000,10 @@
         <v>257.0</v>
       </c>
       <c r="G485" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="H485" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H485" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="486">
@@ -15156,10 +15156,10 @@
         <v>45.0</v>
       </c>
       <c r="G491" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H491" t="n">
         <v>18.0</v>
-      </c>
-      <c r="H491" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="492">
@@ -15182,10 +15182,10 @@
         <v>33.0</v>
       </c>
       <c r="G492" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H492" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H492" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="493">
@@ -15208,10 +15208,10 @@
         <v>384.0</v>
       </c>
       <c r="G493" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H493" t="n">
         <v>40.0</v>
-      </c>
-      <c r="H493" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="494">
@@ -15416,10 +15416,10 @@
         <v>76.0</v>
       </c>
       <c r="G501" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H501" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H501" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="502">
@@ -15439,13 +15439,13 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>665.0</v>
+        <v>671.0</v>
       </c>
       <c r="G502" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H502" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="503">
@@ -15468,10 +15468,10 @@
         <v>22.0</v>
       </c>
       <c r="G503" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H503" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H503" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="504">
@@ -15520,10 +15520,10 @@
         <v>44.0</v>
       </c>
       <c r="G505" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H505" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H505" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="506">
@@ -15546,10 +15546,10 @@
         <v>43.0</v>
       </c>
       <c r="G506" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H506" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H506" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="507">
@@ -15624,10 +15624,10 @@
         <v>197.0</v>
       </c>
       <c r="G509" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H509" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H509" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="510">
@@ -15676,10 +15676,10 @@
         <v>1.0</v>
       </c>
       <c r="G511" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H511" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H511" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="512">
@@ -15702,10 +15702,10 @@
         <v>99.0</v>
       </c>
       <c r="G512" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H512" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H512" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="513">
@@ -15754,10 +15754,10 @@
         <v>70.0</v>
       </c>
       <c r="G514" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H514" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H514" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="515">
@@ -15780,10 +15780,10 @@
         <v>185.0</v>
       </c>
       <c r="G515" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H515" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H515" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="516">
@@ -15806,10 +15806,10 @@
         <v>0.0</v>
       </c>
       <c r="G516" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H516" t="n">
         <v>49.0</v>
-      </c>
-      <c r="H516" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="517">
@@ -15858,10 +15858,10 @@
         <v>2508.0</v>
       </c>
       <c r="G518" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="H518" t="n">
         <v>307.0</v>
-      </c>
-      <c r="H518" t="n">
-        <v>45.0</v>
       </c>
     </row>
     <row r="519">
@@ -15884,10 +15884,10 @@
         <v>174.0</v>
       </c>
       <c r="G519" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H519" t="n">
         <v>26.0</v>
-      </c>
-      <c r="H519" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="520">
@@ -15910,10 +15910,10 @@
         <v>204.0</v>
       </c>
       <c r="G520" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H520" t="n">
         <v>6.0</v>
-      </c>
-      <c r="H520" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="521">
@@ -15936,10 +15936,10 @@
         <v>30.0</v>
       </c>
       <c r="G521" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H521" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H521" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="522">
@@ -15962,10 +15962,10 @@
         <v>206.0</v>
       </c>
       <c r="G522" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H522" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H522" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="523">
@@ -16014,10 +16014,10 @@
         <v>112.0</v>
       </c>
       <c r="G524" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H524" t="n">
         <v>13.0</v>
-      </c>
-      <c r="H524" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="525">
@@ -16066,10 +16066,10 @@
         <v>220.0</v>
       </c>
       <c r="G526" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H526" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H526" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="527">
@@ -16089,13 +16089,13 @@
         <v>775</v>
       </c>
       <c r="F527" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G527" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H527" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H527" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="528">
@@ -16118,10 +16118,10 @@
         <v>72.0</v>
       </c>
       <c r="G528" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H528" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="529">
@@ -16144,10 +16144,10 @@
         <v>24.0</v>
       </c>
       <c r="G529" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H529" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H529" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="530">
@@ -16170,10 +16170,10 @@
         <v>445.0</v>
       </c>
       <c r="G530" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="H530" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H530" t="n">
-        <v>9.0</v>
       </c>
     </row>
     <row r="531">
@@ -16196,10 +16196,10 @@
         <v>20.0</v>
       </c>
       <c r="G531" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H531" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H531" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="532">
@@ -16248,10 +16248,10 @@
         <v>65.0</v>
       </c>
       <c r="G533" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H533" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H533" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="534">
@@ -16274,10 +16274,10 @@
         <v>1.0</v>
       </c>
       <c r="G534" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H534" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H534" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="535">
@@ -16326,10 +16326,10 @@
         <v>81.0</v>
       </c>
       <c r="G536" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H536" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H536" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="537">
@@ -16378,10 +16378,10 @@
         <v>29.0</v>
       </c>
       <c r="G538" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H538" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H538" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="539">
@@ -16401,7 +16401,7 @@
         <v>776</v>
       </c>
       <c r="F539" t="n">
-        <v>171.0</v>
+        <v>173.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -16456,10 +16456,10 @@
         <v>17.0</v>
       </c>
       <c r="G541" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H541" t="n">
         <v>13.0</v>
-      </c>
-      <c r="H541" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="542">
@@ -16482,10 +16482,10 @@
         <v>94.0</v>
       </c>
       <c r="G542" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H542" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H542" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="543">
@@ -16508,10 +16508,10 @@
         <v>26.0</v>
       </c>
       <c r="G543" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H543" t="n">
         <v>52.0</v>
-      </c>
-      <c r="H543" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="544">
@@ -16531,13 +16531,13 @@
         <v>776</v>
       </c>
       <c r="F544" t="n">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="G544" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H544" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H544" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="545">
@@ -16586,10 +16586,10 @@
         <v>54.0</v>
       </c>
       <c r="G546" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H546" t="n">
         <v>49.0</v>
-      </c>
-      <c r="H546" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="547">
@@ -16609,13 +16609,13 @@
         <v>776</v>
       </c>
       <c r="F547" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="G547" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H547" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H547" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="548">
@@ -16690,10 +16690,10 @@
         <v>23.0</v>
       </c>
       <c r="G550" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H550" t="n">
         <v>130.0</v>
-      </c>
-      <c r="H550" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="551">
@@ -16742,10 +16742,10 @@
         <v>87.0</v>
       </c>
       <c r="G552" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H552" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H552" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="553">
@@ -16768,10 +16768,10 @@
         <v>9.0</v>
       </c>
       <c r="G553" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H553" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H553" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="554">
@@ -16846,10 +16846,10 @@
         <v>210.0</v>
       </c>
       <c r="G556" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H556" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H556" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="557">
@@ -16872,10 +16872,10 @@
         <v>110.0</v>
       </c>
       <c r="G557" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H557" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="558">
@@ -16898,10 +16898,10 @@
         <v>135.0</v>
       </c>
       <c r="G558" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H558" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="559">
@@ -16950,10 +16950,10 @@
         <v>20.0</v>
       </c>
       <c r="G560" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H560" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="561">
@@ -16976,10 +16976,10 @@
         <v>7.0</v>
       </c>
       <c r="G561" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H561" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H561" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="562">
@@ -16999,13 +16999,13 @@
         <v>775</v>
       </c>
       <c r="F562" t="n">
-        <v>226.0</v>
+        <v>228.0</v>
       </c>
       <c r="G562" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H562" t="n">
         <v>29.0</v>
-      </c>
-      <c r="H562" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="563">
@@ -17158,10 +17158,10 @@
         <v>30.0</v>
       </c>
       <c r="G568" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H568" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H568" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="569">
@@ -17262,10 +17262,10 @@
         <v>92.0</v>
       </c>
       <c r="G572" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H572" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H572" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="573">
@@ -17288,10 +17288,10 @@
         <v>0.0</v>
       </c>
       <c r="G573" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H573" t="n">
         <v>20.0</v>
-      </c>
-      <c r="H573" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="574">
@@ -17314,10 +17314,10 @@
         <v>288.0</v>
       </c>
       <c r="G574" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H574" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="575">
@@ -17392,10 +17392,10 @@
         <v>43.0</v>
       </c>
       <c r="G577" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H577" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H577" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="578">
@@ -17444,10 +17444,10 @@
         <v>26.0</v>
       </c>
       <c r="G579" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H579" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H579" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="580">
@@ -17519,7 +17519,7 @@
         <v>776</v>
       </c>
       <c r="F582" t="n">
-        <v>303.0</v>
+        <v>305.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -17548,10 +17548,10 @@
         <v>8.0</v>
       </c>
       <c r="G583" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H583" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="584">
@@ -17626,10 +17626,10 @@
         <v>108.0</v>
       </c>
       <c r="G586" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H586" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="587">
@@ -17701,7 +17701,7 @@
         <v>775</v>
       </c>
       <c r="F589" t="n">
-        <v>331.0</v>
+        <v>332.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>
@@ -17860,10 +17860,10 @@
         <v>49.0</v>
       </c>
       <c r="G595" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H595" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H595" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="596">
@@ -17912,10 +17912,10 @@
         <v>77.0</v>
       </c>
       <c r="G597" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H597" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H597" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="598">
@@ -17990,10 +17990,10 @@
         <v>106.0</v>
       </c>
       <c r="G600" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H600" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="601">
@@ -18068,10 +18068,10 @@
         <v>178.0</v>
       </c>
       <c r="G603" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H603" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H603" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="604">
@@ -18120,10 +18120,10 @@
         <v>348.0</v>
       </c>
       <c r="G605" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="H605" t="n">
         <v>12.0</v>
-      </c>
-      <c r="H605" t="n">
-        <v>11.0</v>
       </c>
     </row>
     <row r="606">
@@ -18146,10 +18146,10 @@
         <v>257.0</v>
       </c>
       <c r="G606" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H606" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H606" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="607">
@@ -18172,10 +18172,10 @@
         <v>19.0</v>
       </c>
       <c r="G607" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H607" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H607" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="608">
@@ -18195,7 +18195,7 @@
         <v>776</v>
       </c>
       <c r="F608" t="n">
-        <v>419.0</v>
+        <v>420.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18250,10 +18250,10 @@
         <v>32.0</v>
       </c>
       <c r="G610" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H610" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H610" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="611">
@@ -18276,10 +18276,10 @@
         <v>222.0</v>
       </c>
       <c r="G611" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H611" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H611" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="612">
@@ -18328,10 +18328,10 @@
         <v>221.0</v>
       </c>
       <c r="G613" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H613" t="n">
         <v>18.0</v>
-      </c>
-      <c r="H613" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="614">
@@ -18380,10 +18380,10 @@
         <v>93.0</v>
       </c>
       <c r="G615" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H615" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="616">
@@ -18432,10 +18432,10 @@
         <v>18.0</v>
       </c>
       <c r="G617" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H617" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H617" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="618">
@@ -18458,10 +18458,10 @@
         <v>93.0</v>
       </c>
       <c r="G618" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H618" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H618" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="619">
@@ -18484,10 +18484,10 @@
         <v>90.0</v>
       </c>
       <c r="G619" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H619" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H619" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="620">
@@ -18562,10 +18562,10 @@
         <v>23.0</v>
       </c>
       <c r="G622" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H622" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H622" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="623">
@@ -18588,10 +18588,10 @@
         <v>6.0</v>
       </c>
       <c r="G623" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H623" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="624">
@@ -18614,10 +18614,10 @@
         <v>24.0</v>
       </c>
       <c r="G624" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H624" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H624" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="625">
@@ -18666,10 +18666,10 @@
         <v>220.0</v>
       </c>
       <c r="G626" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H626" t="n">
         <v>32.0</v>
-      </c>
-      <c r="H626" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="627">
@@ -18770,10 +18770,10 @@
         <v>69.0</v>
       </c>
       <c r="G630" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H630" t="n">
         <v>1851.0</v>
-      </c>
-      <c r="H630" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="631">
@@ -18793,7 +18793,7 @@
         <v>775</v>
       </c>
       <c r="F631" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -18822,10 +18822,10 @@
         <v>18.0</v>
       </c>
       <c r="G632" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H632" t="n">
         <v>19.0</v>
-      </c>
-      <c r="H632" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="633">
@@ -18874,10 +18874,10 @@
         <v>77.0</v>
       </c>
       <c r="G634" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H634" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H634" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="635">
@@ -18978,10 +18978,10 @@
         <v>79.0</v>
       </c>
       <c r="G638" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H638" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H638" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="639">
@@ -19030,10 +19030,10 @@
         <v>102.0</v>
       </c>
       <c r="G640" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H640" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="641">
@@ -19056,10 +19056,10 @@
         <v>144.0</v>
       </c>
       <c r="G641" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H641" t="n">
         <v>79.0</v>
-      </c>
-      <c r="H641" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="642">
@@ -19082,10 +19082,10 @@
         <v>35.0</v>
       </c>
       <c r="G642" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H642" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H642" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="643">
@@ -19108,10 +19108,10 @@
         <v>27.0</v>
       </c>
       <c r="G643" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H643" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="644">
@@ -19212,10 +19212,10 @@
         <v>57.0</v>
       </c>
       <c r="G647" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H647" t="n">
         <v>19.0</v>
-      </c>
-      <c r="H647" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="648">
@@ -19238,10 +19238,10 @@
         <v>176.0</v>
       </c>
       <c r="G648" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H648" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H648" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="649">
@@ -19264,10 +19264,10 @@
         <v>6.0</v>
       </c>
       <c r="G649" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H649" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H649" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="650">
@@ -19394,10 +19394,10 @@
         <v>133.0</v>
       </c>
       <c r="G654" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H654" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H654" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="655">
@@ -19420,10 +19420,10 @@
         <v>19.0</v>
       </c>
       <c r="G655" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H655" t="n">
         <v>14.0</v>
-      </c>
-      <c r="H655" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="656">
@@ -19443,7 +19443,7 @@
         <v>776</v>
       </c>
       <c r="F656" t="n">
-        <v>148.0</v>
+        <v>150.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19472,10 +19472,10 @@
         <v>25.0</v>
       </c>
       <c r="G657" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H657" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H657" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="658">
@@ -19498,10 +19498,10 @@
         <v>95.0</v>
       </c>
       <c r="G658" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H658" t="n">
         <v>44.0</v>
-      </c>
-      <c r="H658" t="n">
-        <v>7.0</v>
       </c>
     </row>
     <row r="659">
@@ -19602,10 +19602,10 @@
         <v>0.0</v>
       </c>
       <c r="G662" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H662" t="n">
         <v>16.0</v>
-      </c>
-      <c r="H662" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="663">
@@ -19654,10 +19654,10 @@
         <v>115.0</v>
       </c>
       <c r="G664" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H664" t="n">
         <v>35.0</v>
-      </c>
-      <c r="H664" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="665">
@@ -19680,10 +19680,10 @@
         <v>0.0</v>
       </c>
       <c r="G665" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H665" t="n">
         <v>39.0</v>
-      </c>
-      <c r="H665" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="666">
@@ -19732,10 +19732,10 @@
         <v>64.0</v>
       </c>
       <c r="G667" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H667" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="668">
@@ -19758,10 +19758,10 @@
         <v>105.0</v>
       </c>
       <c r="G668" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H668" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="669">
@@ -19784,10 +19784,10 @@
         <v>0.0</v>
       </c>
       <c r="G669" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H669" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H669" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="670">
@@ -19810,10 +19810,10 @@
         <v>135.0</v>
       </c>
       <c r="G670" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H670" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="671">
@@ -19859,7 +19859,7 @@
         <v>776</v>
       </c>
       <c r="F672" t="n">
-        <v>124.0</v>
+        <v>135.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -19885,13 +19885,13 @@
         <v>775</v>
       </c>
       <c r="F673" t="n">
-        <v>153.0</v>
+        <v>156.0</v>
       </c>
       <c r="G673" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H673" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="674">
@@ -19911,7 +19911,7 @@
         <v>775</v>
       </c>
       <c r="F674" t="n">
-        <v>78.0</v>
+        <v>80.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19963,7 +19963,7 @@
         <v>776</v>
       </c>
       <c r="F676" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -20067,7 +20067,7 @@
         <v>776</v>
       </c>
       <c r="F680" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G680" t="n">
         <v>0.0</v>
@@ -20119,7 +20119,7 @@
         <v>776</v>
       </c>
       <c r="F682" t="n">
-        <v>74.0</v>
+        <v>78.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20145,7 +20145,7 @@
         <v>776</v>
       </c>
       <c r="F683" t="n">
-        <v>86.0</v>
+        <v>90.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20200,10 +20200,10 @@
         <v>14.0</v>
       </c>
       <c r="G685" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H685" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="686">
@@ -20226,10 +20226,10 @@
         <v>58.0</v>
       </c>
       <c r="G686" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="H686" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H686" t="n">
-        <v>12.0</v>
       </c>
     </row>
     <row r="687">
@@ -20249,13 +20249,13 @@
         <v>775</v>
       </c>
       <c r="F687" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G687" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H687" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H687" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="688">
@@ -20278,10 +20278,10 @@
         <v>55.0</v>
       </c>
       <c r="G688" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H688" t="n">
         <v>12.0</v>
-      </c>
-      <c r="H688" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="689">
@@ -20301,7 +20301,7 @@
         <v>776</v>
       </c>
       <c r="F689" t="n">
-        <v>102.0</v>
+        <v>106.0</v>
       </c>
       <c r="G689" t="n">
         <v>0.0</v>
@@ -20327,7 +20327,7 @@
         <v>775</v>
       </c>
       <c r="F690" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G690" t="n">
         <v>0.0</v>
@@ -20379,7 +20379,7 @@
         <v>776</v>
       </c>
       <c r="F692" t="n">
-        <v>153.0</v>
+        <v>158.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20408,10 +20408,10 @@
         <v>452.0</v>
       </c>
       <c r="G693" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H693" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H693" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="694">
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>186.0</v>
+        <v>188.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20535,7 +20535,7 @@
         <v>776</v>
       </c>
       <c r="F698" t="n">
-        <v>167.0</v>
+        <v>171.0</v>
       </c>
       <c r="G698" t="n">
         <v>0.0</v>
@@ -20590,10 +20590,10 @@
         <v>215.0</v>
       </c>
       <c r="G700" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H700" t="n">
         <v>5.0</v>
-      </c>
-      <c r="H700" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="701">
@@ -20717,13 +20717,13 @@
         <v>775</v>
       </c>
       <c r="F705" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G705" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H705" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="706">
@@ -20769,7 +20769,7 @@
         <v>775</v>
       </c>
       <c r="F707" t="n">
-        <v>135.0</v>
+        <v>137.0</v>
       </c>
       <c r="G707" t="n">
         <v>0.0</v>
@@ -20795,7 +20795,7 @@
         <v>776</v>
       </c>
       <c r="F708" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -20850,10 +20850,10 @@
         <v>98.0</v>
       </c>
       <c r="G710" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H710" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="711">
@@ -21032,10 +21032,10 @@
         <v>194.0</v>
       </c>
       <c r="G717" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H717" t="n">
         <v>20.0</v>
-      </c>
-      <c r="H717" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="718">
@@ -21055,13 +21055,13 @@
         <v>777</v>
       </c>
       <c r="F718" t="n">
-        <v>55.0</v>
+        <v>64.0</v>
       </c>
       <c r="G718" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H718" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H718" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="719">
@@ -21107,10 +21107,10 @@
         <v>777</v>
       </c>
       <c r="F720" t="n">
-        <v>74.0</v>
+        <v>77.0</v>
       </c>
       <c r="G720" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H720" t="n">
         <v>0.0</v>
@@ -21344,10 +21344,10 @@
         <v>93.0</v>
       </c>
       <c r="G729" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H729" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="730">
@@ -21370,10 +21370,10 @@
         <v>51.0</v>
       </c>
       <c r="G730" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H730" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="731">
@@ -21630,10 +21630,10 @@
         <v>244.0</v>
       </c>
       <c r="G740" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H740" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H740" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="741">
@@ -21708,10 +21708,10 @@
         <v>20.0</v>
       </c>
       <c r="G743" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H743" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="744">
@@ -21760,10 +21760,10 @@
         <v>15.0</v>
       </c>
       <c r="G745" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H745" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="746">
@@ -21835,13 +21835,13 @@
         <v>775</v>
       </c>
       <c r="F748" t="n">
-        <v>337.0</v>
+        <v>341.0</v>
       </c>
       <c r="G748" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H748" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="749">
@@ -21864,10 +21864,10 @@
         <v>157.0</v>
       </c>
       <c r="G749" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H749" t="n">
         <v>16.0</v>
-      </c>
-      <c r="H749" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="750">
@@ -21913,7 +21913,7 @@
         <v>776</v>
       </c>
       <c r="F751" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="G751" t="n">
         <v>0.0</v>
@@ -22020,10 +22020,10 @@
         <v>0.0</v>
       </c>
       <c r="G755" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H755" t="n">
         <v>51.0</v>
-      </c>
-      <c r="H755" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="756">
@@ -22043,13 +22043,13 @@
         <v>775</v>
       </c>
       <c r="F756" t="n">
-        <v>224.0</v>
+        <v>227.0</v>
       </c>
       <c r="G756" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H756" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="757">
@@ -22072,10 +22072,10 @@
         <v>85.0</v>
       </c>
       <c r="G757" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H757" t="n">
         <v>11.0</v>
-      </c>
-      <c r="H757" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="758">
@@ -22124,10 +22124,10 @@
         <v>433.0</v>
       </c>
       <c r="G759" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H759" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="760">
@@ -22147,7 +22147,7 @@
         <v>775</v>
       </c>
       <c r="F760" t="n">
-        <v>210.0</v>
+        <v>213.0</v>
       </c>
       <c r="G760" t="n">
         <v>0.0</v>
@@ -22670,10 +22670,10 @@
         <v>525.0</v>
       </c>
       <c r="G780" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H780" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H780" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="781">
@@ -22722,10 +22722,10 @@
         <v>525.0</v>
       </c>
       <c r="G782" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H782" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H782" t="n">
-        <v>2.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2829,7 +2829,7 @@
         <v>775</v>
       </c>
       <c r="F17" t="n">
-        <v>255.0</v>
+        <v>257.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -2907,7 +2907,7 @@
         <v>775</v>
       </c>
       <c r="F20" t="n">
-        <v>168.0</v>
+        <v>171.0</v>
       </c>
       <c r="G20" t="n">
         <v>1.0</v>
@@ -2933,7 +2933,7 @@
         <v>775</v>
       </c>
       <c r="F21" t="n">
-        <v>99.0</v>
+        <v>103.0</v>
       </c>
       <c r="G21" t="n">
         <v>2.0</v>
@@ -3011,7 +3011,7 @@
         <v>776</v>
       </c>
       <c r="F24" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3089,7 +3089,7 @@
         <v>775</v>
       </c>
       <c r="F27" t="n">
-        <v>120.0</v>
+        <v>125.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -3349,7 +3349,7 @@
         <v>775</v>
       </c>
       <c r="F37" t="n">
-        <v>225.0</v>
+        <v>228.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3401,7 +3401,7 @@
         <v>775</v>
       </c>
       <c r="F39" t="n">
-        <v>264.0</v>
+        <v>265.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>144.0</v>
+        <v>147.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3895,7 +3895,7 @@
         <v>775</v>
       </c>
       <c r="F58" t="n">
-        <v>273.0</v>
+        <v>275.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -3921,7 +3921,7 @@
         <v>775</v>
       </c>
       <c r="F59" t="n">
-        <v>290.0</v>
+        <v>292.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -3973,7 +3973,7 @@
         <v>775</v>
       </c>
       <c r="F61" t="n">
-        <v>115.0</v>
+        <v>122.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -4051,7 +4051,7 @@
         <v>775</v>
       </c>
       <c r="F64" t="n">
-        <v>219.0</v>
+        <v>222.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -4155,7 +4155,7 @@
         <v>775</v>
       </c>
       <c r="F68" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
       <c r="G68" t="n">
         <v>3.0</v>
@@ -4311,7 +4311,7 @@
         <v>775</v>
       </c>
       <c r="F74" t="n">
-        <v>169.0</v>
+        <v>171.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -4389,7 +4389,7 @@
         <v>775</v>
       </c>
       <c r="F77" t="n">
-        <v>57.0</v>
+        <v>59.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>475.0</v>
+        <v>477.0</v>
       </c>
       <c r="G82" t="n">
         <v>1.0</v>
@@ -4545,7 +4545,7 @@
         <v>776</v>
       </c>
       <c r="F83" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4623,7 +4623,7 @@
         <v>775</v>
       </c>
       <c r="F86" t="n">
-        <v>64.0</v>
+        <v>73.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -4883,7 +4883,7 @@
         <v>775</v>
       </c>
       <c r="F96" t="n">
-        <v>135.0</v>
+        <v>137.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>255.0</v>
+        <v>261.0</v>
       </c>
       <c r="G127" t="n">
         <v>7.0</v>
@@ -5845,7 +5845,7 @@
         <v>775</v>
       </c>
       <c r="F133" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="G133" t="n">
         <v>0.0</v>
@@ -5897,7 +5897,7 @@
         <v>775</v>
       </c>
       <c r="F135" t="n">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="G135" t="n">
         <v>0.0</v>
@@ -5949,7 +5949,7 @@
         <v>775</v>
       </c>
       <c r="F137" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G137" t="n">
         <v>1.0</v>
@@ -6079,7 +6079,7 @@
         <v>775</v>
       </c>
       <c r="F142" t="n">
-        <v>20.0</v>
+        <v>23.0</v>
       </c>
       <c r="G142" t="n">
         <v>0.0</v>
@@ -6339,7 +6339,7 @@
         <v>776</v>
       </c>
       <c r="F152" t="n">
-        <v>59.0</v>
+        <v>65.0</v>
       </c>
       <c r="G152" t="n">
         <v>0.0</v>
@@ -6521,7 +6521,7 @@
         <v>775</v>
       </c>
       <c r="F159" t="n">
-        <v>141.0</v>
+        <v>144.0</v>
       </c>
       <c r="G159" t="n">
         <v>1.0</v>
@@ -6547,7 +6547,7 @@
         <v>776</v>
       </c>
       <c r="F160" t="n">
-        <v>57.0</v>
+        <v>61.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -6573,7 +6573,7 @@
         <v>775</v>
       </c>
       <c r="F161" t="n">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6651,7 +6651,7 @@
         <v>775</v>
       </c>
       <c r="F164" t="n">
-        <v>344.0</v>
+        <v>347.0</v>
       </c>
       <c r="G164" t="n">
         <v>0.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7145,7 +7145,7 @@
         <v>775</v>
       </c>
       <c r="F183" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G183" t="n">
         <v>1.0</v>
@@ -7197,7 +7197,7 @@
         <v>775</v>
       </c>
       <c r="F185" t="n">
-        <v>159.0</v>
+        <v>163.0</v>
       </c>
       <c r="G185" t="n">
         <v>0.0</v>
@@ -7379,7 +7379,7 @@
         <v>776</v>
       </c>
       <c r="F192" t="n">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="G192" t="n">
         <v>0.0</v>
@@ -7587,7 +7587,7 @@
         <v>776</v>
       </c>
       <c r="F200" t="n">
-        <v>276.0</v>
+        <v>278.0</v>
       </c>
       <c r="G200" t="n">
         <v>1.0</v>
@@ -7613,7 +7613,7 @@
         <v>775</v>
       </c>
       <c r="F201" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G201" t="n">
         <v>0.0</v>
@@ -7873,7 +7873,7 @@
         <v>776</v>
       </c>
       <c r="F211" t="n">
-        <v>65.0</v>
+        <v>74.0</v>
       </c>
       <c r="G211" t="n">
         <v>0.0</v>
@@ -8081,7 +8081,7 @@
         <v>776</v>
       </c>
       <c r="F219" t="n">
-        <v>189.0</v>
+        <v>194.0</v>
       </c>
       <c r="G219" t="n">
         <v>0.0</v>
@@ -8341,7 +8341,7 @@
         <v>775</v>
       </c>
       <c r="F229" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
       <c r="G229" t="n">
         <v>2.0</v>
@@ -8367,7 +8367,7 @@
         <v>775</v>
       </c>
       <c r="F230" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="G230" t="n">
         <v>1.0</v>
@@ -8419,7 +8419,7 @@
         <v>775</v>
       </c>
       <c r="F232" t="n">
-        <v>153.0</v>
+        <v>158.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
@@ -8471,7 +8471,7 @@
         <v>775</v>
       </c>
       <c r="F234" t="n">
-        <v>390.0</v>
+        <v>398.0</v>
       </c>
       <c r="G234" t="n">
         <v>0.0</v>
@@ -8549,7 +8549,7 @@
         <v>775</v>
       </c>
       <c r="F237" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G237" t="n">
         <v>0.0</v>
@@ -8913,7 +8913,7 @@
         <v>775</v>
       </c>
       <c r="F251" t="n">
-        <v>157.0</v>
+        <v>160.0</v>
       </c>
       <c r="G251" t="n">
         <v>7.0</v>
@@ -9069,7 +9069,7 @@
         <v>775</v>
       </c>
       <c r="F257" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G257" t="n">
         <v>3.0</v>
@@ -9095,7 +9095,7 @@
         <v>775</v>
       </c>
       <c r="F258" t="n">
-        <v>959.0</v>
+        <v>961.0</v>
       </c>
       <c r="G258" t="n">
         <v>16.0</v>
@@ -9199,7 +9199,7 @@
         <v>775</v>
       </c>
       <c r="F262" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G262" t="n">
         <v>1.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>260.0</v>
+        <v>273.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -9303,7 +9303,7 @@
         <v>775</v>
       </c>
       <c r="F266" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G266" t="n">
         <v>0.0</v>
@@ -9407,7 +9407,7 @@
         <v>775</v>
       </c>
       <c r="F270" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G270" t="n">
         <v>1.0</v>
@@ -9693,7 +9693,7 @@
         <v>775</v>
       </c>
       <c r="F281" t="n">
-        <v>523.0</v>
+        <v>537.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -9719,7 +9719,7 @@
         <v>775</v>
       </c>
       <c r="F282" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>67.0</v>
+        <v>69.0</v>
       </c>
       <c r="G291" t="n">
         <v>2.0</v>
@@ -10135,7 +10135,7 @@
         <v>775</v>
       </c>
       <c r="F298" t="n">
-        <v>216.0</v>
+        <v>218.0</v>
       </c>
       <c r="G298" t="n">
         <v>4.0</v>
@@ -10239,7 +10239,7 @@
         <v>776</v>
       </c>
       <c r="F302" t="n">
-        <v>63.0</v>
+        <v>70.0</v>
       </c>
       <c r="G302" t="n">
         <v>0.0</v>
@@ -10421,7 +10421,7 @@
         <v>775</v>
       </c>
       <c r="F309" t="n">
-        <v>318.0</v>
+        <v>320.0</v>
       </c>
       <c r="G309" t="n">
         <v>4.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1083.0</v>
+        <v>1094.0</v>
       </c>
       <c r="G310" t="n">
         <v>6.0</v>
@@ -10603,7 +10603,7 @@
         <v>775</v>
       </c>
       <c r="F316" t="n">
-        <v>190.0</v>
+        <v>192.0</v>
       </c>
       <c r="G316" t="n">
         <v>0.0</v>
@@ -10785,7 +10785,7 @@
         <v>775</v>
       </c>
       <c r="F323" t="n">
-        <v>579.0</v>
+        <v>582.0</v>
       </c>
       <c r="G323" t="n">
         <v>2.0</v>
@@ -10811,7 +10811,7 @@
         <v>776</v>
       </c>
       <c r="F324" t="n">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11149,7 +11149,7 @@
         <v>775</v>
       </c>
       <c r="F337" t="n">
-        <v>78.0</v>
+        <v>88.0</v>
       </c>
       <c r="G337" t="n">
         <v>0.0</v>
@@ -11695,7 +11695,7 @@
         <v>775</v>
       </c>
       <c r="F358" t="n">
-        <v>129.0</v>
+        <v>133.0</v>
       </c>
       <c r="G358" t="n">
         <v>0.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>554.0</v>
+        <v>556.0</v>
       </c>
       <c r="G363" t="n">
         <v>6.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12215,7 +12215,7 @@
         <v>776</v>
       </c>
       <c r="F378" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G378" t="n">
         <v>0.0</v>
@@ -12345,7 +12345,7 @@
         <v>775</v>
       </c>
       <c r="F383" t="n">
-        <v>102.0</v>
+        <v>107.0</v>
       </c>
       <c r="G383" t="n">
         <v>0.0</v>
@@ -12761,7 +12761,7 @@
         <v>775</v>
       </c>
       <c r="F399" t="n">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="G399" t="n">
         <v>5.0</v>
@@ -12865,7 +12865,7 @@
         <v>775</v>
       </c>
       <c r="F403" t="n">
-        <v>143.0</v>
+        <v>145.0</v>
       </c>
       <c r="G403" t="n">
         <v>1.0</v>
@@ -12917,7 +12917,7 @@
         <v>777</v>
       </c>
       <c r="F405" t="n">
-        <v>478.0</v>
+        <v>484.0</v>
       </c>
       <c r="G405" t="n">
         <v>1.0</v>
@@ -13177,7 +13177,7 @@
         <v>775</v>
       </c>
       <c r="F415" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G415" t="n">
         <v>0.0</v>
@@ -13411,7 +13411,7 @@
         <v>777</v>
       </c>
       <c r="F424" t="n">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
@@ -13619,7 +13619,7 @@
         <v>775</v>
       </c>
       <c r="F432" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G432" t="n">
         <v>0.0</v>
@@ -13671,7 +13671,7 @@
         <v>775</v>
       </c>
       <c r="F434" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G434" t="n">
         <v>0.0</v>
@@ -13905,7 +13905,7 @@
         <v>775</v>
       </c>
       <c r="F443" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
       <c r="G443" t="n">
         <v>2.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>613.0</v>
+        <v>619.0</v>
       </c>
       <c r="G446" t="n">
         <v>3.0</v>
@@ -14009,7 +14009,7 @@
         <v>775</v>
       </c>
       <c r="F447" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
       <c r="G447" t="n">
         <v>0.0</v>
@@ -14061,7 +14061,7 @@
         <v>776</v>
       </c>
       <c r="F449" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G449" t="n">
         <v>1.0</v>
@@ -14113,7 +14113,7 @@
         <v>775</v>
       </c>
       <c r="F451" t="n">
-        <v>784.0</v>
+        <v>793.0</v>
       </c>
       <c r="G451" t="n">
         <v>2.0</v>
@@ -14269,7 +14269,7 @@
         <v>775</v>
       </c>
       <c r="F457" t="n">
-        <v>123.0</v>
+        <v>126.0</v>
       </c>
       <c r="G457" t="n">
         <v>6.0</v>
@@ -14503,7 +14503,7 @@
         <v>775</v>
       </c>
       <c r="F466" t="n">
-        <v>212.0</v>
+        <v>221.0</v>
       </c>
       <c r="G466" t="n">
         <v>0.0</v>
@@ -14555,7 +14555,7 @@
         <v>775</v>
       </c>
       <c r="F468" t="n">
-        <v>541.0</v>
+        <v>547.0</v>
       </c>
       <c r="G468" t="n">
         <v>3.0</v>
@@ -14581,7 +14581,7 @@
         <v>775</v>
       </c>
       <c r="F469" t="n">
-        <v>197.0</v>
+        <v>200.0</v>
       </c>
       <c r="G469" t="n">
         <v>1.0</v>
@@ -14607,7 +14607,7 @@
         <v>775</v>
       </c>
       <c r="F470" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G470" t="n">
         <v>0.0</v>
@@ -14685,7 +14685,7 @@
         <v>775</v>
       </c>
       <c r="F473" t="n">
-        <v>111.0</v>
+        <v>119.0</v>
       </c>
       <c r="G473" t="n">
         <v>0.0</v>
@@ -14919,7 +14919,7 @@
         <v>776</v>
       </c>
       <c r="F482" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
       <c r="G482" t="n">
         <v>0.0</v>
@@ -14945,7 +14945,7 @@
         <v>775</v>
       </c>
       <c r="F483" t="n">
-        <v>535.0</v>
+        <v>536.0</v>
       </c>
       <c r="G483" t="n">
         <v>0.0</v>
@@ -14971,7 +14971,7 @@
         <v>775</v>
       </c>
       <c r="F484" t="n">
-        <v>80.0</v>
+        <v>84.0</v>
       </c>
       <c r="G484" t="n">
         <v>0.0</v>
@@ -15049,7 +15049,7 @@
         <v>775</v>
       </c>
       <c r="F487" t="n">
-        <v>119.0</v>
+        <v>122.0</v>
       </c>
       <c r="G487" t="n">
         <v>5.0</v>
@@ -15075,7 +15075,7 @@
         <v>776</v>
       </c>
       <c r="F488" t="n">
-        <v>72.0</v>
+        <v>74.0</v>
       </c>
       <c r="G488" t="n">
         <v>0.0</v>
@@ -15101,7 +15101,7 @@
         <v>776</v>
       </c>
       <c r="F489" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G489" t="n">
         <v>0.0</v>
@@ -15205,7 +15205,7 @@
         <v>775</v>
       </c>
       <c r="F493" t="n">
-        <v>384.0</v>
+        <v>386.0</v>
       </c>
       <c r="G493" t="n">
         <v>2.0</v>
@@ -15621,7 +15621,7 @@
         <v>775</v>
       </c>
       <c r="F509" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
       <c r="G509" t="n">
         <v>0.0</v>
@@ -15647,7 +15647,7 @@
         <v>776</v>
       </c>
       <c r="F510" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G510" t="n">
         <v>0.0</v>
@@ -15699,7 +15699,7 @@
         <v>775</v>
       </c>
       <c r="F512" t="n">
-        <v>99.0</v>
+        <v>104.0</v>
       </c>
       <c r="G512" t="n">
         <v>0.0</v>
@@ -15829,7 +15829,7 @@
         <v>777</v>
       </c>
       <c r="F517" t="n">
-        <v>340.0</v>
+        <v>350.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2508.0</v>
+        <v>2514.0</v>
       </c>
       <c r="G518" t="n">
         <v>45.0</v>
@@ -16037,7 +16037,7 @@
         <v>775</v>
       </c>
       <c r="F525" t="n">
-        <v>65.0</v>
+        <v>69.0</v>
       </c>
       <c r="G525" t="n">
         <v>0.0</v>
@@ -16297,7 +16297,7 @@
         <v>775</v>
       </c>
       <c r="F535" t="n">
-        <v>203.0</v>
+        <v>204.0</v>
       </c>
       <c r="G535" t="n">
         <v>0.0</v>
@@ -16921,7 +16921,7 @@
         <v>775</v>
       </c>
       <c r="F559" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G559" t="n">
         <v>0.0</v>
@@ -17077,7 +17077,7 @@
         <v>775</v>
       </c>
       <c r="F565" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
@@ -17103,7 +17103,7 @@
         <v>775</v>
       </c>
       <c r="F566" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G566" t="n">
         <v>0.0</v>
@@ -17311,7 +17311,7 @@
         <v>775</v>
       </c>
       <c r="F574" t="n">
-        <v>288.0</v>
+        <v>291.0</v>
       </c>
       <c r="G574" t="n">
         <v>1.0</v>
@@ -17389,7 +17389,7 @@
         <v>775</v>
       </c>
       <c r="F577" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G577" t="n">
         <v>1.0</v>
@@ -17779,7 +17779,7 @@
         <v>775</v>
       </c>
       <c r="F592" t="n">
-        <v>74.0</v>
+        <v>77.0</v>
       </c>
       <c r="G592" t="n">
         <v>0.0</v>
@@ -17805,7 +17805,7 @@
         <v>775</v>
       </c>
       <c r="F593" t="n">
-        <v>39.0</v>
+        <v>43.0</v>
       </c>
       <c r="G593" t="n">
         <v>0.0</v>
@@ -17831,7 +17831,7 @@
         <v>775</v>
       </c>
       <c r="F594" t="n">
-        <v>86.0</v>
+        <v>90.0</v>
       </c>
       <c r="G594" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         <v>775</v>
       </c>
       <c r="F599" t="n">
-        <v>288.0</v>
+        <v>292.0</v>
       </c>
       <c r="G599" t="n">
         <v>0.0</v>
@@ -18273,7 +18273,7 @@
         <v>775</v>
       </c>
       <c r="F611" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="G611" t="n">
         <v>3.0</v>
@@ -18377,7 +18377,7 @@
         <v>775</v>
       </c>
       <c r="F615" t="n">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="G615" t="n">
         <v>1.0</v>
@@ -19027,7 +19027,7 @@
         <v>775</v>
       </c>
       <c r="F640" t="n">
-        <v>102.0</v>
+        <v>105.0</v>
       </c>
       <c r="G640" t="n">
         <v>1.0</v>
@@ -19131,7 +19131,7 @@
         <v>776</v>
       </c>
       <c r="F644" t="n">
-        <v>174.0</v>
+        <v>184.0</v>
       </c>
       <c r="G644" t="n">
         <v>0.0</v>
@@ -19625,7 +19625,7 @@
         <v>775</v>
       </c>
       <c r="F663" t="n">
-        <v>59.0</v>
+        <v>67.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>217.0</v>
+        <v>229.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20561,7 +20561,7 @@
         <v>776</v>
       </c>
       <c r="F699" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G699" t="n">
         <v>0.0</v>
@@ -20613,7 +20613,7 @@
         <v>776</v>
       </c>
       <c r="F701" t="n">
-        <v>42.0</v>
+        <v>49.0</v>
       </c>
       <c r="G701" t="n">
         <v>0.0</v>
@@ -20821,7 +20821,7 @@
         <v>776</v>
       </c>
       <c r="F709" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G709" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -21211,7 +21211,7 @@
         <v>776</v>
       </c>
       <c r="F724" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G724" t="n">
         <v>0.0</v>
@@ -21237,7 +21237,7 @@
         <v>776</v>
       </c>
       <c r="F725" t="n">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="G725" t="n">
         <v>0.0</v>
@@ -21549,7 +21549,7 @@
         <v>776</v>
       </c>
       <c r="F737" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G737" t="n">
         <v>0.0</v>
@@ -21653,7 +21653,7 @@
         <v>778</v>
       </c>
       <c r="F741" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -21939,7 +21939,7 @@
         <v>775</v>
       </c>
       <c r="F752" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G752" t="n">
         <v>0.0</v>
@@ -21991,7 +21991,7 @@
         <v>775</v>
       </c>
       <c r="F754" t="n">
-        <v>416.0</v>
+        <v>418.0</v>
       </c>
       <c r="G754" t="n">
         <v>0.0</v>
@@ -22251,7 +22251,7 @@
         <v>776</v>
       </c>
       <c r="F764" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G764" t="n">
         <v>0.0</v>
@@ -22433,7 +22433,7 @@
         <v>778</v>
       </c>
       <c r="F771" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>525.0</v>
+        <v>527.0</v>
       </c>
       <c r="G780" t="n">
         <v>2.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>525.0</v>
+        <v>527.0</v>
       </c>
       <c r="G782" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>652.0</v>
+        <v>656.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2725,7 +2725,7 @@
         <v>777</v>
       </c>
       <c r="F13" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -2803,7 +2803,7 @@
         <v>775</v>
       </c>
       <c r="F16" t="n">
-        <v>429.0</v>
+        <v>431.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -3167,7 +3167,7 @@
         <v>775</v>
       </c>
       <c r="F30" t="n">
-        <v>39.0</v>
+        <v>43.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -3453,7 +3453,7 @@
         <v>775</v>
       </c>
       <c r="F41" t="n">
-        <v>351.0</v>
+        <v>352.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -4129,7 +4129,7 @@
         <v>776</v>
       </c>
       <c r="F67" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -4259,7 +4259,7 @@
         <v>775</v>
       </c>
       <c r="F72" t="n">
-        <v>150.0</v>
+        <v>152.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4753,7 +4753,7 @@
         <v>775</v>
       </c>
       <c r="F91" t="n">
-        <v>486.0</v>
+        <v>487.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>554.0</v>
+        <v>556.0</v>
       </c>
       <c r="G104" t="n">
         <v>4.0</v>
@@ -5559,7 +5559,7 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>484.0</v>
+        <v>485.0</v>
       </c>
       <c r="G122" t="n">
         <v>1.0</v>
@@ -6027,7 +6027,7 @@
         <v>775</v>
       </c>
       <c r="F140" t="n">
-        <v>698.0</v>
+        <v>701.0</v>
       </c>
       <c r="G140" t="n">
         <v>2.0</v>
@@ -6235,7 +6235,7 @@
         <v>775</v>
       </c>
       <c r="F148" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6833,7 +6833,7 @@
         <v>775</v>
       </c>
       <c r="F171" t="n">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
       <c r="G171" t="n">
         <v>1.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>550.0</v>
+        <v>551.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7457,7 +7457,7 @@
         <v>775</v>
       </c>
       <c r="F195" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G195" t="n">
         <v>0.0</v>
@@ -7613,7 +7613,7 @@
         <v>775</v>
       </c>
       <c r="F201" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="G201" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1033.0</v>
+        <v>1036.0</v>
       </c>
       <c r="G203" t="n">
         <v>1.0</v>
@@ -7847,7 +7847,7 @@
         <v>776</v>
       </c>
       <c r="F210" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G210" t="n">
         <v>0.0</v>
@@ -8575,7 +8575,7 @@
         <v>775</v>
       </c>
       <c r="F238" t="n">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
       <c r="G238" t="n">
         <v>1.0</v>
@@ -8679,7 +8679,7 @@
         <v>775</v>
       </c>
       <c r="F242" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="G242" t="n">
         <v>0.0</v>
@@ -8783,7 +8783,7 @@
         <v>776</v>
       </c>
       <c r="F246" t="n">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G246" t="n">
         <v>0.0</v>
@@ -8991,7 +8991,7 @@
         <v>775</v>
       </c>
       <c r="F254" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G254" t="n">
         <v>1.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>273.0</v>
+        <v>277.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -10213,7 +10213,7 @@
         <v>775</v>
       </c>
       <c r="F301" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G301" t="n">
         <v>0.0</v>
@@ -10681,7 +10681,7 @@
         <v>775</v>
       </c>
       <c r="F319" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G319" t="n">
         <v>0.0</v>
@@ -10759,7 +10759,7 @@
         <v>776</v>
       </c>
       <c r="F322" t="n">
-        <v>275.0</v>
+        <v>277.0</v>
       </c>
       <c r="G322" t="n">
         <v>0.0</v>
@@ -10941,7 +10941,7 @@
         <v>775</v>
       </c>
       <c r="F329" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G329" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         <v>775</v>
       </c>
       <c r="F340" t="n">
-        <v>433.0</v>
+        <v>436.0</v>
       </c>
       <c r="G340" t="n">
         <v>1.0</v>
@@ -11539,7 +11539,7 @@
         <v>775</v>
       </c>
       <c r="F352" t="n">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
       <c r="G352" t="n">
         <v>0.0</v>
@@ -11591,7 +11591,7 @@
         <v>776</v>
       </c>
       <c r="F354" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
       <c r="G354" t="n">
         <v>1.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>171.0</v>
+        <v>175.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -13125,7 +13125,7 @@
         <v>775</v>
       </c>
       <c r="F413" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G413" t="n">
         <v>0.0</v>
@@ -13255,7 +13255,7 @@
         <v>775</v>
       </c>
       <c r="F418" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="G418" t="n">
         <v>0.0</v>
@@ -14659,7 +14659,7 @@
         <v>775</v>
       </c>
       <c r="F472" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G472" t="n">
         <v>4.0</v>
@@ -14997,10 +14997,10 @@
         <v>775</v>
       </c>
       <c r="F485" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G485" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="H485" t="n">
         <v>8.0</v>
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>671.0</v>
+        <v>672.0</v>
       </c>
       <c r="G502" t="n">
         <v>2.0</v>
@@ -15907,7 +15907,7 @@
         <v>776</v>
       </c>
       <c r="F520" t="n">
-        <v>204.0</v>
+        <v>206.0</v>
       </c>
       <c r="G520" t="n">
         <v>0.0</v>
@@ -16401,7 +16401,7 @@
         <v>776</v>
       </c>
       <c r="F539" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G539" t="n">
         <v>0.0</v>
@@ -16479,7 +16479,7 @@
         <v>775</v>
       </c>
       <c r="F542" t="n">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="G542" t="n">
         <v>0.0</v>
@@ -16583,7 +16583,7 @@
         <v>775</v>
       </c>
       <c r="F546" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G546" t="n">
         <v>0.0</v>
@@ -16843,7 +16843,7 @@
         <v>775</v>
       </c>
       <c r="F556" t="n">
-        <v>210.0</v>
+        <v>212.0</v>
       </c>
       <c r="G556" t="n">
         <v>0.0</v>
@@ -17233,7 +17233,7 @@
         <v>776</v>
       </c>
       <c r="F571" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G571" t="n">
         <v>0.0</v>
@@ -18429,7 +18429,7 @@
         <v>775</v>
       </c>
       <c r="F617" t="n">
-        <v>18.0</v>
+        <v>24.0</v>
       </c>
       <c r="G617" t="n">
         <v>0.0</v>
@@ -18793,7 +18793,7 @@
         <v>775</v>
       </c>
       <c r="F631" t="n">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -19105,7 +19105,7 @@
         <v>775</v>
       </c>
       <c r="F643" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G643" t="n">
         <v>2.0</v>
@@ -19313,7 +19313,7 @@
         <v>775</v>
       </c>
       <c r="F651" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G651" t="n">
         <v>0.0</v>
@@ -19859,7 +19859,7 @@
         <v>776</v>
       </c>
       <c r="F672" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -19885,7 +19885,7 @@
         <v>775</v>
       </c>
       <c r="F673" t="n">
-        <v>156.0</v>
+        <v>158.0</v>
       </c>
       <c r="G673" t="n">
         <v>1.0</v>
@@ -19963,7 +19963,7 @@
         <v>776</v>
       </c>
       <c r="F676" t="n">
-        <v>129.0</v>
+        <v>132.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -20119,7 +20119,7 @@
         <v>776</v>
       </c>
       <c r="F682" t="n">
-        <v>78.0</v>
+        <v>82.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20145,7 +20145,7 @@
         <v>776</v>
       </c>
       <c r="F683" t="n">
-        <v>90.0</v>
+        <v>92.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20379,7 +20379,7 @@
         <v>776</v>
       </c>
       <c r="F692" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>452.0</v>
+        <v>456.0</v>
       </c>
       <c r="G693" t="n">
         <v>0.0</v>
@@ -20431,7 +20431,7 @@
         <v>776</v>
       </c>
       <c r="F694" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G694" t="n">
         <v>0.0</v>
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>188.0</v>
+        <v>192.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20691,7 +20691,7 @@
         <v>775</v>
       </c>
       <c r="F704" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G704" t="n">
         <v>0.0</v>
@@ -20925,7 +20925,7 @@
         <v>777</v>
       </c>
       <c r="F713" t="n">
-        <v>258.0</v>
+        <v>260.0</v>
       </c>
       <c r="G713" t="n">
         <v>0.0</v>
@@ -21055,7 +21055,7 @@
         <v>777</v>
       </c>
       <c r="F718" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G718" t="n">
         <v>0.0</v>
@@ -21107,7 +21107,7 @@
         <v>777</v>
       </c>
       <c r="F720" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G720" t="n">
         <v>1.0</v>
@@ -22121,7 +22121,7 @@
         <v>776</v>
       </c>
       <c r="F759" t="n">
-        <v>433.0</v>
+        <v>436.0</v>
       </c>
       <c r="G759" t="n">
         <v>1.0</v>
@@ -22407,7 +22407,7 @@
         <v>778</v>
       </c>
       <c r="F770" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G770" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3297,7 +3297,7 @@
         <v>775</v>
       </c>
       <c r="F35" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
       <c r="G35" t="n">
         <v>2.0</v>
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -5507,7 +5507,7 @@
         <v>775</v>
       </c>
       <c r="F120" t="n">
-        <v>419.0</v>
+        <v>421.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -5747,7 +5747,7 @@
         <v>3.0</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="130">
@@ -5949,7 +5949,7 @@
         <v>775</v>
       </c>
       <c r="F137" t="n">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
       <c r="G137" t="n">
         <v>1.0</v>
@@ -6703,7 +6703,7 @@
         <v>775</v>
       </c>
       <c r="F166" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G166" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1036.0</v>
+        <v>1037.0</v>
       </c>
       <c r="G203" t="n">
         <v>1.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -10317,7 +10317,7 @@
         <v>775</v>
       </c>
       <c r="F305" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G305" t="n">
         <v>0.0</v>
@@ -11461,7 +11461,7 @@
         <v>775</v>
       </c>
       <c r="F349" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G349" t="n">
         <v>2.0</v>
@@ -12839,7 +12839,7 @@
         <v>775</v>
       </c>
       <c r="F402" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G402" t="n">
         <v>2.0</v>
@@ -13879,7 +13879,7 @@
         <v>775</v>
       </c>
       <c r="F442" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="G442" t="n">
         <v>1.0</v>
@@ -14165,7 +14165,7 @@
         <v>775</v>
       </c>
       <c r="F453" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G453" t="n">
         <v>0.0</v>
@@ -14555,7 +14555,7 @@
         <v>775</v>
       </c>
       <c r="F468" t="n">
-        <v>547.0</v>
+        <v>548.0</v>
       </c>
       <c r="G468" t="n">
         <v>3.0</v>
@@ -14685,7 +14685,7 @@
         <v>775</v>
       </c>
       <c r="F473" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="G473" t="n">
         <v>0.0</v>
@@ -15959,7 +15959,7 @@
         <v>775</v>
       </c>
       <c r="F522" t="n">
-        <v>206.0</v>
+        <v>213.0</v>
       </c>
       <c r="G522" t="n">
         <v>0.0</v>
@@ -16063,7 +16063,7 @@
         <v>775</v>
       </c>
       <c r="F526" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G526" t="n">
         <v>0.0</v>
@@ -17291,7 +17291,7 @@
         <v>0.0</v>
       </c>
       <c r="H573" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="574">
@@ -17415,7 +17415,7 @@
         <v>775</v>
       </c>
       <c r="F578" t="n">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="G578" t="n">
         <v>0.0</v>
@@ -18377,7 +18377,7 @@
         <v>775</v>
       </c>
       <c r="F615" t="n">
-        <v>95.0</v>
+        <v>100.0</v>
       </c>
       <c r="G615" t="n">
         <v>1.0</v>
@@ -21419,7 +21419,7 @@
         <v>776</v>
       </c>
       <c r="F732" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G732" t="n">
         <v>0.0</v>
@@ -21549,7 +21549,7 @@
         <v>776</v>
       </c>
       <c r="F737" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G737" t="n">
         <v>0.0</v>
@@ -21653,7 +21653,7 @@
         <v>778</v>
       </c>
       <c r="F741" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -22433,7 +22433,7 @@
         <v>778</v>
       </c>
       <c r="F771" t="n">
-        <v>110.0</v>
+        <v>112.0</v>
       </c>
       <c r="G771" t="n">
         <v>0.0</v>
@@ -22459,10 +22459,10 @@
         <v>778</v>
       </c>
       <c r="F772" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G772" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H772" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="G780" t="n">
         <v>2.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="G782" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3401,7 +3401,7 @@
         <v>775</v>
       </c>
       <c r="F39" t="n">
-        <v>265.0</v>
+        <v>266.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -5403,7 +5403,7 @@
         <v>775</v>
       </c>
       <c r="F116" t="n">
-        <v>195.0</v>
+        <v>198.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -7561,7 +7561,7 @@
         <v>775</v>
       </c>
       <c r="F199" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G199" t="n">
         <v>0.0</v>
@@ -9693,7 +9693,7 @@
         <v>775</v>
       </c>
       <c r="F281" t="n">
-        <v>537.0</v>
+        <v>541.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -13411,7 +13411,7 @@
         <v>777</v>
       </c>
       <c r="F424" t="n">
-        <v>282.0</v>
+        <v>285.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
@@ -15829,7 +15829,7 @@
         <v>777</v>
       </c>
       <c r="F517" t="n">
-        <v>350.0</v>
+        <v>353.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>229.0</v>
+        <v>231.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20275,7 +20275,7 @@
         <v>777</v>
       </c>
       <c r="F688" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G688" t="n">
         <v>0.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>456.0</v>
+        <v>457.0</v>
       </c>
       <c r="G693" t="n">
         <v>0.0</v>
@@ -21211,7 +21211,7 @@
         <v>776</v>
       </c>
       <c r="F724" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G724" t="n">
         <v>0.0</v>
@@ -21653,7 +21653,7 @@
         <v>778</v>
       </c>
       <c r="F741" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G741" t="n">
         <v>0.0</v>
@@ -22563,7 +22563,7 @@
         <v>778</v>
       </c>
       <c r="F776" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G776" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>528.0</v>
+        <v>530.0</v>
       </c>
       <c r="G780" t="n">
         <v>2.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>528.0</v>
+        <v>530.0</v>
       </c>
       <c r="G782" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2673,7 +2673,7 @@
         <v>775</v>
       </c>
       <c r="F11" t="n">
-        <v>306.0</v>
+        <v>309.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -2907,7 +2907,7 @@
         <v>775</v>
       </c>
       <c r="F20" t="n">
-        <v>171.0</v>
+        <v>178.0</v>
       </c>
       <c r="G20" t="n">
         <v>1.0</v>
@@ -3089,7 +3089,7 @@
         <v>775</v>
       </c>
       <c r="F27" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -3245,7 +3245,7 @@
         <v>775</v>
       </c>
       <c r="F33" t="n">
-        <v>118.0</v>
+        <v>122.0</v>
       </c>
       <c r="G33" t="n">
         <v>1.0</v>
@@ -3895,7 +3895,7 @@
         <v>775</v>
       </c>
       <c r="F58" t="n">
-        <v>275.0</v>
+        <v>283.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -3973,7 +3973,7 @@
         <v>775</v>
       </c>
       <c r="F61" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -4051,7 +4051,7 @@
         <v>775</v>
       </c>
       <c r="F64" t="n">
-        <v>222.0</v>
+        <v>225.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -4363,7 +4363,7 @@
         <v>776</v>
       </c>
       <c r="F76" t="n">
-        <v>360.0</v>
+        <v>361.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -4389,7 +4389,7 @@
         <v>775</v>
       </c>
       <c r="F77" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>477.0</v>
+        <v>481.0</v>
       </c>
       <c r="G82" t="n">
         <v>1.0</v>
@@ -4623,7 +4623,7 @@
         <v>775</v>
       </c>
       <c r="F86" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -5143,7 +5143,7 @@
         <v>775</v>
       </c>
       <c r="F106" t="n">
-        <v>108.0</v>
+        <v>111.0</v>
       </c>
       <c r="G106" t="n">
         <v>1.0</v>
@@ -5351,7 +5351,7 @@
         <v>775</v>
       </c>
       <c r="F114" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
       <c r="G114" t="n">
         <v>2.0</v>
@@ -5403,7 +5403,7 @@
         <v>775</v>
       </c>
       <c r="F116" t="n">
-        <v>198.0</v>
+        <v>199.0</v>
       </c>
       <c r="G116" t="n">
         <v>0.0</v>
@@ -5689,7 +5689,7 @@
         <v>775</v>
       </c>
       <c r="F127" t="n">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="G127" t="n">
         <v>7.0</v>
@@ -5715,7 +5715,7 @@
         <v>775</v>
       </c>
       <c r="F128" t="n">
-        <v>87.0</v>
+        <v>89.0</v>
       </c>
       <c r="G128" t="n">
         <v>1.0</v>
@@ -5949,7 +5949,7 @@
         <v>775</v>
       </c>
       <c r="F137" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="G137" t="n">
         <v>1.0</v>
@@ -6339,7 +6339,7 @@
         <v>776</v>
       </c>
       <c r="F152" t="n">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="G152" t="n">
         <v>0.0</v>
@@ -6547,7 +6547,7 @@
         <v>776</v>
       </c>
       <c r="F160" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G160" t="n">
         <v>0.0</v>
@@ -6963,7 +6963,7 @@
         <v>775</v>
       </c>
       <c r="F176" t="n">
-        <v>112.0</v>
+        <v>115.0</v>
       </c>
       <c r="G176" t="n">
         <v>1.0</v>
@@ -7197,7 +7197,7 @@
         <v>775</v>
       </c>
       <c r="F185" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
       <c r="G185" t="n">
         <v>0.0</v>
@@ -7379,7 +7379,7 @@
         <v>776</v>
       </c>
       <c r="F192" t="n">
-        <v>90.0</v>
+        <v>96.0</v>
       </c>
       <c r="G192" t="n">
         <v>0.0</v>
@@ -7431,7 +7431,7 @@
         <v>776</v>
       </c>
       <c r="F194" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G194" t="n">
         <v>0.0</v>
@@ -7587,7 +7587,7 @@
         <v>776</v>
       </c>
       <c r="F200" t="n">
-        <v>278.0</v>
+        <v>284.0</v>
       </c>
       <c r="G200" t="n">
         <v>1.0</v>
@@ -7873,7 +7873,7 @@
         <v>776</v>
       </c>
       <c r="F211" t="n">
-        <v>74.0</v>
+        <v>78.0</v>
       </c>
       <c r="G211" t="n">
         <v>0.0</v>
@@ -8081,7 +8081,7 @@
         <v>776</v>
       </c>
       <c r="F219" t="n">
-        <v>194.0</v>
+        <v>198.0</v>
       </c>
       <c r="G219" t="n">
         <v>0.0</v>
@@ -8211,7 +8211,7 @@
         <v>776</v>
       </c>
       <c r="F224" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G224" t="n">
         <v>0.0</v>
@@ -8341,7 +8341,7 @@
         <v>775</v>
       </c>
       <c r="F229" t="n">
-        <v>289.0</v>
+        <v>292.0</v>
       </c>
       <c r="G229" t="n">
         <v>2.0</v>
@@ -8419,7 +8419,7 @@
         <v>775</v>
       </c>
       <c r="F232" t="n">
-        <v>158.0</v>
+        <v>165.0</v>
       </c>
       <c r="G232" t="n">
         <v>0.0</v>
@@ -8887,7 +8887,7 @@
         <v>775</v>
       </c>
       <c r="F250" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G250" t="n">
         <v>0.0</v>
@@ -8913,7 +8913,7 @@
         <v>775</v>
       </c>
       <c r="F251" t="n">
-        <v>160.0</v>
+        <v>164.0</v>
       </c>
       <c r="G251" t="n">
         <v>7.0</v>
@@ -9095,7 +9095,7 @@
         <v>775</v>
       </c>
       <c r="F258" t="n">
-        <v>961.0</v>
+        <v>964.0</v>
       </c>
       <c r="G258" t="n">
         <v>16.0</v>
@@ -9199,7 +9199,7 @@
         <v>775</v>
       </c>
       <c r="F262" t="n">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
       <c r="G262" t="n">
         <v>1.0</v>
@@ -9355,7 +9355,7 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="G268" t="n">
         <v>0.0</v>
@@ -9615,7 +9615,7 @@
         <v>775</v>
       </c>
       <c r="F278" t="n">
-        <v>174.0</v>
+        <v>176.0</v>
       </c>
       <c r="G278" t="n">
         <v>0.0</v>
@@ -9849,7 +9849,7 @@
         <v>775</v>
       </c>
       <c r="F287" t="n">
-        <v>235.0</v>
+        <v>238.0</v>
       </c>
       <c r="G287" t="n">
         <v>1.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>69.0</v>
+        <v>73.0</v>
       </c>
       <c r="G291" t="n">
         <v>2.0</v>
@@ -10057,7 +10057,7 @@
         <v>775</v>
       </c>
       <c r="F295" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G295" t="n">
         <v>0.0</v>
@@ -10421,7 +10421,7 @@
         <v>775</v>
       </c>
       <c r="F309" t="n">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
       <c r="G309" t="n">
         <v>4.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1094.0</v>
+        <v>1103.0</v>
       </c>
       <c r="G310" t="n">
         <v>6.0</v>
@@ -10785,7 +10785,7 @@
         <v>775</v>
       </c>
       <c r="F323" t="n">
-        <v>582.0</v>
+        <v>586.0</v>
       </c>
       <c r="G323" t="n">
         <v>2.0</v>
@@ -10811,7 +10811,7 @@
         <v>776</v>
       </c>
       <c r="F324" t="n">
-        <v>23.0</v>
+        <v>26.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11097,7 +11097,7 @@
         <v>775</v>
       </c>
       <c r="F335" t="n">
-        <v>148.0</v>
+        <v>154.0</v>
       </c>
       <c r="G335" t="n">
         <v>0.0</v>
@@ -11123,7 +11123,7 @@
         <v>775</v>
       </c>
       <c r="F336" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="G336" t="n">
         <v>0.0</v>
@@ -11305,10 +11305,10 @@
         <v>775</v>
       </c>
       <c r="F343" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
       <c r="G343" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H343" t="n">
         <v>23.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>556.0</v>
+        <v>560.0</v>
       </c>
       <c r="G363" t="n">
         <v>6.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12241,7 +12241,7 @@
         <v>775</v>
       </c>
       <c r="F379" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G379" t="n">
         <v>0.0</v>
@@ -12501,7 +12501,7 @@
         <v>775</v>
       </c>
       <c r="F389" t="n">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
       <c r="G389" t="n">
         <v>0.0</v>
@@ -13463,10 +13463,10 @@
         <v>776</v>
       </c>
       <c r="F426" t="n">
-        <v>242.0</v>
+        <v>252.0</v>
       </c>
       <c r="G426" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H426" t="n">
         <v>0.0</v>
@@ -13905,7 +13905,7 @@
         <v>775</v>
       </c>
       <c r="F443" t="n">
-        <v>87.0</v>
+        <v>93.0</v>
       </c>
       <c r="G443" t="n">
         <v>2.0</v>
@@ -14061,7 +14061,7 @@
         <v>776</v>
       </c>
       <c r="F449" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G449" t="n">
         <v>1.0</v>
@@ -14113,7 +14113,7 @@
         <v>775</v>
       </c>
       <c r="F451" t="n">
-        <v>793.0</v>
+        <v>795.0</v>
       </c>
       <c r="G451" t="n">
         <v>2.0</v>
@@ -14269,7 +14269,7 @@
         <v>775</v>
       </c>
       <c r="F457" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G457" t="n">
         <v>6.0</v>
@@ -14503,7 +14503,7 @@
         <v>775</v>
       </c>
       <c r="F466" t="n">
-        <v>221.0</v>
+        <v>229.0</v>
       </c>
       <c r="G466" t="n">
         <v>0.0</v>
@@ -14555,7 +14555,7 @@
         <v>775</v>
       </c>
       <c r="F468" t="n">
-        <v>548.0</v>
+        <v>555.0</v>
       </c>
       <c r="G468" t="n">
         <v>3.0</v>
@@ -14581,7 +14581,7 @@
         <v>775</v>
       </c>
       <c r="F469" t="n">
-        <v>200.0</v>
+        <v>203.0</v>
       </c>
       <c r="G469" t="n">
         <v>1.0</v>
@@ -14763,7 +14763,7 @@
         <v>775</v>
       </c>
       <c r="F476" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="G476" t="n">
         <v>0.0</v>
@@ -15049,7 +15049,7 @@
         <v>775</v>
       </c>
       <c r="F487" t="n">
-        <v>122.0</v>
+        <v>125.0</v>
       </c>
       <c r="G487" t="n">
         <v>5.0</v>
@@ -15101,7 +15101,7 @@
         <v>776</v>
       </c>
       <c r="F489" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G489" t="n">
         <v>0.0</v>
@@ -15205,7 +15205,7 @@
         <v>775</v>
       </c>
       <c r="F493" t="n">
-        <v>386.0</v>
+        <v>395.0</v>
       </c>
       <c r="G493" t="n">
         <v>2.0</v>
@@ -15309,7 +15309,7 @@
         <v>776</v>
       </c>
       <c r="F497" t="n">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
       <c r="G497" t="n">
         <v>0.0</v>
@@ -15569,7 +15569,7 @@
         <v>776</v>
       </c>
       <c r="F507" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="G507" t="n">
         <v>0.0</v>
@@ -15621,7 +15621,7 @@
         <v>775</v>
       </c>
       <c r="F509" t="n">
-        <v>198.0</v>
+        <v>201.0</v>
       </c>
       <c r="G509" t="n">
         <v>0.0</v>
@@ -15699,7 +15699,7 @@
         <v>775</v>
       </c>
       <c r="F512" t="n">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="G512" t="n">
         <v>0.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2514.0</v>
+        <v>2516.0</v>
       </c>
       <c r="G518" t="n">
         <v>45.0</v>
@@ -16297,7 +16297,7 @@
         <v>775</v>
       </c>
       <c r="F535" t="n">
-        <v>204.0</v>
+        <v>211.0</v>
       </c>
       <c r="G535" t="n">
         <v>0.0</v>
@@ -16791,7 +16791,7 @@
         <v>776</v>
       </c>
       <c r="F554" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="G554" t="n">
         <v>0.0</v>
@@ -17233,7 +17233,7 @@
         <v>776</v>
       </c>
       <c r="F571" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G571" t="n">
         <v>0.0</v>
@@ -17389,7 +17389,7 @@
         <v>775</v>
       </c>
       <c r="F577" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G577" t="n">
         <v>1.0</v>
@@ -17545,7 +17545,7 @@
         <v>776</v>
       </c>
       <c r="F583" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
       <c r="G583" t="n">
         <v>2.0</v>
@@ -17649,7 +17649,7 @@
         <v>775</v>
       </c>
       <c r="F587" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G587" t="n">
         <v>0.0</v>
@@ -17961,7 +17961,7 @@
         <v>775</v>
       </c>
       <c r="F599" t="n">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="G599" t="n">
         <v>0.0</v>
@@ -19053,7 +19053,7 @@
         <v>775</v>
       </c>
       <c r="F641" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G641" t="n">
         <v>2.0</v>
@@ -21627,10 +21627,10 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>244.0</v>
+        <v>246.0</v>
       </c>
       <c r="G740" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H740" t="n">
         <v>8.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -3635,7 +3635,7 @@
         <v>775</v>
       </c>
       <c r="F48" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -4337,7 +4337,7 @@
         <v>776</v>
       </c>
       <c r="F75" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>481.0</v>
+        <v>483.0</v>
       </c>
       <c r="G82" t="n">
         <v>1.0</v>
@@ -4571,7 +4571,7 @@
         <v>775</v>
       </c>
       <c r="F84" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -4753,7 +4753,7 @@
         <v>775</v>
       </c>
       <c r="F91" t="n">
-        <v>487.0</v>
+        <v>492.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -6573,7 +6573,7 @@
         <v>775</v>
       </c>
       <c r="F161" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6599,7 +6599,7 @@
         <v>776</v>
       </c>
       <c r="F162" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G162" t="n">
         <v>0.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7249,7 +7249,7 @@
         <v>776</v>
       </c>
       <c r="F187" t="n">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="G187" t="n">
         <v>0.0</v>
@@ -7301,7 +7301,7 @@
         <v>776</v>
       </c>
       <c r="F189" t="n">
-        <v>714.0</v>
+        <v>717.0</v>
       </c>
       <c r="G189" t="n">
         <v>0.0</v>
@@ -8289,7 +8289,7 @@
         <v>775</v>
       </c>
       <c r="F227" t="n">
-        <v>261.0</v>
+        <v>264.0</v>
       </c>
       <c r="G227" t="n">
         <v>1.0</v>
@@ -8575,7 +8575,7 @@
         <v>775</v>
       </c>
       <c r="F238" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G238" t="n">
         <v>1.0</v>
@@ -9329,7 +9329,7 @@
         <v>775</v>
       </c>
       <c r="F267" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G267" t="n">
         <v>0.0</v>
@@ -9979,7 +9979,7 @@
         <v>775</v>
       </c>
       <c r="F292" t="n">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
       <c r="G292" t="n">
         <v>0.0</v>
@@ -10811,7 +10811,7 @@
         <v>776</v>
       </c>
       <c r="F324" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -11311,7 +11311,7 @@
         <v>4.0</v>
       </c>
       <c r="H343" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="344">
@@ -11461,7 +11461,7 @@
         <v>775</v>
       </c>
       <c r="F349" t="n">
-        <v>127.0</v>
+        <v>129.0</v>
       </c>
       <c r="G349" t="n">
         <v>2.0</v>
@@ -12475,7 +12475,7 @@
         <v>776</v>
       </c>
       <c r="F388" t="n">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
       <c r="G388" t="n">
         <v>0.0</v>
@@ -15283,7 +15283,7 @@
         <v>776</v>
       </c>
       <c r="F496" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G496" t="n">
         <v>0.0</v>
@@ -15725,7 +15725,7 @@
         <v>776</v>
       </c>
       <c r="F513" t="n">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="G513" t="n">
         <v>0.0</v>
@@ -15959,7 +15959,7 @@
         <v>775</v>
       </c>
       <c r="F522" t="n">
-        <v>213.0</v>
+        <v>216.0</v>
       </c>
       <c r="G522" t="n">
         <v>0.0</v>
@@ -16531,7 +16531,7 @@
         <v>776</v>
       </c>
       <c r="F544" t="n">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="G544" t="n">
         <v>2.0</v>
@@ -16609,7 +16609,7 @@
         <v>776</v>
       </c>
       <c r="F547" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -16947,7 +16947,7 @@
         <v>775</v>
       </c>
       <c r="F560" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G560" t="n">
         <v>1.0</v>
@@ -16999,7 +16999,7 @@
         <v>775</v>
       </c>
       <c r="F562" t="n">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="G562" t="n">
         <v>1.0</v>
@@ -17519,7 +17519,7 @@
         <v>776</v>
       </c>
       <c r="F582" t="n">
-        <v>305.0</v>
+        <v>307.0</v>
       </c>
       <c r="G582" t="n">
         <v>0.0</v>
@@ -17857,7 +17857,7 @@
         <v>775</v>
       </c>
       <c r="F595" t="n">
-        <v>49.0</v>
+        <v>53.0</v>
       </c>
       <c r="G595" t="n">
         <v>0.0</v>
@@ -21604,7 +21604,7 @@
         <v>115.0</v>
       </c>
       <c r="G739" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H739" t="n">
         <v>0.0</v>
@@ -21656,7 +21656,7 @@
         <v>91.0</v>
       </c>
       <c r="G741" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H741" t="n">
         <v>0.0</v>
@@ -21682,7 +21682,7 @@
         <v>205.0</v>
       </c>
       <c r="G742" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H742" t="n">
         <v>0.0</v>
@@ -22670,7 +22670,7 @@
         <v>530.0</v>
       </c>
       <c r="G780" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H780" t="n">
         <v>3.0</v>
@@ -22722,7 +22722,7 @@
         <v>530.0</v>
       </c>
       <c r="G782" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H782" t="n">
         <v>3.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2673,7 +2673,7 @@
         <v>775</v>
       </c>
       <c r="F11" t="n">
-        <v>309.0</v>
+        <v>315.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -2907,7 +2907,7 @@
         <v>775</v>
       </c>
       <c r="F20" t="n">
-        <v>178.0</v>
+        <v>184.0</v>
       </c>
       <c r="G20" t="n">
         <v>1.0</v>
@@ -3011,7 +3011,7 @@
         <v>776</v>
       </c>
       <c r="F24" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3063,7 +3063,7 @@
         <v>776</v>
       </c>
       <c r="F26" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -3089,7 +3089,7 @@
         <v>775</v>
       </c>
       <c r="F27" t="n">
-        <v>126.0</v>
+        <v>131.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -3193,7 +3193,7 @@
         <v>775</v>
       </c>
       <c r="F31" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -3245,7 +3245,7 @@
         <v>775</v>
       </c>
       <c r="F33" t="n">
-        <v>122.0</v>
+        <v>125.0</v>
       </c>
       <c r="G33" t="n">
         <v>1.0</v>
@@ -3349,7 +3349,7 @@
         <v>775</v>
       </c>
       <c r="F37" t="n">
-        <v>228.0</v>
+        <v>229.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -3401,7 +3401,7 @@
         <v>775</v>
       </c>
       <c r="F39" t="n">
-        <v>266.0</v>
+        <v>268.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -3531,7 +3531,7 @@
         <v>775</v>
       </c>
       <c r="F44" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -3765,7 +3765,7 @@
         <v>775</v>
       </c>
       <c r="F53" t="n">
-        <v>221.0</v>
+        <v>230.0</v>
       </c>
       <c r="G53" t="n">
         <v>1.0</v>
@@ -3843,7 +3843,7 @@
         <v>775</v>
       </c>
       <c r="F56" t="n">
-        <v>62.0</v>
+        <v>70.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -3895,7 +3895,7 @@
         <v>775</v>
       </c>
       <c r="F58" t="n">
-        <v>283.0</v>
+        <v>286.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -3921,7 +3921,7 @@
         <v>775</v>
       </c>
       <c r="F59" t="n">
-        <v>292.0</v>
+        <v>295.0</v>
       </c>
       <c r="G59" t="n">
         <v>0.0</v>
@@ -3973,7 +3973,7 @@
         <v>775</v>
       </c>
       <c r="F61" t="n">
-        <v>123.0</v>
+        <v>129.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -4077,7 +4077,7 @@
         <v>776</v>
       </c>
       <c r="F65" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -4311,7 +4311,7 @@
         <v>775</v>
       </c>
       <c r="F74" t="n">
-        <v>171.0</v>
+        <v>178.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -4727,7 +4727,7 @@
         <v>775</v>
       </c>
       <c r="F90" t="n">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -4883,7 +4883,7 @@
         <v>775</v>
       </c>
       <c r="F96" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -4909,7 +4909,7 @@
         <v>775</v>
       </c>
       <c r="F97" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -5143,7 +5143,7 @@
         <v>775</v>
       </c>
       <c r="F106" t="n">
-        <v>111.0</v>
+        <v>113.0</v>
       </c>
       <c r="G106" t="n">
         <v>1.0</v>
@@ -5195,7 +5195,7 @@
         <v>776</v>
       </c>
       <c r="F108" t="n">
-        <v>18.0</v>
+        <v>23.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -5351,7 +5351,7 @@
         <v>775</v>
       </c>
       <c r="F114" t="n">
-        <v>246.0</v>
+        <v>248.0</v>
       </c>
       <c r="G114" t="n">
         <v>2.0</v>
@@ -5507,7 +5507,7 @@
         <v>775</v>
       </c>
       <c r="F120" t="n">
-        <v>421.0</v>
+        <v>422.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -5611,7 +5611,7 @@
         <v>775</v>
       </c>
       <c r="F124" t="n">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="G124" t="n">
         <v>1.0</v>
@@ -5637,7 +5637,7 @@
         <v>775</v>
       </c>
       <c r="F125" t="n">
-        <v>123.0</v>
+        <v>133.0</v>
       </c>
       <c r="G125" t="n">
         <v>0.0</v>
@@ -6157,7 +6157,7 @@
         <v>776</v>
       </c>
       <c r="F145" t="n">
-        <v>202.0</v>
+        <v>206.0</v>
       </c>
       <c r="G145" t="n">
         <v>1.0</v>
@@ -6521,7 +6521,7 @@
         <v>775</v>
       </c>
       <c r="F159" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="G159" t="n">
         <v>1.0</v>
@@ -6729,7 +6729,7 @@
         <v>776</v>
       </c>
       <c r="F167" t="n">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
       <c r="G167" t="n">
         <v>0.0</v>
@@ -7379,7 +7379,7 @@
         <v>776</v>
       </c>
       <c r="F192" t="n">
-        <v>96.0</v>
+        <v>98.0</v>
       </c>
       <c r="G192" t="n">
         <v>0.0</v>
@@ -7405,7 +7405,7 @@
         <v>776</v>
       </c>
       <c r="F193" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7613,7 +7613,7 @@
         <v>775</v>
       </c>
       <c r="F201" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="G201" t="n">
         <v>0.0</v>
@@ -7665,7 +7665,7 @@
         <v>776</v>
       </c>
       <c r="F203" t="n">
-        <v>1037.0</v>
+        <v>1038.0</v>
       </c>
       <c r="G203" t="n">
         <v>1.0</v>
@@ -7873,7 +7873,7 @@
         <v>776</v>
       </c>
       <c r="F211" t="n">
-        <v>78.0</v>
+        <v>80.0</v>
       </c>
       <c r="G211" t="n">
         <v>0.0</v>
@@ -7899,7 +7899,7 @@
         <v>775</v>
       </c>
       <c r="F212" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G212" t="n">
         <v>0.0</v>
@@ -7951,7 +7951,7 @@
         <v>775</v>
       </c>
       <c r="F214" t="n">
-        <v>33.0</v>
+        <v>37.0</v>
       </c>
       <c r="G214" t="n">
         <v>0.0</v>
@@ -8341,7 +8341,7 @@
         <v>775</v>
       </c>
       <c r="F229" t="n">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="G229" t="n">
         <v>2.0</v>
@@ -8523,7 +8523,7 @@
         <v>776</v>
       </c>
       <c r="F236" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G236" t="n">
         <v>0.0</v>
@@ -8887,7 +8887,7 @@
         <v>775</v>
       </c>
       <c r="F250" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G250" t="n">
         <v>0.0</v>
@@ -8913,7 +8913,7 @@
         <v>775</v>
       </c>
       <c r="F251" t="n">
-        <v>164.0</v>
+        <v>167.0</v>
       </c>
       <c r="G251" t="n">
         <v>7.0</v>
@@ -8991,7 +8991,7 @@
         <v>775</v>
       </c>
       <c r="F254" t="n">
-        <v>85.0</v>
+        <v>88.0</v>
       </c>
       <c r="G254" t="n">
         <v>1.0</v>
@@ -9095,7 +9095,7 @@
         <v>775</v>
       </c>
       <c r="F258" t="n">
-        <v>964.0</v>
+        <v>966.0</v>
       </c>
       <c r="G258" t="n">
         <v>16.0</v>
@@ -9121,7 +9121,7 @@
         <v>775</v>
       </c>
       <c r="F259" t="n">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="G259" t="n">
         <v>0.0</v>
@@ -9199,7 +9199,7 @@
         <v>775</v>
       </c>
       <c r="F262" t="n">
-        <v>42.0</v>
+        <v>46.0</v>
       </c>
       <c r="G262" t="n">
         <v>1.0</v>
@@ -9251,7 +9251,7 @@
         <v>775</v>
       </c>
       <c r="F264" t="n">
-        <v>278.0</v>
+        <v>279.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -9355,7 +9355,7 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>255.0</v>
+        <v>257.0</v>
       </c>
       <c r="G268" t="n">
         <v>0.0</v>
@@ -9491,7 +9491,7 @@
         <v>0.0</v>
       </c>
       <c r="H273" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="274">
@@ -9589,7 +9589,7 @@
         <v>775</v>
       </c>
       <c r="F277" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G277" t="n">
         <v>0.0</v>
@@ -9673,7 +9673,7 @@
         <v>0.0</v>
       </c>
       <c r="H280" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="281">
@@ -9693,7 +9693,7 @@
         <v>775</v>
       </c>
       <c r="F281" t="n">
-        <v>541.0</v>
+        <v>549.0</v>
       </c>
       <c r="G281" t="n">
         <v>0.0</v>
@@ -9719,7 +9719,7 @@
         <v>775</v>
       </c>
       <c r="F282" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -9849,7 +9849,7 @@
         <v>775</v>
       </c>
       <c r="F287" t="n">
-        <v>238.0</v>
+        <v>241.0</v>
       </c>
       <c r="G287" t="n">
         <v>1.0</v>
@@ -9875,7 +9875,7 @@
         <v>775</v>
       </c>
       <c r="F288" t="n">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G288" t="n">
         <v>0.0</v>
@@ -10005,7 +10005,7 @@
         <v>775</v>
       </c>
       <c r="F293" t="n">
-        <v>306.0</v>
+        <v>309.0</v>
       </c>
       <c r="G293" t="n">
         <v>2.0</v>
@@ -10031,7 +10031,7 @@
         <v>775</v>
       </c>
       <c r="F294" t="n">
-        <v>246.0</v>
+        <v>248.0</v>
       </c>
       <c r="G294" t="n">
         <v>0.0</v>
@@ -10421,7 +10421,7 @@
         <v>775</v>
       </c>
       <c r="F309" t="n">
-        <v>321.0</v>
+        <v>323.0</v>
       </c>
       <c r="G309" t="n">
         <v>4.0</v>
@@ -10447,7 +10447,7 @@
         <v>775</v>
       </c>
       <c r="F310" t="n">
-        <v>1103.0</v>
+        <v>1110.0</v>
       </c>
       <c r="G310" t="n">
         <v>6.0</v>
@@ -10785,7 +10785,7 @@
         <v>775</v>
       </c>
       <c r="F323" t="n">
-        <v>586.0</v>
+        <v>591.0</v>
       </c>
       <c r="G323" t="n">
         <v>2.0</v>
@@ -10811,7 +10811,7 @@
         <v>776</v>
       </c>
       <c r="F324" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G324" t="n">
         <v>0.0</v>
@@ -10889,7 +10889,7 @@
         <v>775</v>
       </c>
       <c r="F327" t="n">
-        <v>111.0</v>
+        <v>113.0</v>
       </c>
       <c r="G327" t="n">
         <v>1.0</v>
@@ -11045,7 +11045,7 @@
         <v>775</v>
       </c>
       <c r="F333" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G333" t="n">
         <v>1.0</v>
@@ -11123,7 +11123,7 @@
         <v>775</v>
       </c>
       <c r="F336" t="n">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="G336" t="n">
         <v>0.0</v>
@@ -11695,7 +11695,7 @@
         <v>775</v>
       </c>
       <c r="F358" t="n">
-        <v>133.0</v>
+        <v>135.0</v>
       </c>
       <c r="G358" t="n">
         <v>0.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>175.0</v>
+        <v>177.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11825,7 +11825,7 @@
         <v>775</v>
       </c>
       <c r="F363" t="n">
-        <v>560.0</v>
+        <v>564.0</v>
       </c>
       <c r="G363" t="n">
         <v>6.0</v>
@@ -12111,7 +12111,7 @@
         <v>776</v>
       </c>
       <c r="F374" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="G374" t="n">
         <v>0.0</v>
@@ -12527,7 +12527,7 @@
         <v>775</v>
       </c>
       <c r="F390" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="G390" t="n">
         <v>2.0</v>
@@ -12631,7 +12631,7 @@
         <v>776</v>
       </c>
       <c r="F394" t="n">
-        <v>18.0</v>
+        <v>24.0</v>
       </c>
       <c r="G394" t="n">
         <v>0.0</v>
@@ -12917,7 +12917,7 @@
         <v>777</v>
       </c>
       <c r="F405" t="n">
-        <v>484.0</v>
+        <v>492.0</v>
       </c>
       <c r="G405" t="n">
         <v>1.0</v>
@@ -12943,7 +12943,7 @@
         <v>776</v>
       </c>
       <c r="F406" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G406" t="n">
         <v>1.0</v>
@@ -13073,7 +13073,7 @@
         <v>775</v>
       </c>
       <c r="F411" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G411" t="n">
         <v>0.0</v>
@@ -13255,7 +13255,7 @@
         <v>775</v>
       </c>
       <c r="F418" t="n">
-        <v>191.0</v>
+        <v>192.0</v>
       </c>
       <c r="G418" t="n">
         <v>0.0</v>
@@ -13411,7 +13411,7 @@
         <v>777</v>
       </c>
       <c r="F424" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
       <c r="G424" t="n">
         <v>0.0</v>
@@ -13463,7 +13463,7 @@
         <v>776</v>
       </c>
       <c r="F426" t="n">
-        <v>252.0</v>
+        <v>254.0</v>
       </c>
       <c r="G426" t="n">
         <v>0.0</v>
@@ -13619,7 +13619,7 @@
         <v>775</v>
       </c>
       <c r="F432" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G432" t="n">
         <v>0.0</v>
@@ -13671,7 +13671,7 @@
         <v>775</v>
       </c>
       <c r="F434" t="n">
-        <v>103.0</v>
+        <v>108.0</v>
       </c>
       <c r="G434" t="n">
         <v>0.0</v>
@@ -13983,7 +13983,7 @@
         <v>775</v>
       </c>
       <c r="F446" t="n">
-        <v>619.0</v>
+        <v>626.0</v>
       </c>
       <c r="G446" t="n">
         <v>3.0</v>
@@ -14061,7 +14061,7 @@
         <v>776</v>
       </c>
       <c r="F449" t="n">
-        <v>127.0</v>
+        <v>130.0</v>
       </c>
       <c r="G449" t="n">
         <v>1.0</v>
@@ -14113,7 +14113,7 @@
         <v>775</v>
       </c>
       <c r="F451" t="n">
-        <v>795.0</v>
+        <v>800.0</v>
       </c>
       <c r="G451" t="n">
         <v>2.0</v>
@@ -14217,7 +14217,7 @@
         <v>775</v>
       </c>
       <c r="F455" t="n">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
       <c r="G455" t="n">
         <v>0.0</v>
@@ -14243,7 +14243,7 @@
         <v>775</v>
       </c>
       <c r="F456" t="n">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
       <c r="G456" t="n">
         <v>0.0</v>
@@ -14321,7 +14321,7 @@
         <v>776</v>
       </c>
       <c r="F459" t="n">
-        <v>383.0</v>
+        <v>386.0</v>
       </c>
       <c r="G459" t="n">
         <v>0.0</v>
@@ -14477,7 +14477,7 @@
         <v>775</v>
       </c>
       <c r="F465" t="n">
-        <v>59.0</v>
+        <v>63.0</v>
       </c>
       <c r="G465" t="n">
         <v>0.0</v>
@@ -14503,7 +14503,7 @@
         <v>775</v>
       </c>
       <c r="F466" t="n">
-        <v>229.0</v>
+        <v>231.0</v>
       </c>
       <c r="G466" t="n">
         <v>0.0</v>
@@ -14529,7 +14529,7 @@
         <v>775</v>
       </c>
       <c r="F467" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="G467" t="n">
         <v>0.0</v>
@@ -14555,7 +14555,7 @@
         <v>775</v>
       </c>
       <c r="F468" t="n">
-        <v>555.0</v>
+        <v>564.0</v>
       </c>
       <c r="G468" t="n">
         <v>3.0</v>
@@ -14685,7 +14685,7 @@
         <v>775</v>
       </c>
       <c r="F473" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G473" t="n">
         <v>0.0</v>
@@ -14789,7 +14789,7 @@
         <v>776</v>
       </c>
       <c r="F477" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G477" t="n">
         <v>0.0</v>
@@ -14945,7 +14945,7 @@
         <v>775</v>
       </c>
       <c r="F483" t="n">
-        <v>536.0</v>
+        <v>539.0</v>
       </c>
       <c r="G483" t="n">
         <v>0.0</v>
@@ -15003,7 +15003,7 @@
         <v>11.0</v>
       </c>
       <c r="H485" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="486">
@@ -15595,7 +15595,7 @@
         <v>776</v>
       </c>
       <c r="F508" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G508" t="n">
         <v>0.0</v>
@@ -15621,7 +15621,7 @@
         <v>775</v>
       </c>
       <c r="F509" t="n">
-        <v>201.0</v>
+        <v>206.0</v>
       </c>
       <c r="G509" t="n">
         <v>0.0</v>
@@ -16037,7 +16037,7 @@
         <v>775</v>
       </c>
       <c r="F525" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G525" t="n">
         <v>0.0</v>
@@ -16141,7 +16141,7 @@
         <v>775</v>
       </c>
       <c r="F529" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G529" t="n">
         <v>0.0</v>
@@ -16479,7 +16479,7 @@
         <v>775</v>
       </c>
       <c r="F542" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G542" t="n">
         <v>0.0</v>
@@ -16791,7 +16791,7 @@
         <v>776</v>
       </c>
       <c r="F554" t="n">
-        <v>176.0</v>
+        <v>178.0</v>
       </c>
       <c r="G554" t="n">
         <v>0.0</v>
@@ -16921,7 +16921,7 @@
         <v>775</v>
       </c>
       <c r="F559" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G559" t="n">
         <v>0.0</v>
@@ -17025,7 +17025,7 @@
         <v>776</v>
       </c>
       <c r="F563" t="n">
-        <v>360.0</v>
+        <v>361.0</v>
       </c>
       <c r="G563" t="n">
         <v>0.0</v>
@@ -17233,7 +17233,7 @@
         <v>776</v>
       </c>
       <c r="F571" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G571" t="n">
         <v>0.0</v>
@@ -17311,7 +17311,7 @@
         <v>775</v>
       </c>
       <c r="F574" t="n">
-        <v>291.0</v>
+        <v>296.0</v>
       </c>
       <c r="G574" t="n">
         <v>1.0</v>
@@ -17779,7 +17779,7 @@
         <v>775</v>
       </c>
       <c r="F592" t="n">
-        <v>77.0</v>
+        <v>81.0</v>
       </c>
       <c r="G592" t="n">
         <v>0.0</v>
@@ -18013,7 +18013,7 @@
         <v>775</v>
       </c>
       <c r="F601" t="n">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="G601" t="n">
         <v>0.0</v>
@@ -18065,7 +18065,7 @@
         <v>775</v>
       </c>
       <c r="F603" t="n">
-        <v>178.0</v>
+        <v>183.0</v>
       </c>
       <c r="G603" t="n">
         <v>0.0</v>
@@ -18377,7 +18377,7 @@
         <v>775</v>
       </c>
       <c r="F615" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G615" t="n">
         <v>1.0</v>
@@ -18975,7 +18975,7 @@
         <v>775</v>
       </c>
       <c r="F638" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G638" t="n">
         <v>0.0</v>
@@ -19105,7 +19105,7 @@
         <v>775</v>
       </c>
       <c r="F643" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="G643" t="n">
         <v>2.0</v>
@@ -19625,7 +19625,7 @@
         <v>775</v>
       </c>
       <c r="F663" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G663" t="n">
         <v>0.0</v>
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>231.0</v>
+        <v>238.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20405,7 +20405,7 @@
         <v>777</v>
       </c>
       <c r="F693" t="n">
-        <v>457.0</v>
+        <v>460.0</v>
       </c>
       <c r="G693" t="n">
         <v>0.0</v>
@@ -20561,7 +20561,7 @@
         <v>776</v>
       </c>
       <c r="F699" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G699" t="n">
         <v>0.0</v>
@@ -20587,7 +20587,7 @@
         <v>777</v>
       </c>
       <c r="F700" t="n">
-        <v>215.0</v>
+        <v>225.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -20613,7 +20613,7 @@
         <v>776</v>
       </c>
       <c r="F701" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G701" t="n">
         <v>0.0</v>
@@ -20639,7 +20639,7 @@
         <v>776</v>
       </c>
       <c r="F702" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G702" t="n">
         <v>0.0</v>
@@ -21211,7 +21211,7 @@
         <v>776</v>
       </c>
       <c r="F724" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="G724" t="n">
         <v>0.0</v>
@@ -21237,7 +21237,7 @@
         <v>776</v>
       </c>
       <c r="F725" t="n">
-        <v>15.0</v>
+        <v>28.0</v>
       </c>
       <c r="G725" t="n">
         <v>0.0</v>
@@ -21289,7 +21289,7 @@
         <v>776</v>
       </c>
       <c r="F727" t="n">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
       <c r="G727" t="n">
         <v>0.0</v>
@@ -21653,10 +21653,10 @@
         <v>778</v>
       </c>
       <c r="F741" t="n">
-        <v>91.0</v>
+        <v>94.0</v>
       </c>
       <c r="G741" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H741" t="n">
         <v>0.0</v>
@@ -22459,7 +22459,7 @@
         <v>778</v>
       </c>
       <c r="F772" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G772" t="n">
         <v>3.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>530.0</v>
+        <v>532.0</v>
       </c>
       <c r="G780" t="n">
         <v>5.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>530.0</v>
+        <v>532.0</v>
       </c>
       <c r="G782" t="n">
         <v>5.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2439,7 +2439,7 @@
         <v>775</v>
       </c>
       <c r="F2" t="n">
-        <v>656.0</v>
+        <v>660.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2465,7 +2465,7 @@
         <v>775</v>
       </c>
       <c r="F3" t="n">
-        <v>59.0</v>
+        <v>61.0</v>
       </c>
       <c r="G3" t="n">
         <v>4.0</v>
@@ -2751,7 +2751,7 @@
         <v>775</v>
       </c>
       <c r="F14" t="n">
-        <v>504.0</v>
+        <v>514.0</v>
       </c>
       <c r="G14" t="n">
         <v>9.0</v>
@@ -2803,7 +2803,7 @@
         <v>775</v>
       </c>
       <c r="F16" t="n">
-        <v>431.0</v>
+        <v>433.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2959,7 +2959,7 @@
         <v>776</v>
       </c>
       <c r="F22" t="n">
-        <v>411.0</v>
+        <v>415.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3323,7 +3323,7 @@
         <v>775</v>
       </c>
       <c r="F36" t="n">
-        <v>563.0</v>
+        <v>567.0</v>
       </c>
       <c r="G36" t="n">
         <v>4.0</v>
@@ -3401,7 +3401,7 @@
         <v>775</v>
       </c>
       <c r="F39" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -3453,7 +3453,7 @@
         <v>775</v>
       </c>
       <c r="F41" t="n">
-        <v>352.0</v>
+        <v>353.0</v>
       </c>
       <c r="G41" t="n">
         <v>2.0</v>
@@ -3557,7 +3557,7 @@
         <v>775</v>
       </c>
       <c r="F45" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -3791,7 +3791,7 @@
         <v>775</v>
       </c>
       <c r="F54" t="n">
-        <v>142.0</v>
+        <v>145.0</v>
       </c>
       <c r="G54" t="n">
         <v>1.0</v>
@@ -4259,7 +4259,7 @@
         <v>775</v>
       </c>
       <c r="F72" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -4441,7 +4441,7 @@
         <v>775</v>
       </c>
       <c r="F79" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="G79" t="n">
         <v>15.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>483.0</v>
+        <v>485.0</v>
       </c>
       <c r="G82" t="n">
         <v>1.0</v>
@@ -4987,7 +4987,7 @@
         <v>776</v>
       </c>
       <c r="F100" t="n">
-        <v>464.0</v>
+        <v>473.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -5091,7 +5091,7 @@
         <v>775</v>
       </c>
       <c r="F104" t="n">
-        <v>556.0</v>
+        <v>557.0</v>
       </c>
       <c r="G104" t="n">
         <v>4.0</v>
@@ -5221,7 +5221,7 @@
         <v>776</v>
       </c>
       <c r="F109" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -5559,7 +5559,7 @@
         <v>775</v>
       </c>
       <c r="F122" t="n">
-        <v>485.0</v>
+        <v>488.0</v>
       </c>
       <c r="G122" t="n">
         <v>1.0</v>
@@ -5897,7 +5897,7 @@
         <v>775</v>
       </c>
       <c r="F135" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="G135" t="n">
         <v>0.0</v>
@@ -6027,7 +6027,7 @@
         <v>775</v>
       </c>
       <c r="F140" t="n">
-        <v>701.0</v>
+        <v>704.0</v>
       </c>
       <c r="G140" t="n">
         <v>2.0</v>
@@ -6131,7 +6131,7 @@
         <v>775</v>
       </c>
       <c r="F144" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="G144" t="n">
         <v>0.0</v>
@@ -6235,7 +6235,7 @@
         <v>775</v>
       </c>
       <c r="F148" t="n">
-        <v>49.0</v>
+        <v>52.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -6781,7 +6781,7 @@
         <v>776</v>
       </c>
       <c r="F169" t="n">
-        <v>203.0</v>
+        <v>204.0</v>
       </c>
       <c r="G169" t="n">
         <v>0.0</v>
@@ -6885,7 +6885,7 @@
         <v>775</v>
       </c>
       <c r="F173" t="n">
-        <v>247.0</v>
+        <v>254.0</v>
       </c>
       <c r="G173" t="n">
         <v>6.0</v>
@@ -7015,7 +7015,7 @@
         <v>775</v>
       </c>
       <c r="F178" t="n">
-        <v>286.0</v>
+        <v>288.0</v>
       </c>
       <c r="G178" t="n">
         <v>0.0</v>
@@ -7041,7 +7041,7 @@
         <v>776</v>
       </c>
       <c r="F179" t="n">
-        <v>551.0</v>
+        <v>554.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7151,7 +7151,7 @@
         <v>1.0</v>
       </c>
       <c r="H183" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="184">
@@ -7847,7 +7847,7 @@
         <v>776</v>
       </c>
       <c r="F210" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G210" t="n">
         <v>0.0</v>
@@ -7977,7 +7977,7 @@
         <v>776</v>
       </c>
       <c r="F215" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G215" t="n">
         <v>0.0</v>
@@ -8835,7 +8835,7 @@
         <v>775</v>
       </c>
       <c r="F248" t="n">
-        <v>165.0</v>
+        <v>169.0</v>
       </c>
       <c r="G248" t="n">
         <v>4.0</v>
@@ -8861,7 +8861,7 @@
         <v>775</v>
       </c>
       <c r="F249" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G249" t="n">
         <v>1.0</v>
@@ -9069,7 +9069,7 @@
         <v>775</v>
       </c>
       <c r="F257" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G257" t="n">
         <v>3.0</v>
@@ -9173,7 +9173,7 @@
         <v>775</v>
       </c>
       <c r="F261" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G261" t="n">
         <v>1.0</v>
@@ -9485,7 +9485,7 @@
         <v>775</v>
       </c>
       <c r="F273" t="n">
-        <v>37.0</v>
+        <v>43.0</v>
       </c>
       <c r="G273" t="n">
         <v>0.0</v>
@@ -9901,7 +9901,7 @@
         <v>775</v>
       </c>
       <c r="F289" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G289" t="n">
         <v>2.0</v>
@@ -9953,7 +9953,7 @@
         <v>775</v>
       </c>
       <c r="F291" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G291" t="n">
         <v>2.0</v>
@@ -10291,7 +10291,7 @@
         <v>775</v>
       </c>
       <c r="F304" t="n">
-        <v>418.0</v>
+        <v>424.0</v>
       </c>
       <c r="G304" t="n">
         <v>1.0</v>
@@ -10577,7 +10577,7 @@
         <v>775</v>
       </c>
       <c r="F315" t="n">
-        <v>547.0</v>
+        <v>554.0</v>
       </c>
       <c r="G315" t="n">
         <v>6.0</v>
@@ -10889,7 +10889,7 @@
         <v>775</v>
       </c>
       <c r="F327" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G327" t="n">
         <v>1.0</v>
@@ -10915,7 +10915,7 @@
         <v>776</v>
       </c>
       <c r="F328" t="n">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="G328" t="n">
         <v>0.0</v>
@@ -11227,7 +11227,7 @@
         <v>775</v>
       </c>
       <c r="F340" t="n">
-        <v>436.0</v>
+        <v>438.0</v>
       </c>
       <c r="G340" t="n">
         <v>1.0</v>
@@ -11253,7 +11253,7 @@
         <v>775</v>
       </c>
       <c r="F341" t="n">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
       <c r="G341" t="n">
         <v>0.0</v>
@@ -11695,7 +11695,7 @@
         <v>775</v>
       </c>
       <c r="F358" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G358" t="n">
         <v>0.0</v>
@@ -11773,7 +11773,7 @@
         <v>776</v>
       </c>
       <c r="F361" t="n">
-        <v>177.0</v>
+        <v>179.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -12137,7 +12137,7 @@
         <v>776</v>
       </c>
       <c r="F375" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G375" t="n">
         <v>0.0</v>
@@ -12371,7 +12371,7 @@
         <v>775</v>
       </c>
       <c r="F384" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G384" t="n">
         <v>1.0</v>
@@ -12553,7 +12553,7 @@
         <v>775</v>
       </c>
       <c r="F391" t="n">
-        <v>270.0</v>
+        <v>271.0</v>
       </c>
       <c r="G391" t="n">
         <v>0.0</v>
@@ -13154,7 +13154,7 @@
         <v>333.0</v>
       </c>
       <c r="G414" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="H414" t="n">
         <v>28.0</v>
@@ -13463,7 +13463,7 @@
         <v>776</v>
       </c>
       <c r="F426" t="n">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="G426" t="n">
         <v>0.0</v>
@@ -14217,7 +14217,7 @@
         <v>775</v>
       </c>
       <c r="F455" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G455" t="n">
         <v>0.0</v>
@@ -14633,7 +14633,7 @@
         <v>775</v>
       </c>
       <c r="F471" t="n">
-        <v>196.0</v>
+        <v>202.0</v>
       </c>
       <c r="G471" t="n">
         <v>7.0</v>
@@ -14997,7 +14997,7 @@
         <v>775</v>
       </c>
       <c r="F485" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="G485" t="n">
         <v>11.0</v>
@@ -15335,7 +15335,7 @@
         <v>775</v>
       </c>
       <c r="F498" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G498" t="n">
         <v>0.0</v>
@@ -15439,7 +15439,7 @@
         <v>775</v>
       </c>
       <c r="F502" t="n">
-        <v>672.0</v>
+        <v>686.0</v>
       </c>
       <c r="G502" t="n">
         <v>2.0</v>
@@ -15855,7 +15855,7 @@
         <v>775</v>
       </c>
       <c r="F518" t="n">
-        <v>2516.0</v>
+        <v>2522.0</v>
       </c>
       <c r="G518" t="n">
         <v>45.0</v>
@@ -16869,7 +16869,7 @@
         <v>775</v>
       </c>
       <c r="F557" t="n">
-        <v>110.0</v>
+        <v>112.0</v>
       </c>
       <c r="G557" t="n">
         <v>2.0</v>
@@ -17701,7 +17701,7 @@
         <v>775</v>
       </c>
       <c r="F589" t="n">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
       <c r="G589" t="n">
         <v>0.0</v>
@@ -18143,7 +18143,7 @@
         <v>775</v>
       </c>
       <c r="F606" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G606" t="n">
         <v>1.0</v>
@@ -18195,7 +18195,7 @@
         <v>776</v>
       </c>
       <c r="F608" t="n">
-        <v>420.0</v>
+        <v>423.0</v>
       </c>
       <c r="G608" t="n">
         <v>0.0</v>
@@ -18793,7 +18793,7 @@
         <v>775</v>
       </c>
       <c r="F631" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -18819,7 +18819,7 @@
         <v>775</v>
       </c>
       <c r="F632" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="G632" t="n">
         <v>0.0</v>
@@ -19183,7 +19183,7 @@
         <v>775</v>
       </c>
       <c r="F646" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G646" t="n">
         <v>0.0</v>
@@ -19443,7 +19443,7 @@
         <v>776</v>
       </c>
       <c r="F656" t="n">
-        <v>150.0</v>
+        <v>153.0</v>
       </c>
       <c r="G656" t="n">
         <v>0.0</v>
@@ -19651,7 +19651,7 @@
         <v>775</v>
       </c>
       <c r="F664" t="n">
-        <v>115.0</v>
+        <v>122.0</v>
       </c>
       <c r="G664" t="n">
         <v>0.0</v>
@@ -19729,7 +19729,7 @@
         <v>775</v>
       </c>
       <c r="F667" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G667" t="n">
         <v>1.0</v>
@@ -19755,7 +19755,7 @@
         <v>775</v>
       </c>
       <c r="F668" t="n">
-        <v>105.0</v>
+        <v>109.0</v>
       </c>
       <c r="G668" t="n">
         <v>5.0</v>
@@ -19885,7 +19885,7 @@
         <v>775</v>
       </c>
       <c r="F673" t="n">
-        <v>158.0</v>
+        <v>164.0</v>
       </c>
       <c r="G673" t="n">
         <v>1.0</v>
@@ -19911,7 +19911,7 @@
         <v>775</v>
       </c>
       <c r="F674" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G674" t="n">
         <v>0.0</v>
@@ -19937,7 +19937,7 @@
         <v>776</v>
       </c>
       <c r="F675" t="n">
-        <v>105.0</v>
+        <v>109.0</v>
       </c>
       <c r="G675" t="n">
         <v>0.0</v>
@@ -19963,7 +19963,7 @@
         <v>776</v>
       </c>
       <c r="F676" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="G676" t="n">
         <v>0.0</v>
@@ -20041,7 +20041,7 @@
         <v>776</v>
       </c>
       <c r="F679" t="n">
-        <v>88.0</v>
+        <v>91.0</v>
       </c>
       <c r="G679" t="n">
         <v>0.0</v>
@@ -20067,7 +20067,7 @@
         <v>776</v>
       </c>
       <c r="F680" t="n">
-        <v>119.0</v>
+        <v>121.0</v>
       </c>
       <c r="G680" t="n">
         <v>0.0</v>
@@ -20093,7 +20093,7 @@
         <v>776</v>
       </c>
       <c r="F681" t="n">
-        <v>52.0</v>
+        <v>57.0</v>
       </c>
       <c r="G681" t="n">
         <v>0.0</v>
@@ -20119,7 +20119,7 @@
         <v>776</v>
       </c>
       <c r="F682" t="n">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="G682" t="n">
         <v>0.0</v>
@@ -20145,7 +20145,7 @@
         <v>776</v>
       </c>
       <c r="F683" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G683" t="n">
         <v>0.0</v>
@@ -20171,7 +20171,7 @@
         <v>776</v>
       </c>
       <c r="F684" t="n">
-        <v>101.0</v>
+        <v>103.0</v>
       </c>
       <c r="G684" t="n">
         <v>0.0</v>
@@ -20197,7 +20197,7 @@
         <v>775</v>
       </c>
       <c r="F685" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G685" t="n">
         <v>1.0</v>
@@ -20249,7 +20249,7 @@
         <v>775</v>
       </c>
       <c r="F687" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G687" t="n">
         <v>0.0</v>
@@ -20301,7 +20301,7 @@
         <v>776</v>
       </c>
       <c r="F689" t="n">
-        <v>106.0</v>
+        <v>111.0</v>
       </c>
       <c r="G689" t="n">
         <v>0.0</v>
@@ -20327,7 +20327,7 @@
         <v>775</v>
       </c>
       <c r="F690" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G690" t="n">
         <v>0.0</v>
@@ -20379,7 +20379,7 @@
         <v>776</v>
       </c>
       <c r="F692" t="n">
-        <v>159.0</v>
+        <v>168.0</v>
       </c>
       <c r="G692" t="n">
         <v>0.0</v>
@@ -20457,7 +20457,7 @@
         <v>776</v>
       </c>
       <c r="F695" t="n">
-        <v>192.0</v>
+        <v>210.0</v>
       </c>
       <c r="G695" t="n">
         <v>0.0</v>
@@ -20613,7 +20613,7 @@
         <v>776</v>
       </c>
       <c r="F701" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G701" t="n">
         <v>0.0</v>
@@ -20743,7 +20743,7 @@
         <v>776</v>
       </c>
       <c r="F706" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20795,7 +20795,7 @@
         <v>776</v>
       </c>
       <c r="F708" t="n">
-        <v>103.0</v>
+        <v>106.0</v>
       </c>
       <c r="G708" t="n">
         <v>0.0</v>
@@ -21055,7 +21055,7 @@
         <v>777</v>
       </c>
       <c r="F718" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G718" t="n">
         <v>0.0</v>
@@ -21081,7 +21081,7 @@
         <v>776</v>
       </c>
       <c r="F719" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G719" t="n">
         <v>0.0</v>
@@ -21237,7 +21237,7 @@
         <v>776</v>
       </c>
       <c r="F725" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="G725" t="n">
         <v>0.0</v>
@@ -21601,10 +21601,10 @@
         <v>778</v>
       </c>
       <c r="F739" t="n">
-        <v>115.0</v>
+        <v>117.0</v>
       </c>
       <c r="G739" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H739" t="n">
         <v>0.0</v>
@@ -21627,7 +21627,7 @@
         <v>778</v>
       </c>
       <c r="F740" t="n">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="G740" t="n">
         <v>0.0</v>
@@ -21653,10 +21653,10 @@
         <v>778</v>
       </c>
       <c r="F741" t="n">
-        <v>94.0</v>
+        <v>98.0</v>
       </c>
       <c r="G741" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H741" t="n">
         <v>0.0</v>
@@ -21679,10 +21679,10 @@
         <v>778</v>
       </c>
       <c r="F742" t="n">
-        <v>205.0</v>
+        <v>208.0</v>
       </c>
       <c r="G742" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H742" t="n">
         <v>0.0</v>
@@ -21835,7 +21835,7 @@
         <v>775</v>
       </c>
       <c r="F748" t="n">
-        <v>341.0</v>
+        <v>344.0</v>
       </c>
       <c r="G748" t="n">
         <v>2.0</v>
@@ -21861,7 +21861,7 @@
         <v>775</v>
       </c>
       <c r="F749" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
       <c r="G749" t="n">
         <v>1.0</v>
@@ -21913,7 +21913,7 @@
         <v>776</v>
       </c>
       <c r="F751" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="G751" t="n">
         <v>0.0</v>
@@ -21939,7 +21939,7 @@
         <v>775</v>
       </c>
       <c r="F752" t="n">
-        <v>77.0</v>
+        <v>87.0</v>
       </c>
       <c r="G752" t="n">
         <v>0.0</v>
@@ -21991,7 +21991,7 @@
         <v>775</v>
       </c>
       <c r="F754" t="n">
-        <v>418.0</v>
+        <v>420.0</v>
       </c>
       <c r="G754" t="n">
         <v>0.0</v>
@@ -22043,7 +22043,7 @@
         <v>775</v>
       </c>
       <c r="F756" t="n">
-        <v>227.0</v>
+        <v>229.0</v>
       </c>
       <c r="G756" t="n">
         <v>2.0</v>
@@ -22121,7 +22121,7 @@
         <v>776</v>
       </c>
       <c r="F759" t="n">
-        <v>436.0</v>
+        <v>439.0</v>
       </c>
       <c r="G759" t="n">
         <v>1.0</v>
@@ -22147,7 +22147,7 @@
         <v>775</v>
       </c>
       <c r="F760" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
       <c r="G760" t="n">
         <v>0.0</v>
@@ -22277,7 +22277,7 @@
         <v>776</v>
       </c>
       <c r="F765" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G765" t="n">
         <v>0.0</v>
@@ -22407,7 +22407,7 @@
         <v>778</v>
       </c>
       <c r="F770" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G770" t="n">
         <v>0.0</v>
@@ -22459,10 +22459,10 @@
         <v>778</v>
       </c>
       <c r="F772" t="n">
-        <v>61.0</v>
+        <v>64.0</v>
       </c>
       <c r="G772" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H772" t="n">
         <v>0.0</v>
@@ -22667,10 +22667,10 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>532.0</v>
+        <v>535.0</v>
       </c>
       <c r="G780" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="H780" t="n">
         <v>3.0</v>
@@ -22719,10 +22719,10 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>532.0</v>
+        <v>535.0</v>
       </c>
       <c r="G782" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="H782" t="n">
         <v>3.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2907,7 +2907,7 @@
         <v>775</v>
       </c>
       <c r="F20" t="n">
-        <v>184.0</v>
+        <v>186.0</v>
       </c>
       <c r="G20" t="n">
         <v>1.0</v>
@@ -3167,7 +3167,7 @@
         <v>775</v>
       </c>
       <c r="F30" t="n">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -3297,7 +3297,7 @@
         <v>775</v>
       </c>
       <c r="F35" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="G35" t="n">
         <v>2.0</v>
@@ -3427,7 +3427,7 @@
         <v>776</v>
       </c>
       <c r="F40" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -4363,7 +4363,7 @@
         <v>776</v>
       </c>
       <c r="F76" t="n">
-        <v>361.0</v>
+        <v>362.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -4519,7 +4519,7 @@
         <v>776</v>
       </c>
       <c r="F82" t="n">
-        <v>485.0</v>
+        <v>486.0</v>
       </c>
       <c r="G82" t="n">
         <v>1.0</v>
@@ -5637,7 +5637,7 @@
         <v>775</v>
       </c>
       <c r="F125" t="n">
-        <v>133.0</v>
+        <v>136.0</v>
       </c>
       <c r="G125" t="n">
         <v>0.0</v>
@@ -6989,7 +6989,7 @@
         <v>776</v>
       </c>
       <c r="F177" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G177" t="n">
         <v>0.0</v>
@@ -7795,7 +7795,7 @@
         <v>775</v>
       </c>
       <c r="F208" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G208" t="n">
         <v>0.0</v>
@@ -9355,7 +9355,7 @@
         <v>775</v>
       </c>
       <c r="F268" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G268" t="n">
         <v>0.0</v>
@@ -9615,7 +9615,7 @@
         <v>775</v>
       </c>
       <c r="F278" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="G278" t="n">
         <v>0.0</v>
@@ -10031,7 +10031,7 @@
         <v>775</v>
       </c>
       <c r="F294" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="G294" t="n">
         <v>0.0</v>
@@ -12137,7 +12137,7 @@
         <v>776</v>
       </c>
       <c r="F375" t="n">
-        <v>189.0</v>
+        <v>191.0</v>
       </c>
       <c r="G375" t="n">
         <v>0.0</v>
@@ -12189,7 +12189,7 @@
         <v>775</v>
       </c>
       <c r="F377" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G377" t="n">
         <v>0.0</v>
@@ -12501,7 +12501,7 @@
         <v>775</v>
       </c>
       <c r="F389" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G389" t="n">
         <v>0.0</v>
@@ -14165,7 +14165,7 @@
         <v>775</v>
       </c>
       <c r="F453" t="n">
-        <v>139.0</v>
+        <v>141.0</v>
       </c>
       <c r="G453" t="n">
         <v>0.0</v>
@@ -14217,7 +14217,7 @@
         <v>775</v>
       </c>
       <c r="F455" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G455" t="n">
         <v>0.0</v>
@@ -15465,7 +15465,7 @@
         <v>775</v>
       </c>
       <c r="F503" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="G503" t="n">
         <v>0.0</v>
@@ -16063,7 +16063,7 @@
         <v>775</v>
       </c>
       <c r="F526" t="n">
-        <v>221.0</v>
+        <v>225.0</v>
       </c>
       <c r="G526" t="n">
         <v>0.0</v>
@@ -16297,7 +16297,7 @@
         <v>775</v>
       </c>
       <c r="F535" t="n">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
       <c r="G535" t="n">
         <v>0.0</v>
@@ -16895,7 +16895,7 @@
         <v>775</v>
       </c>
       <c r="F558" t="n">
-        <v>135.0</v>
+        <v>137.0</v>
       </c>
       <c r="G558" t="n">
         <v>1.0</v>
@@ -17415,7 +17415,7 @@
         <v>775</v>
       </c>
       <c r="F578" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G578" t="n">
         <v>0.0</v>
@@ -18221,7 +18221,7 @@
         <v>776</v>
       </c>
       <c r="F609" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G609" t="n">
         <v>0.0</v>
@@ -18871,7 +18871,7 @@
         <v>775</v>
       </c>
       <c r="F634" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G634" t="n">
         <v>0.0</v>
@@ -21653,10 +21653,10 @@
         <v>778</v>
       </c>
       <c r="F741" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="G741" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H741" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -6235,7 +6235,7 @@
         <v>775</v>
       </c>
       <c r="F148" t="n">
-        <v>52.0</v>
+        <v>55.0</v>
       </c>
       <c r="G148" t="n">
         <v>0.0</v>
@@ -7327,7 +7327,7 @@
         <v>775</v>
       </c>
       <c r="F190" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G190" t="n">
         <v>0.0</v>
@@ -8263,7 +8263,7 @@
         <v>776</v>
       </c>
       <c r="F226" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -8471,7 +8471,7 @@
         <v>775</v>
       </c>
       <c r="F234" t="n">
-        <v>398.0</v>
+        <v>399.0</v>
       </c>
       <c r="G234" t="n">
         <v>0.0</v>
@@ -12917,7 +12917,7 @@
         <v>777</v>
       </c>
       <c r="F405" t="n">
-        <v>492.0</v>
+        <v>499.0</v>
       </c>
       <c r="G405" t="n">
         <v>1.0</v>
@@ -13157,7 +13157,7 @@
         <v>14.0</v>
       </c>
       <c r="H414" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="415">
@@ -19703,7 +19703,7 @@
         <v>777</v>
       </c>
       <c r="F666" t="n">
-        <v>238.0</v>
+        <v>241.0</v>
       </c>
       <c r="G666" t="n">
         <v>0.0</v>
@@ -20587,7 +20587,7 @@
         <v>777</v>
       </c>
       <c r="F700" t="n">
-        <v>225.0</v>
+        <v>239.0</v>
       </c>
       <c r="G700" t="n">
         <v>0.0</v>
@@ -21211,7 +21211,7 @@
         <v>776</v>
       </c>
       <c r="F724" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="G724" t="n">
         <v>0.0</v>
@@ -22459,7 +22459,7 @@
         <v>778</v>
       </c>
       <c r="F772" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G772" t="n">
         <v>0.0</v>
@@ -22667,7 +22667,7 @@
         <v>778</v>
       </c>
       <c r="F780" t="n">
-        <v>535.0</v>
+        <v>536.0</v>
       </c>
       <c r="G780" t="n">
         <v>2.0</v>
@@ -22719,7 +22719,7 @@
         <v>778</v>
       </c>
       <c r="F782" t="n">
-        <v>535.0</v>
+        <v>536.0</v>
       </c>
       <c r="G782" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2292,7 +2292,7 @@
         <v>726</v>
       </c>
       <c r="F2" t="n">
-        <v>660.0</v>
+        <v>661.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2604,7 +2604,7 @@
         <v>726</v>
       </c>
       <c r="F14" t="n">
-        <v>514.0</v>
+        <v>515.0</v>
       </c>
       <c r="G14" t="n">
         <v>9.0</v>
@@ -2656,7 +2656,7 @@
         <v>726</v>
       </c>
       <c r="F16" t="n">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2786,7 +2786,7 @@
         <v>727</v>
       </c>
       <c r="F21" t="n">
-        <v>415.0</v>
+        <v>416.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3150,7 +3150,7 @@
         <v>726</v>
       </c>
       <c r="F35" t="n">
-        <v>567.0</v>
+        <v>570.0</v>
       </c>
       <c r="G35" t="n">
         <v>4.0</v>
@@ -3254,7 +3254,7 @@
         <v>727</v>
       </c>
       <c r="F39" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -3280,7 +3280,7 @@
         <v>726</v>
       </c>
       <c r="F40" t="n">
-        <v>353.0</v>
+        <v>355.0</v>
       </c>
       <c r="G40" t="n">
         <v>2.0</v>
@@ -3904,7 +3904,7 @@
         <v>727</v>
       </c>
       <c r="F64" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -3982,7 +3982,7 @@
         <v>726</v>
       </c>
       <c r="F67" t="n">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
       <c r="G67" t="n">
         <v>31.0</v>
@@ -4268,7 +4268,7 @@
         <v>727</v>
       </c>
       <c r="F78" t="n">
-        <v>488.0</v>
+        <v>490.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -4320,7 +4320,7 @@
         <v>726</v>
       </c>
       <c r="F80" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -4372,7 +4372,7 @@
         <v>726</v>
       </c>
       <c r="F82" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4424,7 +4424,7 @@
         <v>726</v>
       </c>
       <c r="F84" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -4502,7 +4502,7 @@
         <v>726</v>
       </c>
       <c r="F87" t="n">
-        <v>492.0</v>
+        <v>494.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -4554,7 +4554,7 @@
         <v>726</v>
       </c>
       <c r="F89" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -4710,7 +4710,7 @@
         <v>727</v>
       </c>
       <c r="F95" t="n">
-        <v>473.0</v>
+        <v>479.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4814,7 +4814,7 @@
         <v>726</v>
       </c>
       <c r="F99" t="n">
-        <v>557.0</v>
+        <v>573.0</v>
       </c>
       <c r="G99" t="n">
         <v>4.0</v>
@@ -4944,7 +4944,7 @@
         <v>727</v>
       </c>
       <c r="F104" t="n">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -5282,7 +5282,7 @@
         <v>726</v>
       </c>
       <c r="F117" t="n">
-        <v>488.0</v>
+        <v>491.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -5464,7 +5464,7 @@
         <v>726</v>
       </c>
       <c r="F124" t="n">
-        <v>300.0</v>
+        <v>301.0</v>
       </c>
       <c r="G124" t="n">
         <v>3.0</v>
@@ -5490,7 +5490,7 @@
         <v>726</v>
       </c>
       <c r="F125" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G125" t="n">
         <v>0.0</v>
@@ -5698,7 +5698,7 @@
         <v>726</v>
       </c>
       <c r="F133" t="n">
-        <v>66.0</v>
+        <v>70.0</v>
       </c>
       <c r="G133" t="n">
         <v>2.0</v>
@@ -5750,7 +5750,7 @@
         <v>726</v>
       </c>
       <c r="F135" t="n">
-        <v>704.0</v>
+        <v>707.0</v>
       </c>
       <c r="G135" t="n">
         <v>2.0</v>
@@ -5828,7 +5828,7 @@
         <v>726</v>
       </c>
       <c r="F138" t="n">
-        <v>274.0</v>
+        <v>276.0</v>
       </c>
       <c r="G138" t="n">
         <v>0.0</v>
@@ -6452,7 +6452,7 @@
         <v>727</v>
       </c>
       <c r="F162" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G162" t="n">
         <v>0.0</v>
@@ -6530,7 +6530,7 @@
         <v>726</v>
       </c>
       <c r="F165" t="n">
-        <v>339.0</v>
+        <v>340.0</v>
       </c>
       <c r="G165" t="n">
         <v>1.0</v>
@@ -6660,10 +6660,10 @@
         <v>726</v>
       </c>
       <c r="F170" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G170" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -6738,7 +6738,7 @@
         <v>727</v>
       </c>
       <c r="F173" t="n">
-        <v>554.0</v>
+        <v>557.0</v>
       </c>
       <c r="G173" t="n">
         <v>0.0</v>
@@ -7388,7 +7388,7 @@
         <v>726</v>
       </c>
       <c r="F198" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G198" t="n">
         <v>0.0</v>
@@ -7934,7 +7934,7 @@
         <v>726</v>
       </c>
       <c r="F219" t="n">
-        <v>264.0</v>
+        <v>266.0</v>
       </c>
       <c r="G219" t="n">
         <v>1.0</v>
@@ -8038,7 +8038,7 @@
         <v>726</v>
       </c>
       <c r="F223" t="n">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="G223" t="n">
         <v>5.0</v>
@@ -8324,7 +8324,7 @@
         <v>726</v>
       </c>
       <c r="F234" t="n">
-        <v>235.0</v>
+        <v>237.0</v>
       </c>
       <c r="G234" t="n">
         <v>1.0</v>
@@ -8350,7 +8350,7 @@
         <v>726</v>
       </c>
       <c r="F235" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G235" t="n">
         <v>1.0</v>
@@ -8428,7 +8428,7 @@
         <v>726</v>
       </c>
       <c r="F238" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="G238" t="n">
         <v>4.0</v>
@@ -8454,7 +8454,7 @@
         <v>726</v>
       </c>
       <c r="F239" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G239" t="n">
         <v>1.0</v>
@@ -8662,7 +8662,7 @@
         <v>726</v>
       </c>
       <c r="F247" t="n">
-        <v>967.0</v>
+        <v>969.0</v>
       </c>
       <c r="G247" t="n">
         <v>16.0</v>
@@ -8922,7 +8922,7 @@
         <v>726</v>
       </c>
       <c r="F257" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="G257" t="n">
         <v>0.0</v>
@@ -9000,7 +9000,7 @@
         <v>726</v>
       </c>
       <c r="F260" t="n">
-        <v>613.0</v>
+        <v>615.0</v>
       </c>
       <c r="G260" t="n">
         <v>0.0</v>
@@ -9078,7 +9078,7 @@
         <v>726</v>
       </c>
       <c r="F263" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G263" t="n">
         <v>1.0</v>
@@ -9104,7 +9104,7 @@
         <v>726</v>
       </c>
       <c r="F264" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G264" t="n">
         <v>0.0</v>
@@ -9182,7 +9182,7 @@
         <v>726</v>
       </c>
       <c r="F267" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="G267" t="n">
         <v>0.0</v>
@@ -9416,7 +9416,7 @@
         <v>726</v>
       </c>
       <c r="F276" t="n">
-        <v>591.0</v>
+        <v>597.0</v>
       </c>
       <c r="G276" t="n">
         <v>6.0</v>
@@ -9442,7 +9442,7 @@
         <v>726</v>
       </c>
       <c r="F277" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G277" t="n">
         <v>2.0</v>
@@ -9468,7 +9468,7 @@
         <v>726</v>
       </c>
       <c r="F278" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G278" t="n">
         <v>0.0</v>
@@ -9494,7 +9494,7 @@
         <v>726</v>
       </c>
       <c r="F279" t="n">
-        <v>309.0</v>
+        <v>322.0</v>
       </c>
       <c r="G279" t="n">
         <v>2.0</v>
@@ -9754,7 +9754,7 @@
         <v>726</v>
       </c>
       <c r="F289" t="n">
-        <v>424.0</v>
+        <v>426.0</v>
       </c>
       <c r="G289" t="n">
         <v>1.0</v>
@@ -9832,7 +9832,7 @@
         <v>727</v>
       </c>
       <c r="F292" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G292" t="n">
         <v>0.0</v>
@@ -9910,7 +9910,7 @@
         <v>726</v>
       </c>
       <c r="F295" t="n">
-        <v>1111.0</v>
+        <v>1116.0</v>
       </c>
       <c r="G295" t="n">
         <v>6.0</v>
@@ -10014,7 +10014,7 @@
         <v>726</v>
       </c>
       <c r="F299" t="n">
-        <v>554.0</v>
+        <v>558.0</v>
       </c>
       <c r="G299" t="n">
         <v>6.0</v>
@@ -10222,7 +10222,7 @@
         <v>726</v>
       </c>
       <c r="F307" t="n">
-        <v>591.0</v>
+        <v>595.0</v>
       </c>
       <c r="G307" t="n">
         <v>2.0</v>
@@ -10352,7 +10352,7 @@
         <v>727</v>
       </c>
       <c r="F312" t="n">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
       <c r="G312" t="n">
         <v>0.0</v>
@@ -10638,7 +10638,7 @@
         <v>726</v>
       </c>
       <c r="F323" t="n">
-        <v>438.0</v>
+        <v>441.0</v>
       </c>
       <c r="G323" t="n">
         <v>1.0</v>
@@ -10722,7 +10722,7 @@
         <v>4.0</v>
       </c>
       <c r="H326" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="327">
@@ -10872,7 +10872,7 @@
         <v>726</v>
       </c>
       <c r="F332" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="G332" t="n">
         <v>0.0</v>
@@ -11080,7 +11080,7 @@
         <v>727</v>
       </c>
       <c r="F340" t="n">
-        <v>179.0</v>
+        <v>181.0</v>
       </c>
       <c r="G340" t="n">
         <v>0.0</v>
@@ -11808,7 +11808,7 @@
         <v>726</v>
       </c>
       <c r="F368" t="n">
-        <v>271.0</v>
+        <v>272.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -11938,7 +11938,7 @@
         <v>726</v>
       </c>
       <c r="F373" t="n">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
       <c r="G373" t="n">
         <v>0.0</v>
@@ -12328,7 +12328,7 @@
         <v>726</v>
       </c>
       <c r="F388" t="n">
-        <v>333.0</v>
+        <v>340.0</v>
       </c>
       <c r="G388" t="n">
         <v>14.0</v>
@@ -13160,7 +13160,7 @@
         <v>726</v>
       </c>
       <c r="F420" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G420" t="n">
         <v>0.0</v>
@@ -13212,7 +13212,7 @@
         <v>726</v>
       </c>
       <c r="F422" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
       <c r="G422" t="n">
         <v>0.0</v>
@@ -13290,7 +13290,7 @@
         <v>726</v>
       </c>
       <c r="F425" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
       <c r="G425" t="n">
         <v>0.0</v>
@@ -13680,7 +13680,7 @@
         <v>726</v>
       </c>
       <c r="F440" t="n">
-        <v>569.0</v>
+        <v>570.0</v>
       </c>
       <c r="G440" t="n">
         <v>3.0</v>
@@ -13706,7 +13706,7 @@
         <v>726</v>
       </c>
       <c r="F441" t="n">
-        <v>203.0</v>
+        <v>204.0</v>
       </c>
       <c r="G441" t="n">
         <v>1.0</v>
@@ -13732,7 +13732,7 @@
         <v>726</v>
       </c>
       <c r="F442" t="n">
-        <v>35.0</v>
+        <v>40.0</v>
       </c>
       <c r="G442" t="n">
         <v>0.0</v>
@@ -13784,7 +13784,7 @@
         <v>726</v>
       </c>
       <c r="F444" t="n">
-        <v>131.0</v>
+        <v>133.0</v>
       </c>
       <c r="G444" t="n">
         <v>4.0</v>
@@ -14122,10 +14122,10 @@
         <v>726</v>
       </c>
       <c r="F457" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="G457" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="H457" t="n">
         <v>9.0</v>
@@ -14278,7 +14278,7 @@
         <v>726</v>
       </c>
       <c r="F463" t="n">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="G463" t="n">
         <v>0.0</v>
@@ -14330,7 +14330,7 @@
         <v>726</v>
       </c>
       <c r="F465" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G465" t="n">
         <v>0.0</v>
@@ -14486,7 +14486,7 @@
         <v>726</v>
       </c>
       <c r="F471" t="n">
-        <v>686.0</v>
+        <v>692.0</v>
       </c>
       <c r="G471" t="n">
         <v>2.0</v>
@@ -15188,7 +15188,7 @@
         <v>726</v>
       </c>
       <c r="F498" t="n">
-        <v>445.0</v>
+        <v>448.0</v>
       </c>
       <c r="G498" t="n">
         <v>9.0</v>
@@ -15318,7 +15318,7 @@
         <v>726</v>
       </c>
       <c r="F503" t="n">
-        <v>81.0</v>
+        <v>85.0</v>
       </c>
       <c r="G503" t="n">
         <v>0.0</v>
@@ -15396,7 +15396,7 @@
         <v>727</v>
       </c>
       <c r="F506" t="n">
-        <v>174.0</v>
+        <v>176.0</v>
       </c>
       <c r="G506" t="n">
         <v>0.0</v>
@@ -15838,10 +15838,10 @@
         <v>726</v>
       </c>
       <c r="F523" t="n">
-        <v>137.0</v>
+        <v>139.0</v>
       </c>
       <c r="G523" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H523" t="n">
         <v>0.0</v>
@@ -16930,7 +16930,7 @@
         <v>727</v>
       </c>
       <c r="F565" t="n">
-        <v>423.0</v>
+        <v>424.0</v>
       </c>
       <c r="G565" t="n">
         <v>0.0</v>
@@ -16982,7 +16982,7 @@
         <v>726</v>
       </c>
       <c r="F567" t="n">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
       <c r="G567" t="n">
         <v>0.0</v>
@@ -17398,7 +17398,7 @@
         <v>726</v>
       </c>
       <c r="F583" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G583" t="n">
         <v>4.0</v>
@@ -17502,7 +17502,7 @@
         <v>726</v>
       </c>
       <c r="F587" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G587" t="n">
         <v>0.0</v>
@@ -18074,7 +18074,7 @@
         <v>727</v>
       </c>
       <c r="F609" t="n">
-        <v>153.0</v>
+        <v>158.0</v>
       </c>
       <c r="G609" t="n">
         <v>0.0</v>
@@ -18152,7 +18152,7 @@
         <v>726</v>
       </c>
       <c r="F612" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G612" t="n">
         <v>0.0</v>
@@ -18256,7 +18256,7 @@
         <v>726</v>
       </c>
       <c r="F616" t="n">
-        <v>122.0</v>
+        <v>124.0</v>
       </c>
       <c r="G616" t="n">
         <v>0.0</v>
@@ -18360,7 +18360,7 @@
         <v>726</v>
       </c>
       <c r="F620" t="n">
-        <v>109.0</v>
+        <v>116.0</v>
       </c>
       <c r="G620" t="n">
         <v>5.0</v>
@@ -18412,7 +18412,7 @@
         <v>726</v>
       </c>
       <c r="F622" t="n">
-        <v>135.0</v>
+        <v>137.0</v>
       </c>
       <c r="G622" t="n">
         <v>13.0</v>
@@ -18464,7 +18464,7 @@
         <v>727</v>
       </c>
       <c r="F624" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G624" t="n">
         <v>0.0</v>
@@ -18490,7 +18490,7 @@
         <v>726</v>
       </c>
       <c r="F625" t="n">
-        <v>164.0</v>
+        <v>167.0</v>
       </c>
       <c r="G625" t="n">
         <v>1.0</v>
@@ -18516,7 +18516,7 @@
         <v>726</v>
       </c>
       <c r="F626" t="n">
-        <v>81.0</v>
+        <v>85.0</v>
       </c>
       <c r="G626" t="n">
         <v>0.0</v>
@@ -18568,7 +18568,7 @@
         <v>727</v>
       </c>
       <c r="F628" t="n">
-        <v>134.0</v>
+        <v>139.0</v>
       </c>
       <c r="G628" t="n">
         <v>0.0</v>
@@ -18646,7 +18646,7 @@
         <v>727</v>
       </c>
       <c r="F631" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -18672,7 +18672,7 @@
         <v>727</v>
       </c>
       <c r="F632" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G632" t="n">
         <v>0.0</v>
@@ -18698,7 +18698,7 @@
         <v>727</v>
       </c>
       <c r="F633" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G633" t="n">
         <v>0.0</v>
@@ -18724,7 +18724,7 @@
         <v>727</v>
       </c>
       <c r="F634" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G634" t="n">
         <v>0.0</v>
@@ -18750,7 +18750,7 @@
         <v>726</v>
       </c>
       <c r="F635" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
       <c r="G635" t="n">
         <v>1.0</v>
@@ -18776,7 +18776,7 @@
         <v>726</v>
       </c>
       <c r="F636" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G636" t="n">
         <v>12.0</v>
@@ -18808,7 +18808,7 @@
         <v>0.0</v>
       </c>
       <c r="H637" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="638">
@@ -18854,7 +18854,7 @@
         <v>727</v>
       </c>
       <c r="F639" t="n">
-        <v>111.0</v>
+        <v>120.0</v>
       </c>
       <c r="G639" t="n">
         <v>0.0</v>
@@ -18932,7 +18932,7 @@
         <v>727</v>
       </c>
       <c r="F642" t="n">
-        <v>168.0</v>
+        <v>175.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -19010,7 +19010,7 @@
         <v>727</v>
       </c>
       <c r="F645" t="n">
-        <v>210.0</v>
+        <v>218.0</v>
       </c>
       <c r="G645" t="n">
         <v>0.0</v>
@@ -19140,7 +19140,7 @@
         <v>726</v>
       </c>
       <c r="F650" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G650" t="n">
         <v>0.0</v>
@@ -19218,7 +19218,7 @@
         <v>726</v>
       </c>
       <c r="F653" t="n">
-        <v>137.0</v>
+        <v>139.0</v>
       </c>
       <c r="G653" t="n">
         <v>0.0</v>
@@ -19481,7 +19481,7 @@
         <v>66.0</v>
       </c>
       <c r="G663" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H663" t="n">
         <v>2.0</v>
@@ -19504,7 +19504,7 @@
         <v>727</v>
       </c>
       <c r="F664" t="n">
-        <v>68.0</v>
+        <v>81.0</v>
       </c>
       <c r="G664" t="n">
         <v>0.0</v>
@@ -19582,7 +19582,7 @@
         <v>727</v>
       </c>
       <c r="F667" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G667" t="n">
         <v>0.0</v>
@@ -19608,7 +19608,7 @@
         <v>727</v>
       </c>
       <c r="F668" t="n">
-        <v>81.0</v>
+        <v>89.0</v>
       </c>
       <c r="G668" t="n">
         <v>0.0</v>
@@ -20024,10 +20024,10 @@
         <v>729</v>
       </c>
       <c r="F684" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="G684" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H684" t="n">
         <v>0.0</v>
@@ -20050,10 +20050,10 @@
         <v>729</v>
       </c>
       <c r="F685" t="n">
-        <v>247.0</v>
+        <v>248.0</v>
       </c>
       <c r="G685" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H685" t="n">
         <v>8.0</v>
@@ -20258,7 +20258,7 @@
         <v>726</v>
       </c>
       <c r="F693" t="n">
-        <v>344.0</v>
+        <v>346.0</v>
       </c>
       <c r="G693" t="n">
         <v>2.0</v>
@@ -20284,7 +20284,7 @@
         <v>726</v>
       </c>
       <c r="F694" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="G694" t="n">
         <v>1.0</v>
@@ -20336,7 +20336,7 @@
         <v>727</v>
       </c>
       <c r="F696" t="n">
-        <v>177.0</v>
+        <v>178.0</v>
       </c>
       <c r="G696" t="n">
         <v>0.0</v>
@@ -20674,7 +20674,7 @@
         <v>727</v>
       </c>
       <c r="F709" t="n">
-        <v>439.0</v>
+        <v>442.0</v>
       </c>
       <c r="G709" t="n">
         <v>1.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2526,7 +2526,7 @@
         <v>726</v>
       </c>
       <c r="F11" t="n">
-        <v>315.0</v>
+        <v>317.0</v>
       </c>
       <c r="G11" t="n">
         <v>2.0</v>
@@ -2916,7 +2916,7 @@
         <v>726</v>
       </c>
       <c r="F26" t="n">
-        <v>133.0</v>
+        <v>139.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -3020,7 +3020,7 @@
         <v>726</v>
       </c>
       <c r="F30" t="n">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -3072,7 +3072,7 @@
         <v>726</v>
       </c>
       <c r="F32" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G32" t="n">
         <v>1.0</v>
@@ -3176,7 +3176,7 @@
         <v>726</v>
       </c>
       <c r="F36" t="n">
-        <v>229.0</v>
+        <v>230.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -3228,7 +3228,7 @@
         <v>726</v>
       </c>
       <c r="F38" t="n">
-        <v>269.0</v>
+        <v>283.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -3254,7 +3254,7 @@
         <v>727</v>
       </c>
       <c r="F39" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -3488,7 +3488,7 @@
         <v>726</v>
       </c>
       <c r="F48" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -3514,7 +3514,7 @@
         <v>726</v>
       </c>
       <c r="F49" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G49" t="n">
         <v>1.0</v>
@@ -3644,7 +3644,7 @@
         <v>726</v>
       </c>
       <c r="F54" t="n">
-        <v>71.0</v>
+        <v>75.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -3670,7 +3670,7 @@
         <v>726</v>
       </c>
       <c r="F55" t="n">
-        <v>286.0</v>
+        <v>288.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -3696,7 +3696,7 @@
         <v>726</v>
       </c>
       <c r="F56" t="n">
-        <v>296.0</v>
+        <v>299.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -3748,7 +3748,7 @@
         <v>726</v>
       </c>
       <c r="F58" t="n">
-        <v>129.0</v>
+        <v>135.0</v>
       </c>
       <c r="G58" t="n">
         <v>0.0</v>
@@ -4086,7 +4086,7 @@
         <v>726</v>
       </c>
       <c r="F71" t="n">
-        <v>178.0</v>
+        <v>182.0</v>
       </c>
       <c r="G71" t="n">
         <v>1.0</v>
@@ -4268,7 +4268,7 @@
         <v>727</v>
       </c>
       <c r="F78" t="n">
-        <v>490.0</v>
+        <v>497.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -4372,7 +4372,7 @@
         <v>726</v>
       </c>
       <c r="F82" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -4398,7 +4398,7 @@
         <v>726</v>
       </c>
       <c r="F83" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4632,7 +4632,7 @@
         <v>726</v>
       </c>
       <c r="F92" t="n">
-        <v>50.0</v>
+        <v>53.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -4762,7 +4762,7 @@
         <v>726</v>
       </c>
       <c r="F97" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -4866,7 +4866,7 @@
         <v>726</v>
       </c>
       <c r="F101" t="n">
-        <v>113.0</v>
+        <v>116.0</v>
       </c>
       <c r="G101" t="n">
         <v>1.0</v>
@@ -5074,7 +5074,7 @@
         <v>726</v>
       </c>
       <c r="F109" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="G109" t="n">
         <v>2.0</v>
@@ -5126,7 +5126,7 @@
         <v>726</v>
       </c>
       <c r="F111" t="n">
-        <v>199.0</v>
+        <v>201.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
@@ -5334,7 +5334,7 @@
         <v>726</v>
       </c>
       <c r="F119" t="n">
-        <v>261.0</v>
+        <v>265.0</v>
       </c>
       <c r="G119" t="n">
         <v>1.0</v>
@@ -5412,7 +5412,7 @@
         <v>726</v>
       </c>
       <c r="F122" t="n">
-        <v>263.0</v>
+        <v>269.0</v>
       </c>
       <c r="G122" t="n">
         <v>7.0</v>
@@ -5620,7 +5620,7 @@
         <v>726</v>
       </c>
       <c r="F130" t="n">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
       <c r="G130" t="n">
         <v>0.0</v>
@@ -5880,7 +5880,7 @@
         <v>727</v>
       </c>
       <c r="F140" t="n">
-        <v>212.0</v>
+        <v>218.0</v>
       </c>
       <c r="G140" t="n">
         <v>1.0</v>
@@ -6062,7 +6062,7 @@
         <v>727</v>
       </c>
       <c r="F147" t="n">
-        <v>68.0</v>
+        <v>71.0</v>
       </c>
       <c r="G147" t="n">
         <v>0.0</v>
@@ -6244,7 +6244,7 @@
         <v>726</v>
       </c>
       <c r="F154" t="n">
-        <v>153.0</v>
+        <v>157.0</v>
       </c>
       <c r="G154" t="n">
         <v>1.0</v>
@@ -6270,7 +6270,7 @@
         <v>727</v>
       </c>
       <c r="F155" t="n">
-        <v>62.0</v>
+        <v>70.0</v>
       </c>
       <c r="G155" t="n">
         <v>0.0</v>
@@ -6296,7 +6296,7 @@
         <v>726</v>
       </c>
       <c r="F156" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="G156" t="n">
         <v>0.0</v>
@@ -6504,7 +6504,7 @@
         <v>726</v>
       </c>
       <c r="F164" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="G164" t="n">
         <v>0.0</v>
@@ -6608,7 +6608,7 @@
         <v>726</v>
       </c>
       <c r="F168" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G168" t="n">
         <v>1.0</v>
@@ -6663,7 +6663,7 @@
         <v>116.0</v>
       </c>
       <c r="G170" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="H170" t="n">
         <v>0.0</v>
@@ -6816,7 +6816,7 @@
         <v>727</v>
       </c>
       <c r="F176" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -6894,7 +6894,7 @@
         <v>726</v>
       </c>
       <c r="F179" t="n">
-        <v>168.0</v>
+        <v>171.0</v>
       </c>
       <c r="G179" t="n">
         <v>0.0</v>
@@ -7050,7 +7050,7 @@
         <v>727</v>
       </c>
       <c r="F185" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="G185" t="n">
         <v>0.0</v>
@@ -7154,7 +7154,7 @@
         <v>726</v>
       </c>
       <c r="F189" t="n">
-        <v>22.0</v>
+        <v>28.0</v>
       </c>
       <c r="G189" t="n">
         <v>0.0</v>
@@ -7232,7 +7232,7 @@
         <v>727</v>
       </c>
       <c r="F192" t="n">
-        <v>286.0</v>
+        <v>297.0</v>
       </c>
       <c r="G192" t="n">
         <v>1.0</v>
@@ -7258,7 +7258,7 @@
         <v>726</v>
       </c>
       <c r="F193" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G193" t="n">
         <v>0.0</v>
@@ -7726,7 +7726,7 @@
         <v>727</v>
       </c>
       <c r="F211" t="n">
-        <v>198.0</v>
+        <v>205.0</v>
       </c>
       <c r="G211" t="n">
         <v>0.0</v>
@@ -7778,7 +7778,7 @@
         <v>726</v>
       </c>
       <c r="F213" t="n">
-        <v>164.0</v>
+        <v>165.0</v>
       </c>
       <c r="G213" t="n">
         <v>0.0</v>
@@ -7986,7 +7986,7 @@
         <v>726</v>
       </c>
       <c r="F221" t="n">
-        <v>293.0</v>
+        <v>295.0</v>
       </c>
       <c r="G221" t="n">
         <v>2.0</v>
@@ -8012,7 +8012,7 @@
         <v>726</v>
       </c>
       <c r="F222" t="n">
-        <v>142.0</v>
+        <v>148.0</v>
       </c>
       <c r="G222" t="n">
         <v>1.0</v>
@@ -8064,7 +8064,7 @@
         <v>726</v>
       </c>
       <c r="F224" t="n">
-        <v>170.0</v>
+        <v>173.0</v>
       </c>
       <c r="G224" t="n">
         <v>0.0</v>
@@ -8116,7 +8116,7 @@
         <v>726</v>
       </c>
       <c r="F226" t="n">
-        <v>399.0</v>
+        <v>404.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -8142,7 +8142,7 @@
         <v>726</v>
       </c>
       <c r="F227" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="G227" t="n">
         <v>0.0</v>
@@ -8350,7 +8350,7 @@
         <v>726</v>
       </c>
       <c r="F235" t="n">
-        <v>93.0</v>
+        <v>96.0</v>
       </c>
       <c r="G235" t="n">
         <v>1.0</v>
@@ -8506,7 +8506,7 @@
         <v>726</v>
       </c>
       <c r="F241" t="n">
-        <v>168.0</v>
+        <v>175.0</v>
       </c>
       <c r="G241" t="n">
         <v>7.0</v>
@@ -8584,7 +8584,7 @@
         <v>726</v>
       </c>
       <c r="F244" t="n">
-        <v>58.0</v>
+        <v>60.0</v>
       </c>
       <c r="G244" t="n">
         <v>0.0</v>
@@ -8662,7 +8662,7 @@
         <v>726</v>
       </c>
       <c r="F247" t="n">
-        <v>969.0</v>
+        <v>970.0</v>
       </c>
       <c r="G247" t="n">
         <v>16.0</v>
@@ -8818,7 +8818,7 @@
         <v>726</v>
       </c>
       <c r="F253" t="n">
-        <v>279.0</v>
+        <v>291.0</v>
       </c>
       <c r="G253" t="n">
         <v>0.0</v>
@@ -8844,7 +8844,7 @@
         <v>726</v>
       </c>
       <c r="F254" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="G254" t="n">
         <v>0.0</v>
@@ -8948,7 +8948,7 @@
         <v>726</v>
       </c>
       <c r="F258" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G258" t="n">
         <v>1.0</v>
@@ -9130,7 +9130,7 @@
         <v>726</v>
       </c>
       <c r="F265" t="n">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
       <c r="G265" t="n">
         <v>0.0</v>
@@ -9234,7 +9234,7 @@
         <v>726</v>
       </c>
       <c r="F269" t="n">
-        <v>549.0</v>
+        <v>557.0</v>
       </c>
       <c r="G269" t="n">
         <v>0.0</v>
@@ -9338,7 +9338,7 @@
         <v>726</v>
       </c>
       <c r="F273" t="n">
-        <v>242.0</v>
+        <v>244.0</v>
       </c>
       <c r="G273" t="n">
         <v>1.0</v>
@@ -9442,7 +9442,7 @@
         <v>726</v>
       </c>
       <c r="F277" t="n">
-        <v>75.0</v>
+        <v>79.0</v>
       </c>
       <c r="G277" t="n">
         <v>2.0</v>
@@ -9520,7 +9520,7 @@
         <v>726</v>
       </c>
       <c r="F280" t="n">
-        <v>249.0</v>
+        <v>252.0</v>
       </c>
       <c r="G280" t="n">
         <v>0.0</v>
@@ -9572,7 +9572,7 @@
         <v>726</v>
       </c>
       <c r="F282" t="n">
-        <v>94.0</v>
+        <v>101.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -9598,7 +9598,7 @@
         <v>726</v>
       </c>
       <c r="F283" t="n">
-        <v>219.0</v>
+        <v>221.0</v>
       </c>
       <c r="G283" t="n">
         <v>4.0</v>
@@ -9702,7 +9702,7 @@
         <v>727</v>
       </c>
       <c r="F287" t="n">
-        <v>73.0</v>
+        <v>78.0</v>
       </c>
       <c r="G287" t="n">
         <v>0.0</v>
@@ -9858,7 +9858,7 @@
         <v>726</v>
       </c>
       <c r="F293" t="n">
-        <v>137.0</v>
+        <v>142.0</v>
       </c>
       <c r="G293" t="n">
         <v>2.0</v>
@@ -9910,7 +9910,7 @@
         <v>726</v>
       </c>
       <c r="F295" t="n">
-        <v>1116.0</v>
+        <v>1127.0</v>
       </c>
       <c r="G295" t="n">
         <v>6.0</v>
@@ -10040,7 +10040,7 @@
         <v>726</v>
       </c>
       <c r="F300" t="n">
-        <v>192.0</v>
+        <v>193.0</v>
       </c>
       <c r="G300" t="n">
         <v>0.0</v>
@@ -10248,7 +10248,7 @@
         <v>727</v>
       </c>
       <c r="F308" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="G308" t="n">
         <v>0.0</v>
@@ -10300,7 +10300,7 @@
         <v>726</v>
       </c>
       <c r="F310" t="n">
-        <v>74.0</v>
+        <v>77.0</v>
       </c>
       <c r="G310" t="n">
         <v>0.0</v>
@@ -10430,7 +10430,7 @@
         <v>726</v>
       </c>
       <c r="F315" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G315" t="n">
         <v>2.0</v>
@@ -10508,7 +10508,7 @@
         <v>726</v>
       </c>
       <c r="F318" t="n">
-        <v>155.0</v>
+        <v>168.0</v>
       </c>
       <c r="G318" t="n">
         <v>0.0</v>
@@ -10534,7 +10534,7 @@
         <v>726</v>
       </c>
       <c r="F319" t="n">
-        <v>270.0</v>
+        <v>271.0</v>
       </c>
       <c r="G319" t="n">
         <v>0.0</v>
@@ -11002,7 +11002,7 @@
         <v>726</v>
       </c>
       <c r="F337" t="n">
-        <v>136.0</v>
+        <v>140.0</v>
       </c>
       <c r="G337" t="n">
         <v>0.0</v>
@@ -11132,7 +11132,7 @@
         <v>726</v>
       </c>
       <c r="F342" t="n">
-        <v>569.0</v>
+        <v>571.0</v>
       </c>
       <c r="G342" t="n">
         <v>6.0</v>
@@ -11418,7 +11418,7 @@
         <v>727</v>
       </c>
       <c r="F353" t="n">
-        <v>152.0</v>
+        <v>160.0</v>
       </c>
       <c r="G353" t="n">
         <v>0.0</v>
@@ -11496,7 +11496,7 @@
         <v>726</v>
       </c>
       <c r="F356" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G356" t="n">
         <v>0.0</v>
@@ -11626,7 +11626,7 @@
         <v>726</v>
       </c>
       <c r="F361" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="G361" t="n">
         <v>0.0</v>
@@ -11652,7 +11652,7 @@
         <v>726</v>
       </c>
       <c r="F362" t="n">
-        <v>108.0</v>
+        <v>116.0</v>
       </c>
       <c r="G362" t="n">
         <v>0.0</v>
@@ -11990,7 +11990,7 @@
         <v>726</v>
       </c>
       <c r="F375" t="n">
-        <v>140.0</v>
+        <v>146.0</v>
       </c>
       <c r="G375" t="n">
         <v>5.0</v>
@@ -12042,7 +12042,7 @@
         <v>726</v>
       </c>
       <c r="F377" t="n">
-        <v>169.0</v>
+        <v>172.0</v>
       </c>
       <c r="G377" t="n">
         <v>2.0</v>
@@ -12120,7 +12120,7 @@
         <v>728</v>
       </c>
       <c r="F380" t="n">
-        <v>499.0</v>
+        <v>501.0</v>
       </c>
       <c r="G380" t="n">
         <v>1.0</v>
@@ -12354,7 +12354,7 @@
         <v>726</v>
       </c>
       <c r="F389" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G389" t="n">
         <v>0.0</v>
@@ -12406,7 +12406,7 @@
         <v>726</v>
       </c>
       <c r="F391" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="G391" t="n">
         <v>0.0</v>
@@ -12588,7 +12588,7 @@
         <v>728</v>
       </c>
       <c r="F398" t="n">
-        <v>286.0</v>
+        <v>291.0</v>
       </c>
       <c r="G398" t="n">
         <v>0.0</v>
@@ -12796,7 +12796,7 @@
         <v>726</v>
       </c>
       <c r="F406" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G406" t="n">
         <v>0.0</v>
@@ -12848,7 +12848,7 @@
         <v>726</v>
       </c>
       <c r="F408" t="n">
-        <v>108.0</v>
+        <v>111.0</v>
       </c>
       <c r="G408" t="n">
         <v>0.0</v>
@@ -13108,7 +13108,7 @@
         <v>726</v>
       </c>
       <c r="F418" t="n">
-        <v>627.0</v>
+        <v>631.0</v>
       </c>
       <c r="G418" t="n">
         <v>3.0</v>
@@ -13134,7 +13134,7 @@
         <v>726</v>
       </c>
       <c r="F419" t="n">
-        <v>154.0</v>
+        <v>159.0</v>
       </c>
       <c r="G419" t="n">
         <v>0.0</v>
@@ -13186,7 +13186,7 @@
         <v>727</v>
       </c>
       <c r="F421" t="n">
-        <v>131.0</v>
+        <v>136.0</v>
       </c>
       <c r="G421" t="n">
         <v>1.0</v>
@@ -13238,7 +13238,7 @@
         <v>726</v>
       </c>
       <c r="F423" t="n">
-        <v>803.0</v>
+        <v>811.0</v>
       </c>
       <c r="G423" t="n">
         <v>2.0</v>
@@ -13420,7 +13420,7 @@
         <v>726</v>
       </c>
       <c r="F430" t="n">
-        <v>200.0</v>
+        <v>203.0</v>
       </c>
       <c r="G430" t="n">
         <v>0.0</v>
@@ -13446,7 +13446,7 @@
         <v>727</v>
       </c>
       <c r="F431" t="n">
-        <v>387.0</v>
+        <v>394.0</v>
       </c>
       <c r="G431" t="n">
         <v>0.0</v>
@@ -13472,7 +13472,7 @@
         <v>726</v>
       </c>
       <c r="F432" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G432" t="n">
         <v>0.0</v>
@@ -13602,7 +13602,7 @@
         <v>726</v>
       </c>
       <c r="F437" t="n">
-        <v>63.0</v>
+        <v>66.0</v>
       </c>
       <c r="G437" t="n">
         <v>0.0</v>
@@ -13628,7 +13628,7 @@
         <v>726</v>
       </c>
       <c r="F438" t="n">
-        <v>231.0</v>
+        <v>249.0</v>
       </c>
       <c r="G438" t="n">
         <v>0.0</v>
@@ -13680,7 +13680,7 @@
         <v>726</v>
       </c>
       <c r="F440" t="n">
-        <v>570.0</v>
+        <v>575.0</v>
       </c>
       <c r="G440" t="n">
         <v>3.0</v>
@@ -13732,7 +13732,7 @@
         <v>726</v>
       </c>
       <c r="F442" t="n">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
       <c r="G442" t="n">
         <v>0.0</v>
@@ -14070,7 +14070,7 @@
         <v>726</v>
       </c>
       <c r="F455" t="n">
-        <v>539.0</v>
+        <v>541.0</v>
       </c>
       <c r="G455" t="n">
         <v>0.0</v>
@@ -14304,7 +14304,7 @@
         <v>726</v>
       </c>
       <c r="F464" t="n">
-        <v>397.0</v>
+        <v>401.0</v>
       </c>
       <c r="G464" t="n">
         <v>2.0</v>
@@ -14590,7 +14590,7 @@
         <v>727</v>
       </c>
       <c r="F475" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G475" t="n">
         <v>0.0</v>
@@ -14642,7 +14642,7 @@
         <v>726</v>
       </c>
       <c r="F477" t="n">
-        <v>208.0</v>
+        <v>211.0</v>
       </c>
       <c r="G477" t="n">
         <v>0.0</v>
@@ -14850,7 +14850,7 @@
         <v>728</v>
       </c>
       <c r="F485" t="n">
-        <v>353.0</v>
+        <v>360.0</v>
       </c>
       <c r="G485" t="n">
         <v>0.0</v>
@@ -14876,7 +14876,7 @@
         <v>726</v>
       </c>
       <c r="F486" t="n">
-        <v>2529.0</v>
+        <v>2538.0</v>
       </c>
       <c r="G486" t="n">
         <v>45.0</v>
@@ -15292,7 +15292,7 @@
         <v>726</v>
       </c>
       <c r="F502" t="n">
-        <v>214.0</v>
+        <v>219.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15370,7 +15370,7 @@
         <v>726</v>
       </c>
       <c r="F505" t="n">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="G505" t="n">
         <v>0.0</v>
@@ -15474,7 +15474,7 @@
         <v>726</v>
       </c>
       <c r="F509" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G509" t="n">
         <v>0.0</v>
@@ -15994,7 +15994,7 @@
         <v>726</v>
       </c>
       <c r="F529" t="n">
-        <v>58.0</v>
+        <v>61.0</v>
       </c>
       <c r="G529" t="n">
         <v>0.0</v>
@@ -16202,7 +16202,7 @@
         <v>726</v>
       </c>
       <c r="F537" t="n">
-        <v>296.0</v>
+        <v>298.0</v>
       </c>
       <c r="G537" t="n">
         <v>1.0</v>
@@ -16566,7 +16566,7 @@
         <v>726</v>
       </c>
       <c r="F551" t="n">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
       <c r="G551" t="n">
         <v>0.0</v>
@@ -16696,7 +16696,7 @@
         <v>726</v>
       </c>
       <c r="F556" t="n">
-        <v>297.0</v>
+        <v>302.0</v>
       </c>
       <c r="G556" t="n">
         <v>0.0</v>
@@ -16748,7 +16748,7 @@
         <v>726</v>
       </c>
       <c r="F558" t="n">
-        <v>44.0</v>
+        <v>48.0</v>
       </c>
       <c r="G558" t="n">
         <v>0.0</v>
@@ -17112,7 +17112,7 @@
         <v>726</v>
       </c>
       <c r="F572" t="n">
-        <v>101.0</v>
+        <v>109.0</v>
       </c>
       <c r="G572" t="n">
         <v>1.0</v>
@@ -17606,7 +17606,7 @@
         <v>726</v>
       </c>
       <c r="F591" t="n">
-        <v>250.0</v>
+        <v>259.0</v>
       </c>
       <c r="G591" t="n">
         <v>0.0</v>
@@ -17632,7 +17632,7 @@
         <v>726</v>
       </c>
       <c r="F592" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G592" t="n">
         <v>0.0</v>
@@ -17658,7 +17658,7 @@
         <v>726</v>
       </c>
       <c r="F593" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G593" t="n">
         <v>0.0</v>
@@ -17710,7 +17710,7 @@
         <v>726</v>
       </c>
       <c r="F595" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="G595" t="n">
         <v>1.0</v>
@@ -17762,7 +17762,7 @@
         <v>726</v>
       </c>
       <c r="F597" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G597" t="n">
         <v>2.0</v>
@@ -18230,7 +18230,7 @@
         <v>726</v>
       </c>
       <c r="F615" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G615" t="n">
         <v>0.0</v>
@@ -18308,7 +18308,7 @@
         <v>728</v>
       </c>
       <c r="F618" t="n">
-        <v>241.0</v>
+        <v>251.0</v>
       </c>
       <c r="G618" t="n">
         <v>0.0</v>
@@ -18828,7 +18828,7 @@
         <v>728</v>
       </c>
       <c r="F638" t="n">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
       <c r="G638" t="n">
         <v>0.0</v>
@@ -18958,7 +18958,7 @@
         <v>728</v>
       </c>
       <c r="F643" t="n">
-        <v>460.0</v>
+        <v>461.0</v>
       </c>
       <c r="G643" t="n">
         <v>0.0</v>
@@ -19270,7 +19270,7 @@
         <v>727</v>
       </c>
       <c r="F655" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G655" t="n">
         <v>0.0</v>
@@ -19374,7 +19374,7 @@
         <v>728</v>
       </c>
       <c r="F659" t="n">
-        <v>260.0</v>
+        <v>262.0</v>
       </c>
       <c r="G659" t="n">
         <v>0.0</v>
@@ -19634,7 +19634,7 @@
         <v>727</v>
       </c>
       <c r="F669" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -19660,7 +19660,7 @@
         <v>727</v>
       </c>
       <c r="F670" t="n">
-        <v>29.0</v>
+        <v>35.0</v>
       </c>
       <c r="G670" t="n">
         <v>0.0</v>
@@ -19686,7 +19686,7 @@
         <v>727</v>
       </c>
       <c r="F671" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="G671" t="n">
         <v>0.0</v>
@@ -19712,7 +19712,7 @@
         <v>727</v>
       </c>
       <c r="F672" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -20024,10 +20024,10 @@
         <v>729</v>
       </c>
       <c r="F684" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="G684" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="H684" t="n">
         <v>0.0</v>
@@ -20053,7 +20053,7 @@
         <v>248.0</v>
       </c>
       <c r="G685" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H685" t="n">
         <v>8.0</v>
@@ -20518,7 +20518,7 @@
         <v>726</v>
       </c>
       <c r="F703" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G703" t="n">
         <v>0.0</v>
@@ -20596,7 +20596,7 @@
         <v>726</v>
       </c>
       <c r="F706" t="n">
-        <v>19.0</v>
+        <v>24.0</v>
       </c>
       <c r="G706" t="n">
         <v>0.0</v>
@@ -20986,7 +20986,7 @@
         <v>729</v>
       </c>
       <c r="F721" t="n">
-        <v>112.0</v>
+        <v>114.0</v>
       </c>
       <c r="G721" t="n">
         <v>0.0</v>
@@ -21220,7 +21220,7 @@
         <v>729</v>
       </c>
       <c r="F730" t="n">
-        <v>536.0</v>
+        <v>537.0</v>
       </c>
       <c r="G730" t="n">
         <v>2.0</v>
@@ -21272,7 +21272,7 @@
         <v>729</v>
       </c>
       <c r="F732" t="n">
-        <v>536.0</v>
+        <v>537.0</v>
       </c>
       <c r="G732" t="n">
         <v>2.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2292,7 +2292,7 @@
         <v>726</v>
       </c>
       <c r="F2" t="n">
-        <v>661.0</v>
+        <v>664.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -2656,7 +2656,7 @@
         <v>726</v>
       </c>
       <c r="F16" t="n">
-        <v>434.0</v>
+        <v>436.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -2786,7 +2786,7 @@
         <v>727</v>
       </c>
       <c r="F21" t="n">
-        <v>416.0</v>
+        <v>420.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3280,7 +3280,7 @@
         <v>726</v>
       </c>
       <c r="F40" t="n">
-        <v>355.0</v>
+        <v>359.0</v>
       </c>
       <c r="G40" t="n">
         <v>2.0</v>
@@ -3358,7 +3358,7 @@
         <v>726</v>
       </c>
       <c r="F43" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -3592,7 +3592,7 @@
         <v>726</v>
       </c>
       <c r="F52" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="G52" t="n">
         <v>1.0</v>
@@ -3618,7 +3618,7 @@
         <v>726</v>
       </c>
       <c r="F53" t="n">
-        <v>83.0</v>
+        <v>90.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -3722,7 +3722,7 @@
         <v>726</v>
       </c>
       <c r="F57" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G57" t="n">
         <v>0.0</v>
@@ -3748,10 +3748,10 @@
         <v>726</v>
       </c>
       <c r="F58" t="n">
-        <v>135.0</v>
+        <v>141.0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -3826,7 +3826,7 @@
         <v>726</v>
       </c>
       <c r="F61" t="n">
-        <v>225.0</v>
+        <v>230.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -3878,7 +3878,7 @@
         <v>726</v>
       </c>
       <c r="F63" t="n">
-        <v>50.0</v>
+        <v>54.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -3904,7 +3904,7 @@
         <v>727</v>
       </c>
       <c r="F64" t="n">
-        <v>225.0</v>
+        <v>228.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -4034,7 +4034,7 @@
         <v>726</v>
       </c>
       <c r="F69" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -4086,7 +4086,7 @@
         <v>726</v>
       </c>
       <c r="F71" t="n">
-        <v>182.0</v>
+        <v>187.0</v>
       </c>
       <c r="G71" t="n">
         <v>1.0</v>
@@ -4450,7 +4450,7 @@
         <v>726</v>
       </c>
       <c r="F85" t="n">
-        <v>114.0</v>
+        <v>118.0</v>
       </c>
       <c r="G85" t="n">
         <v>2.0</v>
@@ -4710,7 +4710,7 @@
         <v>727</v>
       </c>
       <c r="F95" t="n">
-        <v>479.0</v>
+        <v>481.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -4768,7 +4768,7 @@
         <v>0.0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="98">
@@ -4814,7 +4814,7 @@
         <v>726</v>
       </c>
       <c r="F99" t="n">
-        <v>573.0</v>
+        <v>575.0</v>
       </c>
       <c r="G99" t="n">
         <v>4.0</v>
@@ -4918,7 +4918,7 @@
         <v>727</v>
       </c>
       <c r="F103" t="n">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -4944,7 +4944,7 @@
         <v>727</v>
       </c>
       <c r="F104" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -5282,7 +5282,7 @@
         <v>726</v>
       </c>
       <c r="F117" t="n">
-        <v>491.0</v>
+        <v>494.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -5542,7 +5542,7 @@
         <v>727</v>
       </c>
       <c r="F127" t="n">
-        <v>88.0</v>
+        <v>90.0</v>
       </c>
       <c r="G127" t="n">
         <v>0.0</v>
@@ -5594,7 +5594,7 @@
         <v>726</v>
       </c>
       <c r="F129" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="G129" t="n">
         <v>0.0</v>
@@ -5750,7 +5750,7 @@
         <v>726</v>
       </c>
       <c r="F135" t="n">
-        <v>707.0</v>
+        <v>710.0</v>
       </c>
       <c r="G135" t="n">
         <v>2.0</v>
@@ -5906,7 +5906,7 @@
         <v>726</v>
       </c>
       <c r="F141" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G141" t="n">
         <v>0.0</v>
@@ -5958,7 +5958,7 @@
         <v>726</v>
       </c>
       <c r="F143" t="n">
-        <v>55.0</v>
+        <v>59.0</v>
       </c>
       <c r="G143" t="n">
         <v>0.0</v>
@@ -6296,7 +6296,7 @@
         <v>726</v>
       </c>
       <c r="F156" t="n">
-        <v>203.0</v>
+        <v>204.0</v>
       </c>
       <c r="G156" t="n">
         <v>0.0</v>
@@ -6426,7 +6426,7 @@
         <v>726</v>
       </c>
       <c r="F161" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G161" t="n">
         <v>0.0</v>
@@ -6504,7 +6504,7 @@
         <v>726</v>
       </c>
       <c r="F164" t="n">
-        <v>77.0</v>
+        <v>83.0</v>
       </c>
       <c r="G164" t="n">
         <v>0.0</v>
@@ -6712,7 +6712,7 @@
         <v>726</v>
       </c>
       <c r="F172" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
       <c r="G172" t="n">
         <v>0.0</v>
@@ -6816,7 +6816,7 @@
         <v>727</v>
       </c>
       <c r="F176" t="n">
-        <v>58.0</v>
+        <v>61.0</v>
       </c>
       <c r="G176" t="n">
         <v>0.0</v>
@@ -8246,7 +8246,7 @@
         <v>726</v>
       </c>
       <c r="F231" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="G231" t="n">
         <v>0.0</v>
@@ -8584,7 +8584,7 @@
         <v>726</v>
       </c>
       <c r="F244" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G244" t="n">
         <v>0.0</v>
@@ -9494,7 +9494,7 @@
         <v>726</v>
       </c>
       <c r="F279" t="n">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
       <c r="G279" t="n">
         <v>2.0</v>
@@ -9598,7 +9598,7 @@
         <v>726</v>
       </c>
       <c r="F283" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="G283" t="n">
         <v>4.0</v>
@@ -10118,7 +10118,7 @@
         <v>726</v>
       </c>
       <c r="F303" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G303" t="n">
         <v>0.0</v>
@@ -10534,7 +10534,7 @@
         <v>726</v>
       </c>
       <c r="F319" t="n">
-        <v>271.0</v>
+        <v>273.0</v>
       </c>
       <c r="G319" t="n">
         <v>0.0</v>
@@ -10638,7 +10638,7 @@
         <v>726</v>
       </c>
       <c r="F323" t="n">
-        <v>441.0</v>
+        <v>443.0</v>
       </c>
       <c r="G323" t="n">
         <v>1.0</v>
@@ -10924,7 +10924,7 @@
         <v>727</v>
       </c>
       <c r="F334" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G334" t="n">
         <v>1.0</v>
@@ -11392,7 +11392,7 @@
         <v>727</v>
       </c>
       <c r="F352" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G352" t="n">
         <v>0.0</v>
@@ -11808,7 +11808,7 @@
         <v>726</v>
       </c>
       <c r="F368" t="n">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="G368" t="n">
         <v>0.0</v>
@@ -12354,7 +12354,7 @@
         <v>726</v>
       </c>
       <c r="F389" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G389" t="n">
         <v>0.0</v>
@@ -12536,7 +12536,7 @@
         <v>727</v>
       </c>
       <c r="F396" t="n">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
       <c r="G396" t="n">
         <v>0.0</v>
@@ -13446,7 +13446,7 @@
         <v>727</v>
       </c>
       <c r="F431" t="n">
-        <v>394.0</v>
+        <v>396.0</v>
       </c>
       <c r="G431" t="n">
         <v>0.0</v>
@@ -13654,7 +13654,7 @@
         <v>726</v>
       </c>
       <c r="F439" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G439" t="n">
         <v>0.0</v>
@@ -14044,7 +14044,7 @@
         <v>727</v>
       </c>
       <c r="F454" t="n">
-        <v>156.0</v>
+        <v>158.0</v>
       </c>
       <c r="G454" t="n">
         <v>0.0</v>
@@ -14122,7 +14122,7 @@
         <v>726</v>
       </c>
       <c r="F457" t="n">
-        <v>260.0</v>
+        <v>263.0</v>
       </c>
       <c r="G457" t="n">
         <v>12.0</v>
@@ -14876,7 +14876,7 @@
         <v>726</v>
       </c>
       <c r="F486" t="n">
-        <v>2538.0</v>
+        <v>2541.0</v>
       </c>
       <c r="G486" t="n">
         <v>45.0</v>
@@ -15292,7 +15292,7 @@
         <v>726</v>
       </c>
       <c r="F502" t="n">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="G502" t="n">
         <v>0.0</v>
@@ -15396,7 +15396,7 @@
         <v>727</v>
       </c>
       <c r="F506" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="G506" t="n">
         <v>0.0</v>
@@ -15500,7 +15500,7 @@
         <v>726</v>
       </c>
       <c r="F510" t="n">
-        <v>26.0</v>
+        <v>34.0</v>
       </c>
       <c r="G510" t="n">
         <v>0.0</v>
@@ -15682,7 +15682,7 @@
         <v>726</v>
       </c>
       <c r="F517" t="n">
-        <v>87.0</v>
+        <v>92.0</v>
       </c>
       <c r="G517" t="n">
         <v>0.0</v>
@@ -15786,7 +15786,7 @@
         <v>726</v>
       </c>
       <c r="F521" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
       <c r="G521" t="n">
         <v>0.0</v>
@@ -16462,7 +16462,7 @@
         <v>726</v>
       </c>
       <c r="F547" t="n">
-        <v>333.0</v>
+        <v>334.0</v>
       </c>
       <c r="G547" t="n">
         <v>0.0</v>
@@ -16696,7 +16696,7 @@
         <v>726</v>
       </c>
       <c r="F556" t="n">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
       <c r="G556" t="n">
         <v>0.0</v>
@@ -17190,7 +17190,7 @@
         <v>726</v>
       </c>
       <c r="F575" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G575" t="n">
         <v>0.0</v>
@@ -17580,7 +17580,7 @@
         <v>726</v>
       </c>
       <c r="F590" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G590" t="n">
         <v>0.0</v>
@@ -17684,7 +17684,7 @@
         <v>726</v>
       </c>
       <c r="F594" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G594" t="n">
         <v>0.0</v>
@@ -18516,7 +18516,7 @@
         <v>726</v>
       </c>
       <c r="F626" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G626" t="n">
         <v>0.0</v>
@@ -18542,7 +18542,7 @@
         <v>727</v>
       </c>
       <c r="F627" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G627" t="n">
         <v>0.0</v>
@@ -18568,7 +18568,7 @@
         <v>727</v>
       </c>
       <c r="F628" t="n">
-        <v>139.0</v>
+        <v>141.0</v>
       </c>
       <c r="G628" t="n">
         <v>0.0</v>
@@ -18646,7 +18646,7 @@
         <v>727</v>
       </c>
       <c r="F631" t="n">
-        <v>92.0</v>
+        <v>94.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -18672,7 +18672,7 @@
         <v>727</v>
       </c>
       <c r="F632" t="n">
-        <v>122.0</v>
+        <v>127.0</v>
       </c>
       <c r="G632" t="n">
         <v>0.0</v>
@@ -18698,7 +18698,7 @@
         <v>727</v>
       </c>
       <c r="F633" t="n">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="G633" t="n">
         <v>0.0</v>
@@ -19010,7 +19010,7 @@
         <v>727</v>
       </c>
       <c r="F645" t="n">
-        <v>218.0</v>
+        <v>225.0</v>
       </c>
       <c r="G645" t="n">
         <v>0.0</v>
@@ -19244,7 +19244,7 @@
         <v>727</v>
       </c>
       <c r="F654" t="n">
-        <v>106.0</v>
+        <v>108.0</v>
       </c>
       <c r="G654" t="n">
         <v>0.0</v>
@@ -19504,7 +19504,7 @@
         <v>727</v>
       </c>
       <c r="F664" t="n">
-        <v>81.0</v>
+        <v>85.0</v>
       </c>
       <c r="G664" t="n">
         <v>0.0</v>
@@ -19608,7 +19608,7 @@
         <v>727</v>
       </c>
       <c r="F668" t="n">
-        <v>89.0</v>
+        <v>91.0</v>
       </c>
       <c r="G668" t="n">
         <v>0.0</v>
@@ -20050,7 +20050,7 @@
         <v>729</v>
       </c>
       <c r="F685" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="G685" t="n">
         <v>2.0</v>
@@ -20362,7 +20362,7 @@
         <v>726</v>
       </c>
       <c r="F697" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
       <c r="G697" t="n">
         <v>0.0</v>
@@ -20700,7 +20700,7 @@
         <v>726</v>
       </c>
       <c r="F710" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="G710" t="n">
         <v>0.0</v>

--- a/Download/Comuni_PSA.xlsx
+++ b/Download/Comuni_PSA.xlsx
@@ -2292,7 +2292,7 @@
         <v>726</v>
       </c>
       <c r="F2" t="n">
-        <v>664.0</v>
+        <v>666.0</v>
       </c>
       <c r="G2" t="n">
         <v>3.0</v>
@@ -3150,7 +3150,7 @@
         <v>726</v>
       </c>
       <c r="F35" t="n">
-        <v>570.0</v>
+        <v>572.0</v>
       </c>
       <c r="G35" t="n">
         <v>4.0</v>
@@ -3416,7 +3416,7 @@
         <v>8.0</v>
       </c>
       <c r="H45" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="46">
@@ -4034,7 +4034,7 @@
         <v>726</v>
       </c>
       <c r="F69" t="n">
-        <v>155.0</v>
+        <v>156.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -4268,7 +4268,7 @@
         <v>727</v>
       </c>
       <c r="F78" t="n">
-        <v>497.0</v>
+        <v>499.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -4398,7 +4398,7 @@
         <v>726</v>
       </c>
       <c r="F83" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4632,7 +4632,7 @@
         <v>726</v>
       </c>
       <c r="F92" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -4814,7 +4814,7 @@
         <v>726</v>
       </c>
       <c r="F99" t="n">
-        <v>575.0</v>
+        <v>576.0</v>
       </c>
       <c r="G99" t="n">
         <v>4.0</v>
@@ -5126,7 +5126,7 @@
         <v>726</v>
       </c>
       <c r="F111" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
@@ -5282,7 +5282,7 @@
         <v>726</v>
       </c>
       <c r="F117" t="n">
-        <v>494.0</v>
+        <v>497.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -5802,7 +5802,7 @@
         <v>726</v>
       </c>
       <c r="F137" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G137" t="n">
         <v>0.0</v>
@@ -6036,7 +6036,7 @@
         <v>726</v>
       </c>
       <c r="F146" t="n">
-        <v>226.0</v>
+        <v>228.0</v>
       </c>
       <c r="G146" t="n">
         <v>0.0</v>
@@ -6530,7 +6530,7 @@
         <v>726</v>
       </c>
       <c r="F165" t="n">
-        <v>340.0</v>
+        <v>341.0</v>
       </c>
       <c r="G165" t="n">
         <v>1.0</v>
@@ -6972,7 +6972,7 @@
         <v>726</v>
       </c>
       <c r="F182" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="G182" t="n">
         <v>0.0</v>
@@ -7674,7 +7674,7 @@
         <v>726</v>
       </c>
       <c r="F209" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G209" t="n">
         <v>0.0</v>
@@ -7908,7 +7908,7 @@
         <v>727</v>
       </c>
       <c r="F218" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="G218" t="n">
         <v>0.0</v>
@@ -8012,7 +8012,7 @@
         <v>726</v>
       </c>
       <c r="F222" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G222" t="n">
         <v>1.0</v>
@@ -8116,7 +8116,7 @@
         <v>726</v>
       </c>
       <c r="F226" t="n">
-        <v>404.0</v>
+        <v>421.0</v>
       </c>
       <c r="G226" t="n">
         <v>0.0</v>
@@ -8480,7 +8480,7 @@
         <v>726</v>
       </c>
       <c r="F240" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G240" t="n">
         <v>0.0</v>
@@ -8818,7 +8818,7 @@
         <v>726</v>
       </c>
       <c r="F253" t="n">
-        <v>291.0</v>
+        <v>295.0</v>
       </c>
       <c r="G253" t="n">
         <v>0.0</v>
@@ -9234,7 +9234,7 @@
         <v>726</v>
       </c>
       <c r="F269" t="n">
-        <v>557.0</v>
+        <v>560.0</v>
       </c>
       <c r="G269" t="n">
         <v>0.0</v>
@@ -9442,7 +9442,7 @@
         <v>726</v>
       </c>
       <c r="F277" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G277" t="n">
         <v>2.0</v>
@@ -9572,7 +9572,7 @@
         <v>726</v>
       </c>
       <c r="F282" t="n">
-        <v>101.0</v>
+        <v>103.0</v>
       </c>
       <c r="G282" t="n">
         <v>0.0</v>
@@ -9754,7 +9754,7 @@
         <v>726</v>
       </c>
       <c r="F289" t="n">
-        <v>426.0</v>
+        <v>428.0</v>
       </c>
       <c r="G289" t="n">
         <v>1.0</v>
@@ -9884,7 +9884,7 @@
         <v>726</v>
       </c>
       <c r="F294" t="n">
-        <v>323.0</v>
+        <v>325.0</v>
       </c>
       <c r="G294" t="n">
         <v>4.0</v>
@@ -10014,7 +10014,7 @@
         <v>726</v>
       </c>
       <c r="F299" t="n">
-        <v>558.0</v>
+        <v>560.0</v>
       </c>
       <c r="G299" t="n">
         <v>6.0</v>
@@ -10196,7 +10196,7 @@
         <v>727</v>
       </c>
       <c r="F306" t="n">
-        <v>279.0</v>
+        <v>280.0</v>
       </c>
       <c r="G306" t="n">
         <v>0.0</v>
@@ -10222,10 +10222,10 @@
         <v>726</v>
       </c>
       <c r="F307" t="n">
-        <v>595.0</v>
+        <v>597.0</v>
       </c>
       <c r="G307" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H307" t="n">
         <v>8.0</v>
@@ -11080,7 +11080,7 @@
         <v>727</v>
       </c>
       <c r="F340" t="n">
-        <v>181.0</v>
+        <v>184.0</v>
       </c>
       <c r="G340" t="n">
         <v>0.0</v>
@@ -11106,7 +11106,7 @@
         <v>726</v>
       </c>
       <c r="F341" t="n">
-        <v>171.0</v>
+        <v>173.0</v>
       </c>
       <c r="G341" t="n">
         <v>0.0</v>
@@ -11132,7 +11132,7 @@
         <v>726</v>
       </c>
       <c r="F342" t="n">
-        <v>571.0</v>
+        <v>572.0</v>
       </c>
       <c r="G342" t="n">
         <v>6.0</v>
@@ -12120,7 +12120,7 @@
         <v>728</v>
       </c>
       <c r="F380" t="n">
-        <v>501.0</v>
+        <v>508.0</v>
       </c>
       <c r="G380" t="n">
         <v>1.0</v>
@@ -12588,7 +12588,7 @@
         <v>728</v>
       </c>
       <c r="F398" t="n">
-        <v>291.0</v>
+        <v>294.0</v>
       </c>
       <c r="G398" t="n">
         <v>0.0</v>
@@ -13004,7 +13004,7 @@
         <v>726</v>
       </c>
       <c r="F414" t="n">
-        <v>222.0</v>
+        <v>225.0</v>
       </c>
       <c r="G414" t="n">
         <v>1.0</v>
@@ -13108,7 +13108,7 @@
         <v>726</v>
       </c>
       <c r="F418" t="n">
-        <v>631.0</v>
+        <v>632.0</v>
       </c>
       <c r="G418" t="n">
         <v>3.0</v>
@@ -13394,7 +13394,7 @@
         <v>726</v>
       </c>
       <c r="F429" t="n">
-        <v>128.0</v>
+        <v>130.0</v>
       </c>
       <c r="G429" t="n">
         <v>6.0</v>
@@ -13472,7 +13472,7 @@
         <v>726</v>
       </c>
       <c r="F432" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G432" t="n">
         <v>0.0</v>
@@ -14356,7 +14356,7 @@
         <v>727</v>
       </c>
       <c r="F466" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G466" t="n">
         <v>0.0</v>
@@ -14486,7 +14486,7 @@
         <v>726</v>
       </c>
       <c r="F471" t="n">
-        <v>692.0</v>
+        <v>694.0</v>
       </c>
       <c r="G471" t="n">
         <v>2.0</v>
@@ -16748,7 +16748,7 @@
         <v>726</v>
       </c>
       <c r="F558" t="n">
-        <v>48.0</v>
+        <v>51.0</v>
       </c>
       <c r="G558" t="n">
         <v>0.0</v>
@@ -17502,7 +17502,7 @@
         <v>726</v>
       </c>
       <c r="F587" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G587" t="n">
         <v>0.0</v>
@@ -17710,7 +17710,7 @@
         <v>726</v>
       </c>
       <c r="F595" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="G595" t="n">
         <v>1.0</v>
@@ -18438,7 +18438,7 @@
         <v>727</v>
       </c>
       <c r="F623" t="n">
-        <v>74.0</v>
+        <v>76.0</v>
       </c>
       <c r="G623" t="n">
         <v>0.0</v>
@@ -18646,7 +18646,7 @@
         <v>727</v>
       </c>
       <c r="F631" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G631" t="n">
         <v>0.0</v>
@@ -18932,7 +18932,7 @@
         <v>727</v>
       </c>
       <c r="F642" t="n">
-        <v>175.0</v>
+        <v>177.0</v>
       </c>
       <c r="G642" t="n">
         <v>0.0</v>
@@ -19062,7 +19062,7 @@
         <v>727</v>
       </c>
       <c r="F647" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G647" t="n">
         <v>0.0</v>
@@ -19634,7 +19634,7 @@
         <v>727</v>
       </c>
       <c r="F669" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G669" t="n">
         <v>0.0</v>
@@ -19712,7 +19712,7 @@
         <v>727</v>
       </c>
       <c r="F672" t="n">
-        <v>43.0</v>
+        <v>50.0</v>
       </c>
       <c r="G672" t="n">
         <v>0.0</v>
@@ -20050,7 +20050,7 @@
         <v>729</v>
       </c>
       <c r="F685" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G685" t="n">
         <v>2.0</v>
@@ -20414,7 +20414,7 @@
         <v>726</v>
       </c>
       <c r="F699" t="n">
-        <v>420.0</v>
+        <v>421.0</v>
       </c>
       <c r="G699" t="n">
         <v>0.0</v>
@@ -20674,7 +20674,7 @@
         <v>727</v>
       </c>
       <c r="F709" t="n">
-        <v>442.0</v>
+        <v>443.0</v>
       </c>
       <c r="G709" t="n">
         <v>1.0</v>
@@ -21012,7 +21012,7 @@
         <v>729</v>
       </c>
       <c r="F722" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G722" t="n">
         <v>0.0</v>
@@ -21220,10 +21220,10 @@
         <v>729</v>
       </c>
       <c r="F730" t="n">
-        <v>537.0</v>
+        <v>538.0</v>
       </c>
       <c r="G730" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="H730" t="n">
         <v>3.0</v>
@@ -21272,10 +21272,10 @@
         <v>729</v>
       </c>
       <c r="F732" t="n">
-        <v>537.0</v>
+        <v>538.0</v>
       </c>
       <c r="G732" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="H732" t="n">
         <v>3.0</v>
